--- a/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A59F2D5-10F2-8044-853A-92A4ECA184CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36D023A-7408-6C4F-9576-5B69224C1B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9260" yWindow="780" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
@@ -680,7 +680,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3141" uniqueCount="1550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3138" uniqueCount="1550">
   <si>
     <t>Region</t>
   </si>
@@ -10673,18 +10673,6 @@
     <t>Domain Name</t>
   </si>
   <si>
-    <t>Members</t>
-  </si>
-  <si>
-    <t>Family Name</t>
-  </si>
-  <si>
-    <t>Enable Capabilities</t>
-  </si>
-  <si>
-    <t>User Email</t>
-  </si>
-  <si>
     <t>Backend HealthCheck Protocol(HTTP|HTTPS|TCP|UDP|DNS)</t>
   </si>
   <si>
@@ -10692,350 +10680,6 @@
   </si>
   <si>
     <t>DNS</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;).
-"User Name" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">is a mandatory field.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"Family Name" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">is a mandatory field for IAM tenancies
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"Description" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">is a mandatory field 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"User Email" -</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is an optional field.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"Domain Name" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Name of the identity domain where group resides. eg 'default' for default identity domain. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Leave empty for IDCS tenancies.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Enable Capabilities" -</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Specify comma seperated list of capabilities to be enabled for user. For ex: can_use_api_keys, can_use_console_password, can_use_auth_tokens, can_use_customer_secret_keys, can_use_db_credentials, can_use_oauth2client_credentials, can_use_smtp_credentials.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Defined Tags" -</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
-                                Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
-                                </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Example: Operations.CostCenter=01;Users.Name=user01</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;).
-"Name" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">(Group  Name) is a mandatory field.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Description"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Mandatory for IDCS tenancies.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"Domain Name" </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">- Name of the identity domain where group resides. eg 'default' for default identity domain. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Leave empty for IDCS tenancies.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"Members" -  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>comma seperated usernames. Leave empty if no member needs to be added to the group.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Matching Rule" -</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Specify the matching rule for creating Dynamic Groups; else leave it empty.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Region" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Specify your tenancy's Home Region for creating Groups.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Defined Tags"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
-                                Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
-                              </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF963634"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  Example: Operations.CostCenter=01;Users.Name=user01</t>
-    </r>
   </si>
   <si>
     <r>
@@ -12981,12 +12625,279 @@
       <t>onlyMT is Mount target without any FSS. onlyFSS is File System without any Mount Target or Export (used for replication)</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;).
+"User Name" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">is a mandatory field.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"First Name" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">is a mandatory field.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"User email" -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is an optional field.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"Group Names" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Comma Separated groups assigned to user</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Disable Capabilities" -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Specify comma seperated list of capabilities to be disabled for user. For ex: can_use_api_keys, can_use_console_password, can_use_auth_tokens, can_use_customer_secret_keys, can_use_db_credentials, can_use_oauth2client_credentials, can_use_smtp_credentials. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>By default all these capabilities are enabled for a user.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(can_use_db_credentials, can_use_oauth2client_credentials cannot be disabled through CD3. It is currently not supported by terraform)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Defined Tags" -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
+                                Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
+                                </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Example: Operations.CostCenter=01;Users.Name=user01</t>
+    </r>
+  </si>
+  <si>
+    <t>User Description</t>
+  </si>
+  <si>
+    <t>User email</t>
+  </si>
+  <si>
+    <t>Group Names</t>
+  </si>
+  <si>
+    <t>Disable Capabilities</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;).
+"Name" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Group  Name) is a mandatory field.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Matching Rule" -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Specify the matching rule for creating Dynamic Groups; else leave it empty.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Region" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Specify your tenancy's Home Region for creating Groups.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Defined Tags"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
+                                Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
+                              </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  Example: Operations.CostCenter=01;Users.Name=user01</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="51" x14ac:knownFonts="1">
+  <fonts count="49" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -13305,14 +13216,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF963634"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <i/>
       <u/>
@@ -13354,14 +13257,6 @@
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="13">
@@ -13681,7 +13576,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -13940,7 +13835,6 @@
     </xf>
     <xf numFmtId="0" fontId="40" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="40" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="40" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -13997,23 +13891,14 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -19160,7 +19045,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="79" t="s">
-        <v>1543</v>
+        <v>1537</v>
       </c>
     </row>
   </sheetData>
@@ -19190,22 +19075,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="247" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="139" t="s">
-        <v>1491</v>
-      </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="139" t="s">
-        <v>1490</v>
-      </c>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="141"/>
+      <c r="A1" s="133" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="133" t="s">
+        <v>1484</v>
+      </c>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="137"/>
     </row>
     <row r="2" spans="1:12" s="43" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
@@ -19262,7 +19147,7 @@
         <v>453</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>1496</v>
+        <v>1490</v>
       </c>
       <c r="G3" s="36" t="s">
         <v>21</v>
@@ -19448,19 +19333,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="222" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>927</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="145" t="s">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="141" t="s">
         <v>1334</v>
       </c>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
     </row>
     <row r="2" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -19689,10 +19574,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="43" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>629</v>
       </c>
-      <c r="B1" s="144"/>
+      <c r="B1" s="140"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -19753,16 +19638,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="106" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1406</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
     </row>
     <row r="2" spans="1:8" s="43" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -20048,30 +19933,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="192.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="133" t="s">
         <v>1326</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="146" t="s">
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="142" t="s">
         <v>1296</v>
       </c>
-      <c r="K1" s="146"/>
-      <c r="L1" s="146"/>
-      <c r="M1" s="146"/>
-      <c r="N1" s="146"/>
-      <c r="O1" s="146"/>
-      <c r="P1" s="146"/>
-      <c r="Q1" s="146"/>
-      <c r="R1" s="146"/>
-      <c r="S1" s="146"/>
-      <c r="T1" s="146"/>
+      <c r="K1" s="142"/>
+      <c r="L1" s="142"/>
+      <c r="M1" s="142"/>
+      <c r="N1" s="142"/>
+      <c r="O1" s="142"/>
+      <c r="P1" s="142"/>
+      <c r="Q1" s="142"/>
+      <c r="R1" s="142"/>
+      <c r="S1" s="142"/>
+      <c r="T1" s="142"/>
     </row>
     <row r="2" spans="1:20" s="43" customFormat="1" ht="59.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -26178,18 +26063,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1313</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
     </row>
     <row r="2" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -26300,17 +26185,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1314</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -26402,25 +26287,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1315</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="133"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -26552,28 +26437,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="118.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1316</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="133"/>
-      <c r="R1" s="133"/>
-      <c r="S1" s="133"/>
-      <c r="T1" s="133"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="132"/>
+      <c r="T1" s="132"/>
     </row>
     <row r="2" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
@@ -29055,17 +28940,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="179.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1325</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
@@ -29448,13 +29333,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="43" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1311</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -29706,19 +29591,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="191.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="144" t="s">
         <v>1317</v>
       </c>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="149"/>
-      <c r="G1" s="149"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="149"/>
-      <c r="J1" s="149"/>
-      <c r="K1" s="149"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="145"/>
     </row>
     <row r="2" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -29888,15 +29773,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1318</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
     </row>
     <row r="2" spans="1:7" s="43" customFormat="1" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -30071,32 +29956,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="275.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="146" t="s">
         <v>1407</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="151"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="152"/>
-      <c r="I1" s="139" t="s">
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="148"/>
+      <c r="I1" s="133" t="s">
         <v>1392</v>
       </c>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
-      <c r="V1" s="141"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="137"/>
     </row>
     <row r="2" spans="1:22" s="43" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -30545,26 +30430,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="201" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="139" t="s">
-        <v>1545</v>
-      </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="141"/>
+      <c r="A1" s="133" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="137"/>
     </row>
     <row r="2" spans="1:18" s="43" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -30672,20 +30557,20 @@
       <c r="I4" s="53" t="s">
         <v>634</v>
       </c>
-      <c r="J4" s="128" t="s">
+      <c r="J4" s="127" t="s">
         <v>1475</v>
       </c>
-      <c r="K4" s="128" t="s">
+      <c r="K4" s="127" t="s">
         <v>1476</v>
       </c>
-      <c r="L4" s="128">
+      <c r="L4" s="127">
         <v>100</v>
       </c>
-      <c r="M4" s="128" t="s">
+      <c r="M4" s="127" t="s">
         <v>1477</v>
       </c>
-      <c r="N4" s="128" t="s">
-        <v>1492</v>
+      <c r="N4" s="127" t="s">
+        <v>1486</v>
       </c>
       <c r="O4" s="84" t="b">
         <v>1</v>
@@ -30781,32 +30666,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="133" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="139" t="s">
-        <v>1546</v>
-      </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="153" t="s">
-        <v>1549</v>
-      </c>
-      <c r="N1" s="154"/>
-      <c r="O1" s="154"/>
-      <c r="P1" s="154"/>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="155"/>
+      <c r="A1" s="133" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="149" t="s">
+        <v>1543</v>
+      </c>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
+      <c r="V1" s="151"/>
     </row>
     <row r="2" spans="1:22" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
@@ -30837,13 +30722,13 @@
         <v>111</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>1497</v>
+        <v>1491</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>1493</v>
+        <v>1487</v>
       </c>
       <c r="L2" s="31" t="s">
-        <v>1494</v>
+        <v>1488</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>112</v>
@@ -30867,10 +30752,10 @@
         <v>118</v>
       </c>
       <c r="T2" s="31" t="s">
-        <v>1511</v>
+        <v>1505</v>
       </c>
       <c r="U2" s="31" t="s">
-        <v>1495</v>
+        <v>1489</v>
       </c>
       <c r="V2" s="10" t="s">
         <v>402</v>
@@ -31179,7 +31064,7 @@
         <v>87</v>
       </c>
       <c r="D11" s="87" t="s">
-        <v>1547</v>
+        <v>1541</v>
       </c>
       <c r="E11" s="53" t="s">
         <v>375</v>
@@ -31218,7 +31103,7 @@
       <c r="G12" s="87"/>
       <c r="H12" s="52"/>
       <c r="I12" s="87" t="s">
-        <v>1548</v>
+        <v>1542</v>
       </c>
       <c r="J12" s="52"/>
       <c r="K12" s="52"/>
@@ -31324,45 +31209,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="145" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="133" t="s">
         <v>1408</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="150" t="s">
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="146" t="s">
         <v>1319</v>
       </c>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
-      <c r="V1" s="151"/>
-      <c r="W1" s="151"/>
-      <c r="X1" s="151"/>
-      <c r="Y1" s="151"/>
-      <c r="Z1" s="151"/>
-      <c r="AA1" s="151"/>
-      <c r="AB1" s="151"/>
-      <c r="AC1" s="151"/>
-      <c r="AD1" s="151"/>
-      <c r="AE1" s="151"/>
-      <c r="AF1" s="151"/>
-      <c r="AG1" s="151"/>
-      <c r="AH1" s="151"/>
-      <c r="AI1" s="151"/>
+      <c r="Q1" s="147"/>
+      <c r="R1" s="147"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="147"/>
+      <c r="U1" s="147"/>
+      <c r="V1" s="147"/>
+      <c r="W1" s="147"/>
+      <c r="X1" s="147"/>
+      <c r="Y1" s="147"/>
+      <c r="Z1" s="147"/>
+      <c r="AA1" s="147"/>
+      <c r="AB1" s="147"/>
+      <c r="AC1" s="147"/>
+      <c r="AD1" s="147"/>
+      <c r="AE1" s="147"/>
+      <c r="AF1" s="147"/>
+      <c r="AG1" s="147"/>
+      <c r="AH1" s="147"/>
+      <c r="AI1" s="147"/>
     </row>
     <row r="2" spans="1:35" s="1" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
@@ -31835,27 +31720,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="122.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1320</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="133"/>
-      <c r="R1" s="133"/>
-      <c r="S1" s="133"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="132"/>
     </row>
     <row r="2" spans="1:19" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -32131,30 +32016,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="118" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="133" t="s">
         <v>636</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
-      <c r="V1" s="141"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="137"/>
     </row>
     <row r="2" spans="1:22" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="37" t="s">
@@ -32480,25 +32365,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>637</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="133"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
     </row>
     <row r="2" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
@@ -32743,29 +32628,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="115.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="133" t="s">
         <v>408</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="142" t="s">
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="138" t="s">
         <v>416</v>
       </c>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
-      <c r="O1" s="156"/>
-      <c r="P1" s="156"/>
-      <c r="Q1" s="156"/>
-      <c r="R1" s="156"/>
-      <c r="S1" s="157"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="153"/>
     </row>
     <row r="2" spans="1:19" ht="58.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
@@ -33448,53 +33333,43 @@
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.1640625" customWidth="1"/>
     <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="31.5" customWidth="1"/>
-    <col min="7" max="7" width="24.5" customWidth="1"/>
+    <col min="4" max="4" width="31.33203125" customWidth="1"/>
+    <col min="5" max="5" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="43" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
-        <v>1488</v>
-      </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="136"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="109" t="s">
+    <row r="1" spans="1:5" s="43" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="132" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="110" t="s">
+      <c r="C2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="112" t="s">
-        <v>1479</v>
-      </c>
-      <c r="E2" s="112" t="s">
-        <v>1480</v>
-      </c>
-      <c r="F2" s="111" t="s">
+      <c r="D2" s="30" t="s">
         <v>406</v>
       </c>
-      <c r="G2" s="112" t="s">
+      <c r="E2" s="30" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
         <v>5</v>
       </c>
@@ -33505,11 +33380,9 @@
         <v>431</v>
       </c>
       <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="36"/>
-    </row>
-    <row r="4" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="E3" s="36"/>
+    </row>
+    <row r="4" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="35" t="s">
         <v>5</v>
       </c>
@@ -33520,11 +33393,9 @@
         <v>669</v>
       </c>
       <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="36"/>
-    </row>
-    <row r="5" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="E4" s="36"/>
+    </row>
+    <row r="5" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="35" t="s">
         <v>5</v>
       </c>
@@ -33535,11 +33406,9 @@
         <v>433</v>
       </c>
       <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="36"/>
-    </row>
-    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E5" s="36"/>
+    </row>
+    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="35" t="s">
         <v>5</v>
       </c>
@@ -33550,12 +33419,10 @@
         <v>435</v>
       </c>
       <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="36"/>
-    </row>
-    <row r="7" spans="1:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" s="35" t="s">
+      <c r="E6" s="36"/>
+    </row>
+    <row r="7" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" s="54" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="35" t="s">
@@ -33565,12 +33432,10 @@
         <v>437</v>
       </c>
       <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="36"/>
-    </row>
-    <row r="8" spans="1:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="54" t="s">
+      <c r="E7" s="23"/>
+    </row>
+    <row r="8" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A8" s="35" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="54" t="s">
@@ -33579,12 +33444,10 @@
       <c r="C8" s="54" t="s">
         <v>439</v>
       </c>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-    </row>
-    <row r="9" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D8" s="23"/>
+      <c r="E8" s="35"/>
+    </row>
+    <row r="9" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="35" t="s">
         <v>5</v>
       </c>
@@ -33596,10 +33459,8 @@
       </c>
       <c r="D9" s="35"/>
       <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-    </row>
-    <row r="10" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="35" t="s">
         <v>5</v>
       </c>
@@ -33611,10 +33472,8 @@
       </c>
       <c r="D10" s="35"/>
       <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-    </row>
-    <row r="11" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="35" t="s">
         <v>5</v>
       </c>
@@ -33626,10 +33485,8 @@
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-    </row>
-    <row r="12" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="35" t="s">
         <v>5</v>
       </c>
@@ -33640,34 +33497,34 @@
         <v>605</v>
       </c>
       <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-    </row>
-    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="E12" s="36"/>
+    </row>
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="35" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="64" x14ac:dyDescent="0.2">
-      <c r="A14" s="35" t="s">
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+    </row>
+    <row r="14" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A14" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="22" t="s">
         <v>830</v>
       </c>
-      <c r="C14" s="35" t="s">
+      <c r="C14" s="22" t="s">
         <v>831</v>
       </c>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35" t="s">
+      <c r="D14" s="22" t="s">
         <v>832</v>
       </c>
-      <c r="G14" s="36"/>
-    </row>
-    <row r="15" spans="1:7" ht="48" x14ac:dyDescent="0.2">
-      <c r="A15" s="35" t="s">
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A15" s="36" t="s">
         <v>5</v>
       </c>
       <c r="B15" s="35" t="s">
@@ -33676,15 +33533,13 @@
       <c r="C15" s="35" t="s">
         <v>834</v>
       </c>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35" t="s">
+      <c r="D15" s="35" t="s">
         <v>835</v>
       </c>
-      <c r="G15" s="36"/>
-    </row>
-    <row r="16" spans="1:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="A16" s="35" t="s">
+      <c r="E15" s="36"/>
+    </row>
+    <row r="16" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" s="36" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="35" t="s">
@@ -33693,15 +33548,13 @@
       <c r="C16" s="35" t="s">
         <v>837</v>
       </c>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35" t="s">
+      <c r="D16" s="35" t="s">
         <v>838</v>
       </c>
-      <c r="G16" s="36"/>
-    </row>
-    <row r="17" spans="1:7" ht="48" x14ac:dyDescent="0.2">
-      <c r="A17" s="35" t="s">
+      <c r="E16" s="36"/>
+    </row>
+    <row r="17" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A17" s="36" t="s">
         <v>5</v>
       </c>
       <c r="B17" s="35" t="s">
@@ -33710,34 +33563,21 @@
       <c r="C17" s="35" t="s">
         <v>840</v>
       </c>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35" t="s">
+      <c r="D17" s="35" t="s">
         <v>841</v>
       </c>
-      <c r="G17" s="36"/>
+      <c r="E17" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="H1:XFD1048576 B3:G1048576" xr:uid="{34D02532-918C-2242-9200-0036CF7A8F7F}"/>
+  <dataValidations count="2">
+    <dataValidation allowBlank="1" sqref="B3:D1048576 A1:E1" xr:uid="{8EFF7419-48D3-4C46-B3E5-C58F24B7E6C8}"/>
+    <dataValidation allowBlank="1" prompt="Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt; else leave it empty._x000a_Multiple Tag Key , Values can be specified using semi colon (;) as the delimeter. _x000a_Example: Operations.CostCenter=01;Users.Name=user01" sqref="E3:E1048576" xr:uid="{86EF4A92-0B46-F148-96CE-EDC9C3C9AEDD}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{1DD4F197-DE20-A74C-B8B9-A4750C446198}">
-          <x14:formula1>
-            <xm:f>drop_down_rule_set!$L$2:$L$44</xm:f>
-          </x14:formula1>
-          <xm:sqref>A3:A1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -33756,14 +33596,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="43" customFormat="1" ht="44.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="154" t="s">
         <v>409</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="160"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="156"/>
     </row>
     <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -33917,22 +33757,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="133" t="s">
         <v>661</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="141"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="137"/>
     </row>
     <row r="2" spans="1:14" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
@@ -34472,20 +34312,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="133" t="s">
         <v>661</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
     </row>
     <row r="2" spans="1:12" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
@@ -34507,7 +34347,7 @@
         <v>656</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
       <c r="H2" s="31" t="s">
         <v>1479</v>
@@ -34625,10 +34465,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="53" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
       <c r="H6" s="53" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
       <c r="I6" s="53">
         <v>53</v>
@@ -34691,24 +34531,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="160" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="133" t="s">
         <v>1321</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
     </row>
     <row r="2" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -34912,35 +34752,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="1" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="133" t="s">
         <v>1322</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
-      <c r="V1" s="140"/>
-      <c r="W1" s="140"/>
-      <c r="X1" s="140"/>
-      <c r="Y1" s="140"/>
-      <c r="Z1" s="140"/>
-      <c r="AA1" s="141"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="137"/>
     </row>
     <row r="2" spans="1:27" s="48" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="49" t="s">
@@ -38306,16 +38146,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="119.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="133" t="s">
         <v>1323</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
     </row>
     <row r="2" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="65" t="s">
@@ -41220,29 +41060,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="1" customFormat="1" ht="195" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="146" t="s">
         <v>1324</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="151"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="151"/>
-      <c r="I1" s="151"/>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
+      <c r="R1" s="147"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="147"/>
+      <c r="U1" s="147"/>
       <c r="V1" s="69"/>
       <c r="W1" s="69"/>
       <c r="X1" s="69"/>
@@ -45682,26 +45522,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="150" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="157" t="s">
         <v>1441</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="162"/>
-      <c r="G1" s="162"/>
-      <c r="H1" s="162"/>
-      <c r="I1" s="162"/>
-      <c r="J1" s="162"/>
-      <c r="K1" s="162"/>
-      <c r="L1" s="162"/>
-      <c r="M1" s="162"/>
-      <c r="N1" s="162"/>
-      <c r="O1" s="162"/>
-      <c r="P1" s="162"/>
-      <c r="Q1" s="162"/>
-      <c r="R1" s="163"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
+      <c r="L1" s="158"/>
+      <c r="M1" s="158"/>
+      <c r="N1" s="158"/>
+      <c r="O1" s="158"/>
+      <c r="P1" s="158"/>
+      <c r="Q1" s="158"/>
+      <c r="R1" s="159"/>
       <c r="S1" s="16"/>
     </row>
     <row r="2" spans="1:19" s="48" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -45717,16 +45557,16 @@
       <c r="D2" s="37" t="s">
         <v>1428</v>
       </c>
-      <c r="E2" s="113" t="s">
+      <c r="E2" s="112" t="s">
         <v>1212</v>
       </c>
-      <c r="F2" s="113" t="s">
+      <c r="F2" s="112" t="s">
         <v>1213</v>
       </c>
       <c r="G2" s="37" t="s">
         <v>1214</v>
       </c>
-      <c r="H2" s="113" t="s">
+      <c r="H2" s="112" t="s">
         <v>1215</v>
       </c>
       <c r="I2" s="37" t="s">
@@ -45738,10 +45578,10 @@
       <c r="K2" s="37" t="s">
         <v>1217</v>
       </c>
-      <c r="L2" s="114" t="s">
+      <c r="L2" s="113" t="s">
         <v>1345</v>
       </c>
-      <c r="M2" s="115" t="s">
+      <c r="M2" s="114" t="s">
         <v>1346</v>
       </c>
       <c r="N2" s="37" t="s">
@@ -45795,10 +45635,10 @@
         <v>16</v>
       </c>
       <c r="L3" t="s">
-        <v>1498</v>
+        <v>1492</v>
       </c>
       <c r="M3" t="s">
-        <v>1499</v>
+        <v>1493</v>
       </c>
       <c r="N3" s="35">
         <v>3</v>
@@ -45932,22 +45772,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="150" t="s">
-        <v>1512</v>
-      </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="162"/>
-      <c r="G1" s="162"/>
-      <c r="H1" s="162"/>
-      <c r="I1" s="162"/>
-      <c r="J1" s="162"/>
-      <c r="K1" s="162"/>
-      <c r="L1" s="162"/>
-      <c r="M1" s="162"/>
-      <c r="N1" s="162"/>
+      <c r="A1" s="146" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
+      <c r="L1" s="158"/>
+      <c r="M1" s="158"/>
+      <c r="N1" s="158"/>
     </row>
     <row r="2" spans="1:15" s="43" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="38" t="s">
@@ -45956,7 +45796,7 @@
       <c r="B2" s="38" t="s">
         <v>1211</v>
       </c>
-      <c r="C2" s="113" t="s">
+      <c r="C2" s="112" t="s">
         <v>1221</v>
       </c>
       <c r="D2" s="37" t="s">
@@ -46002,42 +45842,42 @@
         <v>1429</v>
       </c>
       <c r="C3" s="35" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>1498</v>
+      </c>
+      <c r="H3" s="35" t="s">
+        <v>1499</v>
+      </c>
+      <c r="I3" s="35" t="s">
         <v>1500</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="J3" s="35" t="s">
         <v>1501</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="K3" s="35" t="s">
         <v>1502</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="L3" s="35" t="s">
         <v>1503</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="M3" s="35" t="s">
         <v>1504</v>
-      </c>
-      <c r="H3" s="35" t="s">
-        <v>1505</v>
-      </c>
-      <c r="I3" s="35" t="s">
-        <v>1506</v>
-      </c>
-      <c r="J3" s="35" t="s">
-        <v>1507</v>
-      </c>
-      <c r="K3" s="35" t="s">
-        <v>1508</v>
-      </c>
-      <c r="L3" s="35" t="s">
-        <v>1509</v>
-      </c>
-      <c r="M3" s="35" t="s">
-        <v>1510</v>
       </c>
       <c r="N3" s="35" t="s">
         <v>1442</v>
       </c>
-      <c r="O3" s="116"/>
+      <c r="O3" s="115"/>
     </row>
     <row r="4" spans="1:15" s="34" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="35" t="s">
@@ -46047,46 +45887,46 @@
         <v>1438</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1500</v>
+        <v>1494</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1501</v>
+        <v>1495</v>
       </c>
       <c r="E4" s="35"/>
       <c r="F4" s="35" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G4" s="35" t="s">
+        <v>1498</v>
+      </c>
+      <c r="H4" s="35" t="s">
+        <v>1499</v>
+      </c>
+      <c r="I4" s="35" t="s">
+        <v>1500</v>
+      </c>
+      <c r="J4" s="35" t="s">
+        <v>1501</v>
+      </c>
+      <c r="K4" s="35" t="s">
+        <v>1502</v>
+      </c>
+      <c r="L4" s="35" t="s">
         <v>1503</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="M4" s="35" t="s">
         <v>1504</v>
-      </c>
-      <c r="H4" s="35" t="s">
-        <v>1505</v>
-      </c>
-      <c r="I4" s="35" t="s">
-        <v>1506</v>
-      </c>
-      <c r="J4" s="35" t="s">
-        <v>1507</v>
-      </c>
-      <c r="K4" s="35" t="s">
-        <v>1508</v>
-      </c>
-      <c r="L4" s="35" t="s">
-        <v>1509</v>
-      </c>
-      <c r="M4" s="35" t="s">
-        <v>1510</v>
       </c>
       <c r="N4" s="35" t="s">
         <v>1443</v>
       </c>
-      <c r="O4" s="116"/>
+      <c r="O4" s="115"/>
     </row>
     <row r="5" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="117"/>
+      <c r="B5" s="116"/>
       <c r="C5"/>
       <c r="O5"/>
     </row>
@@ -46158,26 +45998,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="287" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="164" t="s">
+      <c r="A1" s="160" t="s">
         <v>1327</v>
       </c>
-      <c r="B1" s="165"/>
-      <c r="C1" s="165"/>
-      <c r="D1" s="165"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
-      <c r="G1" s="165"/>
-      <c r="H1" s="165"/>
-      <c r="I1" s="165"/>
-      <c r="J1" s="165"/>
-      <c r="K1" s="165"/>
-      <c r="L1" s="165"/>
-      <c r="M1" s="165"/>
-      <c r="N1" s="165"/>
-      <c r="O1" s="165"/>
-      <c r="P1" s="165"/>
-      <c r="Q1" s="165"/>
-      <c r="R1" s="166"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
+      <c r="K1" s="161"/>
+      <c r="L1" s="161"/>
+      <c r="M1" s="161"/>
+      <c r="N1" s="161"/>
+      <c r="O1" s="161"/>
+      <c r="P1" s="161"/>
+      <c r="Q1" s="161"/>
+      <c r="R1" s="162"/>
     </row>
     <row r="2" spans="1:18" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -46507,32 +46347,30 @@
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="156.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.1640625" customWidth="1"/>
     <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="18.1640625" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" customWidth="1"/>
-    <col min="8" max="8" width="24.5" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="31.33203125" customWidth="1"/>
+    <col min="5" max="6" width="23.6640625" customWidth="1"/>
+    <col min="7" max="7" width="23.83203125" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="43" customFormat="1" ht="168" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" s="43" customFormat="1" ht="156.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="133" t="s">
-        <v>1487</v>
-      </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
-      <c r="H1" s="138"/>
-    </row>
-    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+        <v>1544</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
         <v>0</v>
       </c>
@@ -46540,25 +46378,22 @@
         <v>1201</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>1481</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>2</v>
+        <v>1545</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>1546</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1483</v>
+        <v>1547</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1482</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>1479</v>
-      </c>
-      <c r="H2" s="30" t="s">
+        <v>1548</v>
+      </c>
+      <c r="G2" s="30" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="36"/>
       <c r="B3" s="36"/>
       <c r="C3" s="36"/>
@@ -46566,9 +46401,8 @@
       <c r="E3" s="36"/>
       <c r="F3" s="36"/>
       <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-    </row>
-    <row r="4" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="36"/>
       <c r="B4" s="36"/>
       <c r="C4" s="36"/>
@@ -46576,9 +46410,8 @@
       <c r="E4" s="36"/>
       <c r="F4" s="36"/>
       <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-    </row>
-    <row r="5" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="36"/>
       <c r="B5" s="36"/>
       <c r="C5" s="36"/>
@@ -46586,9 +46419,8 @@
       <c r="E5" s="36"/>
       <c r="F5" s="36"/>
       <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-    </row>
-    <row r="6" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="36"/>
       <c r="B6" s="36"/>
       <c r="C6" s="36"/>
@@ -46596,9 +46428,8 @@
       <c r="E6" s="36"/>
       <c r="F6" s="36"/>
       <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-    </row>
-    <row r="7" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="36"/>
       <c r="B7" s="36"/>
       <c r="C7" s="36"/>
@@ -46606,9 +46437,8 @@
       <c r="E7" s="36"/>
       <c r="F7" s="36"/>
       <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-    </row>
-    <row r="8" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="36"/>
       <c r="B8" s="36"/>
       <c r="C8" s="36"/>
@@ -46616,9 +46446,8 @@
       <c r="E8" s="36"/>
       <c r="F8" s="36"/>
       <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-    </row>
-    <row r="9" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="36"/>
       <c r="B9" s="36"/>
       <c r="C9" s="36"/>
@@ -46626,9 +46455,8 @@
       <c r="E9" s="36"/>
       <c r="F9" s="36"/>
       <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-    </row>
-    <row r="10" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="36"/>
       <c r="B10" s="36"/>
       <c r="C10" s="36"/>
@@ -46636,9 +46464,8 @@
       <c r="E10" s="36"/>
       <c r="F10" s="36"/>
       <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-    </row>
-    <row r="11" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="36"/>
       <c r="B11" s="36"/>
       <c r="C11" s="36"/>
@@ -46646,9 +46473,8 @@
       <c r="E11" s="36"/>
       <c r="F11" s="36"/>
       <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-    </row>
-    <row r="12" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="36"/>
       <c r="B12" s="36"/>
       <c r="C12" s="36"/>
@@ -46656,9 +46482,8 @@
       <c r="E12" s="36"/>
       <c r="F12" s="36"/>
       <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-    </row>
-    <row r="13" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="36"/>
       <c r="B13" s="36"/>
       <c r="C13" s="36"/>
@@ -46666,9 +46491,8 @@
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
       <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-    </row>
-    <row r="14" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="36"/>
       <c r="B14" s="36"/>
       <c r="C14" s="36"/>
@@ -46676,9 +46500,8 @@
       <c r="E14" s="36"/>
       <c r="F14" s="36"/>
       <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-    </row>
-    <row r="15" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="36"/>
       <c r="B15" s="36"/>
       <c r="C15" s="36"/>
@@ -46686,9 +46509,8 @@
       <c r="E15" s="36"/>
       <c r="F15" s="36"/>
       <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-    </row>
-    <row r="16" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="36"/>
       <c r="B16" s="36"/>
       <c r="C16" s="36"/>
@@ -46696,9 +46518,8 @@
       <c r="E16" s="36"/>
       <c r="F16" s="36"/>
       <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="36"/>
       <c r="B17" s="36"/>
       <c r="C17" s="36"/>
@@ -46706,9 +46527,8 @@
       <c r="E17" s="36"/>
       <c r="F17" s="36"/>
       <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-    </row>
-    <row r="18" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="36"/>
       <c r="B18" s="36"/>
       <c r="C18" s="36"/>
@@ -46716,9 +46536,8 @@
       <c r="E18" s="36"/>
       <c r="F18" s="36"/>
       <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-    </row>
-    <row r="19" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="36"/>
       <c r="B19" s="36"/>
       <c r="C19" s="36"/>
@@ -46726,9 +46545,8 @@
       <c r="E19" s="36"/>
       <c r="F19" s="36"/>
       <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-    </row>
-    <row r="20" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="36"/>
       <c r="B20" s="36"/>
       <c r="C20" s="36"/>
@@ -46736,9 +46554,8 @@
       <c r="E20" s="36"/>
       <c r="F20" s="36"/>
       <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-    </row>
-    <row r="21" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="36"/>
       <c r="B21" s="36"/>
       <c r="C21" s="36"/>
@@ -46746,9 +46563,8 @@
       <c r="E21" s="36"/>
       <c r="F21" s="36"/>
       <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-    </row>
-    <row r="22" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="36"/>
       <c r="B22" s="36"/>
       <c r="C22" s="36"/>
@@ -46756,9 +46572,8 @@
       <c r="E22" s="36"/>
       <c r="F22" s="36"/>
       <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-    </row>
-    <row r="23" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="36"/>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -46766,9 +46581,8 @@
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
       <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-    </row>
-    <row r="24" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="36"/>
       <c r="B24" s="36"/>
       <c r="C24" s="36"/>
@@ -46776,9 +46590,8 @@
       <c r="E24" s="36"/>
       <c r="F24" s="36"/>
       <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-    </row>
-    <row r="25" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="36"/>
       <c r="B25" s="36"/>
       <c r="C25" s="36"/>
@@ -46786,9 +46599,8 @@
       <c r="E25" s="36"/>
       <c r="F25" s="36"/>
       <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-    </row>
-    <row r="26" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="36"/>
       <c r="B26" s="36"/>
       <c r="C26" s="36"/>
@@ -46796,9 +46608,8 @@
       <c r="E26" s="36"/>
       <c r="F26" s="36"/>
       <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-    </row>
-    <row r="27" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="36"/>
       <c r="B27" s="36"/>
       <c r="C27" s="36"/>
@@ -46806,9 +46617,8 @@
       <c r="E27" s="36"/>
       <c r="F27" s="36"/>
       <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
-    </row>
-    <row r="28" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="36"/>
       <c r="B28" s="36"/>
       <c r="C28" s="36"/>
@@ -46816,9 +46626,8 @@
       <c r="E28" s="36"/>
       <c r="F28" s="36"/>
       <c r="G28" s="36"/>
-      <c r="H28" s="36"/>
-    </row>
-    <row r="29" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="36"/>
       <c r="B29" s="36"/>
       <c r="C29" s="36"/>
@@ -46826,9 +46635,8 @@
       <c r="E29" s="36"/>
       <c r="F29" s="36"/>
       <c r="G29" s="36"/>
-      <c r="H29" s="36"/>
-    </row>
-    <row r="30" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="36"/>
       <c r="B30" s="36"/>
       <c r="C30" s="36"/>
@@ -46836,9 +46644,8 @@
       <c r="E30" s="36"/>
       <c r="F30" s="36"/>
       <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-    </row>
-    <row r="31" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="36"/>
       <c r="B31" s="36"/>
       <c r="C31" s="36"/>
@@ -46846,9 +46653,8 @@
       <c r="E31" s="36"/>
       <c r="F31" s="36"/>
       <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-    </row>
-    <row r="32" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="36"/>
       <c r="B32" s="36"/>
       <c r="C32" s="36"/>
@@ -46856,9 +46662,8 @@
       <c r="E32" s="36"/>
       <c r="F32" s="36"/>
       <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-    </row>
-    <row r="33" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="36"/>
       <c r="B33" s="36"/>
       <c r="C33" s="36"/>
@@ -46866,9 +46671,8 @@
       <c r="E33" s="36"/>
       <c r="F33" s="36"/>
       <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-    </row>
-    <row r="34" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="36"/>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -46876,9 +46680,8 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
       <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-    </row>
-    <row r="35" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="36"/>
       <c r="B35" s="36"/>
       <c r="C35" s="36"/>
@@ -46886,9 +46689,8 @@
       <c r="E35" s="36"/>
       <c r="F35" s="36"/>
       <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-    </row>
-    <row r="36" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="36"/>
       <c r="B36" s="36"/>
       <c r="C36" s="36"/>
@@ -46896,9 +46698,8 @@
       <c r="E36" s="36"/>
       <c r="F36" s="36"/>
       <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
-    </row>
-    <row r="37" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="36"/>
       <c r="B37" s="36"/>
       <c r="C37" s="36"/>
@@ -46906,9 +46707,8 @@
       <c r="E37" s="36"/>
       <c r="F37" s="36"/>
       <c r="G37" s="36"/>
-      <c r="H37" s="36"/>
-    </row>
-    <row r="38" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="36"/>
       <c r="B38" s="36"/>
       <c r="C38" s="36"/>
@@ -46916,9 +46716,8 @@
       <c r="E38" s="36"/>
       <c r="F38" s="36"/>
       <c r="G38" s="36"/>
-      <c r="H38" s="36"/>
-    </row>
-    <row r="39" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="36"/>
       <c r="B39" s="36"/>
       <c r="C39" s="36"/>
@@ -46926,9 +46725,8 @@
       <c r="E39" s="36"/>
       <c r="F39" s="36"/>
       <c r="G39" s="36"/>
-      <c r="H39" s="36"/>
-    </row>
-    <row r="40" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="36"/>
       <c r="B40" s="36"/>
       <c r="C40" s="36"/>
@@ -46936,9 +46734,8 @@
       <c r="E40" s="36"/>
       <c r="F40" s="36"/>
       <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-    </row>
-    <row r="41" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="36"/>
       <c r="B41" s="36"/>
       <c r="C41" s="36"/>
@@ -46946,9 +46743,8 @@
       <c r="E41" s="36"/>
       <c r="F41" s="36"/>
       <c r="G41" s="36"/>
-      <c r="H41" s="36"/>
-    </row>
-    <row r="42" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="36"/>
       <c r="B42" s="36"/>
       <c r="C42" s="36"/>
@@ -46956,9 +46752,8 @@
       <c r="E42" s="36"/>
       <c r="F42" s="36"/>
       <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
-    </row>
-    <row r="43" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="36"/>
       <c r="B43" s="36"/>
       <c r="C43" s="36"/>
@@ -46966,9 +46761,8 @@
       <c r="E43" s="36"/>
       <c r="F43" s="36"/>
       <c r="G43" s="36"/>
-      <c r="H43" s="36"/>
-    </row>
-    <row r="44" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="36"/>
       <c r="B44" s="36"/>
       <c r="C44" s="36"/>
@@ -46976,9 +46770,8 @@
       <c r="E44" s="36"/>
       <c r="F44" s="36"/>
       <c r="G44" s="36"/>
-      <c r="H44" s="36"/>
-    </row>
-    <row r="45" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="36"/>
       <c r="B45" s="36"/>
       <c r="C45" s="36"/>
@@ -46986,9 +46779,8 @@
       <c r="E45" s="36"/>
       <c r="F45" s="36"/>
       <c r="G45" s="36"/>
-      <c r="H45" s="36"/>
-    </row>
-    <row r="46" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="36"/>
       <c r="B46" s="36"/>
       <c r="C46" s="36"/>
@@ -46996,9 +46788,8 @@
       <c r="E46" s="36"/>
       <c r="F46" s="36"/>
       <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-    </row>
-    <row r="47" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="36"/>
       <c r="B47" s="36"/>
       <c r="C47" s="36"/>
@@ -47006,9 +46797,8 @@
       <c r="E47" s="36"/>
       <c r="F47" s="36"/>
       <c r="G47" s="36"/>
-      <c r="H47" s="36"/>
-    </row>
-    <row r="48" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="36"/>
       <c r="B48" s="36"/>
       <c r="C48" s="36"/>
@@ -47016,9 +46806,8 @@
       <c r="E48" s="36"/>
       <c r="F48" s="36"/>
       <c r="G48" s="36"/>
-      <c r="H48" s="36"/>
-    </row>
-    <row r="49" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="36"/>
       <c r="B49" s="36"/>
       <c r="C49" s="36"/>
@@ -47026,9 +46815,8 @@
       <c r="E49" s="36"/>
       <c r="F49" s="36"/>
       <c r="G49" s="36"/>
-      <c r="H49" s="36"/>
-    </row>
-    <row r="50" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="36"/>
       <c r="B50" s="36"/>
       <c r="C50" s="36"/>
@@ -47036,9 +46824,8 @@
       <c r="E50" s="36"/>
       <c r="F50" s="36"/>
       <c r="G50" s="36"/>
-      <c r="H50" s="36"/>
-    </row>
-    <row r="51" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="36"/>
       <c r="B51" s="36"/>
       <c r="C51" s="36"/>
@@ -47046,9 +46833,8 @@
       <c r="E51" s="36"/>
       <c r="F51" s="36"/>
       <c r="G51" s="36"/>
-      <c r="H51" s="36"/>
-    </row>
-    <row r="52" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="36"/>
       <c r="B52" s="36"/>
       <c r="C52" s="36"/>
@@ -47056,9 +46842,8 @@
       <c r="E52" s="36"/>
       <c r="F52" s="36"/>
       <c r="G52" s="36"/>
-      <c r="H52" s="36"/>
-    </row>
-    <row r="53" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="36"/>
       <c r="B53" s="36"/>
       <c r="C53" s="36"/>
@@ -47066,9 +46851,8 @@
       <c r="E53" s="36"/>
       <c r="F53" s="36"/>
       <c r="G53" s="36"/>
-      <c r="H53" s="36"/>
-    </row>
-    <row r="54" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="36"/>
       <c r="B54" s="36"/>
       <c r="C54" s="36"/>
@@ -47076,9 +46860,8 @@
       <c r="E54" s="36"/>
       <c r="F54" s="36"/>
       <c r="G54" s="36"/>
-      <c r="H54" s="36"/>
-    </row>
-    <row r="55" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="36"/>
       <c r="B55" s="36"/>
       <c r="C55" s="36"/>
@@ -47086,9 +46869,8 @@
       <c r="E55" s="36"/>
       <c r="F55" s="36"/>
       <c r="G55" s="36"/>
-      <c r="H55" s="36"/>
-    </row>
-    <row r="56" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="36"/>
       <c r="B56" s="36"/>
       <c r="C56" s="36"/>
@@ -47096,9 +46878,8 @@
       <c r="E56" s="36"/>
       <c r="F56" s="36"/>
       <c r="G56" s="36"/>
-      <c r="H56" s="36"/>
-    </row>
-    <row r="57" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="36"/>
       <c r="B57" s="36"/>
       <c r="C57" s="36"/>
@@ -47106,9 +46887,8 @@
       <c r="E57" s="36"/>
       <c r="F57" s="36"/>
       <c r="G57" s="36"/>
-      <c r="H57" s="36"/>
-    </row>
-    <row r="58" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="36"/>
       <c r="B58" s="36"/>
       <c r="C58" s="36"/>
@@ -47116,9 +46896,8 @@
       <c r="E58" s="36"/>
       <c r="F58" s="36"/>
       <c r="G58" s="36"/>
-      <c r="H58" s="36"/>
-    </row>
-    <row r="59" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="36"/>
       <c r="B59" s="36"/>
       <c r="C59" s="36"/>
@@ -47126,9 +46905,8 @@
       <c r="E59" s="36"/>
       <c r="F59" s="36"/>
       <c r="G59" s="36"/>
-      <c r="H59" s="36"/>
-    </row>
-    <row r="60" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="36"/>
       <c r="B60" s="36"/>
       <c r="C60" s="36"/>
@@ -47136,9 +46914,8 @@
       <c r="E60" s="36"/>
       <c r="F60" s="36"/>
       <c r="G60" s="36"/>
-      <c r="H60" s="36"/>
-    </row>
-    <row r="61" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="36"/>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -47146,9 +46923,8 @@
       <c r="E61" s="36"/>
       <c r="F61" s="36"/>
       <c r="G61" s="36"/>
-      <c r="H61" s="36"/>
-    </row>
-    <row r="62" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="36"/>
       <c r="B62" s="36"/>
       <c r="C62" s="36"/>
@@ -47156,9 +46932,8 @@
       <c r="E62" s="36"/>
       <c r="F62" s="36"/>
       <c r="G62" s="36"/>
-      <c r="H62" s="36"/>
-    </row>
-    <row r="63" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="36"/>
       <c r="B63" s="36"/>
       <c r="C63" s="36"/>
@@ -47166,9 +46941,8 @@
       <c r="E63" s="36"/>
       <c r="F63" s="36"/>
       <c r="G63" s="36"/>
-      <c r="H63" s="36"/>
-    </row>
-    <row r="64" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="36"/>
       <c r="B64" s="36"/>
       <c r="C64" s="36"/>
@@ -47176,9 +46950,8 @@
       <c r="E64" s="36"/>
       <c r="F64" s="36"/>
       <c r="G64" s="36"/>
-      <c r="H64" s="36"/>
-    </row>
-    <row r="65" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="36"/>
       <c r="B65" s="36"/>
       <c r="C65" s="36"/>
@@ -47186,9 +46959,8 @@
       <c r="E65" s="36"/>
       <c r="F65" s="36"/>
       <c r="G65" s="36"/>
-      <c r="H65" s="36"/>
-    </row>
-    <row r="66" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="36"/>
       <c r="B66" s="36"/>
       <c r="C66" s="36"/>
@@ -47196,9 +46968,8 @@
       <c r="E66" s="36"/>
       <c r="F66" s="36"/>
       <c r="G66" s="36"/>
-      <c r="H66" s="36"/>
-    </row>
-    <row r="67" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="36"/>
       <c r="B67" s="36"/>
       <c r="C67" s="36"/>
@@ -47206,9 +46977,8 @@
       <c r="E67" s="36"/>
       <c r="F67" s="36"/>
       <c r="G67" s="36"/>
-      <c r="H67" s="36"/>
-    </row>
-    <row r="68" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="36"/>
       <c r="B68" s="36"/>
       <c r="C68" s="36"/>
@@ -47216,9 +46986,8 @@
       <c r="E68" s="36"/>
       <c r="F68" s="36"/>
       <c r="G68" s="36"/>
-      <c r="H68" s="36"/>
-    </row>
-    <row r="69" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="36"/>
       <c r="B69" s="36"/>
       <c r="C69" s="36"/>
@@ -47226,9 +46995,8 @@
       <c r="E69" s="36"/>
       <c r="F69" s="36"/>
       <c r="G69" s="36"/>
-      <c r="H69" s="36"/>
-    </row>
-    <row r="70" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="36"/>
       <c r="B70" s="36"/>
       <c r="C70" s="36"/>
@@ -47236,9 +47004,8 @@
       <c r="E70" s="36"/>
       <c r="F70" s="36"/>
       <c r="G70" s="36"/>
-      <c r="H70" s="36"/>
-    </row>
-    <row r="71" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="36"/>
       <c r="B71" s="36"/>
       <c r="C71" s="36"/>
@@ -47246,9 +47013,8 @@
       <c r="E71" s="36"/>
       <c r="F71" s="36"/>
       <c r="G71" s="36"/>
-      <c r="H71" s="36"/>
-    </row>
-    <row r="72" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="36"/>
       <c r="B72" s="36"/>
       <c r="C72" s="36"/>
@@ -47256,9 +47022,8 @@
       <c r="E72" s="36"/>
       <c r="F72" s="36"/>
       <c r="G72" s="36"/>
-      <c r="H72" s="36"/>
-    </row>
-    <row r="73" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="36"/>
       <c r="B73" s="36"/>
       <c r="C73" s="36"/>
@@ -47266,9 +47031,8 @@
       <c r="E73" s="36"/>
       <c r="F73" s="36"/>
       <c r="G73" s="36"/>
-      <c r="H73" s="36"/>
-    </row>
-    <row r="74" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="36"/>
       <c r="B74" s="36"/>
       <c r="C74" s="36"/>
@@ -47276,9 +47040,8 @@
       <c r="E74" s="36"/>
       <c r="F74" s="36"/>
       <c r="G74" s="36"/>
-      <c r="H74" s="36"/>
-    </row>
-    <row r="75" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="36"/>
       <c r="B75" s="36"/>
       <c r="C75" s="36"/>
@@ -47286,9 +47049,8 @@
       <c r="E75" s="36"/>
       <c r="F75" s="36"/>
       <c r="G75" s="36"/>
-      <c r="H75" s="36"/>
-    </row>
-    <row r="76" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="36"/>
       <c r="B76" s="36"/>
       <c r="C76" s="36"/>
@@ -47296,9 +47058,8 @@
       <c r="E76" s="36"/>
       <c r="F76" s="36"/>
       <c r="G76" s="36"/>
-      <c r="H76" s="36"/>
-    </row>
-    <row r="77" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="36"/>
       <c r="B77" s="36"/>
       <c r="C77" s="36"/>
@@ -47306,9 +47067,8 @@
       <c r="E77" s="36"/>
       <c r="F77" s="36"/>
       <c r="G77" s="36"/>
-      <c r="H77" s="36"/>
-    </row>
-    <row r="78" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="78" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="36"/>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -47316,9 +47076,8 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
       <c r="G78" s="36"/>
-      <c r="H78" s="36"/>
-    </row>
-    <row r="79" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="36"/>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -47326,9 +47085,8 @@
       <c r="E79" s="36"/>
       <c r="F79" s="36"/>
       <c r="G79" s="36"/>
-      <c r="H79" s="36"/>
-    </row>
-    <row r="80" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="80" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="36"/>
       <c r="B80" s="36"/>
       <c r="C80" s="36"/>
@@ -47336,9 +47094,8 @@
       <c r="E80" s="36"/>
       <c r="F80" s="36"/>
       <c r="G80" s="36"/>
-      <c r="H80" s="36"/>
-    </row>
-    <row r="81" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="36"/>
       <c r="B81" s="36"/>
       <c r="C81" s="36"/>
@@ -47346,9 +47103,8 @@
       <c r="E81" s="36"/>
       <c r="F81" s="36"/>
       <c r="G81" s="36"/>
-      <c r="H81" s="36"/>
-    </row>
-    <row r="82" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="36"/>
       <c r="B82" s="36"/>
       <c r="C82" s="36"/>
@@ -47356,9 +47112,8 @@
       <c r="E82" s="36"/>
       <c r="F82" s="36"/>
       <c r="G82" s="36"/>
-      <c r="H82" s="36"/>
-    </row>
-    <row r="83" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="36"/>
       <c r="B83" s="36"/>
       <c r="C83" s="36"/>
@@ -47366,9 +47121,8 @@
       <c r="E83" s="36"/>
       <c r="F83" s="36"/>
       <c r="G83" s="36"/>
-      <c r="H83" s="36"/>
-    </row>
-    <row r="84" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="36"/>
       <c r="B84" s="36"/>
       <c r="C84" s="36"/>
@@ -47376,9 +47130,8 @@
       <c r="E84" s="36"/>
       <c r="F84" s="36"/>
       <c r="G84" s="36"/>
-      <c r="H84" s="36"/>
-    </row>
-    <row r="85" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="36"/>
       <c r="B85" s="36"/>
       <c r="C85" s="36"/>
@@ -47386,9 +47139,8 @@
       <c r="E85" s="36"/>
       <c r="F85" s="36"/>
       <c r="G85" s="36"/>
-      <c r="H85" s="36"/>
-    </row>
-    <row r="86" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="36"/>
       <c r="B86" s="36"/>
       <c r="C86" s="36"/>
@@ -47396,9 +47148,8 @@
       <c r="E86" s="36"/>
       <c r="F86" s="36"/>
       <c r="G86" s="36"/>
-      <c r="H86" s="36"/>
-    </row>
-    <row r="87" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="36"/>
       <c r="B87" s="36"/>
       <c r="C87" s="36"/>
@@ -47406,9 +47157,8 @@
       <c r="E87" s="36"/>
       <c r="F87" s="36"/>
       <c r="G87" s="36"/>
-      <c r="H87" s="36"/>
-    </row>
-    <row r="88" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="36"/>
       <c r="B88" s="36"/>
       <c r="C88" s="36"/>
@@ -47416,9 +47166,8 @@
       <c r="E88" s="36"/>
       <c r="F88" s="36"/>
       <c r="G88" s="36"/>
-      <c r="H88" s="36"/>
-    </row>
-    <row r="89" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="36"/>
       <c r="B89" s="36"/>
       <c r="C89" s="36"/>
@@ -47426,9 +47175,8 @@
       <c r="E89" s="36"/>
       <c r="F89" s="36"/>
       <c r="G89" s="36"/>
-      <c r="H89" s="36"/>
-    </row>
-    <row r="90" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="36"/>
       <c r="B90" s="36"/>
       <c r="C90" s="36"/>
@@ -47436,9 +47184,8 @@
       <c r="E90" s="36"/>
       <c r="F90" s="36"/>
       <c r="G90" s="36"/>
-      <c r="H90" s="36"/>
-    </row>
-    <row r="91" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="36"/>
       <c r="B91" s="36"/>
       <c r="C91" s="36"/>
@@ -47446,9 +47193,8 @@
       <c r="E91" s="36"/>
       <c r="F91" s="36"/>
       <c r="G91" s="36"/>
-      <c r="H91" s="36"/>
-    </row>
-    <row r="92" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="36"/>
       <c r="B92" s="36"/>
       <c r="C92" s="36"/>
@@ -47456,9 +47202,8 @@
       <c r="E92" s="36"/>
       <c r="F92" s="36"/>
       <c r="G92" s="36"/>
-      <c r="H92" s="36"/>
-    </row>
-    <row r="93" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="36"/>
       <c r="B93" s="36"/>
       <c r="C93" s="36"/>
@@ -47466,9 +47211,8 @@
       <c r="E93" s="36"/>
       <c r="F93" s="36"/>
       <c r="G93" s="36"/>
-      <c r="H93" s="36"/>
-    </row>
-    <row r="94" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="36"/>
       <c r="B94" s="36"/>
       <c r="C94" s="36"/>
@@ -47476,9 +47220,8 @@
       <c r="E94" s="36"/>
       <c r="F94" s="36"/>
       <c r="G94" s="36"/>
-      <c r="H94" s="36"/>
-    </row>
-    <row r="95" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="36"/>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -47486,9 +47229,8 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
       <c r="G95" s="36"/>
-      <c r="H95" s="36"/>
-    </row>
-    <row r="96" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="36"/>
       <c r="B96" s="36"/>
       <c r="C96" s="36"/>
@@ -47496,9 +47238,8 @@
       <c r="E96" s="36"/>
       <c r="F96" s="36"/>
       <c r="G96" s="36"/>
-      <c r="H96" s="36"/>
-    </row>
-    <row r="97" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="36"/>
       <c r="B97" s="36"/>
       <c r="C97" s="36"/>
@@ -47506,9 +47247,8 @@
       <c r="E97" s="36"/>
       <c r="F97" s="36"/>
       <c r="G97" s="36"/>
-      <c r="H97" s="36"/>
-    </row>
-    <row r="98" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="36"/>
       <c r="B98" s="36"/>
       <c r="C98" s="36"/>
@@ -47516,9 +47256,8 @@
       <c r="E98" s="36"/>
       <c r="F98" s="36"/>
       <c r="G98" s="36"/>
-      <c r="H98" s="36"/>
-    </row>
-    <row r="99" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="36"/>
       <c r="B99" s="36"/>
       <c r="C99" s="36"/>
@@ -47526,9 +47265,8 @@
       <c r="E99" s="36"/>
       <c r="F99" s="36"/>
       <c r="G99" s="36"/>
-      <c r="H99" s="36"/>
-    </row>
-    <row r="100" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="36"/>
       <c r="B100" s="36"/>
       <c r="C100" s="36"/>
@@ -47536,9 +47274,8 @@
       <c r="E100" s="36"/>
       <c r="F100" s="36"/>
       <c r="G100" s="36"/>
-      <c r="H100" s="36"/>
-    </row>
-    <row r="101" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="36"/>
       <c r="B101" s="36"/>
       <c r="C101" s="36"/>
@@ -47546,33 +47283,20 @@
       <c r="E101" s="36"/>
       <c r="F101" s="36"/>
       <c r="G101" s="36"/>
-      <c r="H101" s="36"/>
-    </row>
-    <row r="102" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    </row>
+    <row r="102" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="B3:C1048576 E3:E1048576 F3:G1048576 H3:H1048576" xr:uid="{2093DACC-A066-2948-81F2-6B8614F267FE}"/>
+    <dataValidation allowBlank="1" sqref="H1:XFD1048576 A1:A2 B2:G1048576" xr:uid="{996E8FCD-41A6-454D-99C0-71CAEC94973E}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{F6B3E541-4E6E-2B43-A809-0F368ECF78E0}">
-          <x14:formula1>
-            <xm:f>drop_down_rule_set!$L$2:$L$44</xm:f>
-          </x14:formula1>
-          <xm:sqref>A3:A1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -47601,71 +47325,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="234" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
-        <v>1542</v>
-      </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="146" t="s">
-        <v>1544</v>
-      </c>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
+      <c r="A1" s="132" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="142" t="s">
+        <v>1538</v>
+      </c>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
     </row>
     <row r="2" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="19" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C2" s="128" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>1510</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>1511</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>1513</v>
+      </c>
+      <c r="G2" s="49" t="s">
         <v>1514</v>
       </c>
-      <c r="C2" s="129" t="s">
+      <c r="H2" s="81" t="s">
         <v>1515</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="I2" s="19" t="s">
         <v>1516</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="J2" s="129" t="s">
         <v>1517</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="K2" s="19" t="s">
+        <v>1518</v>
+      </c>
+      <c r="L2" s="19" t="s">
         <v>1519</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="M2" s="131" t="s">
         <v>1520</v>
       </c>
-      <c r="H2" s="81" t="s">
+      <c r="N2" s="19" t="s">
+        <v>1512</v>
+      </c>
+      <c r="O2" s="19" t="s">
         <v>1521</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>1522</v>
-      </c>
-      <c r="J2" s="130" t="s">
-        <v>1523</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>1524</v>
-      </c>
-      <c r="L2" s="19" t="s">
-        <v>1525</v>
-      </c>
-      <c r="M2" s="132" t="s">
-        <v>1526</v>
-      </c>
-      <c r="N2" s="19" t="s">
-        <v>1518</v>
-      </c>
-      <c r="O2" s="19" t="s">
-        <v>1527</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
@@ -47680,10 +47404,10 @@
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
       <c r="I3" s="35"/>
-      <c r="J3" s="131"/>
+      <c r="J3" s="130"/>
       <c r="K3" s="35"/>
       <c r="L3" s="35"/>
-      <c r="M3" s="131"/>
+      <c r="M3" s="130"/>
       <c r="N3" s="35"/>
       <c r="O3" s="35"/>
     </row>
@@ -47695,30 +47419,30 @@
         <v>1342</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
       <c r="E4" s="35"/>
       <c r="F4" s="35" t="s">
         <v>1342</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>1533</v>
+        <v>1527</v>
       </c>
       <c r="H4" s="35" t="s">
-        <v>1528</v>
+        <v>1522</v>
       </c>
       <c r="I4" s="35" t="s">
-        <v>1529</v>
-      </c>
-      <c r="J4" s="131">
+        <v>1523</v>
+      </c>
+      <c r="J4" s="130">
         <v>256</v>
       </c>
       <c r="K4" s="35"/>
       <c r="L4" s="35"/>
-      <c r="M4" s="131"/>
+      <c r="M4" s="130"/>
       <c r="N4" s="35"/>
       <c r="O4" s="35"/>
     </row>
@@ -47732,22 +47456,22 @@
         <v>424</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
       <c r="H5" s="35" t="s">
-        <v>1535</v>
+        <v>1529</v>
       </c>
       <c r="I5" s="35" t="s">
+        <v>1524</v>
+      </c>
+      <c r="J5" s="130">
+        <v>384</v>
+      </c>
+      <c r="K5" s="35" t="s">
         <v>1530</v>
       </c>
-      <c r="J5" s="131">
-        <v>384</v>
-      </c>
-      <c r="K5" s="35" t="s">
-        <v>1536</v>
-      </c>
       <c r="L5" s="35"/>
-      <c r="M5" s="131"/>
+      <c r="M5" s="130"/>
       <c r="N5" s="35"/>
       <c r="O5" s="35"/>
     </row>
@@ -47759,10 +47483,10 @@
         <v>1342</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>1537</v>
+        <v>1531</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>1538</v>
+        <v>1532</v>
       </c>
       <c r="E6" s="35" t="s">
         <v>5</v>
@@ -47771,22 +47495,22 @@
         <v>1342</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>1533</v>
+        <v>1527</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>1535</v>
+        <v>1529</v>
       </c>
       <c r="I6" s="35" t="s">
-        <v>1529</v>
-      </c>
-      <c r="J6" s="131">
+        <v>1523</v>
+      </c>
+      <c r="J6" s="130">
         <v>128</v>
       </c>
       <c r="K6" s="35"/>
       <c r="L6" s="35" t="b">
         <v>1</v>
       </c>
-      <c r="M6" s="131">
+      <c r="M6" s="130">
         <v>100</v>
       </c>
       <c r="N6" s="35"/>
@@ -47802,20 +47526,20 @@
         <v>424</v>
       </c>
       <c r="G7" s="35" t="s">
+        <v>1528</v>
+      </c>
+      <c r="H7" s="35" t="s">
+        <v>1529</v>
+      </c>
+      <c r="I7" s="35" t="s">
         <v>1534</v>
       </c>
-      <c r="H7" s="35" t="s">
-        <v>1535</v>
-      </c>
-      <c r="I7" s="35" t="s">
-        <v>1540</v>
-      </c>
-      <c r="J7" s="131">
+      <c r="J7" s="130">
         <v>3072</v>
       </c>
       <c r="K7" s="35"/>
       <c r="L7" s="35"/>
-      <c r="M7" s="131"/>
+      <c r="M7" s="130"/>
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
     </row>
@@ -47829,24 +47553,24 @@
         <v>426</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>1539</v>
+        <v>1533</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>1528</v>
+        <v>1522</v>
       </c>
       <c r="I8" s="35" t="s">
-        <v>1530</v>
-      </c>
-      <c r="J8" s="131">
+        <v>1524</v>
+      </c>
+      <c r="J8" s="130">
         <v>521</v>
       </c>
       <c r="K8" s="35" t="s">
-        <v>1541</v>
+        <v>1535</v>
       </c>
       <c r="L8" s="35" t="b">
         <v>1</v>
       </c>
-      <c r="M8" s="131">
+      <c r="M8" s="130">
         <v>365</v>
       </c>
       <c r="N8" s="35"/>
@@ -47862,10 +47586,10 @@
       <c r="G9" s="35"/>
       <c r="H9" s="35"/>
       <c r="I9" s="35"/>
-      <c r="J9" s="131"/>
+      <c r="J9" s="130"/>
       <c r="K9" s="35"/>
       <c r="L9" s="35"/>
-      <c r="M9" s="131"/>
+      <c r="M9" s="130"/>
       <c r="N9" s="35"/>
       <c r="O9" s="35"/>
     </row>
@@ -47879,10 +47603,10 @@
       <c r="G10" s="35"/>
       <c r="H10" s="35"/>
       <c r="I10" s="35"/>
-      <c r="J10" s="131"/>
+      <c r="J10" s="130"/>
       <c r="K10" s="35"/>
       <c r="L10" s="35"/>
-      <c r="M10" s="131"/>
+      <c r="M10" s="130"/>
       <c r="N10" s="35"/>
       <c r="O10" s="35"/>
     </row>
@@ -47896,10 +47620,10 @@
       <c r="G11" s="35"/>
       <c r="H11" s="35"/>
       <c r="I11" s="35"/>
-      <c r="J11" s="131"/>
+      <c r="J11" s="130"/>
       <c r="K11" s="35"/>
       <c r="L11" s="35"/>
-      <c r="M11" s="131"/>
+      <c r="M11" s="130"/>
       <c r="N11" s="35"/>
       <c r="O11" s="35"/>
     </row>
@@ -47913,10 +47637,10 @@
       <c r="G12" s="35"/>
       <c r="H12" s="35"/>
       <c r="I12" s="35"/>
-      <c r="J12" s="131"/>
+      <c r="J12" s="130"/>
       <c r="K12" s="35"/>
       <c r="L12" s="35"/>
-      <c r="M12" s="131"/>
+      <c r="M12" s="130"/>
       <c r="N12" s="35"/>
       <c r="O12" s="35"/>
     </row>
@@ -47930,10 +47654,10 @@
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
       <c r="I13" s="35"/>
-      <c r="J13" s="131"/>
+      <c r="J13" s="130"/>
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
-      <c r="M13" s="131"/>
+      <c r="M13" s="130"/>
       <c r="N13" s="35"/>
       <c r="O13" s="35"/>
     </row>
@@ -47947,10 +47671,10 @@
       <c r="G14" s="35"/>
       <c r="H14" s="35"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="131"/>
+      <c r="J14" s="130"/>
       <c r="K14" s="35"/>
       <c r="L14" s="35"/>
-      <c r="M14" s="131"/>
+      <c r="M14" s="130"/>
       <c r="N14" s="35"/>
       <c r="O14" s="35"/>
     </row>
@@ -47964,10 +47688,10 @@
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
       <c r="I15" s="35"/>
-      <c r="J15" s="131"/>
+      <c r="J15" s="130"/>
       <c r="K15" s="35"/>
       <c r="L15" s="35"/>
-      <c r="M15" s="131"/>
+      <c r="M15" s="130"/>
       <c r="N15" s="35"/>
       <c r="O15" s="35"/>
     </row>
@@ -47981,10 +47705,10 @@
       <c r="G16" s="35"/>
       <c r="H16" s="35"/>
       <c r="I16" s="35"/>
-      <c r="J16" s="131"/>
+      <c r="J16" s="130"/>
       <c r="K16" s="35"/>
       <c r="L16" s="35"/>
-      <c r="M16" s="131"/>
+      <c r="M16" s="130"/>
       <c r="N16" s="35"/>
       <c r="O16" s="35"/>
     </row>
@@ -47998,10 +47722,10 @@
       <c r="G17" s="35"/>
       <c r="H17" s="35"/>
       <c r="I17" s="35"/>
-      <c r="J17" s="131"/>
+      <c r="J17" s="130"/>
       <c r="K17" s="35"/>
       <c r="L17" s="35"/>
-      <c r="M17" s="131"/>
+      <c r="M17" s="130"/>
       <c r="N17" s="35"/>
       <c r="O17" s="35"/>
     </row>
@@ -48015,10 +47739,10 @@
       <c r="G18" s="35"/>
       <c r="H18" s="35"/>
       <c r="I18" s="35"/>
-      <c r="J18" s="131"/>
+      <c r="J18" s="130"/>
       <c r="K18" s="35"/>
       <c r="L18" s="35"/>
-      <c r="M18" s="131"/>
+      <c r="M18" s="130"/>
       <c r="N18" s="35"/>
       <c r="O18" s="35"/>
     </row>
@@ -48032,10 +47756,10 @@
       <c r="G19" s="35"/>
       <c r="H19" s="35"/>
       <c r="I19" s="35"/>
-      <c r="J19" s="131"/>
+      <c r="J19" s="130"/>
       <c r="K19" s="35"/>
       <c r="L19" s="35"/>
-      <c r="M19" s="131"/>
+      <c r="M19" s="130"/>
       <c r="N19" s="35"/>
       <c r="O19" s="35"/>
     </row>
@@ -48049,10 +47773,10 @@
       <c r="G20" s="35"/>
       <c r="H20" s="35"/>
       <c r="I20" s="35"/>
-      <c r="J20" s="131"/>
+      <c r="J20" s="130"/>
       <c r="K20" s="35"/>
       <c r="L20" s="35"/>
-      <c r="M20" s="131"/>
+      <c r="M20" s="130"/>
       <c r="N20" s="35"/>
       <c r="O20" s="35"/>
     </row>
@@ -48066,10 +47790,10 @@
       <c r="G21" s="35"/>
       <c r="H21" s="35"/>
       <c r="I21" s="35"/>
-      <c r="J21" s="131"/>
+      <c r="J21" s="130"/>
       <c r="K21" s="35"/>
       <c r="L21" s="35"/>
-      <c r="M21" s="131"/>
+      <c r="M21" s="130"/>
       <c r="N21" s="35"/>
       <c r="O21" s="35"/>
     </row>
@@ -48083,10 +47807,10 @@
       <c r="G22" s="35"/>
       <c r="H22" s="35"/>
       <c r="I22" s="35"/>
-      <c r="J22" s="131"/>
+      <c r="J22" s="130"/>
       <c r="K22" s="35"/>
       <c r="L22" s="35"/>
-      <c r="M22" s="131"/>
+      <c r="M22" s="130"/>
       <c r="N22" s="35"/>
       <c r="O22" s="35"/>
     </row>
@@ -48100,10 +47824,10 @@
       <c r="G23" s="35"/>
       <c r="H23" s="35"/>
       <c r="I23" s="35"/>
-      <c r="J23" s="131"/>
+      <c r="J23" s="130"/>
       <c r="K23" s="35"/>
       <c r="L23" s="35"/>
-      <c r="M23" s="131"/>
+      <c r="M23" s="130"/>
       <c r="N23" s="35"/>
       <c r="O23" s="35"/>
     </row>
@@ -48117,10 +47841,10 @@
       <c r="G24" s="35"/>
       <c r="H24" s="35"/>
       <c r="I24" s="35"/>
-      <c r="J24" s="131"/>
+      <c r="J24" s="130"/>
       <c r="K24" s="35"/>
       <c r="L24" s="35"/>
-      <c r="M24" s="131"/>
+      <c r="M24" s="130"/>
       <c r="N24" s="35"/>
       <c r="O24" s="35"/>
     </row>
@@ -48134,10 +47858,10 @@
       <c r="G25" s="35"/>
       <c r="H25" s="35"/>
       <c r="I25" s="35"/>
-      <c r="J25" s="131"/>
+      <c r="J25" s="130"/>
       <c r="K25" s="35"/>
       <c r="L25" s="35"/>
-      <c r="M25" s="131"/>
+      <c r="M25" s="130"/>
       <c r="N25" s="35"/>
       <c r="O25" s="35"/>
     </row>
@@ -48151,10 +47875,10 @@
       <c r="G26" s="35"/>
       <c r="H26" s="35"/>
       <c r="I26" s="35"/>
-      <c r="J26" s="131"/>
+      <c r="J26" s="130"/>
       <c r="K26" s="35"/>
       <c r="L26" s="35"/>
-      <c r="M26" s="131"/>
+      <c r="M26" s="130"/>
       <c r="N26" s="35"/>
       <c r="O26" s="35"/>
     </row>
@@ -48168,10 +47892,10 @@
       <c r="G27" s="35"/>
       <c r="H27" s="35"/>
       <c r="I27" s="35"/>
-      <c r="J27" s="131"/>
+      <c r="J27" s="130"/>
       <c r="K27" s="35"/>
       <c r="L27" s="35"/>
-      <c r="M27" s="131"/>
+      <c r="M27" s="130"/>
       <c r="N27" s="35"/>
       <c r="O27" s="35"/>
     </row>
@@ -48185,10 +47909,10 @@
       <c r="G28" s="35"/>
       <c r="H28" s="35"/>
       <c r="I28" s="35"/>
-      <c r="J28" s="131"/>
+      <c r="J28" s="130"/>
       <c r="K28" s="35"/>
       <c r="L28" s="35"/>
-      <c r="M28" s="131"/>
+      <c r="M28" s="130"/>
       <c r="N28" s="35"/>
       <c r="O28" s="35"/>
     </row>
@@ -48202,10 +47926,10 @@
       <c r="G29" s="35"/>
       <c r="H29" s="35"/>
       <c r="I29" s="35"/>
-      <c r="J29" s="131"/>
+      <c r="J29" s="130"/>
       <c r="K29" s="35"/>
       <c r="L29" s="35"/>
-      <c r="M29" s="131"/>
+      <c r="M29" s="130"/>
       <c r="N29" s="35"/>
       <c r="O29" s="35"/>
     </row>
@@ -48219,10 +47943,10 @@
       <c r="G30" s="35"/>
       <c r="H30" s="35"/>
       <c r="I30" s="35"/>
-      <c r="J30" s="131"/>
+      <c r="J30" s="130"/>
       <c r="K30" s="35"/>
       <c r="L30" s="35"/>
-      <c r="M30" s="131"/>
+      <c r="M30" s="130"/>
       <c r="N30" s="35"/>
       <c r="O30" s="35"/>
     </row>
@@ -48236,10 +47960,10 @@
       <c r="G31" s="35"/>
       <c r="H31" s="35"/>
       <c r="I31" s="35"/>
-      <c r="J31" s="131"/>
+      <c r="J31" s="130"/>
       <c r="K31" s="35"/>
       <c r="L31" s="35"/>
-      <c r="M31" s="131"/>
+      <c r="M31" s="130"/>
       <c r="N31" s="35"/>
       <c r="O31" s="35"/>
     </row>
@@ -48253,10 +47977,10 @@
       <c r="G32" s="35"/>
       <c r="H32" s="35"/>
       <c r="I32" s="35"/>
-      <c r="J32" s="131"/>
+      <c r="J32" s="130"/>
       <c r="K32" s="35"/>
       <c r="L32" s="35"/>
-      <c r="M32" s="131"/>
+      <c r="M32" s="130"/>
       <c r="N32" s="35"/>
       <c r="O32" s="35"/>
     </row>
@@ -48270,10 +47994,10 @@
       <c r="G33" s="35"/>
       <c r="H33" s="35"/>
       <c r="I33" s="35"/>
-      <c r="J33" s="131"/>
+      <c r="J33" s="130"/>
       <c r="K33" s="35"/>
       <c r="L33" s="35"/>
-      <c r="M33" s="131"/>
+      <c r="M33" s="130"/>
       <c r="N33" s="35"/>
       <c r="O33" s="35"/>
     </row>
@@ -48287,10 +48011,10 @@
       <c r="G34" s="35"/>
       <c r="H34" s="35"/>
       <c r="I34" s="35"/>
-      <c r="J34" s="131"/>
+      <c r="J34" s="130"/>
       <c r="K34" s="35"/>
       <c r="L34" s="35"/>
-      <c r="M34" s="131"/>
+      <c r="M34" s="130"/>
       <c r="N34" s="35"/>
       <c r="O34" s="35"/>
     </row>
@@ -48304,10 +48028,10 @@
       <c r="G35" s="35"/>
       <c r="H35" s="35"/>
       <c r="I35" s="35"/>
-      <c r="J35" s="131"/>
+      <c r="J35" s="130"/>
       <c r="K35" s="35"/>
       <c r="L35" s="35"/>
-      <c r="M35" s="131"/>
+      <c r="M35" s="130"/>
       <c r="N35" s="35"/>
       <c r="O35" s="35"/>
     </row>
@@ -48321,10 +48045,10 @@
       <c r="G36" s="35"/>
       <c r="H36" s="35"/>
       <c r="I36" s="35"/>
-      <c r="J36" s="131"/>
+      <c r="J36" s="130"/>
       <c r="K36" s="35"/>
       <c r="L36" s="35"/>
-      <c r="M36" s="131"/>
+      <c r="M36" s="130"/>
       <c r="N36" s="35"/>
       <c r="O36" s="35"/>
     </row>
@@ -48338,10 +48062,10 @@
       <c r="G37" s="35"/>
       <c r="H37" s="35"/>
       <c r="I37" s="35"/>
-      <c r="J37" s="131"/>
+      <c r="J37" s="130"/>
       <c r="K37" s="35"/>
       <c r="L37" s="35"/>
-      <c r="M37" s="131"/>
+      <c r="M37" s="130"/>
       <c r="N37" s="35"/>
       <c r="O37" s="35"/>
     </row>
@@ -48355,10 +48079,10 @@
       <c r="G38" s="35"/>
       <c r="H38" s="35"/>
       <c r="I38" s="35"/>
-      <c r="J38" s="131"/>
+      <c r="J38" s="130"/>
       <c r="K38" s="35"/>
       <c r="L38" s="35"/>
-      <c r="M38" s="131"/>
+      <c r="M38" s="130"/>
       <c r="N38" s="35"/>
       <c r="O38" s="35"/>
     </row>
@@ -48372,10 +48096,10 @@
       <c r="G39" s="35"/>
       <c r="H39" s="35"/>
       <c r="I39" s="35"/>
-      <c r="J39" s="131"/>
+      <c r="J39" s="130"/>
       <c r="K39" s="35"/>
       <c r="L39" s="35"/>
-      <c r="M39" s="131"/>
+      <c r="M39" s="130"/>
       <c r="N39" s="35"/>
       <c r="O39" s="35"/>
     </row>
@@ -48389,10 +48113,10 @@
       <c r="G40" s="35"/>
       <c r="H40" s="35"/>
       <c r="I40" s="35"/>
-      <c r="J40" s="131"/>
+      <c r="J40" s="130"/>
       <c r="K40" s="35"/>
       <c r="L40" s="35"/>
-      <c r="M40" s="131"/>
+      <c r="M40" s="130"/>
       <c r="N40" s="35"/>
       <c r="O40" s="35"/>
     </row>
@@ -48406,10 +48130,10 @@
       <c r="G41" s="35"/>
       <c r="H41" s="35"/>
       <c r="I41" s="35"/>
-      <c r="J41" s="131"/>
+      <c r="J41" s="130"/>
       <c r="K41" s="35"/>
       <c r="L41" s="35"/>
-      <c r="M41" s="131"/>
+      <c r="M41" s="130"/>
       <c r="N41" s="35"/>
       <c r="O41" s="35"/>
     </row>
@@ -48423,10 +48147,10 @@
       <c r="G42" s="35"/>
       <c r="H42" s="35"/>
       <c r="I42" s="35"/>
-      <c r="J42" s="131"/>
+      <c r="J42" s="130"/>
       <c r="K42" s="35"/>
       <c r="L42" s="35"/>
-      <c r="M42" s="131"/>
+      <c r="M42" s="130"/>
       <c r="N42" s="35"/>
       <c r="O42" s="35"/>
     </row>
@@ -48440,10 +48164,10 @@
       <c r="G43" s="35"/>
       <c r="H43" s="35"/>
       <c r="I43" s="35"/>
-      <c r="J43" s="131"/>
+      <c r="J43" s="130"/>
       <c r="K43" s="35"/>
       <c r="L43" s="35"/>
-      <c r="M43" s="131"/>
+      <c r="M43" s="130"/>
       <c r="N43" s="35"/>
       <c r="O43" s="35"/>
     </row>
@@ -48457,10 +48181,10 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
       <c r="I44" s="35"/>
-      <c r="J44" s="131"/>
+      <c r="J44" s="130"/>
       <c r="K44" s="35"/>
       <c r="L44" s="35"/>
-      <c r="M44" s="131"/>
+      <c r="M44" s="130"/>
       <c r="N44" s="35"/>
       <c r="O44" s="35"/>
     </row>
@@ -48474,10 +48198,10 @@
       <c r="G45" s="35"/>
       <c r="H45" s="35"/>
       <c r="I45" s="35"/>
-      <c r="J45" s="131"/>
+      <c r="J45" s="130"/>
       <c r="K45" s="35"/>
       <c r="L45" s="35"/>
-      <c r="M45" s="131"/>
+      <c r="M45" s="130"/>
       <c r="N45" s="35"/>
       <c r="O45" s="35"/>
     </row>
@@ -48491,10 +48215,10 @@
       <c r="G46" s="35"/>
       <c r="H46" s="35"/>
       <c r="I46" s="35"/>
-      <c r="J46" s="131"/>
+      <c r="J46" s="130"/>
       <c r="K46" s="35"/>
       <c r="L46" s="35"/>
-      <c r="M46" s="131"/>
+      <c r="M46" s="130"/>
       <c r="N46" s="35"/>
       <c r="O46" s="35"/>
     </row>
@@ -48508,10 +48232,10 @@
       <c r="G47" s="35"/>
       <c r="H47" s="35"/>
       <c r="I47" s="35"/>
-      <c r="J47" s="131"/>
+      <c r="J47" s="130"/>
       <c r="K47" s="35"/>
       <c r="L47" s="35"/>
-      <c r="M47" s="131"/>
+      <c r="M47" s="130"/>
       <c r="N47" s="35"/>
       <c r="O47" s="35"/>
     </row>
@@ -48525,10 +48249,10 @@
       <c r="G48" s="35"/>
       <c r="H48" s="35"/>
       <c r="I48" s="35"/>
-      <c r="J48" s="131"/>
+      <c r="J48" s="130"/>
       <c r="K48" s="35"/>
       <c r="L48" s="35"/>
-      <c r="M48" s="131"/>
+      <c r="M48" s="130"/>
       <c r="N48" s="35"/>
       <c r="O48" s="35"/>
     </row>
@@ -48542,10 +48266,10 @@
       <c r="G49" s="35"/>
       <c r="H49" s="35"/>
       <c r="I49" s="35"/>
-      <c r="J49" s="131"/>
+      <c r="J49" s="130"/>
       <c r="K49" s="35"/>
       <c r="L49" s="35"/>
-      <c r="M49" s="131"/>
+      <c r="M49" s="130"/>
       <c r="N49" s="35"/>
       <c r="O49" s="35"/>
     </row>
@@ -48559,10 +48283,10 @@
       <c r="G50" s="35"/>
       <c r="H50" s="35"/>
       <c r="I50" s="35"/>
-      <c r="J50" s="131"/>
+      <c r="J50" s="130"/>
       <c r="K50" s="35"/>
       <c r="L50" s="35"/>
-      <c r="M50" s="131"/>
+      <c r="M50" s="130"/>
       <c r="N50" s="35"/>
       <c r="O50" s="35"/>
     </row>
@@ -48576,10 +48300,10 @@
       <c r="G51" s="35"/>
       <c r="H51" s="35"/>
       <c r="I51" s="35"/>
-      <c r="J51" s="131"/>
+      <c r="J51" s="130"/>
       <c r="K51" s="35"/>
       <c r="L51" s="35"/>
-      <c r="M51" s="131"/>
+      <c r="M51" s="130"/>
       <c r="N51" s="35"/>
       <c r="O51" s="35"/>
     </row>
@@ -48593,10 +48317,10 @@
       <c r="G52" s="35"/>
       <c r="H52" s="35"/>
       <c r="I52" s="35"/>
-      <c r="J52" s="131"/>
+      <c r="J52" s="130"/>
       <c r="K52" s="35"/>
       <c r="L52" s="35"/>
-      <c r="M52" s="131"/>
+      <c r="M52" s="130"/>
       <c r="N52" s="35"/>
       <c r="O52" s="35"/>
     </row>
@@ -48610,10 +48334,10 @@
       <c r="G53" s="35"/>
       <c r="H53" s="35"/>
       <c r="I53" s="35"/>
-      <c r="J53" s="131"/>
+      <c r="J53" s="130"/>
       <c r="K53" s="35"/>
       <c r="L53" s="35"/>
-      <c r="M53" s="131"/>
+      <c r="M53" s="130"/>
       <c r="N53" s="35"/>
       <c r="O53" s="35"/>
     </row>
@@ -48627,10 +48351,10 @@
       <c r="G54" s="35"/>
       <c r="H54" s="35"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="131"/>
+      <c r="J54" s="130"/>
       <c r="K54" s="35"/>
       <c r="L54" s="35"/>
-      <c r="M54" s="131"/>
+      <c r="M54" s="130"/>
       <c r="N54" s="35"/>
       <c r="O54" s="35"/>
     </row>
@@ -48644,10 +48368,10 @@
       <c r="G55" s="35"/>
       <c r="H55" s="35"/>
       <c r="I55" s="35"/>
-      <c r="J55" s="131"/>
+      <c r="J55" s="130"/>
       <c r="K55" s="35"/>
       <c r="L55" s="35"/>
-      <c r="M55" s="131"/>
+      <c r="M55" s="130"/>
       <c r="N55" s="35"/>
       <c r="O55" s="35"/>
     </row>
@@ -48661,10 +48385,10 @@
       <c r="G56" s="35"/>
       <c r="H56" s="35"/>
       <c r="I56" s="35"/>
-      <c r="J56" s="131"/>
+      <c r="J56" s="130"/>
       <c r="K56" s="35"/>
       <c r="L56" s="35"/>
-      <c r="M56" s="131"/>
+      <c r="M56" s="130"/>
       <c r="N56" s="35"/>
       <c r="O56" s="35"/>
     </row>
@@ -48678,10 +48402,10 @@
       <c r="G57" s="35"/>
       <c r="H57" s="35"/>
       <c r="I57" s="35"/>
-      <c r="J57" s="131"/>
+      <c r="J57" s="130"/>
       <c r="K57" s="35"/>
       <c r="L57" s="35"/>
-      <c r="M57" s="131"/>
+      <c r="M57" s="130"/>
       <c r="N57" s="35"/>
       <c r="O57" s="35"/>
     </row>
@@ -48695,10 +48419,10 @@
       <c r="G58" s="35"/>
       <c r="H58" s="35"/>
       <c r="I58" s="35"/>
-      <c r="J58" s="131"/>
+      <c r="J58" s="130"/>
       <c r="K58" s="35"/>
       <c r="L58" s="35"/>
-      <c r="M58" s="131"/>
+      <c r="M58" s="130"/>
       <c r="N58" s="35"/>
       <c r="O58" s="35"/>
     </row>
@@ -48712,10 +48436,10 @@
       <c r="G59" s="35"/>
       <c r="H59" s="35"/>
       <c r="I59" s="35"/>
-      <c r="J59" s="131"/>
+      <c r="J59" s="130"/>
       <c r="K59" s="35"/>
       <c r="L59" s="35"/>
-      <c r="M59" s="131"/>
+      <c r="M59" s="130"/>
       <c r="N59" s="35"/>
       <c r="O59" s="35"/>
     </row>
@@ -48729,10 +48453,10 @@
       <c r="G60" s="35"/>
       <c r="H60" s="35"/>
       <c r="I60" s="35"/>
-      <c r="J60" s="131"/>
+      <c r="J60" s="130"/>
       <c r="K60" s="35"/>
       <c r="L60" s="35"/>
-      <c r="M60" s="131"/>
+      <c r="M60" s="130"/>
       <c r="N60" s="35"/>
       <c r="O60" s="35"/>
     </row>
@@ -48746,10 +48470,10 @@
       <c r="G61" s="35"/>
       <c r="H61" s="35"/>
       <c r="I61" s="35"/>
-      <c r="J61" s="131"/>
+      <c r="J61" s="130"/>
       <c r="K61" s="35"/>
       <c r="L61" s="35"/>
-      <c r="M61" s="131"/>
+      <c r="M61" s="130"/>
       <c r="N61" s="35"/>
       <c r="O61" s="35"/>
     </row>
@@ -48763,10 +48487,10 @@
       <c r="G62" s="35"/>
       <c r="H62" s="35"/>
       <c r="I62" s="35"/>
-      <c r="J62" s="131"/>
+      <c r="J62" s="130"/>
       <c r="K62" s="35"/>
       <c r="L62" s="35"/>
-      <c r="M62" s="131"/>
+      <c r="M62" s="130"/>
       <c r="N62" s="35"/>
       <c r="O62" s="35"/>
     </row>
@@ -48780,10 +48504,10 @@
       <c r="G63" s="35"/>
       <c r="H63" s="35"/>
       <c r="I63" s="35"/>
-      <c r="J63" s="131"/>
+      <c r="J63" s="130"/>
       <c r="K63" s="35"/>
       <c r="L63" s="35"/>
-      <c r="M63" s="131"/>
+      <c r="M63" s="130"/>
       <c r="N63" s="35"/>
       <c r="O63" s="35"/>
     </row>
@@ -48797,10 +48521,10 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
       <c r="I64" s="35"/>
-      <c r="J64" s="131"/>
+      <c r="J64" s="130"/>
       <c r="K64" s="35"/>
       <c r="L64" s="35"/>
-      <c r="M64" s="131"/>
+      <c r="M64" s="130"/>
       <c r="N64" s="35"/>
       <c r="O64" s="35"/>
     </row>
@@ -48814,10 +48538,10 @@
       <c r="G65" s="35"/>
       <c r="H65" s="35"/>
       <c r="I65" s="35"/>
-      <c r="J65" s="131"/>
+      <c r="J65" s="130"/>
       <c r="K65" s="35"/>
       <c r="L65" s="35"/>
-      <c r="M65" s="131"/>
+      <c r="M65" s="130"/>
       <c r="N65" s="35"/>
       <c r="O65" s="35"/>
     </row>
@@ -57657,14 +57381,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="43" customFormat="1" ht="134.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1353</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="138"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="136"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -57725,16 +57449,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="43" customFormat="1" ht="113" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1312</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
     </row>
     <row r="2" spans="1:8" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
@@ -61125,19 +60849,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="133" t="s">
         <v>576</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="142" t="s">
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="138" t="s">
         <v>850</v>
       </c>
-      <c r="H1" s="143"/>
-      <c r="I1" s="144"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="140"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="40" t="s">
@@ -61502,13 +61226,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="43" customFormat="1" ht="92" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
-        <v>1489</v>
-      </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
+      <c r="A1" s="132" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="109" t="s">
@@ -61523,7 +61247,7 @@
       <c r="D2" s="110" t="s">
         <v>1422</v>
       </c>
-      <c r="E2" s="112" t="s">
+      <c r="E2" s="111" t="s">
         <v>402</v>
       </c>
     </row>
@@ -61567,31 +61291,31 @@
     <col min="5" max="5" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" style="125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5" style="126" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" style="126" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" style="124" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5" style="125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" style="125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="65.6640625" customWidth="1"/>
-    <col min="14" max="14" width="41.5" style="127" customWidth="1"/>
+    <col min="14" max="14" width="41.5" style="126" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="43" customFormat="1" ht="207" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1471</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="138"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="136"/>
     </row>
     <row r="2" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="109" t="s">
@@ -61606,34 +61330,34 @@
       <c r="D2" s="110" t="s">
         <v>1444</v>
       </c>
-      <c r="E2" s="112" t="s">
+      <c r="E2" s="111" t="s">
         <v>1445</v>
       </c>
-      <c r="F2" s="112" t="s">
+      <c r="F2" s="111" t="s">
         <v>1446</v>
       </c>
-      <c r="G2" s="112" t="s">
+      <c r="G2" s="111" t="s">
         <v>1447</v>
       </c>
-      <c r="H2" s="118" t="s">
+      <c r="H2" s="117" t="s">
         <v>1448</v>
       </c>
-      <c r="I2" s="119" t="s">
+      <c r="I2" s="118" t="s">
         <v>1449</v>
       </c>
-      <c r="J2" s="119" t="s">
+      <c r="J2" s="118" t="s">
         <v>1450</v>
       </c>
-      <c r="K2" s="112" t="s">
+      <c r="K2" s="111" t="s">
         <v>1451</v>
       </c>
-      <c r="L2" s="112" t="s">
+      <c r="L2" s="111" t="s">
         <v>1452</v>
       </c>
-      <c r="M2" s="112" t="s">
+      <c r="M2" s="111" t="s">
         <v>1453</v>
       </c>
-      <c r="N2" s="120" t="s">
+      <c r="N2" s="119" t="s">
         <v>402</v>
       </c>
     </row>
@@ -61659,11 +61383,11 @@
       <c r="G3" s="35">
         <v>10</v>
       </c>
-      <c r="H3" s="121"/>
-      <c r="I3" s="122" t="s">
+      <c r="H3" s="120"/>
+      <c r="I3" s="121" t="s">
         <v>1458</v>
       </c>
-      <c r="J3" s="122" t="s">
+      <c r="J3" s="121" t="s">
         <v>1459</v>
       </c>
       <c r="K3" s="35"/>
@@ -61685,7 +61409,7 @@
         <v>1462</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1513</v>
+        <v>1507</v>
       </c>
       <c r="F4" s="35" t="s">
         <v>1463</v>
@@ -61693,17 +61417,17 @@
       <c r="G4" s="35">
         <v>100</v>
       </c>
-      <c r="H4" s="121">
+      <c r="H4" s="120">
         <v>5</v>
       </c>
-      <c r="I4" s="122"/>
-      <c r="J4" s="122"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
       <c r="K4" s="35" t="s">
         <v>1464</v>
       </c>
-      <c r="L4" s="123"/>
+      <c r="L4" s="122"/>
       <c r="M4" s="35"/>
-      <c r="N4" s="124"/>
+      <c r="N4" s="123"/>
     </row>
     <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="35"/>
@@ -61713,9 +61437,9 @@
       <c r="E5" s="35"/>
       <c r="F5" s="35"/>
       <c r="G5" s="35"/>
-      <c r="H5" s="121"/>
-      <c r="I5" s="122"/>
-      <c r="J5" s="122"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="121"/>
+      <c r="J5" s="121"/>
       <c r="K5" s="35" t="s">
         <v>1470</v>
       </c>
@@ -61725,7 +61449,7 @@
       <c r="M5" s="35" t="s">
         <v>1466</v>
       </c>
-      <c r="N5" s="124"/>
+      <c r="N5" s="123"/>
     </row>
     <row r="6" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="35"/>
@@ -61735,9 +61459,9 @@
       <c r="E6" s="35"/>
       <c r="F6" s="35"/>
       <c r="G6" s="35"/>
-      <c r="H6" s="121"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="122"/>
+      <c r="H6" s="120"/>
+      <c r="I6" s="121"/>
+      <c r="J6" s="121"/>
       <c r="K6" s="35" t="s">
         <v>1467</v>
       </c>
@@ -61745,7 +61469,7 @@
         <v>1468</v>
       </c>
       <c r="M6" s="35"/>
-      <c r="N6" s="124"/>
+      <c r="N6" s="123"/>
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="35" t="s">
@@ -61757,13 +61481,13 @@
       <c r="E7" s="35"/>
       <c r="F7" s="35"/>
       <c r="G7" s="35"/>
-      <c r="H7" s="121"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="122"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="121"/>
+      <c r="J7" s="121"/>
       <c r="K7" s="35"/>
       <c r="L7" s="35"/>
       <c r="M7" s="35"/>
-      <c r="N7" s="124"/>
+      <c r="N7" s="123"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36D023A-7408-6C4F-9576-5B69224C1B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9652563-8262-6745-A6F3-AEEA8A7DC222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9260" yWindow="780" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
@@ -281,7 +281,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Mansatory for Autotune Type - PERFORMANCE_BASED or BOTH</t>
+          <t>Mandatory for Autotune Type - PERFORMANCE_BASED or BOTH</t>
         </r>
       </text>
     </comment>
@@ -290,40 +290,6 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Suruchi</author>
-  </authors>
-  <commentList>
-    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{571B8153-5A5A-9343-B63E-0C9467A00B5E}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Enter OCID of the snapshot policy to be attached to the FSS.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Microsoft Office User</author>
@@ -572,7 +538,7 @@
 </comments>
 </file>
 
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Suruchi</author>
@@ -634,7 +600,7 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Suruchi</author>
@@ -12384,182 +12350,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
-Columns: Region, Compartment Name, Availability Domain, MountTarget Name, MountTarget SubnetName, FSS name, Path are mandatory.
-Freeform and Defined Tags - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>If specified, Applies to FSS object only and not to other components like Mount Target.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Enter subnet name as : </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&lt;</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">vcn-name&gt;_&lt;subnet-name&gt;
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Source Snapshot:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Accepts OCID of the source snapshot  or the name of the key defined under variable  fss_source_ocids in variables_&lt;region&gt;.tf file</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Replication Information: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Format - TargetFSS(OCID or Name)::ReplicationInterval::ReplicationName. Multiple replication values are seperated by newline in the same cell(\n is not supported). Ensure Target FSS for replication must not have exports created.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Defined Tags" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
-                             Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
-                           </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Example: Operations.CostCenter=01;Users.Name=user01</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
     <t>onlyMT</t>
   </si>
   <si>
@@ -12890,6 +12680,204 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  Example: Operations.CostCenter=01;Users.Name=user01</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
+Columns: Region, Compartment Name, Availability Domain, MountTarget Name, MountTarget SubnetName, FSS name, Path are mandatory.
+Freeform and Defined Tags - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>If specified, Applies to FSS object only and not to other components like Mount Target.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Enter subnet name as : </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">vcn-name&gt;_&lt;subnet-name&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Source Snapshot:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Accepts OCID of the source snapshot  or the name of the key defined under variable  fss_source_ocids in variables_&lt;region&gt;.tf file
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Snapshot Policy - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accepts OCID of the snapshot policy or the name in format: &lt;snaphot_policy_compartment_name&gt;@&lt;snaphost_policy_name&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Replication Information: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Format - TargetFSS(OCID or Name)::ReplicationInterval::ReplicationName. Multiple replication values are seperated by newline in the same cell(\n is not supported). Ensure Target FSS for replication must not have exports created.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Defined Tags" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
+                             Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
+                           </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Example: Operations.CostCenter=01;Users.Name=user01</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
     </r>
   </si>
 </sst>
@@ -30638,7 +30626,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
@@ -30667,7 +30655,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="133" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="133" t="s">
-        <v>1540</v>
+        <v>1549</v>
       </c>
       <c r="B1" s="134"/>
       <c r="C1" s="134"/>
@@ -30681,7 +30669,7 @@
       <c r="K1" s="134"/>
       <c r="L1" s="137"/>
       <c r="M1" s="149" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="N1" s="150"/>
       <c r="O1" s="150"/>
@@ -31064,7 +31052,7 @@
         <v>87</v>
       </c>
       <c r="D11" s="87" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="E11" s="53" t="s">
         <v>375</v>
@@ -31103,7 +31091,7 @@
       <c r="G12" s="87"/>
       <c r="H12" s="52"/>
       <c r="I12" s="87" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="J12" s="52"/>
       <c r="K12" s="52"/>
@@ -31130,7 +31118,6 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
@@ -33345,7 +33332,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="43" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="132" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="B1" s="132"/>
       <c r="C1" s="132"/>
@@ -46361,7 +46348,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="43" customFormat="1" ht="156.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="133" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="B1" s="134"/>
       <c r="C1" s="134"/>
@@ -46378,16 +46365,16 @@
         <v>1201</v>
       </c>
       <c r="C2" s="30" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>1545</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>1546</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>1547</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>1548</v>
       </c>
       <c r="G2" s="30" t="s">
         <v>402</v>

--- a/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9652563-8262-6745-A6F3-AEEA8A7DC222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDE99A4-8C34-8140-A186-D06711898BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -646,7 +646,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3138" uniqueCount="1550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3138" uniqueCount="1549">
   <si>
     <t>Region</t>
   </si>
@@ -10090,9 +10090,6 @@
   </si>
   <si>
     <t>Quota Policy</t>
-  </si>
-  <si>
-    <t>ashburn</t>
   </si>
   <si>
     <t>OracleAnalyticsQuota</t>
@@ -19033,7 +19030,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="79" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
     </row>
   </sheetData>
@@ -19064,7 +19061,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="247" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="133" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="B1" s="134"/>
       <c r="C1" s="134"/>
@@ -19072,7 +19069,7 @@
       <c r="E1" s="134"/>
       <c r="F1" s="137"/>
       <c r="G1" s="133" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H1" s="134"/>
       <c r="I1" s="134"/>
@@ -19135,7 +19132,7 @@
         <v>453</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="G3" s="36" t="s">
         <v>21</v>
@@ -30419,7 +30416,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="201" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="133" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="B1" s="134"/>
       <c r="C1" s="134"/>
@@ -30471,16 +30468,16 @@
         <v>411</v>
       </c>
       <c r="K2" s="31" t="s">
+        <v>1471</v>
+      </c>
+      <c r="L2" s="31" t="s">
         <v>1472</v>
       </c>
-      <c r="L2" s="31" t="s">
+      <c r="M2" s="31" t="s">
         <v>1473</v>
       </c>
-      <c r="M2" s="31" t="s">
-        <v>1474</v>
-      </c>
       <c r="N2" s="31" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="O2" s="31" t="s">
         <v>632</v>
@@ -30546,19 +30543,19 @@
         <v>634</v>
       </c>
       <c r="J4" s="127" t="s">
+        <v>1474</v>
+      </c>
+      <c r="K4" s="127" t="s">
         <v>1475</v>
-      </c>
-      <c r="K4" s="127" t="s">
-        <v>1476</v>
       </c>
       <c r="L4" s="127">
         <v>100</v>
       </c>
       <c r="M4" s="127" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="N4" s="127" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="O4" s="84" t="b">
         <v>1</v>
@@ -30655,7 +30652,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="133" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="133" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="B1" s="134"/>
       <c r="C1" s="134"/>
@@ -30669,7 +30666,7 @@
       <c r="K1" s="134"/>
       <c r="L1" s="137"/>
       <c r="M1" s="149" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="N1" s="150"/>
       <c r="O1" s="150"/>
@@ -30710,13 +30707,13 @@
         <v>111</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="K2" s="31" t="s">
+        <v>1486</v>
+      </c>
+      <c r="L2" s="31" t="s">
         <v>1487</v>
-      </c>
-      <c r="L2" s="31" t="s">
-        <v>1488</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>112</v>
@@ -30740,10 +30737,10 @@
         <v>118</v>
       </c>
       <c r="T2" s="31" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="U2" s="31" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="V2" s="10" t="s">
         <v>402</v>
@@ -31052,7 +31049,7 @@
         <v>87</v>
       </c>
       <c r="D11" s="87" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="E11" s="53" t="s">
         <v>375</v>
@@ -31091,7 +31088,7 @@
       <c r="G12" s="87"/>
       <c r="H12" s="52"/>
       <c r="I12" s="87" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="J12" s="52"/>
       <c r="K12" s="52"/>
@@ -31340,7 +31337,7 @@
         <v>1421</v>
       </c>
       <c r="AI2" s="31" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -31618,7 +31615,7 @@
       <c r="AG6" s="52"/>
       <c r="AH6" s="52"/>
       <c r="AI6" s="53" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
   </sheetData>
@@ -33332,7 +33329,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="43" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="132" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="B1" s="132"/>
       <c r="C1" s="132"/>
@@ -34334,10 +34331,10 @@
         <v>656</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="I2" s="31" t="s">
         <v>156</v>
@@ -34452,10 +34449,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="53" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H6" s="53" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="I6" s="53">
         <v>53</v>
@@ -45510,7 +45507,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="157" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B1" s="158"/>
       <c r="C1" s="158"/>
@@ -45542,7 +45539,7 @@
         <v>1211</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="E2" s="112" t="s">
         <v>1212</v>
@@ -45595,49 +45592,49 @@
         <v>424</v>
       </c>
       <c r="C3" s="35" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D3" s="35" t="s">
         <v>1429</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="E3" s="35" t="s">
         <v>1430</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="F3" s="35" t="s">
         <v>1431</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="G3" s="35" t="s">
         <v>1432</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="H3" s="35" t="s">
         <v>1433</v>
-      </c>
-      <c r="H3" s="35" t="s">
-        <v>1434</v>
       </c>
       <c r="I3" s="35" t="s">
         <v>56</v>
       </c>
       <c r="J3" s="35" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="K3" s="35">
         <v>16</v>
       </c>
       <c r="L3" t="s">
+        <v>1491</v>
+      </c>
+      <c r="M3" t="s">
         <v>1492</v>
-      </c>
-      <c r="M3" t="s">
-        <v>1493</v>
       </c>
       <c r="N3" s="35">
         <v>3</v>
       </c>
       <c r="O3" s="35" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="P3" s="35" t="b">
         <v>0</v>
       </c>
       <c r="Q3" s="35" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="R3" s="32"/>
     </row>
@@ -45649,18 +45646,18 @@
         <v>424</v>
       </c>
       <c r="C4" s="35" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D4" s="35" t="s">
         <v>1438</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>1439</v>
       </c>
       <c r="E4" s="35"/>
       <c r="F4" s="35"/>
       <c r="G4" s="35" t="s">
+        <v>1432</v>
+      </c>
+      <c r="H4" s="35" t="s">
         <v>1433</v>
-      </c>
-      <c r="H4" s="35" t="s">
-        <v>1434</v>
       </c>
       <c r="I4" s="35" t="s">
         <v>56</v>
@@ -45677,7 +45674,7 @@
         <v>3</v>
       </c>
       <c r="O4" s="35" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="P4" s="35" t="b">
         <v>0</v>
@@ -45760,7 +45757,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="146" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="B1" s="158"/>
       <c r="C1" s="158"/>
@@ -45826,43 +45823,43 @@
         <v>5</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C3" s="35" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D3" s="35" t="s">
         <v>1494</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="E3" s="35" t="s">
         <v>1495</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="F3" s="35" t="s">
         <v>1496</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="G3" s="35" t="s">
         <v>1497</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="H3" s="35" t="s">
         <v>1498</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="I3" s="35" t="s">
         <v>1499</v>
       </c>
-      <c r="I3" s="35" t="s">
+      <c r="J3" s="35" t="s">
         <v>1500</v>
       </c>
-      <c r="J3" s="35" t="s">
+      <c r="K3" s="35" t="s">
         <v>1501</v>
       </c>
-      <c r="K3" s="35" t="s">
+      <c r="L3" s="35" t="s">
         <v>1502</v>
       </c>
-      <c r="L3" s="35" t="s">
+      <c r="M3" s="35" t="s">
         <v>1503</v>
       </c>
-      <c r="M3" s="35" t="s">
-        <v>1504</v>
-      </c>
       <c r="N3" s="35" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="O3" s="115"/>
     </row>
@@ -45871,41 +45868,41 @@
         <v>5</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="C4" s="35" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D4" s="35" t="s">
         <v>1494</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>1495</v>
       </c>
       <c r="E4" s="35"/>
       <c r="F4" s="35" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G4" s="35" t="s">
         <v>1497</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="H4" s="35" t="s">
         <v>1498</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="I4" s="35" t="s">
         <v>1499</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="J4" s="35" t="s">
         <v>1500</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="K4" s="35" t="s">
         <v>1501</v>
       </c>
-      <c r="K4" s="35" t="s">
+      <c r="L4" s="35" t="s">
         <v>1502</v>
       </c>
-      <c r="L4" s="35" t="s">
+      <c r="M4" s="35" t="s">
         <v>1503</v>
       </c>
-      <c r="M4" s="35" t="s">
-        <v>1504</v>
-      </c>
       <c r="N4" s="35" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="O4" s="115"/>
     </row>
@@ -46348,7 +46345,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="43" customFormat="1" ht="156.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="133" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="B1" s="134"/>
       <c r="C1" s="134"/>
@@ -46365,16 +46362,16 @@
         <v>1201</v>
       </c>
       <c r="C2" s="30" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>1544</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>1545</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>1546</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>1547</v>
       </c>
       <c r="G2" s="30" t="s">
         <v>402</v>
@@ -47313,7 +47310,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="234" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="132" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B1" s="132"/>
       <c r="C1" s="132"/>
@@ -47322,7 +47319,7 @@
       <c r="F1" s="132"/>
       <c r="G1" s="132"/>
       <c r="H1" s="142" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="I1" s="132"/>
       <c r="J1" s="132"/>
@@ -47337,46 +47334,46 @@
         <v>0</v>
       </c>
       <c r="B2" s="19" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C2" s="128" t="s">
         <v>1508</v>
       </c>
-      <c r="C2" s="128" t="s">
+      <c r="D2" s="19" t="s">
         <v>1509</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="E2" s="19" t="s">
         <v>1510</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="F2" s="19" t="s">
+        <v>1512</v>
+      </c>
+      <c r="G2" s="49" t="s">
+        <v>1513</v>
+      </c>
+      <c r="H2" s="81" t="s">
+        <v>1514</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>1515</v>
+      </c>
+      <c r="J2" s="129" t="s">
+        <v>1516</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>1517</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>1518</v>
+      </c>
+      <c r="M2" s="131" t="s">
+        <v>1519</v>
+      </c>
+      <c r="N2" s="19" t="s">
         <v>1511</v>
       </c>
-      <c r="F2" s="19" t="s">
-        <v>1513</v>
-      </c>
-      <c r="G2" s="49" t="s">
-        <v>1514</v>
-      </c>
-      <c r="H2" s="81" t="s">
-        <v>1515</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>1516</v>
-      </c>
-      <c r="J2" s="129" t="s">
-        <v>1517</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>1518</v>
-      </c>
-      <c r="L2" s="19" t="s">
-        <v>1519</v>
-      </c>
-      <c r="M2" s="131" t="s">
+      <c r="O2" s="19" t="s">
         <v>1520</v>
-      </c>
-      <c r="N2" s="19" t="s">
-        <v>1512</v>
-      </c>
-      <c r="O2" s="19" t="s">
-        <v>1521</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
@@ -47406,23 +47403,23 @@
         <v>1342</v>
       </c>
       <c r="C4" s="35" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D4" s="35" t="s">
         <v>1525</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>1526</v>
       </c>
       <c r="E4" s="35"/>
       <c r="F4" s="35" t="s">
         <v>1342</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="H4" s="35" t="s">
+        <v>1521</v>
+      </c>
+      <c r="I4" s="35" t="s">
         <v>1522</v>
-      </c>
-      <c r="I4" s="35" t="s">
-        <v>1523</v>
       </c>
       <c r="J4" s="130">
         <v>256</v>
@@ -47443,19 +47440,19 @@
         <v>424</v>
       </c>
       <c r="G5" s="35" t="s">
+        <v>1527</v>
+      </c>
+      <c r="H5" s="35" t="s">
         <v>1528</v>
       </c>
-      <c r="H5" s="35" t="s">
-        <v>1529</v>
-      </c>
       <c r="I5" s="35" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="J5" s="130">
         <v>384</v>
       </c>
       <c r="K5" s="35" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="L5" s="35"/>
       <c r="M5" s="130"/>
@@ -47470,10 +47467,10 @@
         <v>1342</v>
       </c>
       <c r="C6" s="35" t="s">
+        <v>1530</v>
+      </c>
+      <c r="D6" s="35" t="s">
         <v>1531</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>1532</v>
       </c>
       <c r="E6" s="35" t="s">
         <v>5</v>
@@ -47482,13 +47479,13 @@
         <v>1342</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="I6" s="35" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="J6" s="130">
         <v>128</v>
@@ -47513,13 +47510,13 @@
         <v>424</v>
       </c>
       <c r="G7" s="35" t="s">
+        <v>1527</v>
+      </c>
+      <c r="H7" s="35" t="s">
         <v>1528</v>
       </c>
-      <c r="H7" s="35" t="s">
-        <v>1529</v>
-      </c>
       <c r="I7" s="35" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="J7" s="130">
         <v>3072</v>
@@ -47540,19 +47537,19 @@
         <v>426</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="I8" s="35" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="J8" s="130">
         <v>521</v>
       </c>
       <c r="K8" s="35" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="L8" s="35" t="b">
         <v>1</v>
@@ -61214,7 +61211,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="43" customFormat="1" ht="92" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="132" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="B1" s="132"/>
       <c r="C1" s="132"/>
@@ -61240,16 +61237,16 @@
     </row>
     <row r="3" spans="1:5" ht="112" x14ac:dyDescent="0.2">
       <c r="A3" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="63" t="s">
         <v>1423</v>
       </c>
-      <c r="B3" s="63" t="s">
+      <c r="C3" s="63" t="s">
         <v>1424</v>
       </c>
-      <c r="C3" s="63" t="s">
-        <v>1425</v>
-      </c>
       <c r="D3" s="35" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="E3" s="36"/>
     </row>
@@ -61288,7 +61285,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="43" customFormat="1" ht="207" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="132" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
@@ -61315,34 +61312,34 @@
         <v>2</v>
       </c>
       <c r="D2" s="110" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E2" s="111" t="s">
         <v>1444</v>
       </c>
-      <c r="E2" s="111" t="s">
+      <c r="F2" s="111" t="s">
         <v>1445</v>
       </c>
-      <c r="F2" s="111" t="s">
+      <c r="G2" s="111" t="s">
         <v>1446</v>
       </c>
-      <c r="G2" s="111" t="s">
+      <c r="H2" s="117" t="s">
         <v>1447</v>
       </c>
-      <c r="H2" s="117" t="s">
+      <c r="I2" s="118" t="s">
         <v>1448</v>
       </c>
-      <c r="I2" s="118" t="s">
+      <c r="J2" s="118" t="s">
         <v>1449</v>
       </c>
-      <c r="J2" s="118" t="s">
+      <c r="K2" s="111" t="s">
         <v>1450</v>
       </c>
-      <c r="K2" s="111" t="s">
+      <c r="L2" s="111" t="s">
         <v>1451</v>
       </c>
-      <c r="L2" s="111" t="s">
+      <c r="M2" s="111" t="s">
         <v>1452</v>
-      </c>
-      <c r="M2" s="111" t="s">
-        <v>1453</v>
       </c>
       <c r="N2" s="119" t="s">
         <v>402</v>
@@ -61350,32 +61347,32 @@
     </row>
     <row r="3" spans="1:14" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
-        <v>314</v>
+        <v>5</v>
       </c>
       <c r="B3" s="35" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C3" s="35" t="s">
         <v>1454</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="D3" s="35" t="s">
         <v>1455</v>
-      </c>
-      <c r="D3" s="35" t="s">
-        <v>1456</v>
       </c>
       <c r="E3" s="35" t="s">
         <v>384</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="G3" s="35">
         <v>10</v>
       </c>
       <c r="H3" s="120"/>
       <c r="I3" s="121" t="s">
+        <v>1457</v>
+      </c>
+      <c r="J3" s="121" t="s">
         <v>1458</v>
-      </c>
-      <c r="J3" s="121" t="s">
-        <v>1459</v>
       </c>
       <c r="K3" s="35"/>
       <c r="L3" s="35"/>
@@ -61384,22 +61381,22 @@
     </row>
     <row r="4" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="35" t="s">
-        <v>314</v>
+        <v>5</v>
       </c>
       <c r="B4" s="35" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C4" s="35" t="s">
         <v>1460</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="D4" s="35" t="s">
         <v>1461</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="E4" s="35" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F4" s="35" t="s">
         <v>1462</v>
-      </c>
-      <c r="E4" s="35" t="s">
-        <v>1507</v>
-      </c>
-      <c r="F4" s="35" t="s">
-        <v>1463</v>
       </c>
       <c r="G4" s="35">
         <v>100</v>
@@ -61410,7 +61407,7 @@
       <c r="I4" s="121"/>
       <c r="J4" s="121"/>
       <c r="K4" s="35" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="L4" s="122"/>
       <c r="M4" s="35"/>
@@ -61428,13 +61425,13 @@
       <c r="I5" s="121"/>
       <c r="J5" s="121"/>
       <c r="K5" s="35" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="L5" s="36" t="s">
+        <v>1464</v>
+      </c>
+      <c r="M5" s="35" t="s">
         <v>1465</v>
-      </c>
-      <c r="M5" s="35" t="s">
-        <v>1466</v>
       </c>
       <c r="N5" s="123"/>
     </row>
@@ -61450,10 +61447,10 @@
       <c r="I6" s="121"/>
       <c r="J6" s="121"/>
       <c r="K6" s="35" t="s">
+        <v>1466</v>
+      </c>
+      <c r="L6" s="36" t="s">
         <v>1467</v>
-      </c>
-      <c r="L6" s="36" t="s">
-        <v>1468</v>
       </c>
       <c r="M6" s="35"/>
       <c r="N6" s="123"/>

--- a/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDE99A4-8C34-8140-A186-D06711898BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD20AE5-3760-744A-951F-4CCC0D12D566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10353,265 +10353,6 @@
     <t>ACTUAL::100%</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;).
-"Region" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Home Region only</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Scope" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Compartment or Tag</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Target" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Compartment Name or {tagNamespace}.{tagKey}.{tagValue}. Note- It should be a </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Cost Tracking Tag.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Schedule" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MONTH or  SINGLE_USE</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Amount" - T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>he amount of the budget expressed as a whole number in the currency of the customer’s rate card</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Start Day" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>The number of days offset from the first day of the month, at which the budget processing period starts. eg. 18. Mandatory for schedule type - MONTH</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Budget Start Date"/"Budget End Date" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>eg. 2024-05-20. Mandatory for schedule type - SINGLE_USE</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Alert Rules" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&lt;ACTUAL/FORECAST&gt;::&lt;Threshold value %/Threshold Amount&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Alert Recipients": </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> comma seperated email addresses
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Defined Tags"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
-                                Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
-                                </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>Example: Operations.CostCenter=01;Users.Name=user01</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
     <t>Autotune Type</t>
   </si>
   <si>
@@ -12863,6 +12604,254 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Example: Operations.CostCenter=01;Users.Name=user01</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;).
+"Region" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Home Region only</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Scope" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Compartment or Tag</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Target" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Compartment Name or {tagNamespace}.{tagKey}.{tagValue}.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Schedule" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MONTH or  SINGLE_USE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Amount" - T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>he amount of the budget expressed as a whole number in the currency of the customer’s rate card</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Start Day" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The number of days offset from the first day of the month, at which the budget processing period starts. eg. 18. Mandatory for schedule type - MONTH</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Budget Start Date"/"Budget End Date" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>eg. 2024-05-20. Mandatory for schedule type - SINGLE_USE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Alert Rules" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;ACTUAL/FORECAST&gt;::&lt;Threshold value %/Threshold Amount&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Alert Recipients": </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> comma seperated email addresses
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Defined Tags"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
+                                Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
+                                </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>Example: Operations.CostCenter=01;Users.Name=user01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -19030,7 +19019,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="79" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
   </sheetData>
@@ -19061,7 +19050,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="247" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="133" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="B1" s="134"/>
       <c r="C1" s="134"/>
@@ -19069,7 +19058,7 @@
       <c r="E1" s="134"/>
       <c r="F1" s="137"/>
       <c r="G1" s="133" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H1" s="134"/>
       <c r="I1" s="134"/>
@@ -19132,7 +19121,7 @@
         <v>453</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="G3" s="36" t="s">
         <v>21</v>
@@ -30416,7 +30405,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="201" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="133" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="B1" s="134"/>
       <c r="C1" s="134"/>
@@ -30468,16 +30457,16 @@
         <v>411</v>
       </c>
       <c r="K2" s="31" t="s">
+        <v>1470</v>
+      </c>
+      <c r="L2" s="31" t="s">
         <v>1471</v>
       </c>
-      <c r="L2" s="31" t="s">
+      <c r="M2" s="31" t="s">
         <v>1472</v>
       </c>
-      <c r="M2" s="31" t="s">
-        <v>1473</v>
-      </c>
       <c r="N2" s="31" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="O2" s="31" t="s">
         <v>632</v>
@@ -30543,19 +30532,19 @@
         <v>634</v>
       </c>
       <c r="J4" s="127" t="s">
+        <v>1473</v>
+      </c>
+      <c r="K4" s="127" t="s">
         <v>1474</v>
-      </c>
-      <c r="K4" s="127" t="s">
-        <v>1475</v>
       </c>
       <c r="L4" s="127">
         <v>100</v>
       </c>
       <c r="M4" s="127" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="N4" s="127" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="O4" s="84" t="b">
         <v>1</v>
@@ -30652,7 +30641,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="133" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="133" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="B1" s="134"/>
       <c r="C1" s="134"/>
@@ -30666,7 +30655,7 @@
       <c r="K1" s="134"/>
       <c r="L1" s="137"/>
       <c r="M1" s="149" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="N1" s="150"/>
       <c r="O1" s="150"/>
@@ -30707,13 +30696,13 @@
         <v>111</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="K2" s="31" t="s">
+        <v>1485</v>
+      </c>
+      <c r="L2" s="31" t="s">
         <v>1486</v>
-      </c>
-      <c r="L2" s="31" t="s">
-        <v>1487</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>112</v>
@@ -30737,10 +30726,10 @@
         <v>118</v>
       </c>
       <c r="T2" s="31" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="U2" s="31" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="V2" s="10" t="s">
         <v>402</v>
@@ -31049,7 +31038,7 @@
         <v>87</v>
       </c>
       <c r="D11" s="87" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="E11" s="53" t="s">
         <v>375</v>
@@ -31088,7 +31077,7 @@
       <c r="G12" s="87"/>
       <c r="H12" s="52"/>
       <c r="I12" s="87" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="J12" s="52"/>
       <c r="K12" s="52"/>
@@ -33329,7 +33318,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="43" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="132" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B1" s="132"/>
       <c r="C1" s="132"/>
@@ -34331,10 +34320,10 @@
         <v>656</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="I2" s="31" t="s">
         <v>156</v>
@@ -34449,10 +34438,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="53" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H6" s="53" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="I6" s="53">
         <v>53</v>
@@ -45619,10 +45608,10 @@
         <v>16</v>
       </c>
       <c r="L3" t="s">
+        <v>1490</v>
+      </c>
+      <c r="M3" t="s">
         <v>1491</v>
-      </c>
-      <c r="M3" t="s">
-        <v>1492</v>
       </c>
       <c r="N3" s="35">
         <v>3</v>
@@ -45757,7 +45746,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="146" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="B1" s="158"/>
       <c r="C1" s="158"/>
@@ -45826,37 +45815,37 @@
         <v>1428</v>
       </c>
       <c r="C3" s="35" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D3" s="35" t="s">
         <v>1493</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="E3" s="35" t="s">
         <v>1494</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="F3" s="35" t="s">
         <v>1495</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="G3" s="35" t="s">
         <v>1496</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="H3" s="35" t="s">
         <v>1497</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="I3" s="35" t="s">
         <v>1498</v>
       </c>
-      <c r="I3" s="35" t="s">
+      <c r="J3" s="35" t="s">
         <v>1499</v>
       </c>
-      <c r="J3" s="35" t="s">
+      <c r="K3" s="35" t="s">
         <v>1500</v>
       </c>
-      <c r="K3" s="35" t="s">
+      <c r="L3" s="35" t="s">
         <v>1501</v>
       </c>
-      <c r="L3" s="35" t="s">
+      <c r="M3" s="35" t="s">
         <v>1502</v>
-      </c>
-      <c r="M3" s="35" t="s">
-        <v>1503</v>
       </c>
       <c r="N3" s="35" t="s">
         <v>1441</v>
@@ -45871,35 +45860,35 @@
         <v>1437</v>
       </c>
       <c r="C4" s="35" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D4" s="35" t="s">
         <v>1493</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>1494</v>
       </c>
       <c r="E4" s="35"/>
       <c r="F4" s="35" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G4" s="35" t="s">
         <v>1496</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="H4" s="35" t="s">
         <v>1497</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="I4" s="35" t="s">
         <v>1498</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="J4" s="35" t="s">
         <v>1499</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="K4" s="35" t="s">
         <v>1500</v>
       </c>
-      <c r="K4" s="35" t="s">
+      <c r="L4" s="35" t="s">
         <v>1501</v>
       </c>
-      <c r="L4" s="35" t="s">
+      <c r="M4" s="35" t="s">
         <v>1502</v>
-      </c>
-      <c r="M4" s="35" t="s">
-        <v>1503</v>
       </c>
       <c r="N4" s="35" t="s">
         <v>1442</v>
@@ -46345,7 +46334,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="43" customFormat="1" ht="156.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="133" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B1" s="134"/>
       <c r="C1" s="134"/>
@@ -46362,16 +46351,16 @@
         <v>1201</v>
       </c>
       <c r="C2" s="30" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>1543</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>1544</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>1545</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>1546</v>
       </c>
       <c r="G2" s="30" t="s">
         <v>402</v>
@@ -47310,7 +47299,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="234" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="132" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="B1" s="132"/>
       <c r="C1" s="132"/>
@@ -47319,7 +47308,7 @@
       <c r="F1" s="132"/>
       <c r="G1" s="132"/>
       <c r="H1" s="142" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="I1" s="132"/>
       <c r="J1" s="132"/>
@@ -47334,46 +47323,46 @@
         <v>0</v>
       </c>
       <c r="B2" s="19" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C2" s="128" t="s">
         <v>1507</v>
       </c>
-      <c r="C2" s="128" t="s">
+      <c r="D2" s="19" t="s">
         <v>1508</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="E2" s="19" t="s">
         <v>1509</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="F2" s="19" t="s">
+        <v>1511</v>
+      </c>
+      <c r="G2" s="49" t="s">
+        <v>1512</v>
+      </c>
+      <c r="H2" s="81" t="s">
+        <v>1513</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>1514</v>
+      </c>
+      <c r="J2" s="129" t="s">
+        <v>1515</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>1516</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>1517</v>
+      </c>
+      <c r="M2" s="131" t="s">
+        <v>1518</v>
+      </c>
+      <c r="N2" s="19" t="s">
         <v>1510</v>
       </c>
-      <c r="F2" s="19" t="s">
-        <v>1512</v>
-      </c>
-      <c r="G2" s="49" t="s">
-        <v>1513</v>
-      </c>
-      <c r="H2" s="81" t="s">
-        <v>1514</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>1515</v>
-      </c>
-      <c r="J2" s="129" t="s">
-        <v>1516</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>1517</v>
-      </c>
-      <c r="L2" s="19" t="s">
-        <v>1518</v>
-      </c>
-      <c r="M2" s="131" t="s">
+      <c r="O2" s="19" t="s">
         <v>1519</v>
-      </c>
-      <c r="N2" s="19" t="s">
-        <v>1511</v>
-      </c>
-      <c r="O2" s="19" t="s">
-        <v>1520</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
@@ -47403,23 +47392,23 @@
         <v>1342</v>
       </c>
       <c r="C4" s="35" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D4" s="35" t="s">
         <v>1524</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>1525</v>
       </c>
       <c r="E4" s="35"/>
       <c r="F4" s="35" t="s">
         <v>1342</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="H4" s="35" t="s">
+        <v>1520</v>
+      </c>
+      <c r="I4" s="35" t="s">
         <v>1521</v>
-      </c>
-      <c r="I4" s="35" t="s">
-        <v>1522</v>
       </c>
       <c r="J4" s="130">
         <v>256</v>
@@ -47440,19 +47429,19 @@
         <v>424</v>
       </c>
       <c r="G5" s="35" t="s">
+        <v>1526</v>
+      </c>
+      <c r="H5" s="35" t="s">
         <v>1527</v>
       </c>
-      <c r="H5" s="35" t="s">
-        <v>1528</v>
-      </c>
       <c r="I5" s="35" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="J5" s="130">
         <v>384</v>
       </c>
       <c r="K5" s="35" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="L5" s="35"/>
       <c r="M5" s="130"/>
@@ -47467,10 +47456,10 @@
         <v>1342</v>
       </c>
       <c r="C6" s="35" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D6" s="35" t="s">
         <v>1530</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>1531</v>
       </c>
       <c r="E6" s="35" t="s">
         <v>5</v>
@@ -47479,13 +47468,13 @@
         <v>1342</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="I6" s="35" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="J6" s="130">
         <v>128</v>
@@ -47510,13 +47499,13 @@
         <v>424</v>
       </c>
       <c r="G7" s="35" t="s">
+        <v>1526</v>
+      </c>
+      <c r="H7" s="35" t="s">
         <v>1527</v>
       </c>
-      <c r="H7" s="35" t="s">
-        <v>1528</v>
-      </c>
       <c r="I7" s="35" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="J7" s="130">
         <v>3072</v>
@@ -47537,19 +47526,19 @@
         <v>426</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="I8" s="35" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="J8" s="130">
         <v>521</v>
       </c>
       <c r="K8" s="35" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="L8" s="35" t="b">
         <v>1</v>
@@ -61211,7 +61200,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="43" customFormat="1" ht="92" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="132" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="B1" s="132"/>
       <c r="C1" s="132"/>
@@ -61285,7 +61274,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="43" customFormat="1" ht="207" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="132" t="s">
-        <v>1470</v>
+        <v>1548</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
@@ -61393,7 +61382,7 @@
         <v>1461</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="F4" s="35" t="s">
         <v>1462</v>

--- a/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lasyavadavalli/PycharmProjects/CD3Lasya/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD20AE5-3760-744A-951F-4CCC0D12D566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A10103-C4DD-AD49-8360-00DBD71F49CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13771,7 +13771,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -13942,6 +13941,9 @@
     </xf>
     <xf numFmtId="0" fontId="35" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -19049,22 +19051,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="247" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1483</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="133" t="s">
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="132" t="s">
         <v>1482</v>
       </c>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="137"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="136"/>
     </row>
     <row r="2" spans="1:12" s="43" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
@@ -19307,19 +19309,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="222" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>927</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="141" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="140" t="s">
         <v>1334</v>
       </c>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
     </row>
     <row r="2" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -19340,7 +19342,7 @@
       <c r="F2" s="30" t="s">
         <v>490</v>
       </c>
-      <c r="G2" s="95" t="s">
+      <c r="G2" s="94" t="s">
         <v>491</v>
       </c>
       <c r="H2" s="31" t="s">
@@ -19548,10 +19550,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="43" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>629</v>
       </c>
-      <c r="B1" s="140"/>
+      <c r="B1" s="139"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -19612,16 +19614,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="106" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>1406</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
     </row>
     <row r="2" spans="1:8" s="43" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -19907,30 +19909,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="192.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1326</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="142" t="s">
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="141" t="s">
         <v>1296</v>
       </c>
-      <c r="K1" s="142"/>
-      <c r="L1" s="142"/>
-      <c r="M1" s="142"/>
-      <c r="N1" s="142"/>
-      <c r="O1" s="142"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="142"/>
-      <c r="R1" s="142"/>
-      <c r="S1" s="142"/>
-      <c r="T1" s="142"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
     </row>
     <row r="2" spans="1:20" s="43" customFormat="1" ht="59.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -26037,18 +26039,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>1313</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
     </row>
     <row r="2" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -26159,17 +26161,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>1314</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -26261,25 +26263,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>1315</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
-      <c r="P1" s="132"/>
-      <c r="Q1" s="132"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -26411,28 +26413,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="118.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>1316</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
-      <c r="P1" s="132"/>
-      <c r="Q1" s="132"/>
-      <c r="R1" s="132"/>
-      <c r="S1" s="132"/>
-      <c r="T1" s="132"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="131"/>
+      <c r="S1" s="131"/>
+      <c r="T1" s="131"/>
     </row>
     <row r="2" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
@@ -28914,17 +28916,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="179.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>1325</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
@@ -28961,11 +28963,11 @@
       </c>
       <c r="B3" s="32"/>
       <c r="C3" s="32"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -29307,13 +29309,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="43" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>1311</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -29565,19 +29567,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="191.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="144" t="s">
+      <c r="A1" s="143" t="s">
         <v>1317</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
     </row>
     <row r="2" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -29615,19 +29617,19 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="34" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
+      <c r="B3" s="105"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="105"/>
+      <c r="K3" s="105"/>
     </row>
     <row r="4" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A4" s="36" t="s">
@@ -29747,15 +29749,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>1318</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
     </row>
     <row r="2" spans="1:7" s="43" customFormat="1" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -29930,32 +29932,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="275.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="145" t="s">
         <v>1407</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="133" t="s">
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="132" t="s">
         <v>1392</v>
       </c>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="134"/>
-      <c r="T1" s="134"/>
-      <c r="U1" s="134"/>
-      <c r="V1" s="137"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="133"/>
+      <c r="O1" s="133"/>
+      <c r="P1" s="133"/>
+      <c r="Q1" s="133"/>
+      <c r="R1" s="133"/>
+      <c r="S1" s="133"/>
+      <c r="T1" s="133"/>
+      <c r="U1" s="133"/>
+      <c r="V1" s="136"/>
     </row>
     <row r="2" spans="1:22" s="43" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -30404,26 +30406,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="201" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1537</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="137"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="133"/>
+      <c r="O1" s="133"/>
+      <c r="P1" s="133"/>
+      <c r="Q1" s="133"/>
+      <c r="R1" s="136"/>
     </row>
     <row r="2" spans="1:18" s="43" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -30531,19 +30533,19 @@
       <c r="I4" s="53" t="s">
         <v>634</v>
       </c>
-      <c r="J4" s="127" t="s">
+      <c r="J4" s="126" t="s">
         <v>1473</v>
       </c>
-      <c r="K4" s="127" t="s">
+      <c r="K4" s="126" t="s">
         <v>1474</v>
       </c>
-      <c r="L4" s="127">
+      <c r="L4" s="126">
         <v>100</v>
       </c>
-      <c r="M4" s="127" t="s">
+      <c r="M4" s="126" t="s">
         <v>1475</v>
       </c>
-      <c r="N4" s="127" t="s">
+      <c r="N4" s="126" t="s">
         <v>1484</v>
       </c>
       <c r="O4" s="84" t="b">
@@ -30608,6 +30610,24 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{5F2F54D4-DE5B-A740-A826-1380AC8F6641}">
+          <x14:formula1>
+            <xm:f>drop_down_rule_set!$L$2:$L$44</xm:f>
+          </x14:formula1>
+          <xm:sqref>A3:A1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{0D42991A-073B-0B40-AF45-49EF0E834302}">
+          <x14:formula1>
+            <xm:f>INDIRECT("drop_down_rule_comp!$D$2:$D$"&amp;drop_down_rule_comp!$C$3+1)</xm:f>
+          </x14:formula1>
+          <xm:sqref>B3:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -30640,32 +30660,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="133" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1547</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="149" t="s">
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="148" t="s">
         <v>1540</v>
       </c>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
-      <c r="V1" s="151"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
+      <c r="R1" s="149"/>
+      <c r="S1" s="149"/>
+      <c r="T1" s="149"/>
+      <c r="U1" s="149"/>
+      <c r="V1" s="150"/>
     </row>
     <row r="2" spans="1:22" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
@@ -31182,45 +31202,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="145" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1408</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="146" t="s">
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="133"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="145" t="s">
         <v>1319</v>
       </c>
-      <c r="Q1" s="147"/>
-      <c r="R1" s="147"/>
-      <c r="S1" s="147"/>
-      <c r="T1" s="147"/>
-      <c r="U1" s="147"/>
-      <c r="V1" s="147"/>
-      <c r="W1" s="147"/>
-      <c r="X1" s="147"/>
-      <c r="Y1" s="147"/>
-      <c r="Z1" s="147"/>
-      <c r="AA1" s="147"/>
-      <c r="AB1" s="147"/>
-      <c r="AC1" s="147"/>
-      <c r="AD1" s="147"/>
-      <c r="AE1" s="147"/>
-      <c r="AF1" s="147"/>
-      <c r="AG1" s="147"/>
-      <c r="AH1" s="147"/>
-      <c r="AI1" s="147"/>
+      <c r="Q1" s="146"/>
+      <c r="R1" s="146"/>
+      <c r="S1" s="146"/>
+      <c r="T1" s="146"/>
+      <c r="U1" s="146"/>
+      <c r="V1" s="146"/>
+      <c r="W1" s="146"/>
+      <c r="X1" s="146"/>
+      <c r="Y1" s="146"/>
+      <c r="Z1" s="146"/>
+      <c r="AA1" s="146"/>
+      <c r="AB1" s="146"/>
+      <c r="AC1" s="146"/>
+      <c r="AD1" s="146"/>
+      <c r="AE1" s="146"/>
+      <c r="AF1" s="146"/>
+      <c r="AG1" s="146"/>
+      <c r="AH1" s="146"/>
+      <c r="AI1" s="146"/>
     </row>
     <row r="2" spans="1:35" s="1" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
@@ -31372,90 +31392,90 @@
       <c r="A4" s="53" t="s">
         <v>314</v>
       </c>
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="95" t="s">
         <v>424</v>
       </c>
-      <c r="C4" s="96" t="s">
+      <c r="C4" s="95" t="s">
         <v>945</v>
       </c>
-      <c r="D4" s="96" t="s">
+      <c r="D4" s="95" t="s">
         <v>1410</v>
       </c>
-      <c r="E4" s="96" t="s">
+      <c r="E4" s="95" t="s">
         <v>1412</v>
       </c>
-      <c r="F4" s="96" t="s">
+      <c r="F4" s="95" t="s">
         <v>944</v>
       </c>
-      <c r="G4" s="96" t="b">
+      <c r="G4" s="95" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="96" t="s">
+      <c r="H4" s="95" t="s">
         <v>969</v>
       </c>
-      <c r="I4" s="96" t="s">
+      <c r="I4" s="95" t="s">
         <v>969</v>
       </c>
       <c r="J4" s="53" t="b">
         <v>0</v>
       </c>
-      <c r="K4" s="96" t="s">
+      <c r="K4" s="95" t="s">
         <v>943</v>
       </c>
-      <c r="L4" s="96" t="s">
+      <c r="L4" s="95" t="s">
         <v>942</v>
       </c>
-      <c r="M4" s="96" t="s">
+      <c r="M4" s="95" t="s">
         <v>855</v>
       </c>
-      <c r="N4" s="96" t="s">
+      <c r="N4" s="95" t="s">
         <v>1414</v>
       </c>
-      <c r="O4" s="96" t="s">
+      <c r="O4" s="95" t="s">
         <v>1412</v>
       </c>
-      <c r="P4" s="96">
+      <c r="P4" s="95">
         <v>1</v>
       </c>
-      <c r="Q4" s="96" t="s">
+      <c r="Q4" s="95" t="s">
         <v>934</v>
       </c>
-      <c r="R4" s="96">
+      <c r="R4" s="95">
         <v>32</v>
       </c>
-      <c r="S4" s="96" t="s">
+      <c r="S4" s="95" t="s">
         <v>972</v>
       </c>
-      <c r="T4" s="96">
+      <c r="T4" s="95">
         <v>32</v>
       </c>
-      <c r="U4" s="96" t="s">
+      <c r="U4" s="95" t="s">
         <v>854</v>
       </c>
-      <c r="V4" s="96" t="s">
+      <c r="V4" s="95" t="s">
         <v>970</v>
       </c>
-      <c r="W4" s="96" t="s">
+      <c r="W4" s="95" t="s">
         <v>96</v>
       </c>
-      <c r="X4" s="96" t="s">
+      <c r="X4" s="95" t="s">
         <v>1418</v>
       </c>
-      <c r="Y4" s="96"/>
-      <c r="Z4" s="96"/>
-      <c r="AA4" s="96"/>
-      <c r="AB4" s="97" t="s">
+      <c r="Y4" s="95"/>
+      <c r="Z4" s="95"/>
+      <c r="AA4" s="95"/>
+      <c r="AB4" s="96" t="s">
         <v>941</v>
       </c>
-      <c r="AC4" s="96" t="s">
+      <c r="AC4" s="95" t="s">
         <v>99</v>
       </c>
-      <c r="AD4" s="96"/>
-      <c r="AE4" s="97"/>
-      <c r="AF4" s="97"/>
-      <c r="AG4" s="97"/>
-      <c r="AH4" s="97"/>
-      <c r="AI4" s="97"/>
+      <c r="AD4" s="95"/>
+      <c r="AE4" s="96"/>
+      <c r="AF4" s="96"/>
+      <c r="AG4" s="96"/>
+      <c r="AH4" s="96"/>
+      <c r="AI4" s="96"/>
     </row>
     <row r="5" spans="1:35" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="53" t="s">
@@ -31463,7 +31483,7 @@
       </c>
       <c r="B5" s="53"/>
       <c r="C5" s="53"/>
-      <c r="D5" s="96"/>
+      <c r="D5" s="95"/>
       <c r="E5" s="52"/>
       <c r="F5" s="53"/>
       <c r="G5" s="53"/>
@@ -31476,7 +31496,7 @@
       <c r="N5" s="53" t="s">
         <v>1415</v>
       </c>
-      <c r="O5" s="96" t="s">
+      <c r="O5" s="95" t="s">
         <v>1412</v>
       </c>
       <c r="P5" s="53">
@@ -31495,13 +31515,13 @@
         <v>32</v>
       </c>
       <c r="U5" s="53"/>
-      <c r="V5" s="96" t="s">
+      <c r="V5" s="95" t="s">
         <v>970</v>
       </c>
       <c r="W5" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="X5" s="96" t="s">
+      <c r="X5" s="95" t="s">
         <v>1419</v>
       </c>
       <c r="Y5" s="53"/>
@@ -31524,7 +31544,7 @@
       <c r="A6" s="53" t="s">
         <v>314</v>
       </c>
-      <c r="B6" s="96" t="s">
+      <c r="B6" s="95" t="s">
         <v>424</v>
       </c>
       <c r="C6" s="53" t="s">
@@ -31542,7 +31562,7 @@
       <c r="G6" s="53" t="b">
         <v>0</v>
       </c>
-      <c r="H6" s="96" t="s">
+      <c r="H6" s="95" t="s">
         <v>969</v>
       </c>
       <c r="I6" s="53" t="s">
@@ -31557,7 +31577,7 @@
       <c r="N6" s="53" t="s">
         <v>1416</v>
       </c>
-      <c r="O6" s="96" t="s">
+      <c r="O6" s="95" t="s">
         <v>1412</v>
       </c>
       <c r="P6" s="53">
@@ -31575,26 +31595,26 @@
       <c r="T6" s="53">
         <v>32</v>
       </c>
-      <c r="U6" s="96" t="s">
+      <c r="U6" s="95" t="s">
         <v>854</v>
       </c>
-      <c r="V6" s="96" t="s">
+      <c r="V6" s="95" t="s">
         <v>970</v>
       </c>
       <c r="W6" s="53" t="s">
         <v>96</v>
       </c>
-      <c r="X6" s="96" t="s">
+      <c r="X6" s="95" t="s">
         <v>1419</v>
       </c>
       <c r="Y6" s="53">
         <v>2</v>
       </c>
       <c r="Z6" s="53"/>
-      <c r="AA6" s="96" t="s">
+      <c r="AA6" s="95" t="s">
         <v>970</v>
       </c>
-      <c r="AB6" s="98"/>
+      <c r="AB6" s="97"/>
       <c r="AC6" s="53" t="s">
         <v>99</v>
       </c>
@@ -31693,27 +31713,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="122.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>1320</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
-      <c r="P1" s="132"/>
-      <c r="Q1" s="132"/>
-      <c r="R1" s="132"/>
-      <c r="S1" s="132"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="131"/>
+      <c r="S1" s="131"/>
     </row>
     <row r="2" spans="1:19" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -31989,30 +32009,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="118" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>636</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="134"/>
-      <c r="T1" s="134"/>
-      <c r="U1" s="134"/>
-      <c r="V1" s="137"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="133"/>
+      <c r="O1" s="133"/>
+      <c r="P1" s="133"/>
+      <c r="Q1" s="133"/>
+      <c r="R1" s="133"/>
+      <c r="S1" s="133"/>
+      <c r="T1" s="133"/>
+      <c r="U1" s="133"/>
+      <c r="V1" s="136"/>
     </row>
     <row r="2" spans="1:22" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="37" t="s">
@@ -32338,25 +32358,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>637</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
-      <c r="P1" s="132"/>
-      <c r="Q1" s="132"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
     </row>
     <row r="2" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
@@ -32600,30 +32620,30 @@
     <col min="18" max="18" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="115.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+    <row r="1" spans="1:19" ht="159" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="132" t="s">
         <v>408</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="138" t="s">
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="137" t="s">
         <v>416</v>
       </c>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="153"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="152"/>
     </row>
     <row r="2" spans="1:19" ht="58.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
@@ -33317,13 +33337,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="43" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>1546</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -33551,6 +33571,18 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{47B1B38E-AFF8-7049-B4BD-5E408E8FEEB7}">
+          <x14:formula1>
+            <xm:f>drop_down_rule_set!$L$2:$L$44</xm:f>
+          </x14:formula1>
+          <xm:sqref>A3:A1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -33569,14 +33601,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="43" customFormat="1" ht="44.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="153" t="s">
         <v>409</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="156"/>
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="155"/>
     </row>
     <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -33730,22 +33762,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>661</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="137"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="136"/>
     </row>
     <row r="2" spans="1:14" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
@@ -34285,20 +34317,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>661</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
     </row>
     <row r="2" spans="1:12" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
@@ -34504,24 +34536,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="160" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1321</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="133"/>
+      <c r="O1" s="133"/>
+      <c r="P1" s="133"/>
     </row>
     <row r="2" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -34725,35 +34757,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="1" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1322</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="134"/>
-      <c r="T1" s="134"/>
-      <c r="U1" s="134"/>
-      <c r="V1" s="134"/>
-      <c r="W1" s="134"/>
-      <c r="X1" s="134"/>
-      <c r="Y1" s="134"/>
-      <c r="Z1" s="134"/>
-      <c r="AA1" s="137"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="133"/>
+      <c r="O1" s="133"/>
+      <c r="P1" s="133"/>
+      <c r="Q1" s="133"/>
+      <c r="R1" s="133"/>
+      <c r="S1" s="133"/>
+      <c r="T1" s="133"/>
+      <c r="U1" s="133"/>
+      <c r="V1" s="133"/>
+      <c r="W1" s="133"/>
+      <c r="X1" s="133"/>
+      <c r="Y1" s="133"/>
+      <c r="Z1" s="133"/>
+      <c r="AA1" s="136"/>
     </row>
     <row r="2" spans="1:27" s="48" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="49" t="s">
@@ -34945,7 +34977,7 @@
       <c r="AA4" s="52"/>
     </row>
     <row r="5" spans="1:27" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="52" t="s">
         <v>314</v>
       </c>
       <c r="B5" s="85" t="s">
@@ -38119,16 +38151,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="119.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1323</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
     </row>
     <row r="2" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="65" t="s">
@@ -41033,29 +41065,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="1" customFormat="1" ht="195" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="145" t="s">
         <v>1324</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
-      <c r="R1" s="147"/>
-      <c r="S1" s="147"/>
-      <c r="T1" s="147"/>
-      <c r="U1" s="147"/>
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
+      <c r="J1" s="146"/>
+      <c r="K1" s="146"/>
+      <c r="L1" s="146"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="146"/>
+      <c r="O1" s="146"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="146"/>
+      <c r="R1" s="146"/>
+      <c r="S1" s="146"/>
+      <c r="T1" s="146"/>
+      <c r="U1" s="146"/>
       <c r="V1" s="69"/>
       <c r="W1" s="69"/>
       <c r="X1" s="69"/>
@@ -45495,26 +45527,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="150" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="156" t="s">
         <v>1440</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
-      <c r="R1" s="159"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
+      <c r="K1" s="157"/>
+      <c r="L1" s="157"/>
+      <c r="M1" s="157"/>
+      <c r="N1" s="157"/>
+      <c r="O1" s="157"/>
+      <c r="P1" s="157"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="158"/>
       <c r="S1" s="16"/>
     </row>
     <row r="2" spans="1:19" s="48" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -45530,16 +45562,16 @@
       <c r="D2" s="37" t="s">
         <v>1427</v>
       </c>
-      <c r="E2" s="112" t="s">
+      <c r="E2" s="111" t="s">
         <v>1212</v>
       </c>
-      <c r="F2" s="112" t="s">
+      <c r="F2" s="111" t="s">
         <v>1213</v>
       </c>
       <c r="G2" s="37" t="s">
         <v>1214</v>
       </c>
-      <c r="H2" s="112" t="s">
+      <c r="H2" s="111" t="s">
         <v>1215</v>
       </c>
       <c r="I2" s="37" t="s">
@@ -45551,10 +45583,10 @@
       <c r="K2" s="37" t="s">
         <v>1217</v>
       </c>
-      <c r="L2" s="113" t="s">
+      <c r="L2" s="112" t="s">
         <v>1345</v>
       </c>
-      <c r="M2" s="114" t="s">
+      <c r="M2" s="113" t="s">
         <v>1346</v>
       </c>
       <c r="N2" s="37" t="s">
@@ -45672,7 +45704,7 @@
       <c r="R4" s="32"/>
     </row>
     <row r="5" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="99" t="s">
+      <c r="A5" s="162" t="s">
         <v>4</v>
       </c>
     </row>
@@ -45716,6 +45748,24 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" prompt="Select an OCI Region." xr:uid="{357730DE-E609-484D-9CA9-DE05C5244025}">
+          <x14:formula1>
+            <xm:f>drop_down_rule_set!$L$2:$L$44</xm:f>
+          </x14:formula1>
+          <xm:sqref>A3:A1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{47F4B22B-03E7-EA41-B3D7-A07B2AD5AABB}">
+          <x14:formula1>
+            <xm:f>INDIRECT("drop_down_rule_comp!$D$2:$D$"&amp;drop_down_rule_comp!$C$3+1)</xm:f>
+          </x14:formula1>
+          <xm:sqref>B3:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -45744,23 +45794,23 @@
     <col min="15" max="15" width="46.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="146" t="s">
+    <row r="1" spans="1:15" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="145" t="s">
         <v>1504</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
+      <c r="K1" s="157"/>
+      <c r="L1" s="157"/>
+      <c r="M1" s="157"/>
+      <c r="N1" s="157"/>
     </row>
     <row r="2" spans="1:15" s="43" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="38" t="s">
@@ -45769,7 +45819,7 @@
       <c r="B2" s="38" t="s">
         <v>1211</v>
       </c>
-      <c r="C2" s="112" t="s">
+      <c r="C2" s="111" t="s">
         <v>1221</v>
       </c>
       <c r="D2" s="37" t="s">
@@ -45808,7 +45858,7 @@
       <c r="O2" s="48"/>
     </row>
     <row r="3" spans="1:15" s="34" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="54" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="35" t="s">
@@ -45850,13 +45900,13 @@
       <c r="N3" s="35" t="s">
         <v>1441</v>
       </c>
-      <c r="O3" s="115"/>
+      <c r="O3" s="114"/>
     </row>
     <row r="4" spans="1:15" s="34" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="76" t="s">
         <v>1437</v>
       </c>
       <c r="C4" s="35" t="s">
@@ -45893,13 +45943,13 @@
       <c r="N4" s="35" t="s">
         <v>1442</v>
       </c>
-      <c r="O4" s="115"/>
+      <c r="O4" s="114"/>
     </row>
     <row r="5" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="99" t="s">
+      <c r="A5" s="162" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="116"/>
+      <c r="B5" s="115"/>
       <c r="C5"/>
       <c r="O5"/>
     </row>
@@ -45939,6 +45989,18 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" prompt="Select an OCI Region." xr:uid="{7BB79F72-2125-C54B-A1F2-16A034FAB05E}">
+          <x14:formula1>
+            <xm:f>drop_down_rule_set!$L$2:$L$44</xm:f>
+          </x14:formula1>
+          <xm:sqref>A3:A1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -45971,26 +46033,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="287" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="159" t="s">
         <v>1327</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="161"/>
-      <c r="G1" s="161"/>
-      <c r="H1" s="161"/>
-      <c r="I1" s="161"/>
-      <c r="J1" s="161"/>
-      <c r="K1" s="161"/>
-      <c r="L1" s="161"/>
-      <c r="M1" s="161"/>
-      <c r="N1" s="161"/>
-      <c r="O1" s="161"/>
-      <c r="P1" s="161"/>
-      <c r="Q1" s="161"/>
-      <c r="R1" s="162"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
+      <c r="J1" s="160"/>
+      <c r="K1" s="160"/>
+      <c r="L1" s="160"/>
+      <c r="M1" s="160"/>
+      <c r="N1" s="160"/>
+      <c r="O1" s="160"/>
+      <c r="P1" s="160"/>
+      <c r="Q1" s="160"/>
+      <c r="R1" s="161"/>
     </row>
     <row r="2" spans="1:18" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -46333,15 +46395,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="43" customFormat="1" ht="156.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>1541</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
     </row>
     <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -47270,6 +47332,18 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{815A3179-AB51-F848-9924-ADDDAEA75ADA}">
+          <x14:formula1>
+            <xm:f>drop_down_rule_set!$L$2:$L$44</xm:f>
+          </x14:formula1>
+          <xm:sqref>A3:A1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -47298,25 +47372,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="234" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>1534</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="142" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="141" t="s">
         <v>1536</v>
       </c>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
     </row>
     <row r="2" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -47325,7 +47399,7 @@
       <c r="B2" s="19" t="s">
         <v>1506</v>
       </c>
-      <c r="C2" s="128" t="s">
+      <c r="C2" s="127" t="s">
         <v>1507</v>
       </c>
       <c r="D2" s="19" t="s">
@@ -47346,7 +47420,7 @@
       <c r="I2" s="19" t="s">
         <v>1514</v>
       </c>
-      <c r="J2" s="129" t="s">
+      <c r="J2" s="128" t="s">
         <v>1515</v>
       </c>
       <c r="K2" s="19" t="s">
@@ -47355,7 +47429,7 @@
       <c r="L2" s="19" t="s">
         <v>1517</v>
       </c>
-      <c r="M2" s="131" t="s">
+      <c r="M2" s="130" t="s">
         <v>1518</v>
       </c>
       <c r="N2" s="19" t="s">
@@ -47377,10 +47451,10 @@
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
       <c r="I3" s="35"/>
-      <c r="J3" s="130"/>
+      <c r="J3" s="129"/>
       <c r="K3" s="35"/>
       <c r="L3" s="35"/>
-      <c r="M3" s="130"/>
+      <c r="M3" s="129"/>
       <c r="N3" s="35"/>
       <c r="O3" s="35"/>
     </row>
@@ -47410,12 +47484,12 @@
       <c r="I4" s="35" t="s">
         <v>1521</v>
       </c>
-      <c r="J4" s="130">
+      <c r="J4" s="129">
         <v>256</v>
       </c>
       <c r="K4" s="35"/>
       <c r="L4" s="35"/>
-      <c r="M4" s="130"/>
+      <c r="M4" s="129"/>
       <c r="N4" s="35"/>
       <c r="O4" s="35"/>
     </row>
@@ -47437,14 +47511,14 @@
       <c r="I5" s="35" t="s">
         <v>1522</v>
       </c>
-      <c r="J5" s="130">
+      <c r="J5" s="129">
         <v>384</v>
       </c>
       <c r="K5" s="35" t="s">
         <v>1528</v>
       </c>
       <c r="L5" s="35"/>
-      <c r="M5" s="130"/>
+      <c r="M5" s="129"/>
       <c r="N5" s="35"/>
       <c r="O5" s="35"/>
     </row>
@@ -47476,14 +47550,14 @@
       <c r="I6" s="35" t="s">
         <v>1521</v>
       </c>
-      <c r="J6" s="130">
+      <c r="J6" s="129">
         <v>128</v>
       </c>
       <c r="K6" s="35"/>
       <c r="L6" s="35" t="b">
         <v>1</v>
       </c>
-      <c r="M6" s="130">
+      <c r="M6" s="129">
         <v>100</v>
       </c>
       <c r="N6" s="35"/>
@@ -47507,12 +47581,12 @@
       <c r="I7" s="35" t="s">
         <v>1532</v>
       </c>
-      <c r="J7" s="130">
+      <c r="J7" s="129">
         <v>3072</v>
       </c>
       <c r="K7" s="35"/>
       <c r="L7" s="35"/>
-      <c r="M7" s="130"/>
+      <c r="M7" s="129"/>
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
     </row>
@@ -47534,7 +47608,7 @@
       <c r="I8" s="35" t="s">
         <v>1522</v>
       </c>
-      <c r="J8" s="130">
+      <c r="J8" s="129">
         <v>521</v>
       </c>
       <c r="K8" s="35" t="s">
@@ -47543,7 +47617,7 @@
       <c r="L8" s="35" t="b">
         <v>1</v>
       </c>
-      <c r="M8" s="130">
+      <c r="M8" s="129">
         <v>365</v>
       </c>
       <c r="N8" s="35"/>
@@ -47559,10 +47633,10 @@
       <c r="G9" s="35"/>
       <c r="H9" s="35"/>
       <c r="I9" s="35"/>
-      <c r="J9" s="130"/>
+      <c r="J9" s="129"/>
       <c r="K9" s="35"/>
       <c r="L9" s="35"/>
-      <c r="M9" s="130"/>
+      <c r="M9" s="129"/>
       <c r="N9" s="35"/>
       <c r="O9" s="35"/>
     </row>
@@ -47576,10 +47650,10 @@
       <c r="G10" s="35"/>
       <c r="H10" s="35"/>
       <c r="I10" s="35"/>
-      <c r="J10" s="130"/>
+      <c r="J10" s="129"/>
       <c r="K10" s="35"/>
       <c r="L10" s="35"/>
-      <c r="M10" s="130"/>
+      <c r="M10" s="129"/>
       <c r="N10" s="35"/>
       <c r="O10" s="35"/>
     </row>
@@ -47593,10 +47667,10 @@
       <c r="G11" s="35"/>
       <c r="H11" s="35"/>
       <c r="I11" s="35"/>
-      <c r="J11" s="130"/>
+      <c r="J11" s="129"/>
       <c r="K11" s="35"/>
       <c r="L11" s="35"/>
-      <c r="M11" s="130"/>
+      <c r="M11" s="129"/>
       <c r="N11" s="35"/>
       <c r="O11" s="35"/>
     </row>
@@ -47610,10 +47684,10 @@
       <c r="G12" s="35"/>
       <c r="H12" s="35"/>
       <c r="I12" s="35"/>
-      <c r="J12" s="130"/>
+      <c r="J12" s="129"/>
       <c r="K12" s="35"/>
       <c r="L12" s="35"/>
-      <c r="M12" s="130"/>
+      <c r="M12" s="129"/>
       <c r="N12" s="35"/>
       <c r="O12" s="35"/>
     </row>
@@ -47627,10 +47701,10 @@
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
       <c r="I13" s="35"/>
-      <c r="J13" s="130"/>
+      <c r="J13" s="129"/>
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
-      <c r="M13" s="130"/>
+      <c r="M13" s="129"/>
       <c r="N13" s="35"/>
       <c r="O13" s="35"/>
     </row>
@@ -47644,10 +47718,10 @@
       <c r="G14" s="35"/>
       <c r="H14" s="35"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="130"/>
+      <c r="J14" s="129"/>
       <c r="K14" s="35"/>
       <c r="L14" s="35"/>
-      <c r="M14" s="130"/>
+      <c r="M14" s="129"/>
       <c r="N14" s="35"/>
       <c r="O14" s="35"/>
     </row>
@@ -47661,10 +47735,10 @@
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
       <c r="I15" s="35"/>
-      <c r="J15" s="130"/>
+      <c r="J15" s="129"/>
       <c r="K15" s="35"/>
       <c r="L15" s="35"/>
-      <c r="M15" s="130"/>
+      <c r="M15" s="129"/>
       <c r="N15" s="35"/>
       <c r="O15" s="35"/>
     </row>
@@ -47678,10 +47752,10 @@
       <c r="G16" s="35"/>
       <c r="H16" s="35"/>
       <c r="I16" s="35"/>
-      <c r="J16" s="130"/>
+      <c r="J16" s="129"/>
       <c r="K16" s="35"/>
       <c r="L16" s="35"/>
-      <c r="M16" s="130"/>
+      <c r="M16" s="129"/>
       <c r="N16" s="35"/>
       <c r="O16" s="35"/>
     </row>
@@ -47695,10 +47769,10 @@
       <c r="G17" s="35"/>
       <c r="H17" s="35"/>
       <c r="I17" s="35"/>
-      <c r="J17" s="130"/>
+      <c r="J17" s="129"/>
       <c r="K17" s="35"/>
       <c r="L17" s="35"/>
-      <c r="M17" s="130"/>
+      <c r="M17" s="129"/>
       <c r="N17" s="35"/>
       <c r="O17" s="35"/>
     </row>
@@ -47712,10 +47786,10 @@
       <c r="G18" s="35"/>
       <c r="H18" s="35"/>
       <c r="I18" s="35"/>
-      <c r="J18" s="130"/>
+      <c r="J18" s="129"/>
       <c r="K18" s="35"/>
       <c r="L18" s="35"/>
-      <c r="M18" s="130"/>
+      <c r="M18" s="129"/>
       <c r="N18" s="35"/>
       <c r="O18" s="35"/>
     </row>
@@ -47729,10 +47803,10 @@
       <c r="G19" s="35"/>
       <c r="H19" s="35"/>
       <c r="I19" s="35"/>
-      <c r="J19" s="130"/>
+      <c r="J19" s="129"/>
       <c r="K19" s="35"/>
       <c r="L19" s="35"/>
-      <c r="M19" s="130"/>
+      <c r="M19" s="129"/>
       <c r="N19" s="35"/>
       <c r="O19" s="35"/>
     </row>
@@ -47746,10 +47820,10 @@
       <c r="G20" s="35"/>
       <c r="H20" s="35"/>
       <c r="I20" s="35"/>
-      <c r="J20" s="130"/>
+      <c r="J20" s="129"/>
       <c r="K20" s="35"/>
       <c r="L20" s="35"/>
-      <c r="M20" s="130"/>
+      <c r="M20" s="129"/>
       <c r="N20" s="35"/>
       <c r="O20" s="35"/>
     </row>
@@ -47763,10 +47837,10 @@
       <c r="G21" s="35"/>
       <c r="H21" s="35"/>
       <c r="I21" s="35"/>
-      <c r="J21" s="130"/>
+      <c r="J21" s="129"/>
       <c r="K21" s="35"/>
       <c r="L21" s="35"/>
-      <c r="M21" s="130"/>
+      <c r="M21" s="129"/>
       <c r="N21" s="35"/>
       <c r="O21" s="35"/>
     </row>
@@ -47780,10 +47854,10 @@
       <c r="G22" s="35"/>
       <c r="H22" s="35"/>
       <c r="I22" s="35"/>
-      <c r="J22" s="130"/>
+      <c r="J22" s="129"/>
       <c r="K22" s="35"/>
       <c r="L22" s="35"/>
-      <c r="M22" s="130"/>
+      <c r="M22" s="129"/>
       <c r="N22" s="35"/>
       <c r="O22" s="35"/>
     </row>
@@ -47797,10 +47871,10 @@
       <c r="G23" s="35"/>
       <c r="H23" s="35"/>
       <c r="I23" s="35"/>
-      <c r="J23" s="130"/>
+      <c r="J23" s="129"/>
       <c r="K23" s="35"/>
       <c r="L23" s="35"/>
-      <c r="M23" s="130"/>
+      <c r="M23" s="129"/>
       <c r="N23" s="35"/>
       <c r="O23" s="35"/>
     </row>
@@ -47814,10 +47888,10 @@
       <c r="G24" s="35"/>
       <c r="H24" s="35"/>
       <c r="I24" s="35"/>
-      <c r="J24" s="130"/>
+      <c r="J24" s="129"/>
       <c r="K24" s="35"/>
       <c r="L24" s="35"/>
-      <c r="M24" s="130"/>
+      <c r="M24" s="129"/>
       <c r="N24" s="35"/>
       <c r="O24" s="35"/>
     </row>
@@ -47831,10 +47905,10 @@
       <c r="G25" s="35"/>
       <c r="H25" s="35"/>
       <c r="I25" s="35"/>
-      <c r="J25" s="130"/>
+      <c r="J25" s="129"/>
       <c r="K25" s="35"/>
       <c r="L25" s="35"/>
-      <c r="M25" s="130"/>
+      <c r="M25" s="129"/>
       <c r="N25" s="35"/>
       <c r="O25" s="35"/>
     </row>
@@ -47848,10 +47922,10 @@
       <c r="G26" s="35"/>
       <c r="H26" s="35"/>
       <c r="I26" s="35"/>
-      <c r="J26" s="130"/>
+      <c r="J26" s="129"/>
       <c r="K26" s="35"/>
       <c r="L26" s="35"/>
-      <c r="M26" s="130"/>
+      <c r="M26" s="129"/>
       <c r="N26" s="35"/>
       <c r="O26" s="35"/>
     </row>
@@ -47865,10 +47939,10 @@
       <c r="G27" s="35"/>
       <c r="H27" s="35"/>
       <c r="I27" s="35"/>
-      <c r="J27" s="130"/>
+      <c r="J27" s="129"/>
       <c r="K27" s="35"/>
       <c r="L27" s="35"/>
-      <c r="M27" s="130"/>
+      <c r="M27" s="129"/>
       <c r="N27" s="35"/>
       <c r="O27" s="35"/>
     </row>
@@ -47882,10 +47956,10 @@
       <c r="G28" s="35"/>
       <c r="H28" s="35"/>
       <c r="I28" s="35"/>
-      <c r="J28" s="130"/>
+      <c r="J28" s="129"/>
       <c r="K28" s="35"/>
       <c r="L28" s="35"/>
-      <c r="M28" s="130"/>
+      <c r="M28" s="129"/>
       <c r="N28" s="35"/>
       <c r="O28" s="35"/>
     </row>
@@ -47899,10 +47973,10 @@
       <c r="G29" s="35"/>
       <c r="H29" s="35"/>
       <c r="I29" s="35"/>
-      <c r="J29" s="130"/>
+      <c r="J29" s="129"/>
       <c r="K29" s="35"/>
       <c r="L29" s="35"/>
-      <c r="M29" s="130"/>
+      <c r="M29" s="129"/>
       <c r="N29" s="35"/>
       <c r="O29" s="35"/>
     </row>
@@ -47916,10 +47990,10 @@
       <c r="G30" s="35"/>
       <c r="H30" s="35"/>
       <c r="I30" s="35"/>
-      <c r="J30" s="130"/>
+      <c r="J30" s="129"/>
       <c r="K30" s="35"/>
       <c r="L30" s="35"/>
-      <c r="M30" s="130"/>
+      <c r="M30" s="129"/>
       <c r="N30" s="35"/>
       <c r="O30" s="35"/>
     </row>
@@ -47933,10 +48007,10 @@
       <c r="G31" s="35"/>
       <c r="H31" s="35"/>
       <c r="I31" s="35"/>
-      <c r="J31" s="130"/>
+      <c r="J31" s="129"/>
       <c r="K31" s="35"/>
       <c r="L31" s="35"/>
-      <c r="M31" s="130"/>
+      <c r="M31" s="129"/>
       <c r="N31" s="35"/>
       <c r="O31" s="35"/>
     </row>
@@ -47950,10 +48024,10 @@
       <c r="G32" s="35"/>
       <c r="H32" s="35"/>
       <c r="I32" s="35"/>
-      <c r="J32" s="130"/>
+      <c r="J32" s="129"/>
       <c r="K32" s="35"/>
       <c r="L32" s="35"/>
-      <c r="M32" s="130"/>
+      <c r="M32" s="129"/>
       <c r="N32" s="35"/>
       <c r="O32" s="35"/>
     </row>
@@ -47967,10 +48041,10 @@
       <c r="G33" s="35"/>
       <c r="H33" s="35"/>
       <c r="I33" s="35"/>
-      <c r="J33" s="130"/>
+      <c r="J33" s="129"/>
       <c r="K33" s="35"/>
       <c r="L33" s="35"/>
-      <c r="M33" s="130"/>
+      <c r="M33" s="129"/>
       <c r="N33" s="35"/>
       <c r="O33" s="35"/>
     </row>
@@ -47984,10 +48058,10 @@
       <c r="G34" s="35"/>
       <c r="H34" s="35"/>
       <c r="I34" s="35"/>
-      <c r="J34" s="130"/>
+      <c r="J34" s="129"/>
       <c r="K34" s="35"/>
       <c r="L34" s="35"/>
-      <c r="M34" s="130"/>
+      <c r="M34" s="129"/>
       <c r="N34" s="35"/>
       <c r="O34" s="35"/>
     </row>
@@ -48001,10 +48075,10 @@
       <c r="G35" s="35"/>
       <c r="H35" s="35"/>
       <c r="I35" s="35"/>
-      <c r="J35" s="130"/>
+      <c r="J35" s="129"/>
       <c r="K35" s="35"/>
       <c r="L35" s="35"/>
-      <c r="M35" s="130"/>
+      <c r="M35" s="129"/>
       <c r="N35" s="35"/>
       <c r="O35" s="35"/>
     </row>
@@ -48018,10 +48092,10 @@
       <c r="G36" s="35"/>
       <c r="H36" s="35"/>
       <c r="I36" s="35"/>
-      <c r="J36" s="130"/>
+      <c r="J36" s="129"/>
       <c r="K36" s="35"/>
       <c r="L36" s="35"/>
-      <c r="M36" s="130"/>
+      <c r="M36" s="129"/>
       <c r="N36" s="35"/>
       <c r="O36" s="35"/>
     </row>
@@ -48035,10 +48109,10 @@
       <c r="G37" s="35"/>
       <c r="H37" s="35"/>
       <c r="I37" s="35"/>
-      <c r="J37" s="130"/>
+      <c r="J37" s="129"/>
       <c r="K37" s="35"/>
       <c r="L37" s="35"/>
-      <c r="M37" s="130"/>
+      <c r="M37" s="129"/>
       <c r="N37" s="35"/>
       <c r="O37" s="35"/>
     </row>
@@ -48052,10 +48126,10 @@
       <c r="G38" s="35"/>
       <c r="H38" s="35"/>
       <c r="I38" s="35"/>
-      <c r="J38" s="130"/>
+      <c r="J38" s="129"/>
       <c r="K38" s="35"/>
       <c r="L38" s="35"/>
-      <c r="M38" s="130"/>
+      <c r="M38" s="129"/>
       <c r="N38" s="35"/>
       <c r="O38" s="35"/>
     </row>
@@ -48069,10 +48143,10 @@
       <c r="G39" s="35"/>
       <c r="H39" s="35"/>
       <c r="I39" s="35"/>
-      <c r="J39" s="130"/>
+      <c r="J39" s="129"/>
       <c r="K39" s="35"/>
       <c r="L39" s="35"/>
-      <c r="M39" s="130"/>
+      <c r="M39" s="129"/>
       <c r="N39" s="35"/>
       <c r="O39" s="35"/>
     </row>
@@ -48086,10 +48160,10 @@
       <c r="G40" s="35"/>
       <c r="H40" s="35"/>
       <c r="I40" s="35"/>
-      <c r="J40" s="130"/>
+      <c r="J40" s="129"/>
       <c r="K40" s="35"/>
       <c r="L40" s="35"/>
-      <c r="M40" s="130"/>
+      <c r="M40" s="129"/>
       <c r="N40" s="35"/>
       <c r="O40" s="35"/>
     </row>
@@ -48103,10 +48177,10 @@
       <c r="G41" s="35"/>
       <c r="H41" s="35"/>
       <c r="I41" s="35"/>
-      <c r="J41" s="130"/>
+      <c r="J41" s="129"/>
       <c r="K41" s="35"/>
       <c r="L41" s="35"/>
-      <c r="M41" s="130"/>
+      <c r="M41" s="129"/>
       <c r="N41" s="35"/>
       <c r="O41" s="35"/>
     </row>
@@ -48120,10 +48194,10 @@
       <c r="G42" s="35"/>
       <c r="H42" s="35"/>
       <c r="I42" s="35"/>
-      <c r="J42" s="130"/>
+      <c r="J42" s="129"/>
       <c r="K42" s="35"/>
       <c r="L42" s="35"/>
-      <c r="M42" s="130"/>
+      <c r="M42" s="129"/>
       <c r="N42" s="35"/>
       <c r="O42" s="35"/>
     </row>
@@ -48137,10 +48211,10 @@
       <c r="G43" s="35"/>
       <c r="H43" s="35"/>
       <c r="I43" s="35"/>
-      <c r="J43" s="130"/>
+      <c r="J43" s="129"/>
       <c r="K43" s="35"/>
       <c r="L43" s="35"/>
-      <c r="M43" s="130"/>
+      <c r="M43" s="129"/>
       <c r="N43" s="35"/>
       <c r="O43" s="35"/>
     </row>
@@ -48154,10 +48228,10 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
       <c r="I44" s="35"/>
-      <c r="J44" s="130"/>
+      <c r="J44" s="129"/>
       <c r="K44" s="35"/>
       <c r="L44" s="35"/>
-      <c r="M44" s="130"/>
+      <c r="M44" s="129"/>
       <c r="N44" s="35"/>
       <c r="O44" s="35"/>
     </row>
@@ -48171,10 +48245,10 @@
       <c r="G45" s="35"/>
       <c r="H45" s="35"/>
       <c r="I45" s="35"/>
-      <c r="J45" s="130"/>
+      <c r="J45" s="129"/>
       <c r="K45" s="35"/>
       <c r="L45" s="35"/>
-      <c r="M45" s="130"/>
+      <c r="M45" s="129"/>
       <c r="N45" s="35"/>
       <c r="O45" s="35"/>
     </row>
@@ -48188,10 +48262,10 @@
       <c r="G46" s="35"/>
       <c r="H46" s="35"/>
       <c r="I46" s="35"/>
-      <c r="J46" s="130"/>
+      <c r="J46" s="129"/>
       <c r="K46" s="35"/>
       <c r="L46" s="35"/>
-      <c r="M46" s="130"/>
+      <c r="M46" s="129"/>
       <c r="N46" s="35"/>
       <c r="O46" s="35"/>
     </row>
@@ -48205,10 +48279,10 @@
       <c r="G47" s="35"/>
       <c r="H47" s="35"/>
       <c r="I47" s="35"/>
-      <c r="J47" s="130"/>
+      <c r="J47" s="129"/>
       <c r="K47" s="35"/>
       <c r="L47" s="35"/>
-      <c r="M47" s="130"/>
+      <c r="M47" s="129"/>
       <c r="N47" s="35"/>
       <c r="O47" s="35"/>
     </row>
@@ -48222,10 +48296,10 @@
       <c r="G48" s="35"/>
       <c r="H48" s="35"/>
       <c r="I48" s="35"/>
-      <c r="J48" s="130"/>
+      <c r="J48" s="129"/>
       <c r="K48" s="35"/>
       <c r="L48" s="35"/>
-      <c r="M48" s="130"/>
+      <c r="M48" s="129"/>
       <c r="N48" s="35"/>
       <c r="O48" s="35"/>
     </row>
@@ -48239,10 +48313,10 @@
       <c r="G49" s="35"/>
       <c r="H49" s="35"/>
       <c r="I49" s="35"/>
-      <c r="J49" s="130"/>
+      <c r="J49" s="129"/>
       <c r="K49" s="35"/>
       <c r="L49" s="35"/>
-      <c r="M49" s="130"/>
+      <c r="M49" s="129"/>
       <c r="N49" s="35"/>
       <c r="O49" s="35"/>
     </row>
@@ -48256,10 +48330,10 @@
       <c r="G50" s="35"/>
       <c r="H50" s="35"/>
       <c r="I50" s="35"/>
-      <c r="J50" s="130"/>
+      <c r="J50" s="129"/>
       <c r="K50" s="35"/>
       <c r="L50" s="35"/>
-      <c r="M50" s="130"/>
+      <c r="M50" s="129"/>
       <c r="N50" s="35"/>
       <c r="O50" s="35"/>
     </row>
@@ -48273,10 +48347,10 @@
       <c r="G51" s="35"/>
       <c r="H51" s="35"/>
       <c r="I51" s="35"/>
-      <c r="J51" s="130"/>
+      <c r="J51" s="129"/>
       <c r="K51" s="35"/>
       <c r="L51" s="35"/>
-      <c r="M51" s="130"/>
+      <c r="M51" s="129"/>
       <c r="N51" s="35"/>
       <c r="O51" s="35"/>
     </row>
@@ -48290,10 +48364,10 @@
       <c r="G52" s="35"/>
       <c r="H52" s="35"/>
       <c r="I52" s="35"/>
-      <c r="J52" s="130"/>
+      <c r="J52" s="129"/>
       <c r="K52" s="35"/>
       <c r="L52" s="35"/>
-      <c r="M52" s="130"/>
+      <c r="M52" s="129"/>
       <c r="N52" s="35"/>
       <c r="O52" s="35"/>
     </row>
@@ -48307,10 +48381,10 @@
       <c r="G53" s="35"/>
       <c r="H53" s="35"/>
       <c r="I53" s="35"/>
-      <c r="J53" s="130"/>
+      <c r="J53" s="129"/>
       <c r="K53" s="35"/>
       <c r="L53" s="35"/>
-      <c r="M53" s="130"/>
+      <c r="M53" s="129"/>
       <c r="N53" s="35"/>
       <c r="O53" s="35"/>
     </row>
@@ -48324,10 +48398,10 @@
       <c r="G54" s="35"/>
       <c r="H54" s="35"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="130"/>
+      <c r="J54" s="129"/>
       <c r="K54" s="35"/>
       <c r="L54" s="35"/>
-      <c r="M54" s="130"/>
+      <c r="M54" s="129"/>
       <c r="N54" s="35"/>
       <c r="O54" s="35"/>
     </row>
@@ -48341,10 +48415,10 @@
       <c r="G55" s="35"/>
       <c r="H55" s="35"/>
       <c r="I55" s="35"/>
-      <c r="J55" s="130"/>
+      <c r="J55" s="129"/>
       <c r="K55" s="35"/>
       <c r="L55" s="35"/>
-      <c r="M55" s="130"/>
+      <c r="M55" s="129"/>
       <c r="N55" s="35"/>
       <c r="O55" s="35"/>
     </row>
@@ -48358,10 +48432,10 @@
       <c r="G56" s="35"/>
       <c r="H56" s="35"/>
       <c r="I56" s="35"/>
-      <c r="J56" s="130"/>
+      <c r="J56" s="129"/>
       <c r="K56" s="35"/>
       <c r="L56" s="35"/>
-      <c r="M56" s="130"/>
+      <c r="M56" s="129"/>
       <c r="N56" s="35"/>
       <c r="O56" s="35"/>
     </row>
@@ -48375,10 +48449,10 @@
       <c r="G57" s="35"/>
       <c r="H57" s="35"/>
       <c r="I57" s="35"/>
-      <c r="J57" s="130"/>
+      <c r="J57" s="129"/>
       <c r="K57" s="35"/>
       <c r="L57" s="35"/>
-      <c r="M57" s="130"/>
+      <c r="M57" s="129"/>
       <c r="N57" s="35"/>
       <c r="O57" s="35"/>
     </row>
@@ -48392,10 +48466,10 @@
       <c r="G58" s="35"/>
       <c r="H58" s="35"/>
       <c r="I58" s="35"/>
-      <c r="J58" s="130"/>
+      <c r="J58" s="129"/>
       <c r="K58" s="35"/>
       <c r="L58" s="35"/>
-      <c r="M58" s="130"/>
+      <c r="M58" s="129"/>
       <c r="N58" s="35"/>
       <c r="O58" s="35"/>
     </row>
@@ -48409,10 +48483,10 @@
       <c r="G59" s="35"/>
       <c r="H59" s="35"/>
       <c r="I59" s="35"/>
-      <c r="J59" s="130"/>
+      <c r="J59" s="129"/>
       <c r="K59" s="35"/>
       <c r="L59" s="35"/>
-      <c r="M59" s="130"/>
+      <c r="M59" s="129"/>
       <c r="N59" s="35"/>
       <c r="O59" s="35"/>
     </row>
@@ -48426,10 +48500,10 @@
       <c r="G60" s="35"/>
       <c r="H60" s="35"/>
       <c r="I60" s="35"/>
-      <c r="J60" s="130"/>
+      <c r="J60" s="129"/>
       <c r="K60" s="35"/>
       <c r="L60" s="35"/>
-      <c r="M60" s="130"/>
+      <c r="M60" s="129"/>
       <c r="N60" s="35"/>
       <c r="O60" s="35"/>
     </row>
@@ -48443,10 +48517,10 @@
       <c r="G61" s="35"/>
       <c r="H61" s="35"/>
       <c r="I61" s="35"/>
-      <c r="J61" s="130"/>
+      <c r="J61" s="129"/>
       <c r="K61" s="35"/>
       <c r="L61" s="35"/>
-      <c r="M61" s="130"/>
+      <c r="M61" s="129"/>
       <c r="N61" s="35"/>
       <c r="O61" s="35"/>
     </row>
@@ -48460,10 +48534,10 @@
       <c r="G62" s="35"/>
       <c r="H62" s="35"/>
       <c r="I62" s="35"/>
-      <c r="J62" s="130"/>
+      <c r="J62" s="129"/>
       <c r="K62" s="35"/>
       <c r="L62" s="35"/>
-      <c r="M62" s="130"/>
+      <c r="M62" s="129"/>
       <c r="N62" s="35"/>
       <c r="O62" s="35"/>
     </row>
@@ -48477,10 +48551,10 @@
       <c r="G63" s="35"/>
       <c r="H63" s="35"/>
       <c r="I63" s="35"/>
-      <c r="J63" s="130"/>
+      <c r="J63" s="129"/>
       <c r="K63" s="35"/>
       <c r="L63" s="35"/>
-      <c r="M63" s="130"/>
+      <c r="M63" s="129"/>
       <c r="N63" s="35"/>
       <c r="O63" s="35"/>
     </row>
@@ -48494,10 +48568,10 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
       <c r="I64" s="35"/>
-      <c r="J64" s="130"/>
+      <c r="J64" s="129"/>
       <c r="K64" s="35"/>
       <c r="L64" s="35"/>
-      <c r="M64" s="130"/>
+      <c r="M64" s="129"/>
       <c r="N64" s="35"/>
       <c r="O64" s="35"/>
     </row>
@@ -48511,10 +48585,10 @@
       <c r="G65" s="35"/>
       <c r="H65" s="35"/>
       <c r="I65" s="35"/>
-      <c r="J65" s="130"/>
+      <c r="J65" s="129"/>
       <c r="K65" s="35"/>
       <c r="L65" s="35"/>
-      <c r="M65" s="130"/>
+      <c r="M65" s="129"/>
       <c r="N65" s="35"/>
       <c r="O65" s="35"/>
     </row>
@@ -48580,46 +48654,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="99" t="s">
         <v>1047</v>
       </c>
-      <c r="B1" s="100" t="s">
+      <c r="B1" s="99" t="s">
         <v>585</v>
       </c>
-      <c r="C1" s="101" t="s">
+      <c r="C1" s="100" t="s">
         <v>1048</v>
       </c>
-      <c r="D1" s="101" t="s">
+      <c r="D1" s="100" t="s">
         <v>1049</v>
       </c>
-      <c r="E1" s="100" t="s">
+      <c r="E1" s="99" t="s">
         <v>1050</v>
       </c>
-      <c r="F1" s="102" t="s">
+      <c r="F1" s="101" t="s">
         <v>589</v>
       </c>
-      <c r="G1" s="102" t="s">
+      <c r="G1" s="101" t="s">
         <v>318</v>
       </c>
-      <c r="H1" s="102" t="s">
+      <c r="H1" s="101" t="s">
         <v>317</v>
       </c>
-      <c r="I1" s="103" t="s">
+      <c r="I1" s="102" t="s">
         <v>587</v>
       </c>
-      <c r="J1" s="103" t="s">
+      <c r="J1" s="102" t="s">
         <v>588</v>
       </c>
-      <c r="K1" s="102" t="s">
+      <c r="K1" s="101" t="s">
         <v>583</v>
       </c>
-      <c r="L1" s="101" t="s">
+      <c r="L1" s="100" t="s">
         <v>1051</v>
       </c>
-      <c r="M1" s="101"/>
+      <c r="M1" s="100"/>
     </row>
     <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="103" t="s">
         <v>1052</v>
       </c>
       <c r="B2" s="45" t="s">
@@ -48637,7 +48711,7 @@
       <c r="F2" s="45" t="s">
         <v>322</v>
       </c>
-      <c r="G2" s="105" t="s">
+      <c r="G2" s="104" t="s">
         <v>328</v>
       </c>
       <c r="H2" s="36" t="s">
@@ -48657,7 +48731,7 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="104" t="s">
+      <c r="A3" s="103" t="s">
         <v>1057</v>
       </c>
       <c r="B3" s="36" t="s">
@@ -48675,7 +48749,7 @@
       <c r="F3" s="36" t="s">
         <v>1061</v>
       </c>
-      <c r="G3" s="105" t="s">
+      <c r="G3" s="104" t="s">
         <v>1062</v>
       </c>
       <c r="H3" s="36" t="s">
@@ -48695,7 +48769,7 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="104" t="s">
+      <c r="A4" s="103" t="s">
         <v>1065</v>
       </c>
       <c r="B4" s="36" t="s">
@@ -48717,7 +48791,7 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="104" t="s">
+      <c r="A5" s="103" t="s">
         <v>331</v>
       </c>
       <c r="B5" s="36" t="s">
@@ -48739,7 +48813,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="103" t="s">
         <v>1075</v>
       </c>
       <c r="B6" s="36"/>
@@ -48756,7 +48830,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="104" t="s">
+      <c r="A7" s="103" t="s">
         <v>1079</v>
       </c>
       <c r="B7" s="36"/>
@@ -48773,7 +48847,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="104" t="s">
+      <c r="A8" s="103" t="s">
         <v>1083</v>
       </c>
       <c r="B8" s="36"/>
@@ -48790,7 +48864,7 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="104" t="s">
+      <c r="A9" s="103" t="s">
         <v>1087</v>
       </c>
       <c r="B9" s="36"/>
@@ -48807,7 +48881,7 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="104" t="s">
+      <c r="A10" s="103" t="s">
         <v>1090</v>
       </c>
       <c r="B10" s="36"/>
@@ -48824,7 +48898,7 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="104" t="s">
+      <c r="A11" s="103" t="s">
         <v>1094</v>
       </c>
       <c r="B11" s="36"/>
@@ -48841,7 +48915,7 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="104" t="s">
+      <c r="A12" s="103" t="s">
         <v>1098</v>
       </c>
       <c r="B12" s="36"/>
@@ -48858,7 +48932,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="104" t="s">
+      <c r="A13" s="103" t="s">
         <v>1102</v>
       </c>
       <c r="B13" s="36"/>
@@ -48875,7 +48949,7 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="104" t="s">
+      <c r="A14" s="103" t="s">
         <v>332</v>
       </c>
       <c r="B14" s="36"/>
@@ -50027,7 +50101,7 @@
         <f t="array" aca="1" ref="AT2:AT6" ca="1">_xlfn.UNIQUE(INDIRECT("B2:B"&amp;$G$5),FALSE,FALSE)</f>
         <v>VCN::fwl-vcn</v>
       </c>
-      <c r="AU2" s="107" t="str">
+      <c r="AU2" s="106" t="str">
         <f ca="1">_xlfn.IFNA(IF($H2+1&gt;$G$2,"",INDEX(INDIRECT("SubnetsVLANs!$D$"&amp;$H2+2&amp;":$D$"&amp;$G$2),MATCH("Subnet*",INDIRECT("SubnetsVLANs!$E$"&amp;$H2+2&amp;":$E$"&amp;$G$2),0))),"")</f>
         <v>fwl-mgmt</v>
       </c>
@@ -50185,7 +50259,7 @@
         <f ca="1"/>
         <v>VCN::prod-vcn</v>
       </c>
-      <c r="AU3" s="107" t="str">
+      <c r="AU3" s="106" t="str">
         <f t="shared" ref="AU3:AU66" ca="1" si="1">_xlfn.IFNA(IF($H3+1&gt;$G$2,"",INDEX(INDIRECT("SubnetsVLANs!$D$"&amp;$H3+2&amp;":$D$"&amp;$G$2),MATCH("Subnet*",INDIRECT("SubnetsVLANs!$E$"&amp;$H3+2&amp;":$E$"&amp;$G$2),0))),"")</f>
         <v>fwl-pub</v>
       </c>
@@ -50313,7 +50387,7 @@
         <f ca="1"/>
         <v>VCN::nonprod-vcn</v>
       </c>
-      <c r="AU4" s="107" t="str">
+      <c r="AU4" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>fwl-priv</v>
       </c>
@@ -50420,7 +50494,7 @@
         <f ca="1"/>
         <v>VCN::exa-vcn</v>
       </c>
-      <c r="AU5" s="107" t="str">
+      <c r="AU5" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>fwl-ha</v>
       </c>
@@ -50519,7 +50593,7 @@
         <f ca="1"/>
         <v/>
       </c>
-      <c r="AU6" s="107" t="str">
+      <c r="AU6" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>prod-web</v>
       </c>
@@ -50605,7 +50679,7 @@
       <c r="AL7" s="58"/>
       <c r="AM7" s="58"/>
       <c r="AN7" s="58"/>
-      <c r="AU7" s="107" t="str">
+      <c r="AU7" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>prod-app</v>
       </c>
@@ -50691,7 +50765,7 @@
       <c r="AL8" s="58"/>
       <c r="AM8" s="58"/>
       <c r="AN8" s="58"/>
-      <c r="AU8" s="107" t="str">
+      <c r="AU8" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>prod-db</v>
       </c>
@@ -50777,7 +50851,7 @@
       <c r="AL9" s="58"/>
       <c r="AM9" s="58"/>
       <c r="AN9" s="58"/>
-      <c r="AU9" s="107" t="str">
+      <c r="AU9" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>nonprod-web</v>
       </c>
@@ -50863,7 +50937,7 @@
       <c r="AL10" s="58"/>
       <c r="AM10" s="58"/>
       <c r="AN10" s="58"/>
-      <c r="AU10" s="107" t="str">
+      <c r="AU10" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>nonprod-app</v>
       </c>
@@ -50949,7 +51023,7 @@
       <c r="AL11" s="58"/>
       <c r="AM11" s="58"/>
       <c r="AN11" s="58"/>
-      <c r="AU11" s="107" t="str">
+      <c r="AU11" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>nonprod-db</v>
       </c>
@@ -51033,7 +51107,7 @@
       <c r="AL12" s="58"/>
       <c r="AM12" s="58"/>
       <c r="AN12" s="58"/>
-      <c r="AU12" s="107" t="str">
+      <c r="AU12" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>exa-clnt</v>
       </c>
@@ -51117,7 +51191,7 @@
       <c r="AL13" s="58"/>
       <c r="AM13" s="58"/>
       <c r="AN13" s="58"/>
-      <c r="AU13" s="107" t="str">
+      <c r="AU13" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>exa-bkup</v>
       </c>
@@ -51198,7 +51272,7 @@
       <c r="AL14" s="58"/>
       <c r="AM14" s="58"/>
       <c r="AN14" s="58"/>
-      <c r="AU14" s="107" t="str">
+      <c r="AU14" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>exa-bkup</v>
       </c>
@@ -51275,7 +51349,7 @@
       <c r="AL15" s="58"/>
       <c r="AM15" s="58"/>
       <c r="AN15" s="58"/>
-      <c r="AU15" s="107" t="str">
+      <c r="AU15" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -51352,7 +51426,7 @@
       <c r="AL16" s="58"/>
       <c r="AM16" s="58"/>
       <c r="AN16" s="58"/>
-      <c r="AU16" s="107" t="str">
+      <c r="AU16" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -51429,7 +51503,7 @@
       <c r="AL17" s="58"/>
       <c r="AM17" s="58"/>
       <c r="AN17" s="58"/>
-      <c r="AU17" s="107" t="str">
+      <c r="AU17" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -51506,7 +51580,7 @@
       <c r="AL18" s="58"/>
       <c r="AM18" s="58"/>
       <c r="AN18" s="58"/>
-      <c r="AU18" s="107" t="str">
+      <c r="AU18" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -51583,7 +51657,7 @@
       <c r="AL19" s="58"/>
       <c r="AM19" s="58"/>
       <c r="AN19" s="58"/>
-      <c r="AU19" s="107" t="str">
+      <c r="AU19" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -51660,7 +51734,7 @@
       <c r="AL20" s="58"/>
       <c r="AM20" s="58"/>
       <c r="AN20" s="58"/>
-      <c r="AU20" s="107" t="str">
+      <c r="AU20" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -51737,7 +51811,7 @@
       <c r="AL21" s="58"/>
       <c r="AM21" s="58"/>
       <c r="AN21" s="58"/>
-      <c r="AU21" s="107" t="str">
+      <c r="AU21" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -51814,7 +51888,7 @@
       <c r="AL22" s="58"/>
       <c r="AM22" s="58"/>
       <c r="AN22" s="58"/>
-      <c r="AU22" s="107" t="str">
+      <c r="AU22" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -51891,7 +51965,7 @@
       <c r="AL23" s="58"/>
       <c r="AM23" s="58"/>
       <c r="AN23" s="58"/>
-      <c r="AU23" s="107" t="str">
+      <c r="AU23" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -51968,7 +52042,7 @@
       <c r="AL24" s="58"/>
       <c r="AM24" s="58"/>
       <c r="AN24" s="58"/>
-      <c r="AU24" s="107" t="str">
+      <c r="AU24" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52045,7 +52119,7 @@
       <c r="AL25" s="58"/>
       <c r="AM25" s="58"/>
       <c r="AN25" s="58"/>
-      <c r="AU25" s="107" t="str">
+      <c r="AU25" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52122,7 +52196,7 @@
       <c r="AL26" s="58"/>
       <c r="AM26" s="58"/>
       <c r="AN26" s="58"/>
-      <c r="AU26" s="107" t="str">
+      <c r="AU26" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52199,7 +52273,7 @@
       <c r="AL27" s="58"/>
       <c r="AM27" s="58"/>
       <c r="AN27" s="58"/>
-      <c r="AU27" s="107" t="str">
+      <c r="AU27" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52276,7 +52350,7 @@
       <c r="AL28" s="58"/>
       <c r="AM28" s="58"/>
       <c r="AN28" s="58"/>
-      <c r="AU28" s="107" t="str">
+      <c r="AU28" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52353,7 +52427,7 @@
       <c r="AL29" s="58"/>
       <c r="AM29" s="58"/>
       <c r="AN29" s="58"/>
-      <c r="AU29" s="107" t="str">
+      <c r="AU29" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52430,7 +52504,7 @@
       <c r="AL30" s="58"/>
       <c r="AM30" s="58"/>
       <c r="AN30" s="58"/>
-      <c r="AU30" s="107" t="str">
+      <c r="AU30" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52507,7 +52581,7 @@
       <c r="AL31" s="58"/>
       <c r="AM31" s="58"/>
       <c r="AN31" s="58"/>
-      <c r="AU31" s="107" t="str">
+      <c r="AU31" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52584,7 +52658,7 @@
       <c r="AL32" s="58"/>
       <c r="AM32" s="58"/>
       <c r="AN32" s="58"/>
-      <c r="AU32" s="107" t="str">
+      <c r="AU32" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52661,7 +52735,7 @@
       <c r="AL33" s="58"/>
       <c r="AM33" s="58"/>
       <c r="AN33" s="58"/>
-      <c r="AU33" s="107" t="str">
+      <c r="AU33" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52738,7 +52812,7 @@
       <c r="AL34" s="58"/>
       <c r="AM34" s="58"/>
       <c r="AN34" s="58"/>
-      <c r="AU34" s="107" t="str">
+      <c r="AU34" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52815,7 +52889,7 @@
       <c r="AL35" s="58"/>
       <c r="AM35" s="58"/>
       <c r="AN35" s="58"/>
-      <c r="AU35" s="107" t="str">
+      <c r="AU35" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52892,7 +52966,7 @@
       <c r="AL36" s="58"/>
       <c r="AM36" s="58"/>
       <c r="AN36" s="58"/>
-      <c r="AU36" s="107" t="str">
+      <c r="AU36" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52969,7 +53043,7 @@
       <c r="AL37" s="58"/>
       <c r="AM37" s="58"/>
       <c r="AN37" s="58"/>
-      <c r="AU37" s="107" t="str">
+      <c r="AU37" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53046,7 +53120,7 @@
       <c r="AL38" s="58"/>
       <c r="AM38" s="58"/>
       <c r="AN38" s="58"/>
-      <c r="AU38" s="107" t="str">
+      <c r="AU38" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53123,7 +53197,7 @@
       <c r="AL39" s="58"/>
       <c r="AM39" s="58"/>
       <c r="AN39" s="58"/>
-      <c r="AU39" s="107" t="str">
+      <c r="AU39" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53199,7 +53273,7 @@
       <c r="AL40" s="58"/>
       <c r="AM40" s="58"/>
       <c r="AN40" s="58"/>
-      <c r="AU40" s="107" t="str">
+      <c r="AU40" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53250,7 +53324,7 @@
         <v/>
       </c>
       <c r="AK41" s="62"/>
-      <c r="AU41" s="107" t="str">
+      <c r="AU41" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53300,7 +53374,7 @@
         <f t="array" aca="1" ref="Z42" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A42,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A42,4,4,1,"instances")))</f>
         <v/>
       </c>
-      <c r="AU42" s="107" t="str">
+      <c r="AU42" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53350,7 +53424,7 @@
         <f t="array" aca="1" ref="Z43" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A43,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A43,4,4,1,"instances")))</f>
         <v/>
       </c>
-      <c r="AU43" s="107" t="str">
+      <c r="AU43" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53400,7 +53474,7 @@
         <f t="array" aca="1" ref="Z44" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A44,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A44,4,4,1,"instances")))</f>
         <v/>
       </c>
-      <c r="AU44" s="107" t="str">
+      <c r="AU44" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53450,7 +53524,7 @@
         <f t="array" aca="1" ref="Z45" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A45,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A45,4,4,1,"instances")))</f>
         <v/>
       </c>
-      <c r="AU45" s="107" t="str">
+      <c r="AU45" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53497,7 +53571,7 @@
         <f t="array" aca="1" ref="Z46" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A46,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A46,4,4,1,"instances")))</f>
         <v/>
       </c>
-      <c r="AU46" s="107" t="str">
+      <c r="AU46" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53544,7 +53618,7 @@
         <f t="array" aca="1" ref="Z47" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A47,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A47,4,4,1,"instances")))</f>
         <v/>
       </c>
-      <c r="AU47" s="107" t="str">
+      <c r="AU47" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53591,7 +53665,7 @@
         <f t="array" aca="1" ref="Z48" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A48,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A48,4,4,1,"instances")))</f>
         <v/>
       </c>
-      <c r="AU48" s="107" t="str">
+      <c r="AU48" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53638,7 +53712,7 @@
         <f t="array" aca="1" ref="Z49" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A49,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A49,4,4,1,"instances")))</f>
         <v/>
       </c>
-      <c r="AU49" s="107" t="str">
+      <c r="AU49" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53659,7 +53733,7 @@
       <c r="I50" s="36"/>
       <c r="J50" s="36"/>
       <c r="AG50" s="63"/>
-      <c r="AU50" s="107" t="str">
+      <c r="AU50" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53680,7 +53754,7 @@
       <c r="I51" s="36"/>
       <c r="J51" s="36"/>
       <c r="L51" s="57"/>
-      <c r="AU51" s="107" t="str">
+      <c r="AU51" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53702,7 +53776,7 @@
       <c r="I52" s="36"/>
       <c r="J52" s="36"/>
       <c r="L52" s="57"/>
-      <c r="AU52" s="107" t="str">
+      <c r="AU52" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53723,7 +53797,7 @@
       </c>
       <c r="I53" s="36"/>
       <c r="J53" s="36"/>
-      <c r="AU53" s="107" t="str">
+      <c r="AU53" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53744,7 +53818,7 @@
       </c>
       <c r="I54" s="36"/>
       <c r="J54" s="36"/>
-      <c r="AU54" s="107" t="str">
+      <c r="AU54" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53765,7 +53839,7 @@
       </c>
       <c r="I55" s="36"/>
       <c r="J55" s="36"/>
-      <c r="AU55" s="107" t="str">
+      <c r="AU55" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53786,7 +53860,7 @@
       </c>
       <c r="I56" s="36"/>
       <c r="J56" s="36"/>
-      <c r="AU56" s="107" t="str">
+      <c r="AU56" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53807,7 +53881,7 @@
       </c>
       <c r="I57" s="36"/>
       <c r="J57" s="36"/>
-      <c r="AU57" s="107" t="str">
+      <c r="AU57" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53828,7 +53902,7 @@
       </c>
       <c r="I58" s="36"/>
       <c r="J58" s="36"/>
-      <c r="AU58" s="107" t="str">
+      <c r="AU58" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53849,7 +53923,7 @@
       </c>
       <c r="I59" s="36"/>
       <c r="J59" s="36"/>
-      <c r="AU59" s="107" t="str">
+      <c r="AU59" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53870,7 +53944,7 @@
       </c>
       <c r="I60" s="36"/>
       <c r="J60" s="36"/>
-      <c r="AU60" s="107" t="str">
+      <c r="AU60" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53891,7 +53965,7 @@
       </c>
       <c r="I61" s="36"/>
       <c r="J61" s="36"/>
-      <c r="AU61" s="107" t="str">
+      <c r="AU61" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53912,7 +53986,7 @@
       </c>
       <c r="I62" s="36"/>
       <c r="J62" s="36"/>
-      <c r="AU62" s="107" t="str">
+      <c r="AU62" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53933,7 +54007,7 @@
       </c>
       <c r="I63" s="36"/>
       <c r="J63" s="36"/>
-      <c r="AU63" s="107" t="str">
+      <c r="AU63" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53954,7 +54028,7 @@
       </c>
       <c r="I64" s="36"/>
       <c r="J64" s="36"/>
-      <c r="AU64" s="107" t="str">
+      <c r="AU64" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53975,7 +54049,7 @@
       </c>
       <c r="I65" s="36"/>
       <c r="J65" s="36"/>
-      <c r="AU65" s="107" t="str">
+      <c r="AU65" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53996,7 +54070,7 @@
       </c>
       <c r="I66" s="36"/>
       <c r="J66" s="36"/>
-      <c r="AU66" s="107" t="str">
+      <c r="AU66" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -54017,7 +54091,7 @@
       </c>
       <c r="I67" s="36"/>
       <c r="J67" s="36"/>
-      <c r="AU67" s="107" t="str">
+      <c r="AU67" s="106" t="str">
         <f t="shared" ref="AU67:AU130" ca="1" si="3">_xlfn.IFNA(IF($H67+1&gt;$G$2,"",INDEX(INDIRECT("SubnetsVLANs!$D$"&amp;$H67+2&amp;":$D$"&amp;$G$2),MATCH("Subnet*",INDIRECT("SubnetsVLANs!$E$"&amp;$H67+2&amp;":$E$"&amp;$G$2),0))),"")</f>
         <v/>
       </c>
@@ -54038,7 +54112,7 @@
       </c>
       <c r="I68" s="36"/>
       <c r="J68" s="36"/>
-      <c r="AU68" s="107" t="str">
+      <c r="AU68" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54059,7 +54133,7 @@
       </c>
       <c r="I69" s="36"/>
       <c r="J69" s="36"/>
-      <c r="AU69" s="107" t="str">
+      <c r="AU69" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54080,7 +54154,7 @@
       </c>
       <c r="I70" s="36"/>
       <c r="J70" s="36"/>
-      <c r="AU70" s="107" t="str">
+      <c r="AU70" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54101,7 +54175,7 @@
       </c>
       <c r="I71" s="36"/>
       <c r="J71" s="36"/>
-      <c r="AU71" s="107" t="str">
+      <c r="AU71" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54122,7 +54196,7 @@
       </c>
       <c r="I72" s="36"/>
       <c r="J72" s="36"/>
-      <c r="AU72" s="107" t="str">
+      <c r="AU72" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54143,7 +54217,7 @@
       </c>
       <c r="I73" s="36"/>
       <c r="J73" s="36"/>
-      <c r="AU73" s="107" t="str">
+      <c r="AU73" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54164,7 +54238,7 @@
       </c>
       <c r="I74" s="36"/>
       <c r="J74" s="36"/>
-      <c r="AU74" s="107" t="str">
+      <c r="AU74" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54185,7 +54259,7 @@
       </c>
       <c r="I75" s="36"/>
       <c r="J75" s="36"/>
-      <c r="AU75" s="107" t="str">
+      <c r="AU75" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54206,7 +54280,7 @@
       </c>
       <c r="I76" s="36"/>
       <c r="J76" s="36"/>
-      <c r="AU76" s="107" t="str">
+      <c r="AU76" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54227,7 +54301,7 @@
       </c>
       <c r="I77" s="36"/>
       <c r="J77" s="36"/>
-      <c r="AU77" s="107" t="str">
+      <c r="AU77" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54248,7 +54322,7 @@
       </c>
       <c r="I78" s="36"/>
       <c r="J78" s="36"/>
-      <c r="AU78" s="107" t="str">
+      <c r="AU78" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54269,7 +54343,7 @@
       </c>
       <c r="I79" s="36"/>
       <c r="J79" s="36"/>
-      <c r="AU79" s="107" t="str">
+      <c r="AU79" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54290,7 +54364,7 @@
       </c>
       <c r="I80" s="36"/>
       <c r="J80" s="36"/>
-      <c r="AU80" s="107" t="str">
+      <c r="AU80" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54311,7 +54385,7 @@
       </c>
       <c r="I81" s="36"/>
       <c r="J81" s="36"/>
-      <c r="AU81" s="107" t="str">
+      <c r="AU81" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54332,7 +54406,7 @@
       </c>
       <c r="I82" s="36"/>
       <c r="J82" s="36"/>
-      <c r="AU82" s="107" t="str">
+      <c r="AU82" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54353,7 +54427,7 @@
       </c>
       <c r="I83" s="36"/>
       <c r="J83" s="36"/>
-      <c r="AU83" s="107" t="str">
+      <c r="AU83" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54374,7 +54448,7 @@
       </c>
       <c r="I84" s="36"/>
       <c r="J84" s="36"/>
-      <c r="AU84" s="107" t="str">
+      <c r="AU84" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54395,7 +54469,7 @@
       </c>
       <c r="I85" s="36"/>
       <c r="J85" s="36"/>
-      <c r="AU85" s="107" t="str">
+      <c r="AU85" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54416,7 +54490,7 @@
       </c>
       <c r="I86" s="36"/>
       <c r="J86" s="36"/>
-      <c r="AU86" s="107" t="str">
+      <c r="AU86" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54437,7 +54511,7 @@
       </c>
       <c r="I87" s="36"/>
       <c r="J87" s="36"/>
-      <c r="AU87" s="107" t="str">
+      <c r="AU87" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54458,7 +54532,7 @@
       </c>
       <c r="I88" s="36"/>
       <c r="J88" s="36"/>
-      <c r="AU88" s="107" t="str">
+      <c r="AU88" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54479,7 +54553,7 @@
       </c>
       <c r="I89" s="36"/>
       <c r="J89" s="36"/>
-      <c r="AU89" s="107" t="str">
+      <c r="AU89" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54500,7 +54574,7 @@
       </c>
       <c r="I90" s="36"/>
       <c r="J90" s="36"/>
-      <c r="AU90" s="107" t="str">
+      <c r="AU90" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54521,7 +54595,7 @@
       </c>
       <c r="I91" s="36"/>
       <c r="J91" s="36"/>
-      <c r="AU91" s="107" t="str">
+      <c r="AU91" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54542,7 +54616,7 @@
       </c>
       <c r="I92" s="36"/>
       <c r="J92" s="36"/>
-      <c r="AU92" s="107" t="str">
+      <c r="AU92" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54563,7 +54637,7 @@
       </c>
       <c r="I93" s="36"/>
       <c r="J93" s="36"/>
-      <c r="AU93" s="107" t="str">
+      <c r="AU93" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54584,7 +54658,7 @@
       </c>
       <c r="I94" s="36"/>
       <c r="J94" s="36"/>
-      <c r="AU94" s="107" t="str">
+      <c r="AU94" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54605,7 +54679,7 @@
       </c>
       <c r="I95" s="36"/>
       <c r="J95" s="36"/>
-      <c r="AU95" s="107" t="str">
+      <c r="AU95" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54626,7 +54700,7 @@
       </c>
       <c r="I96" s="36"/>
       <c r="J96" s="36"/>
-      <c r="AU96" s="107" t="str">
+      <c r="AU96" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54647,7 +54721,7 @@
       </c>
       <c r="I97" s="36"/>
       <c r="J97" s="36"/>
-      <c r="AU97" s="107" t="str">
+      <c r="AU97" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54668,7 +54742,7 @@
       </c>
       <c r="I98" s="36"/>
       <c r="J98" s="36"/>
-      <c r="AU98" s="107" t="str">
+      <c r="AU98" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54689,7 +54763,7 @@
       </c>
       <c r="I99" s="36"/>
       <c r="J99" s="36"/>
-      <c r="AU99" s="107" t="str">
+      <c r="AU99" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54710,7 +54784,7 @@
       </c>
       <c r="I100" s="36"/>
       <c r="J100" s="36"/>
-      <c r="AU100" s="107" t="str">
+      <c r="AU100" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54731,7 +54805,7 @@
       </c>
       <c r="I101" s="36"/>
       <c r="J101" s="36"/>
-      <c r="AU101" s="107" t="str">
+      <c r="AU101" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54752,7 +54826,7 @@
       </c>
       <c r="I102" s="36"/>
       <c r="J102" s="36"/>
-      <c r="AU102" s="107" t="str">
+      <c r="AU102" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54773,7 +54847,7 @@
       </c>
       <c r="I103" s="36"/>
       <c r="J103" s="36"/>
-      <c r="AU103" s="107" t="str">
+      <c r="AU103" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54794,7 +54868,7 @@
       </c>
       <c r="I104" s="36"/>
       <c r="J104" s="36"/>
-      <c r="AU104" s="107" t="str">
+      <c r="AU104" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54815,7 +54889,7 @@
       </c>
       <c r="I105" s="36"/>
       <c r="J105" s="36"/>
-      <c r="AU105" s="107" t="str">
+      <c r="AU105" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54836,7 +54910,7 @@
       </c>
       <c r="I106" s="36"/>
       <c r="J106" s="36"/>
-      <c r="AU106" s="107" t="str">
+      <c r="AU106" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54857,7 +54931,7 @@
       </c>
       <c r="I107" s="36"/>
       <c r="J107" s="36"/>
-      <c r="AU107" s="107" t="str">
+      <c r="AU107" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54878,7 +54952,7 @@
       </c>
       <c r="I108" s="36"/>
       <c r="J108" s="36"/>
-      <c r="AU108" s="107" t="str">
+      <c r="AU108" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54899,7 +54973,7 @@
       </c>
       <c r="I109" s="36"/>
       <c r="J109" s="36"/>
-      <c r="AU109" s="107" t="str">
+      <c r="AU109" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54920,7 +54994,7 @@
       </c>
       <c r="I110" s="36"/>
       <c r="J110" s="36"/>
-      <c r="AU110" s="107" t="str">
+      <c r="AU110" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54941,7 +55015,7 @@
       </c>
       <c r="I111" s="36"/>
       <c r="J111" s="36"/>
-      <c r="AU111" s="107" t="str">
+      <c r="AU111" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54962,7 +55036,7 @@
       </c>
       <c r="I112" s="36"/>
       <c r="J112" s="36"/>
-      <c r="AU112" s="107" t="str">
+      <c r="AU112" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54983,7 +55057,7 @@
       </c>
       <c r="I113" s="36"/>
       <c r="J113" s="36"/>
-      <c r="AU113" s="107" t="str">
+      <c r="AU113" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55004,7 +55078,7 @@
       </c>
       <c r="I114" s="36"/>
       <c r="J114" s="36"/>
-      <c r="AU114" s="107" t="str">
+      <c r="AU114" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55025,7 +55099,7 @@
       </c>
       <c r="I115" s="36"/>
       <c r="J115" s="36"/>
-      <c r="AU115" s="107" t="str">
+      <c r="AU115" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55046,7 +55120,7 @@
       </c>
       <c r="I116" s="36"/>
       <c r="J116" s="36"/>
-      <c r="AU116" s="107" t="str">
+      <c r="AU116" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55067,7 +55141,7 @@
       </c>
       <c r="I117" s="36"/>
       <c r="J117" s="36"/>
-      <c r="AU117" s="107" t="str">
+      <c r="AU117" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55088,7 +55162,7 @@
       </c>
       <c r="I118" s="36"/>
       <c r="J118" s="36"/>
-      <c r="AU118" s="107" t="str">
+      <c r="AU118" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55109,7 +55183,7 @@
       </c>
       <c r="I119" s="36"/>
       <c r="J119" s="36"/>
-      <c r="AU119" s="107" t="str">
+      <c r="AU119" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55130,7 +55204,7 @@
       </c>
       <c r="I120" s="36"/>
       <c r="J120" s="36"/>
-      <c r="AU120" s="107" t="str">
+      <c r="AU120" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55151,7 +55225,7 @@
       </c>
       <c r="I121" s="36"/>
       <c r="J121" s="36"/>
-      <c r="AU121" s="107" t="str">
+      <c r="AU121" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55172,7 +55246,7 @@
       </c>
       <c r="I122" s="36"/>
       <c r="J122" s="36"/>
-      <c r="AU122" s="107" t="str">
+      <c r="AU122" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55193,7 +55267,7 @@
       </c>
       <c r="I123" s="36"/>
       <c r="J123" s="36"/>
-      <c r="AU123" s="107" t="str">
+      <c r="AU123" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55214,7 +55288,7 @@
       </c>
       <c r="I124" s="36"/>
       <c r="J124" s="36"/>
-      <c r="AU124" s="107" t="str">
+      <c r="AU124" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55235,7 +55309,7 @@
       </c>
       <c r="I125" s="36"/>
       <c r="J125" s="36"/>
-      <c r="AU125" s="107" t="str">
+      <c r="AU125" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55256,7 +55330,7 @@
       </c>
       <c r="I126" s="36"/>
       <c r="J126" s="36"/>
-      <c r="AU126" s="107" t="str">
+      <c r="AU126" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55277,7 +55351,7 @@
       </c>
       <c r="I127" s="36"/>
       <c r="J127" s="36"/>
-      <c r="AU127" s="107" t="str">
+      <c r="AU127" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55298,7 +55372,7 @@
       </c>
       <c r="I128" s="36"/>
       <c r="J128" s="36"/>
-      <c r="AU128" s="107" t="str">
+      <c r="AU128" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55319,7 +55393,7 @@
       </c>
       <c r="I129" s="36"/>
       <c r="J129" s="36"/>
-      <c r="AU129" s="107" t="str">
+      <c r="AU129" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55340,7 +55414,7 @@
       </c>
       <c r="I130" s="36"/>
       <c r="J130" s="36"/>
-      <c r="AU130" s="107" t="str">
+      <c r="AU130" s="106" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55361,7 +55435,7 @@
       </c>
       <c r="I131" s="36"/>
       <c r="J131" s="36"/>
-      <c r="AU131" s="107" t="str">
+      <c r="AU131" s="106" t="str">
         <f t="shared" ref="AU131:AU194" ca="1" si="5">_xlfn.IFNA(IF($H131+1&gt;$G$2,"",INDEX(INDIRECT("SubnetsVLANs!$D$"&amp;$H131+2&amp;":$D$"&amp;$G$2),MATCH("Subnet*",INDIRECT("SubnetsVLANs!$E$"&amp;$H131+2&amp;":$E$"&amp;$G$2),0))),"")</f>
         <v/>
       </c>
@@ -55382,7 +55456,7 @@
       </c>
       <c r="I132" s="36"/>
       <c r="J132" s="36"/>
-      <c r="AU132" s="107" t="str">
+      <c r="AU132" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55403,7 +55477,7 @@
       </c>
       <c r="I133" s="36"/>
       <c r="J133" s="36"/>
-      <c r="AU133" s="107" t="str">
+      <c r="AU133" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55424,7 +55498,7 @@
       </c>
       <c r="I134" s="36"/>
       <c r="J134" s="36"/>
-      <c r="AU134" s="107" t="str">
+      <c r="AU134" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55445,7 +55519,7 @@
       </c>
       <c r="I135" s="36"/>
       <c r="J135" s="36"/>
-      <c r="AU135" s="107" t="str">
+      <c r="AU135" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55466,7 +55540,7 @@
       </c>
       <c r="I136" s="36"/>
       <c r="J136" s="36"/>
-      <c r="AU136" s="107" t="str">
+      <c r="AU136" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55487,7 +55561,7 @@
       </c>
       <c r="I137" s="36"/>
       <c r="J137" s="36"/>
-      <c r="AU137" s="107" t="str">
+      <c r="AU137" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55508,7 +55582,7 @@
       </c>
       <c r="I138" s="36"/>
       <c r="J138" s="36"/>
-      <c r="AU138" s="107" t="str">
+      <c r="AU138" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55529,7 +55603,7 @@
       </c>
       <c r="I139" s="36"/>
       <c r="J139" s="36"/>
-      <c r="AU139" s="107" t="str">
+      <c r="AU139" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55550,7 +55624,7 @@
       </c>
       <c r="I140" s="36"/>
       <c r="J140" s="36"/>
-      <c r="AU140" s="107" t="str">
+      <c r="AU140" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55571,7 +55645,7 @@
       </c>
       <c r="I141" s="36"/>
       <c r="J141" s="36"/>
-      <c r="AU141" s="107" t="str">
+      <c r="AU141" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55592,7 +55666,7 @@
       </c>
       <c r="I142" s="36"/>
       <c r="J142" s="36"/>
-      <c r="AU142" s="107" t="str">
+      <c r="AU142" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55613,7 +55687,7 @@
       </c>
       <c r="I143" s="36"/>
       <c r="J143" s="36"/>
-      <c r="AU143" s="107" t="str">
+      <c r="AU143" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55634,7 +55708,7 @@
       </c>
       <c r="I144" s="36"/>
       <c r="J144" s="36"/>
-      <c r="AU144" s="107" t="str">
+      <c r="AU144" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55655,7 +55729,7 @@
       </c>
       <c r="I145" s="36"/>
       <c r="J145" s="36"/>
-      <c r="AU145" s="107" t="str">
+      <c r="AU145" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55676,7 +55750,7 @@
       </c>
       <c r="I146" s="36"/>
       <c r="J146" s="36"/>
-      <c r="AU146" s="107" t="str">
+      <c r="AU146" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55697,7 +55771,7 @@
       </c>
       <c r="I147" s="36"/>
       <c r="J147" s="36"/>
-      <c r="AU147" s="107" t="str">
+      <c r="AU147" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55718,7 +55792,7 @@
       </c>
       <c r="I148" s="36"/>
       <c r="J148" s="36"/>
-      <c r="AU148" s="107" t="str">
+      <c r="AU148" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55739,7 +55813,7 @@
       </c>
       <c r="I149" s="36"/>
       <c r="J149" s="36"/>
-      <c r="AU149" s="107" t="str">
+      <c r="AU149" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55760,7 +55834,7 @@
       </c>
       <c r="I150" s="36"/>
       <c r="J150" s="36"/>
-      <c r="AU150" s="107" t="str">
+      <c r="AU150" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55781,7 +55855,7 @@
       </c>
       <c r="I151" s="36"/>
       <c r="J151" s="36"/>
-      <c r="AU151" s="107" t="str">
+      <c r="AU151" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55802,7 +55876,7 @@
       </c>
       <c r="I152" s="36"/>
       <c r="J152" s="36"/>
-      <c r="AU152" s="107" t="str">
+      <c r="AU152" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55823,7 +55897,7 @@
       </c>
       <c r="I153" s="36"/>
       <c r="J153" s="36"/>
-      <c r="AU153" s="107" t="str">
+      <c r="AU153" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55844,7 +55918,7 @@
       </c>
       <c r="I154" s="36"/>
       <c r="J154" s="36"/>
-      <c r="AU154" s="107" t="str">
+      <c r="AU154" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55865,7 +55939,7 @@
       </c>
       <c r="I155" s="36"/>
       <c r="J155" s="36"/>
-      <c r="AU155" s="107" t="str">
+      <c r="AU155" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55886,7 +55960,7 @@
       </c>
       <c r="I156" s="36"/>
       <c r="J156" s="36"/>
-      <c r="AU156" s="107" t="str">
+      <c r="AU156" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55907,7 +55981,7 @@
       </c>
       <c r="I157" s="36"/>
       <c r="J157" s="36"/>
-      <c r="AU157" s="107" t="str">
+      <c r="AU157" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55928,7 +56002,7 @@
       </c>
       <c r="I158" s="36"/>
       <c r="J158" s="36"/>
-      <c r="AU158" s="107" t="str">
+      <c r="AU158" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55949,7 +56023,7 @@
       </c>
       <c r="I159" s="36"/>
       <c r="J159" s="36"/>
-      <c r="AU159" s="107" t="str">
+      <c r="AU159" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55970,7 +56044,7 @@
       </c>
       <c r="I160" s="36"/>
       <c r="J160" s="36"/>
-      <c r="AU160" s="107" t="str">
+      <c r="AU160" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55991,7 +56065,7 @@
       </c>
       <c r="I161" s="36"/>
       <c r="J161" s="36"/>
-      <c r="AU161" s="107" t="str">
+      <c r="AU161" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56012,7 +56086,7 @@
       </c>
       <c r="I162" s="36"/>
       <c r="J162" s="36"/>
-      <c r="AU162" s="107" t="str">
+      <c r="AU162" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56033,7 +56107,7 @@
       </c>
       <c r="I163" s="36"/>
       <c r="J163" s="36"/>
-      <c r="AU163" s="107" t="str">
+      <c r="AU163" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56054,7 +56128,7 @@
       </c>
       <c r="I164" s="36"/>
       <c r="J164" s="36"/>
-      <c r="AU164" s="107" t="str">
+      <c r="AU164" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56075,7 +56149,7 @@
       </c>
       <c r="I165" s="36"/>
       <c r="J165" s="36"/>
-      <c r="AU165" s="107" t="str">
+      <c r="AU165" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56096,7 +56170,7 @@
       </c>
       <c r="I166" s="36"/>
       <c r="J166" s="36"/>
-      <c r="AU166" s="107" t="str">
+      <c r="AU166" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56117,7 +56191,7 @@
       </c>
       <c r="I167" s="36"/>
       <c r="J167" s="36"/>
-      <c r="AU167" s="107" t="str">
+      <c r="AU167" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56138,7 +56212,7 @@
       </c>
       <c r="I168" s="36"/>
       <c r="J168" s="36"/>
-      <c r="AU168" s="107" t="str">
+      <c r="AU168" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56159,7 +56233,7 @@
       </c>
       <c r="I169" s="36"/>
       <c r="J169" s="36"/>
-      <c r="AU169" s="107" t="str">
+      <c r="AU169" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56180,7 +56254,7 @@
       </c>
       <c r="I170" s="36"/>
       <c r="J170" s="36"/>
-      <c r="AU170" s="107" t="str">
+      <c r="AU170" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56201,7 +56275,7 @@
       </c>
       <c r="I171" s="36"/>
       <c r="J171" s="36"/>
-      <c r="AU171" s="107" t="str">
+      <c r="AU171" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56222,7 +56296,7 @@
       </c>
       <c r="I172" s="36"/>
       <c r="J172" s="36"/>
-      <c r="AU172" s="107" t="str">
+      <c r="AU172" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56243,7 +56317,7 @@
       </c>
       <c r="I173" s="36"/>
       <c r="J173" s="36"/>
-      <c r="AU173" s="107" t="str">
+      <c r="AU173" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56264,7 +56338,7 @@
       </c>
       <c r="I174" s="36"/>
       <c r="J174" s="36"/>
-      <c r="AU174" s="107" t="str">
+      <c r="AU174" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56285,7 +56359,7 @@
       </c>
       <c r="I175" s="36"/>
       <c r="J175" s="36"/>
-      <c r="AU175" s="107" t="str">
+      <c r="AU175" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56306,7 +56380,7 @@
       </c>
       <c r="I176" s="36"/>
       <c r="J176" s="36"/>
-      <c r="AU176" s="107" t="str">
+      <c r="AU176" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56327,7 +56401,7 @@
       </c>
       <c r="I177" s="36"/>
       <c r="J177" s="36"/>
-      <c r="AU177" s="107" t="str">
+      <c r="AU177" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56348,7 +56422,7 @@
       </c>
       <c r="I178" s="36"/>
       <c r="J178" s="36"/>
-      <c r="AU178" s="107" t="str">
+      <c r="AU178" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56369,7 +56443,7 @@
       </c>
       <c r="I179" s="36"/>
       <c r="J179" s="36"/>
-      <c r="AU179" s="107" t="str">
+      <c r="AU179" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56390,7 +56464,7 @@
       </c>
       <c r="I180" s="36"/>
       <c r="J180" s="36"/>
-      <c r="AU180" s="107" t="str">
+      <c r="AU180" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56411,7 +56485,7 @@
       </c>
       <c r="I181" s="36"/>
       <c r="J181" s="36"/>
-      <c r="AU181" s="107" t="str">
+      <c r="AU181" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56432,7 +56506,7 @@
       </c>
       <c r="I182" s="36"/>
       <c r="J182" s="36"/>
-      <c r="AU182" s="107" t="str">
+      <c r="AU182" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56453,7 +56527,7 @@
       </c>
       <c r="I183" s="36"/>
       <c r="J183" s="36"/>
-      <c r="AU183" s="107" t="str">
+      <c r="AU183" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56474,7 +56548,7 @@
       </c>
       <c r="I184" s="36"/>
       <c r="J184" s="36"/>
-      <c r="AU184" s="107" t="str">
+      <c r="AU184" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56495,7 +56569,7 @@
       </c>
       <c r="I185" s="36"/>
       <c r="J185" s="36"/>
-      <c r="AU185" s="107" t="str">
+      <c r="AU185" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56516,7 +56590,7 @@
       </c>
       <c r="I186" s="36"/>
       <c r="J186" s="36"/>
-      <c r="AU186" s="107" t="str">
+      <c r="AU186" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56537,7 +56611,7 @@
       </c>
       <c r="I187" s="36"/>
       <c r="J187" s="36"/>
-      <c r="AU187" s="107" t="str">
+      <c r="AU187" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56558,7 +56632,7 @@
       </c>
       <c r="I188" s="36"/>
       <c r="J188" s="36"/>
-      <c r="AU188" s="107" t="str">
+      <c r="AU188" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56579,7 +56653,7 @@
       </c>
       <c r="I189" s="36"/>
       <c r="J189" s="36"/>
-      <c r="AU189" s="107" t="str">
+      <c r="AU189" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56600,7 +56674,7 @@
       </c>
       <c r="I190" s="36"/>
       <c r="J190" s="36"/>
-      <c r="AU190" s="107" t="str">
+      <c r="AU190" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56621,7 +56695,7 @@
       </c>
       <c r="I191" s="36"/>
       <c r="J191" s="36"/>
-      <c r="AU191" s="107" t="str">
+      <c r="AU191" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56642,7 +56716,7 @@
       </c>
       <c r="I192" s="36"/>
       <c r="J192" s="36"/>
-      <c r="AU192" s="107" t="str">
+      <c r="AU192" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56663,7 +56737,7 @@
       </c>
       <c r="I193" s="36"/>
       <c r="J193" s="36"/>
-      <c r="AU193" s="107" t="str">
+      <c r="AU193" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56684,7 +56758,7 @@
       </c>
       <c r="I194" s="36"/>
       <c r="J194" s="36"/>
-      <c r="AU194" s="107" t="str">
+      <c r="AU194" s="106" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56705,7 +56779,7 @@
       </c>
       <c r="I195" s="36"/>
       <c r="J195" s="36"/>
-      <c r="AU195" s="107" t="str">
+      <c r="AU195" s="106" t="str">
         <f t="shared" ref="AU195:AU200" ca="1" si="7">_xlfn.IFNA(IF($H195+1&gt;$G$2,"",INDEX(INDIRECT("SubnetsVLANs!$D$"&amp;$H195+2&amp;":$D$"&amp;$G$2),MATCH("Subnet*",INDIRECT("SubnetsVLANs!$E$"&amp;$H195+2&amp;":$E$"&amp;$G$2),0))),"")</f>
         <v/>
       </c>
@@ -56726,7 +56800,7 @@
       </c>
       <c r="I196" s="36"/>
       <c r="J196" s="36"/>
-      <c r="AU196" s="107" t="str">
+      <c r="AU196" s="106" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
@@ -56747,7 +56821,7 @@
       </c>
       <c r="I197" s="36"/>
       <c r="J197" s="36"/>
-      <c r="AU197" s="107" t="str">
+      <c r="AU197" s="106" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
@@ -56768,7 +56842,7 @@
       </c>
       <c r="I198" s="36"/>
       <c r="J198" s="36"/>
-      <c r="AU198" s="107" t="str">
+      <c r="AU198" s="106" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
@@ -56789,7 +56863,7 @@
       </c>
       <c r="I199" s="36"/>
       <c r="J199" s="36"/>
-      <c r="AU199" s="107" t="str">
+      <c r="AU199" s="106" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
@@ -56810,7 +56884,7 @@
       </c>
       <c r="I200" s="36"/>
       <c r="J200" s="36"/>
-      <c r="AU200" s="107" t="str">
+      <c r="AU200" s="106" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
@@ -57354,14 +57428,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="43" customFormat="1" ht="134.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>1353</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="136"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="135"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -57422,16 +57496,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="43" customFormat="1" ht="113" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>1312</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
     </row>
     <row r="2" spans="1:8" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
@@ -58439,7 +58513,7 @@
       <c r="E80" s="35" t="s">
         <v>1365</v>
       </c>
-      <c r="F80" s="108"/>
+      <c r="F80" s="107"/>
       <c r="G80" s="35"/>
       <c r="H80" s="35"/>
     </row>
@@ -59560,7 +59634,7 @@
       <c r="D171" s="35" t="s">
         <v>603</v>
       </c>
-      <c r="E171" s="99" t="s">
+      <c r="E171" s="98" t="s">
         <v>1030</v>
       </c>
       <c r="F171" s="35"/>
@@ -60822,19 +60896,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="132" t="s">
         <v>576</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="138" t="s">
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="137" t="s">
         <v>850</v>
       </c>
-      <c r="H1" s="139"/>
-      <c r="I1" s="140"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="139"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="40" t="s">
@@ -61199,28 +61273,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="43" customFormat="1" ht="92" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>1481</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="109" t="s">
+      <c r="A2" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="110" t="s">
+      <c r="C2" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="110" t="s">
+      <c r="D2" s="109" t="s">
         <v>1422</v>
       </c>
-      <c r="E2" s="111" t="s">
+      <c r="E2" s="110" t="s">
         <v>402</v>
       </c>
     </row>
@@ -61247,6 +61321,18 @@
     <dataValidation allowBlank="1" sqref="A1:XFD1" xr:uid="{69821E7D-0BEE-4017-9F1B-D7BEFAB77982}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{2E2303BB-372A-3948-A232-9907FC736C12}">
+          <x14:formula1>
+            <xm:f>drop_down_rule_set!$L$2:$L$44</xm:f>
+          </x14:formula1>
+          <xm:sqref>A3:A1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -61264,73 +61350,73 @@
     <col min="5" max="5" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" style="124" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5" style="125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" style="125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" style="123" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5" style="124" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" style="124" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="65.6640625" customWidth="1"/>
-    <col min="14" max="14" width="41.5" style="126" customWidth="1"/>
+    <col min="14" max="14" width="41.5" style="125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="43" customFormat="1" ht="207" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>1548</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="136"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="135"/>
     </row>
     <row r="2" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="109" t="s">
+      <c r="A2" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="110" t="s">
+      <c r="C2" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="110" t="s">
+      <c r="D2" s="109" t="s">
         <v>1443</v>
       </c>
-      <c r="E2" s="111" t="s">
+      <c r="E2" s="110" t="s">
         <v>1444</v>
       </c>
-      <c r="F2" s="111" t="s">
+      <c r="F2" s="110" t="s">
         <v>1445</v>
       </c>
-      <c r="G2" s="111" t="s">
+      <c r="G2" s="110" t="s">
         <v>1446</v>
       </c>
-      <c r="H2" s="117" t="s">
+      <c r="H2" s="116" t="s">
         <v>1447</v>
       </c>
-      <c r="I2" s="118" t="s">
+      <c r="I2" s="117" t="s">
         <v>1448</v>
       </c>
-      <c r="J2" s="118" t="s">
+      <c r="J2" s="117" t="s">
         <v>1449</v>
       </c>
-      <c r="K2" s="111" t="s">
+      <c r="K2" s="110" t="s">
         <v>1450</v>
       </c>
-      <c r="L2" s="111" t="s">
+      <c r="L2" s="110" t="s">
         <v>1451</v>
       </c>
-      <c r="M2" s="111" t="s">
+      <c r="M2" s="110" t="s">
         <v>1452</v>
       </c>
-      <c r="N2" s="119" t="s">
+      <c r="N2" s="118" t="s">
         <v>402</v>
       </c>
     </row>
@@ -61356,11 +61442,11 @@
       <c r="G3" s="35">
         <v>10</v>
       </c>
-      <c r="H3" s="120"/>
-      <c r="I3" s="121" t="s">
+      <c r="H3" s="119"/>
+      <c r="I3" s="120" t="s">
         <v>1457</v>
       </c>
-      <c r="J3" s="121" t="s">
+      <c r="J3" s="120" t="s">
         <v>1458</v>
       </c>
       <c r="K3" s="35"/>
@@ -61390,17 +61476,17 @@
       <c r="G4" s="35">
         <v>100</v>
       </c>
-      <c r="H4" s="120">
+      <c r="H4" s="119">
         <v>5</v>
       </c>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
       <c r="K4" s="35" t="s">
         <v>1463</v>
       </c>
-      <c r="L4" s="122"/>
+      <c r="L4" s="121"/>
       <c r="M4" s="35"/>
-      <c r="N4" s="123"/>
+      <c r="N4" s="122"/>
     </row>
     <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="35"/>
@@ -61410,9 +61496,9 @@
       <c r="E5" s="35"/>
       <c r="F5" s="35"/>
       <c r="G5" s="35"/>
-      <c r="H5" s="120"/>
-      <c r="I5" s="121"/>
-      <c r="J5" s="121"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="120"/>
       <c r="K5" s="35" t="s">
         <v>1469</v>
       </c>
@@ -61422,7 +61508,7 @@
       <c r="M5" s="35" t="s">
         <v>1465</v>
       </c>
-      <c r="N5" s="123"/>
+      <c r="N5" s="122"/>
     </row>
     <row r="6" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="35"/>
@@ -61432,9 +61518,9 @@
       <c r="E6" s="35"/>
       <c r="F6" s="35"/>
       <c r="G6" s="35"/>
-      <c r="H6" s="120"/>
-      <c r="I6" s="121"/>
-      <c r="J6" s="121"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="120"/>
+      <c r="J6" s="120"/>
       <c r="K6" s="35" t="s">
         <v>1466</v>
       </c>
@@ -61442,7 +61528,7 @@
         <v>1467</v>
       </c>
       <c r="M6" s="35"/>
-      <c r="N6" s="123"/>
+      <c r="N6" s="122"/>
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="35" t="s">
@@ -61454,13 +61540,13 @@
       <c r="E7" s="35"/>
       <c r="F7" s="35"/>
       <c r="G7" s="35"/>
-      <c r="H7" s="120"/>
-      <c r="I7" s="121"/>
-      <c r="J7" s="121"/>
+      <c r="H7" s="119"/>
+      <c r="I7" s="120"/>
+      <c r="J7" s="120"/>
       <c r="K7" s="35"/>
       <c r="L7" s="35"/>
       <c r="M7" s="35"/>
-      <c r="N7" s="123"/>
+      <c r="N7" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -61492,5 +61578,17 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{02290C8B-B188-2048-8777-E965DBFF9BA3}">
+          <x14:formula1>
+            <xm:f>drop_down_rule_set!$L$2:$L$44</xm:f>
+          </x14:formula1>
+          <xm:sqref>A3:A1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lasyavadavalli/PycharmProjects/CD3Lasya/cd3_automation_toolkit/example/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A10103-C4DD-AD49-8360-00DBD71F49CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD20AE5-3760-744A-951F-4CCC0D12D566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13771,6 +13771,7 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -13941,9 +13942,6 @@
     </xf>
     <xf numFmtId="0" fontId="35" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -19051,22 +19049,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="247" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="133" t="s">
         <v>1483</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="132" t="s">
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="133" t="s">
         <v>1482</v>
       </c>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="136"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="137"/>
     </row>
     <row r="2" spans="1:12" s="43" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
@@ -19309,19 +19307,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="222" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="132" t="s">
         <v>927</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="140" t="s">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="141" t="s">
         <v>1334</v>
       </c>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
     </row>
     <row r="2" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -19342,7 +19340,7 @@
       <c r="F2" s="30" t="s">
         <v>490</v>
       </c>
-      <c r="G2" s="94" t="s">
+      <c r="G2" s="95" t="s">
         <v>491</v>
       </c>
       <c r="H2" s="31" t="s">
@@ -19550,10 +19548,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="43" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="132" t="s">
         <v>629</v>
       </c>
-      <c r="B1" s="139"/>
+      <c r="B1" s="140"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -19614,16 +19612,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="106" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="132" t="s">
         <v>1406</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
     </row>
     <row r="2" spans="1:8" s="43" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -19909,30 +19907,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="192.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="133" t="s">
         <v>1326</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="141" t="s">
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="142" t="s">
         <v>1296</v>
       </c>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="141"/>
+      <c r="K1" s="142"/>
+      <c r="L1" s="142"/>
+      <c r="M1" s="142"/>
+      <c r="N1" s="142"/>
+      <c r="O1" s="142"/>
+      <c r="P1" s="142"/>
+      <c r="Q1" s="142"/>
+      <c r="R1" s="142"/>
+      <c r="S1" s="142"/>
+      <c r="T1" s="142"/>
     </row>
     <row r="2" spans="1:20" s="43" customFormat="1" ht="59.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -26039,18 +26037,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="132" t="s">
         <v>1313</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
     </row>
     <row r="2" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -26161,17 +26159,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="132" t="s">
         <v>1314</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -26263,25 +26261,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="132" t="s">
         <v>1315</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="131"/>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="131"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -26413,28 +26411,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="118.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="132" t="s">
         <v>1316</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="131"/>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="131"/>
-      <c r="R1" s="131"/>
-      <c r="S1" s="131"/>
-      <c r="T1" s="131"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="132"/>
+      <c r="T1" s="132"/>
     </row>
     <row r="2" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
@@ -28916,17 +28914,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="179.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="132" t="s">
         <v>1325</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="142"/>
-      <c r="H1" s="142"/>
-      <c r="I1" s="142"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
@@ -28963,11 +28961,11 @@
       </c>
       <c r="B3" s="32"/>
       <c r="C3" s="32"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="105"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="106"/>
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -29309,13 +29307,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="43" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="132" t="s">
         <v>1311</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -29567,19 +29565,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="191.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="144" t="s">
         <v>1317</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="145"/>
     </row>
     <row r="2" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -29617,19 +29615,19 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="34" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="105" t="s">
+      <c r="A3" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="105"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="105"/>
-      <c r="I3" s="105"/>
-      <c r="J3" s="105"/>
-      <c r="K3" s="105"/>
+      <c r="B3" s="106"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="106"/>
+      <c r="K3" s="106"/>
     </row>
     <row r="4" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A4" s="36" t="s">
@@ -29749,15 +29747,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="132" t="s">
         <v>1318</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
     </row>
     <row r="2" spans="1:7" s="43" customFormat="1" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -29932,32 +29930,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="275.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="146" t="s">
         <v>1407</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="132" t="s">
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="148"/>
+      <c r="I1" s="133" t="s">
         <v>1392</v>
       </c>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="133"/>
-      <c r="R1" s="133"/>
-      <c r="S1" s="133"/>
-      <c r="T1" s="133"/>
-      <c r="U1" s="133"/>
-      <c r="V1" s="136"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="137"/>
     </row>
     <row r="2" spans="1:22" s="43" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -30406,26 +30404,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="201" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="133" t="s">
         <v>1537</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="133"/>
-      <c r="R1" s="136"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="137"/>
     </row>
     <row r="2" spans="1:18" s="43" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -30533,19 +30531,19 @@
       <c r="I4" s="53" t="s">
         <v>634</v>
       </c>
-      <c r="J4" s="126" t="s">
+      <c r="J4" s="127" t="s">
         <v>1473</v>
       </c>
-      <c r="K4" s="126" t="s">
+      <c r="K4" s="127" t="s">
         <v>1474</v>
       </c>
-      <c r="L4" s="126">
+      <c r="L4" s="127">
         <v>100</v>
       </c>
-      <c r="M4" s="126" t="s">
+      <c r="M4" s="127" t="s">
         <v>1475</v>
       </c>
-      <c r="N4" s="126" t="s">
+      <c r="N4" s="127" t="s">
         <v>1484</v>
       </c>
       <c r="O4" s="84" t="b">
@@ -30610,24 +30608,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{5F2F54D4-DE5B-A740-A826-1380AC8F6641}">
-          <x14:formula1>
-            <xm:f>drop_down_rule_set!$L$2:$L$44</xm:f>
-          </x14:formula1>
-          <xm:sqref>A3:A1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{0D42991A-073B-0B40-AF45-49EF0E834302}">
-          <x14:formula1>
-            <xm:f>INDIRECT("drop_down_rule_comp!$D$2:$D$"&amp;drop_down_rule_comp!$C$3+1)</xm:f>
-          </x14:formula1>
-          <xm:sqref>B3:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -30660,32 +30640,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="133" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="133" t="s">
         <v>1547</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="148" t="s">
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="149" t="s">
         <v>1540</v>
       </c>
-      <c r="N1" s="149"/>
-      <c r="O1" s="149"/>
-      <c r="P1" s="149"/>
-      <c r="Q1" s="149"/>
-      <c r="R1" s="149"/>
-      <c r="S1" s="149"/>
-      <c r="T1" s="149"/>
-      <c r="U1" s="149"/>
-      <c r="V1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
+      <c r="V1" s="151"/>
     </row>
     <row r="2" spans="1:22" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
@@ -31202,45 +31182,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="145" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="133" t="s">
         <v>1408</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="136"/>
-      <c r="P1" s="145" t="s">
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="146" t="s">
         <v>1319</v>
       </c>
-      <c r="Q1" s="146"/>
-      <c r="R1" s="146"/>
-      <c r="S1" s="146"/>
-      <c r="T1" s="146"/>
-      <c r="U1" s="146"/>
-      <c r="V1" s="146"/>
-      <c r="W1" s="146"/>
-      <c r="X1" s="146"/>
-      <c r="Y1" s="146"/>
-      <c r="Z1" s="146"/>
-      <c r="AA1" s="146"/>
-      <c r="AB1" s="146"/>
-      <c r="AC1" s="146"/>
-      <c r="AD1" s="146"/>
-      <c r="AE1" s="146"/>
-      <c r="AF1" s="146"/>
-      <c r="AG1" s="146"/>
-      <c r="AH1" s="146"/>
-      <c r="AI1" s="146"/>
+      <c r="Q1" s="147"/>
+      <c r="R1" s="147"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="147"/>
+      <c r="U1" s="147"/>
+      <c r="V1" s="147"/>
+      <c r="W1" s="147"/>
+      <c r="X1" s="147"/>
+      <c r="Y1" s="147"/>
+      <c r="Z1" s="147"/>
+      <c r="AA1" s="147"/>
+      <c r="AB1" s="147"/>
+      <c r="AC1" s="147"/>
+      <c r="AD1" s="147"/>
+      <c r="AE1" s="147"/>
+      <c r="AF1" s="147"/>
+      <c r="AG1" s="147"/>
+      <c r="AH1" s="147"/>
+      <c r="AI1" s="147"/>
     </row>
     <row r="2" spans="1:35" s="1" customFormat="1" ht="62" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
@@ -31392,90 +31372,90 @@
       <c r="A4" s="53" t="s">
         <v>314</v>
       </c>
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="96" t="s">
         <v>424</v>
       </c>
-      <c r="C4" s="95" t="s">
+      <c r="C4" s="96" t="s">
         <v>945</v>
       </c>
-      <c r="D4" s="95" t="s">
+      <c r="D4" s="96" t="s">
         <v>1410</v>
       </c>
-      <c r="E4" s="95" t="s">
+      <c r="E4" s="96" t="s">
         <v>1412</v>
       </c>
-      <c r="F4" s="95" t="s">
+      <c r="F4" s="96" t="s">
         <v>944</v>
       </c>
-      <c r="G4" s="95" t="b">
+      <c r="G4" s="96" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="95" t="s">
+      <c r="H4" s="96" t="s">
         <v>969</v>
       </c>
-      <c r="I4" s="95" t="s">
+      <c r="I4" s="96" t="s">
         <v>969</v>
       </c>
       <c r="J4" s="53" t="b">
         <v>0</v>
       </c>
-      <c r="K4" s="95" t="s">
+      <c r="K4" s="96" t="s">
         <v>943</v>
       </c>
-      <c r="L4" s="95" t="s">
+      <c r="L4" s="96" t="s">
         <v>942</v>
       </c>
-      <c r="M4" s="95" t="s">
+      <c r="M4" s="96" t="s">
         <v>855</v>
       </c>
-      <c r="N4" s="95" t="s">
+      <c r="N4" s="96" t="s">
         <v>1414</v>
       </c>
-      <c r="O4" s="95" t="s">
+      <c r="O4" s="96" t="s">
         <v>1412</v>
       </c>
-      <c r="P4" s="95">
+      <c r="P4" s="96">
         <v>1</v>
       </c>
-      <c r="Q4" s="95" t="s">
+      <c r="Q4" s="96" t="s">
         <v>934</v>
       </c>
-      <c r="R4" s="95">
+      <c r="R4" s="96">
         <v>32</v>
       </c>
-      <c r="S4" s="95" t="s">
+      <c r="S4" s="96" t="s">
         <v>972</v>
       </c>
-      <c r="T4" s="95">
+      <c r="T4" s="96">
         <v>32</v>
       </c>
-      <c r="U4" s="95" t="s">
+      <c r="U4" s="96" t="s">
         <v>854</v>
       </c>
-      <c r="V4" s="95" t="s">
+      <c r="V4" s="96" t="s">
         <v>970</v>
       </c>
-      <c r="W4" s="95" t="s">
+      <c r="W4" s="96" t="s">
         <v>96</v>
       </c>
-      <c r="X4" s="95" t="s">
+      <c r="X4" s="96" t="s">
         <v>1418</v>
       </c>
-      <c r="Y4" s="95"/>
-      <c r="Z4" s="95"/>
-      <c r="AA4" s="95"/>
-      <c r="AB4" s="96" t="s">
+      <c r="Y4" s="96"/>
+      <c r="Z4" s="96"/>
+      <c r="AA4" s="96"/>
+      <c r="AB4" s="97" t="s">
         <v>941</v>
       </c>
-      <c r="AC4" s="95" t="s">
+      <c r="AC4" s="96" t="s">
         <v>99</v>
       </c>
-      <c r="AD4" s="95"/>
-      <c r="AE4" s="96"/>
-      <c r="AF4" s="96"/>
-      <c r="AG4" s="96"/>
-      <c r="AH4" s="96"/>
-      <c r="AI4" s="96"/>
+      <c r="AD4" s="96"/>
+      <c r="AE4" s="97"/>
+      <c r="AF4" s="97"/>
+      <c r="AG4" s="97"/>
+      <c r="AH4" s="97"/>
+      <c r="AI4" s="97"/>
     </row>
     <row r="5" spans="1:35" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="53" t="s">
@@ -31483,7 +31463,7 @@
       </c>
       <c r="B5" s="53"/>
       <c r="C5" s="53"/>
-      <c r="D5" s="95"/>
+      <c r="D5" s="96"/>
       <c r="E5" s="52"/>
       <c r="F5" s="53"/>
       <c r="G5" s="53"/>
@@ -31496,7 +31476,7 @@
       <c r="N5" s="53" t="s">
         <v>1415</v>
       </c>
-      <c r="O5" s="95" t="s">
+      <c r="O5" s="96" t="s">
         <v>1412</v>
       </c>
       <c r="P5" s="53">
@@ -31515,13 +31495,13 @@
         <v>32</v>
       </c>
       <c r="U5" s="53"/>
-      <c r="V5" s="95" t="s">
+      <c r="V5" s="96" t="s">
         <v>970</v>
       </c>
       <c r="W5" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="X5" s="95" t="s">
+      <c r="X5" s="96" t="s">
         <v>1419</v>
       </c>
       <c r="Y5" s="53"/>
@@ -31544,7 +31524,7 @@
       <c r="A6" s="53" t="s">
         <v>314</v>
       </c>
-      <c r="B6" s="95" t="s">
+      <c r="B6" s="96" t="s">
         <v>424</v>
       </c>
       <c r="C6" s="53" t="s">
@@ -31562,7 +31542,7 @@
       <c r="G6" s="53" t="b">
         <v>0</v>
       </c>
-      <c r="H6" s="95" t="s">
+      <c r="H6" s="96" t="s">
         <v>969</v>
       </c>
       <c r="I6" s="53" t="s">
@@ -31577,7 +31557,7 @@
       <c r="N6" s="53" t="s">
         <v>1416</v>
       </c>
-      <c r="O6" s="95" t="s">
+      <c r="O6" s="96" t="s">
         <v>1412</v>
       </c>
       <c r="P6" s="53">
@@ -31595,26 +31575,26 @@
       <c r="T6" s="53">
         <v>32</v>
       </c>
-      <c r="U6" s="95" t="s">
+      <c r="U6" s="96" t="s">
         <v>854</v>
       </c>
-      <c r="V6" s="95" t="s">
+      <c r="V6" s="96" t="s">
         <v>970</v>
       </c>
       <c r="W6" s="53" t="s">
         <v>96</v>
       </c>
-      <c r="X6" s="95" t="s">
+      <c r="X6" s="96" t="s">
         <v>1419</v>
       </c>
       <c r="Y6" s="53">
         <v>2</v>
       </c>
       <c r="Z6" s="53"/>
-      <c r="AA6" s="95" t="s">
+      <c r="AA6" s="96" t="s">
         <v>970</v>
       </c>
-      <c r="AB6" s="97"/>
+      <c r="AB6" s="98"/>
       <c r="AC6" s="53" t="s">
         <v>99</v>
       </c>
@@ -31713,27 +31693,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="122.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="132" t="s">
         <v>1320</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="131"/>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="131"/>
-      <c r="R1" s="131"/>
-      <c r="S1" s="131"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="132"/>
     </row>
     <row r="2" spans="1:19" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -32009,30 +31989,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="118" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="133" t="s">
         <v>636</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="133"/>
-      <c r="R1" s="133"/>
-      <c r="S1" s="133"/>
-      <c r="T1" s="133"/>
-      <c r="U1" s="133"/>
-      <c r="V1" s="136"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="137"/>
     </row>
     <row r="2" spans="1:22" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="37" t="s">
@@ -32358,25 +32338,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="132" t="s">
         <v>637</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="131"/>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="131"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
     </row>
     <row r="2" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
@@ -32620,30 +32600,30 @@
     <col min="18" max="18" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="159" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+    <row r="1" spans="1:19" ht="115.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="133" t="s">
         <v>408</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="137" t="s">
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="138" t="s">
         <v>416</v>
       </c>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="153"/>
     </row>
     <row r="2" spans="1:19" ht="58.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
@@ -33337,13 +33317,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="43" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="132" t="s">
         <v>1546</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -33571,18 +33551,6 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{47B1B38E-AFF8-7049-B4BD-5E408E8FEEB7}">
-          <x14:formula1>
-            <xm:f>drop_down_rule_set!$L$2:$L$44</xm:f>
-          </x14:formula1>
-          <xm:sqref>A3:A1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -33601,14 +33569,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="43" customFormat="1" ht="44.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="153" t="s">
+      <c r="A1" s="154" t="s">
         <v>409</v>
       </c>
-      <c r="B1" s="154"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="155"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="156"/>
     </row>
     <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -33762,22 +33730,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="133" t="s">
         <v>661</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="133"/>
-      <c r="N1" s="136"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="137"/>
     </row>
     <row r="2" spans="1:14" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
@@ -34317,20 +34285,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="133" t="s">
         <v>661</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
     </row>
     <row r="2" spans="1:12" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
@@ -34536,24 +34504,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="160" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="133" t="s">
         <v>1321</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
-      <c r="P1" s="133"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
     </row>
     <row r="2" spans="1:16" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -34757,35 +34725,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="1" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="133" t="s">
         <v>1322</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="133"/>
-      <c r="R1" s="133"/>
-      <c r="S1" s="133"/>
-      <c r="T1" s="133"/>
-      <c r="U1" s="133"/>
-      <c r="V1" s="133"/>
-      <c r="W1" s="133"/>
-      <c r="X1" s="133"/>
-      <c r="Y1" s="133"/>
-      <c r="Z1" s="133"/>
-      <c r="AA1" s="136"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="137"/>
     </row>
     <row r="2" spans="1:27" s="48" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="49" t="s">
@@ -34977,7 +34945,7 @@
       <c r="AA4" s="52"/>
     </row>
     <row r="5" spans="1:27" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="94" t="s">
         <v>314</v>
       </c>
       <c r="B5" s="85" t="s">
@@ -38151,16 +38119,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="119.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="133" t="s">
         <v>1323</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
     </row>
     <row r="2" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="65" t="s">
@@ -41065,29 +41033,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="1" customFormat="1" ht="195" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="146" t="s">
         <v>1324</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
-      <c r="K1" s="146"/>
-      <c r="L1" s="146"/>
-      <c r="M1" s="146"/>
-      <c r="N1" s="146"/>
-      <c r="O1" s="146"/>
-      <c r="P1" s="146"/>
-      <c r="Q1" s="146"/>
-      <c r="R1" s="146"/>
-      <c r="S1" s="146"/>
-      <c r="T1" s="146"/>
-      <c r="U1" s="146"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
+      <c r="R1" s="147"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="147"/>
+      <c r="U1" s="147"/>
       <c r="V1" s="69"/>
       <c r="W1" s="69"/>
       <c r="X1" s="69"/>
@@ -45527,26 +45495,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="150" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="157" t="s">
         <v>1440</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157"/>
-      <c r="K1" s="157"/>
-      <c r="L1" s="157"/>
-      <c r="M1" s="157"/>
-      <c r="N1" s="157"/>
-      <c r="O1" s="157"/>
-      <c r="P1" s="157"/>
-      <c r="Q1" s="157"/>
-      <c r="R1" s="158"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
+      <c r="L1" s="158"/>
+      <c r="M1" s="158"/>
+      <c r="N1" s="158"/>
+      <c r="O1" s="158"/>
+      <c r="P1" s="158"/>
+      <c r="Q1" s="158"/>
+      <c r="R1" s="159"/>
       <c r="S1" s="16"/>
     </row>
     <row r="2" spans="1:19" s="48" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -45562,16 +45530,16 @@
       <c r="D2" s="37" t="s">
         <v>1427</v>
       </c>
-      <c r="E2" s="111" t="s">
+      <c r="E2" s="112" t="s">
         <v>1212</v>
       </c>
-      <c r="F2" s="111" t="s">
+      <c r="F2" s="112" t="s">
         <v>1213</v>
       </c>
       <c r="G2" s="37" t="s">
         <v>1214</v>
       </c>
-      <c r="H2" s="111" t="s">
+      <c r="H2" s="112" t="s">
         <v>1215</v>
       </c>
       <c r="I2" s="37" t="s">
@@ -45583,10 +45551,10 @@
       <c r="K2" s="37" t="s">
         <v>1217</v>
       </c>
-      <c r="L2" s="112" t="s">
+      <c r="L2" s="113" t="s">
         <v>1345</v>
       </c>
-      <c r="M2" s="113" t="s">
+      <c r="M2" s="114" t="s">
         <v>1346</v>
       </c>
       <c r="N2" s="37" t="s">
@@ -45704,7 +45672,7 @@
       <c r="R4" s="32"/>
     </row>
     <row r="5" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="99" t="s">
         <v>4</v>
       </c>
     </row>
@@ -45748,24 +45716,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" prompt="Select an OCI Region." xr:uid="{357730DE-E609-484D-9CA9-DE05C5244025}">
-          <x14:formula1>
-            <xm:f>drop_down_rule_set!$L$2:$L$44</xm:f>
-          </x14:formula1>
-          <xm:sqref>A3:A1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{47F4B22B-03E7-EA41-B3D7-A07B2AD5AABB}">
-          <x14:formula1>
-            <xm:f>INDIRECT("drop_down_rule_comp!$D$2:$D$"&amp;drop_down_rule_comp!$C$3+1)</xm:f>
-          </x14:formula1>
-          <xm:sqref>B3:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -45794,23 +45744,23 @@
     <col min="15" max="15" width="46.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="145" t="s">
+    <row r="1" spans="1:15" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="146" t="s">
         <v>1504</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157"/>
-      <c r="K1" s="157"/>
-      <c r="L1" s="157"/>
-      <c r="M1" s="157"/>
-      <c r="N1" s="157"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
+      <c r="L1" s="158"/>
+      <c r="M1" s="158"/>
+      <c r="N1" s="158"/>
     </row>
     <row r="2" spans="1:15" s="43" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="38" t="s">
@@ -45819,7 +45769,7 @@
       <c r="B2" s="38" t="s">
         <v>1211</v>
       </c>
-      <c r="C2" s="111" t="s">
+      <c r="C2" s="112" t="s">
         <v>1221</v>
       </c>
       <c r="D2" s="37" t="s">
@@ -45858,7 +45808,7 @@
       <c r="O2" s="48"/>
     </row>
     <row r="3" spans="1:15" s="34" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="35" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="35" t="s">
@@ -45900,13 +45850,13 @@
       <c r="N3" s="35" t="s">
         <v>1441</v>
       </c>
-      <c r="O3" s="114"/>
+      <c r="O3" s="115"/>
     </row>
     <row r="4" spans="1:15" s="34" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="76" t="s">
+      <c r="B4" s="35" t="s">
         <v>1437</v>
       </c>
       <c r="C4" s="35" t="s">
@@ -45943,13 +45893,13 @@
       <c r="N4" s="35" t="s">
         <v>1442</v>
       </c>
-      <c r="O4" s="114"/>
+      <c r="O4" s="115"/>
     </row>
     <row r="5" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="115"/>
+      <c r="B5" s="116"/>
       <c r="C5"/>
       <c r="O5"/>
     </row>
@@ -45989,18 +45939,6 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" prompt="Select an OCI Region." xr:uid="{7BB79F72-2125-C54B-A1F2-16A034FAB05E}">
-          <x14:formula1>
-            <xm:f>drop_down_rule_set!$L$2:$L$44</xm:f>
-          </x14:formula1>
-          <xm:sqref>A3:A1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -46033,26 +45971,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="287" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="159" t="s">
+      <c r="A1" s="160" t="s">
         <v>1327</v>
       </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
-      <c r="K1" s="160"/>
-      <c r="L1" s="160"/>
-      <c r="M1" s="160"/>
-      <c r="N1" s="160"/>
-      <c r="O1" s="160"/>
-      <c r="P1" s="160"/>
-      <c r="Q1" s="160"/>
-      <c r="R1" s="161"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
+      <c r="K1" s="161"/>
+      <c r="L1" s="161"/>
+      <c r="M1" s="161"/>
+      <c r="N1" s="161"/>
+      <c r="O1" s="161"/>
+      <c r="P1" s="161"/>
+      <c r="Q1" s="161"/>
+      <c r="R1" s="162"/>
     </row>
     <row r="2" spans="1:18" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -46395,15 +46333,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="43" customFormat="1" ht="156.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="133" t="s">
         <v>1541</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
     </row>
     <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -47332,18 +47270,6 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{815A3179-AB51-F848-9924-ADDDAEA75ADA}">
-          <x14:formula1>
-            <xm:f>drop_down_rule_set!$L$2:$L$44</xm:f>
-          </x14:formula1>
-          <xm:sqref>A3:A1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -47372,25 +47298,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="234" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="132" t="s">
         <v>1534</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="141" t="s">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="142" t="s">
         <v>1536</v>
       </c>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="131"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
     </row>
     <row r="2" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -47399,7 +47325,7 @@
       <c r="B2" s="19" t="s">
         <v>1506</v>
       </c>
-      <c r="C2" s="127" t="s">
+      <c r="C2" s="128" t="s">
         <v>1507</v>
       </c>
       <c r="D2" s="19" t="s">
@@ -47420,7 +47346,7 @@
       <c r="I2" s="19" t="s">
         <v>1514</v>
       </c>
-      <c r="J2" s="128" t="s">
+      <c r="J2" s="129" t="s">
         <v>1515</v>
       </c>
       <c r="K2" s="19" t="s">
@@ -47429,7 +47355,7 @@
       <c r="L2" s="19" t="s">
         <v>1517</v>
       </c>
-      <c r="M2" s="130" t="s">
+      <c r="M2" s="131" t="s">
         <v>1518</v>
       </c>
       <c r="N2" s="19" t="s">
@@ -47451,10 +47377,10 @@
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
       <c r="I3" s="35"/>
-      <c r="J3" s="129"/>
+      <c r="J3" s="130"/>
       <c r="K3" s="35"/>
       <c r="L3" s="35"/>
-      <c r="M3" s="129"/>
+      <c r="M3" s="130"/>
       <c r="N3" s="35"/>
       <c r="O3" s="35"/>
     </row>
@@ -47484,12 +47410,12 @@
       <c r="I4" s="35" t="s">
         <v>1521</v>
       </c>
-      <c r="J4" s="129">
+      <c r="J4" s="130">
         <v>256</v>
       </c>
       <c r="K4" s="35"/>
       <c r="L4" s="35"/>
-      <c r="M4" s="129"/>
+      <c r="M4" s="130"/>
       <c r="N4" s="35"/>
       <c r="O4" s="35"/>
     </row>
@@ -47511,14 +47437,14 @@
       <c r="I5" s="35" t="s">
         <v>1522</v>
       </c>
-      <c r="J5" s="129">
+      <c r="J5" s="130">
         <v>384</v>
       </c>
       <c r="K5" s="35" t="s">
         <v>1528</v>
       </c>
       <c r="L5" s="35"/>
-      <c r="M5" s="129"/>
+      <c r="M5" s="130"/>
       <c r="N5" s="35"/>
       <c r="O5" s="35"/>
     </row>
@@ -47550,14 +47476,14 @@
       <c r="I6" s="35" t="s">
         <v>1521</v>
       </c>
-      <c r="J6" s="129">
+      <c r="J6" s="130">
         <v>128</v>
       </c>
       <c r="K6" s="35"/>
       <c r="L6" s="35" t="b">
         <v>1</v>
       </c>
-      <c r="M6" s="129">
+      <c r="M6" s="130">
         <v>100</v>
       </c>
       <c r="N6" s="35"/>
@@ -47581,12 +47507,12 @@
       <c r="I7" s="35" t="s">
         <v>1532</v>
       </c>
-      <c r="J7" s="129">
+      <c r="J7" s="130">
         <v>3072</v>
       </c>
       <c r="K7" s="35"/>
       <c r="L7" s="35"/>
-      <c r="M7" s="129"/>
+      <c r="M7" s="130"/>
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
     </row>
@@ -47608,7 +47534,7 @@
       <c r="I8" s="35" t="s">
         <v>1522</v>
       </c>
-      <c r="J8" s="129">
+      <c r="J8" s="130">
         <v>521</v>
       </c>
       <c r="K8" s="35" t="s">
@@ -47617,7 +47543,7 @@
       <c r="L8" s="35" t="b">
         <v>1</v>
       </c>
-      <c r="M8" s="129">
+      <c r="M8" s="130">
         <v>365</v>
       </c>
       <c r="N8" s="35"/>
@@ -47633,10 +47559,10 @@
       <c r="G9" s="35"/>
       <c r="H9" s="35"/>
       <c r="I9" s="35"/>
-      <c r="J9" s="129"/>
+      <c r="J9" s="130"/>
       <c r="K9" s="35"/>
       <c r="L9" s="35"/>
-      <c r="M9" s="129"/>
+      <c r="M9" s="130"/>
       <c r="N9" s="35"/>
       <c r="O9" s="35"/>
     </row>
@@ -47650,10 +47576,10 @@
       <c r="G10" s="35"/>
       <c r="H10" s="35"/>
       <c r="I10" s="35"/>
-      <c r="J10" s="129"/>
+      <c r="J10" s="130"/>
       <c r="K10" s="35"/>
       <c r="L10" s="35"/>
-      <c r="M10" s="129"/>
+      <c r="M10" s="130"/>
       <c r="N10" s="35"/>
       <c r="O10" s="35"/>
     </row>
@@ -47667,10 +47593,10 @@
       <c r="G11" s="35"/>
       <c r="H11" s="35"/>
       <c r="I11" s="35"/>
-      <c r="J11" s="129"/>
+      <c r="J11" s="130"/>
       <c r="K11" s="35"/>
       <c r="L11" s="35"/>
-      <c r="M11" s="129"/>
+      <c r="M11" s="130"/>
       <c r="N11" s="35"/>
       <c r="O11" s="35"/>
     </row>
@@ -47684,10 +47610,10 @@
       <c r="G12" s="35"/>
       <c r="H12" s="35"/>
       <c r="I12" s="35"/>
-      <c r="J12" s="129"/>
+      <c r="J12" s="130"/>
       <c r="K12" s="35"/>
       <c r="L12" s="35"/>
-      <c r="M12" s="129"/>
+      <c r="M12" s="130"/>
       <c r="N12" s="35"/>
       <c r="O12" s="35"/>
     </row>
@@ -47701,10 +47627,10 @@
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
       <c r="I13" s="35"/>
-      <c r="J13" s="129"/>
+      <c r="J13" s="130"/>
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
-      <c r="M13" s="129"/>
+      <c r="M13" s="130"/>
       <c r="N13" s="35"/>
       <c r="O13" s="35"/>
     </row>
@@ -47718,10 +47644,10 @@
       <c r="G14" s="35"/>
       <c r="H14" s="35"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="129"/>
+      <c r="J14" s="130"/>
       <c r="K14" s="35"/>
       <c r="L14" s="35"/>
-      <c r="M14" s="129"/>
+      <c r="M14" s="130"/>
       <c r="N14" s="35"/>
       <c r="O14" s="35"/>
     </row>
@@ -47735,10 +47661,10 @@
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
       <c r="I15" s="35"/>
-      <c r="J15" s="129"/>
+      <c r="J15" s="130"/>
       <c r="K15" s="35"/>
       <c r="L15" s="35"/>
-      <c r="M15" s="129"/>
+      <c r="M15" s="130"/>
       <c r="N15" s="35"/>
       <c r="O15" s="35"/>
     </row>
@@ -47752,10 +47678,10 @@
       <c r="G16" s="35"/>
       <c r="H16" s="35"/>
       <c r="I16" s="35"/>
-      <c r="J16" s="129"/>
+      <c r="J16" s="130"/>
       <c r="K16" s="35"/>
       <c r="L16" s="35"/>
-      <c r="M16" s="129"/>
+      <c r="M16" s="130"/>
       <c r="N16" s="35"/>
       <c r="O16" s="35"/>
     </row>
@@ -47769,10 +47695,10 @@
       <c r="G17" s="35"/>
       <c r="H17" s="35"/>
       <c r="I17" s="35"/>
-      <c r="J17" s="129"/>
+      <c r="J17" s="130"/>
       <c r="K17" s="35"/>
       <c r="L17" s="35"/>
-      <c r="M17" s="129"/>
+      <c r="M17" s="130"/>
       <c r="N17" s="35"/>
       <c r="O17" s="35"/>
     </row>
@@ -47786,10 +47712,10 @@
       <c r="G18" s="35"/>
       <c r="H18" s="35"/>
       <c r="I18" s="35"/>
-      <c r="J18" s="129"/>
+      <c r="J18" s="130"/>
       <c r="K18" s="35"/>
       <c r="L18" s="35"/>
-      <c r="M18" s="129"/>
+      <c r="M18" s="130"/>
       <c r="N18" s="35"/>
       <c r="O18" s="35"/>
     </row>
@@ -47803,10 +47729,10 @@
       <c r="G19" s="35"/>
       <c r="H19" s="35"/>
       <c r="I19" s="35"/>
-      <c r="J19" s="129"/>
+      <c r="J19" s="130"/>
       <c r="K19" s="35"/>
       <c r="L19" s="35"/>
-      <c r="M19" s="129"/>
+      <c r="M19" s="130"/>
       <c r="N19" s="35"/>
       <c r="O19" s="35"/>
     </row>
@@ -47820,10 +47746,10 @@
       <c r="G20" s="35"/>
       <c r="H20" s="35"/>
       <c r="I20" s="35"/>
-      <c r="J20" s="129"/>
+      <c r="J20" s="130"/>
       <c r="K20" s="35"/>
       <c r="L20" s="35"/>
-      <c r="M20" s="129"/>
+      <c r="M20" s="130"/>
       <c r="N20" s="35"/>
       <c r="O20" s="35"/>
     </row>
@@ -47837,10 +47763,10 @@
       <c r="G21" s="35"/>
       <c r="H21" s="35"/>
       <c r="I21" s="35"/>
-      <c r="J21" s="129"/>
+      <c r="J21" s="130"/>
       <c r="K21" s="35"/>
       <c r="L21" s="35"/>
-      <c r="M21" s="129"/>
+      <c r="M21" s="130"/>
       <c r="N21" s="35"/>
       <c r="O21" s="35"/>
     </row>
@@ -47854,10 +47780,10 @@
       <c r="G22" s="35"/>
       <c r="H22" s="35"/>
       <c r="I22" s="35"/>
-      <c r="J22" s="129"/>
+      <c r="J22" s="130"/>
       <c r="K22" s="35"/>
       <c r="L22" s="35"/>
-      <c r="M22" s="129"/>
+      <c r="M22" s="130"/>
       <c r="N22" s="35"/>
       <c r="O22" s="35"/>
     </row>
@@ -47871,10 +47797,10 @@
       <c r="G23" s="35"/>
       <c r="H23" s="35"/>
       <c r="I23" s="35"/>
-      <c r="J23" s="129"/>
+      <c r="J23" s="130"/>
       <c r="K23" s="35"/>
       <c r="L23" s="35"/>
-      <c r="M23" s="129"/>
+      <c r="M23" s="130"/>
       <c r="N23" s="35"/>
       <c r="O23" s="35"/>
     </row>
@@ -47888,10 +47814,10 @@
       <c r="G24" s="35"/>
       <c r="H24" s="35"/>
       <c r="I24" s="35"/>
-      <c r="J24" s="129"/>
+      <c r="J24" s="130"/>
       <c r="K24" s="35"/>
       <c r="L24" s="35"/>
-      <c r="M24" s="129"/>
+      <c r="M24" s="130"/>
       <c r="N24" s="35"/>
       <c r="O24" s="35"/>
     </row>
@@ -47905,10 +47831,10 @@
       <c r="G25" s="35"/>
       <c r="H25" s="35"/>
       <c r="I25" s="35"/>
-      <c r="J25" s="129"/>
+      <c r="J25" s="130"/>
       <c r="K25" s="35"/>
       <c r="L25" s="35"/>
-      <c r="M25" s="129"/>
+      <c r="M25" s="130"/>
       <c r="N25" s="35"/>
       <c r="O25" s="35"/>
     </row>
@@ -47922,10 +47848,10 @@
       <c r="G26" s="35"/>
       <c r="H26" s="35"/>
       <c r="I26" s="35"/>
-      <c r="J26" s="129"/>
+      <c r="J26" s="130"/>
       <c r="K26" s="35"/>
       <c r="L26" s="35"/>
-      <c r="M26" s="129"/>
+      <c r="M26" s="130"/>
       <c r="N26" s="35"/>
       <c r="O26" s="35"/>
     </row>
@@ -47939,10 +47865,10 @@
       <c r="G27" s="35"/>
       <c r="H27" s="35"/>
       <c r="I27" s="35"/>
-      <c r="J27" s="129"/>
+      <c r="J27" s="130"/>
       <c r="K27" s="35"/>
       <c r="L27" s="35"/>
-      <c r="M27" s="129"/>
+      <c r="M27" s="130"/>
       <c r="N27" s="35"/>
       <c r="O27" s="35"/>
     </row>
@@ -47956,10 +47882,10 @@
       <c r="G28" s="35"/>
       <c r="H28" s="35"/>
       <c r="I28" s="35"/>
-      <c r="J28" s="129"/>
+      <c r="J28" s="130"/>
       <c r="K28" s="35"/>
       <c r="L28" s="35"/>
-      <c r="M28" s="129"/>
+      <c r="M28" s="130"/>
       <c r="N28" s="35"/>
       <c r="O28" s="35"/>
     </row>
@@ -47973,10 +47899,10 @@
       <c r="G29" s="35"/>
       <c r="H29" s="35"/>
       <c r="I29" s="35"/>
-      <c r="J29" s="129"/>
+      <c r="J29" s="130"/>
       <c r="K29" s="35"/>
       <c r="L29" s="35"/>
-      <c r="M29" s="129"/>
+      <c r="M29" s="130"/>
       <c r="N29" s="35"/>
       <c r="O29" s="35"/>
     </row>
@@ -47990,10 +47916,10 @@
       <c r="G30" s="35"/>
       <c r="H30" s="35"/>
       <c r="I30" s="35"/>
-      <c r="J30" s="129"/>
+      <c r="J30" s="130"/>
       <c r="K30" s="35"/>
       <c r="L30" s="35"/>
-      <c r="M30" s="129"/>
+      <c r="M30" s="130"/>
       <c r="N30" s="35"/>
       <c r="O30" s="35"/>
     </row>
@@ -48007,10 +47933,10 @@
       <c r="G31" s="35"/>
       <c r="H31" s="35"/>
       <c r="I31" s="35"/>
-      <c r="J31" s="129"/>
+      <c r="J31" s="130"/>
       <c r="K31" s="35"/>
       <c r="L31" s="35"/>
-      <c r="M31" s="129"/>
+      <c r="M31" s="130"/>
       <c r="N31" s="35"/>
       <c r="O31" s="35"/>
     </row>
@@ -48024,10 +47950,10 @@
       <c r="G32" s="35"/>
       <c r="H32" s="35"/>
       <c r="I32" s="35"/>
-      <c r="J32" s="129"/>
+      <c r="J32" s="130"/>
       <c r="K32" s="35"/>
       <c r="L32" s="35"/>
-      <c r="M32" s="129"/>
+      <c r="M32" s="130"/>
       <c r="N32" s="35"/>
       <c r="O32" s="35"/>
     </row>
@@ -48041,10 +47967,10 @@
       <c r="G33" s="35"/>
       <c r="H33" s="35"/>
       <c r="I33" s="35"/>
-      <c r="J33" s="129"/>
+      <c r="J33" s="130"/>
       <c r="K33" s="35"/>
       <c r="L33" s="35"/>
-      <c r="M33" s="129"/>
+      <c r="M33" s="130"/>
       <c r="N33" s="35"/>
       <c r="O33" s="35"/>
     </row>
@@ -48058,10 +47984,10 @@
       <c r="G34" s="35"/>
       <c r="H34" s="35"/>
       <c r="I34" s="35"/>
-      <c r="J34" s="129"/>
+      <c r="J34" s="130"/>
       <c r="K34" s="35"/>
       <c r="L34" s="35"/>
-      <c r="M34" s="129"/>
+      <c r="M34" s="130"/>
       <c r="N34" s="35"/>
       <c r="O34" s="35"/>
     </row>
@@ -48075,10 +48001,10 @@
       <c r="G35" s="35"/>
       <c r="H35" s="35"/>
       <c r="I35" s="35"/>
-      <c r="J35" s="129"/>
+      <c r="J35" s="130"/>
       <c r="K35" s="35"/>
       <c r="L35" s="35"/>
-      <c r="M35" s="129"/>
+      <c r="M35" s="130"/>
       <c r="N35" s="35"/>
       <c r="O35" s="35"/>
     </row>
@@ -48092,10 +48018,10 @@
       <c r="G36" s="35"/>
       <c r="H36" s="35"/>
       <c r="I36" s="35"/>
-      <c r="J36" s="129"/>
+      <c r="J36" s="130"/>
       <c r="K36" s="35"/>
       <c r="L36" s="35"/>
-      <c r="M36" s="129"/>
+      <c r="M36" s="130"/>
       <c r="N36" s="35"/>
       <c r="O36" s="35"/>
     </row>
@@ -48109,10 +48035,10 @@
       <c r="G37" s="35"/>
       <c r="H37" s="35"/>
       <c r="I37" s="35"/>
-      <c r="J37" s="129"/>
+      <c r="J37" s="130"/>
       <c r="K37" s="35"/>
       <c r="L37" s="35"/>
-      <c r="M37" s="129"/>
+      <c r="M37" s="130"/>
       <c r="N37" s="35"/>
       <c r="O37" s="35"/>
     </row>
@@ -48126,10 +48052,10 @@
       <c r="G38" s="35"/>
       <c r="H38" s="35"/>
       <c r="I38" s="35"/>
-      <c r="J38" s="129"/>
+      <c r="J38" s="130"/>
       <c r="K38" s="35"/>
       <c r="L38" s="35"/>
-      <c r="M38" s="129"/>
+      <c r="M38" s="130"/>
       <c r="N38" s="35"/>
       <c r="O38" s="35"/>
     </row>
@@ -48143,10 +48069,10 @@
       <c r="G39" s="35"/>
       <c r="H39" s="35"/>
       <c r="I39" s="35"/>
-      <c r="J39" s="129"/>
+      <c r="J39" s="130"/>
       <c r="K39" s="35"/>
       <c r="L39" s="35"/>
-      <c r="M39" s="129"/>
+      <c r="M39" s="130"/>
       <c r="N39" s="35"/>
       <c r="O39" s="35"/>
     </row>
@@ -48160,10 +48086,10 @@
       <c r="G40" s="35"/>
       <c r="H40" s="35"/>
       <c r="I40" s="35"/>
-      <c r="J40" s="129"/>
+      <c r="J40" s="130"/>
       <c r="K40" s="35"/>
       <c r="L40" s="35"/>
-      <c r="M40" s="129"/>
+      <c r="M40" s="130"/>
       <c r="N40" s="35"/>
       <c r="O40" s="35"/>
     </row>
@@ -48177,10 +48103,10 @@
       <c r="G41" s="35"/>
       <c r="H41" s="35"/>
       <c r="I41" s="35"/>
-      <c r="J41" s="129"/>
+      <c r="J41" s="130"/>
       <c r="K41" s="35"/>
       <c r="L41" s="35"/>
-      <c r="M41" s="129"/>
+      <c r="M41" s="130"/>
       <c r="N41" s="35"/>
       <c r="O41" s="35"/>
     </row>
@@ -48194,10 +48120,10 @@
       <c r="G42" s="35"/>
       <c r="H42" s="35"/>
       <c r="I42" s="35"/>
-      <c r="J42" s="129"/>
+      <c r="J42" s="130"/>
       <c r="K42" s="35"/>
       <c r="L42" s="35"/>
-      <c r="M42" s="129"/>
+      <c r="M42" s="130"/>
       <c r="N42" s="35"/>
       <c r="O42" s="35"/>
     </row>
@@ -48211,10 +48137,10 @@
       <c r="G43" s="35"/>
       <c r="H43" s="35"/>
       <c r="I43" s="35"/>
-      <c r="J43" s="129"/>
+      <c r="J43" s="130"/>
       <c r="K43" s="35"/>
       <c r="L43" s="35"/>
-      <c r="M43" s="129"/>
+      <c r="M43" s="130"/>
       <c r="N43" s="35"/>
       <c r="O43" s="35"/>
     </row>
@@ -48228,10 +48154,10 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
       <c r="I44" s="35"/>
-      <c r="J44" s="129"/>
+      <c r="J44" s="130"/>
       <c r="K44" s="35"/>
       <c r="L44" s="35"/>
-      <c r="M44" s="129"/>
+      <c r="M44" s="130"/>
       <c r="N44" s="35"/>
       <c r="O44" s="35"/>
     </row>
@@ -48245,10 +48171,10 @@
       <c r="G45" s="35"/>
       <c r="H45" s="35"/>
       <c r="I45" s="35"/>
-      <c r="J45" s="129"/>
+      <c r="J45" s="130"/>
       <c r="K45" s="35"/>
       <c r="L45" s="35"/>
-      <c r="M45" s="129"/>
+      <c r="M45" s="130"/>
       <c r="N45" s="35"/>
       <c r="O45" s="35"/>
     </row>
@@ -48262,10 +48188,10 @@
       <c r="G46" s="35"/>
       <c r="H46" s="35"/>
       <c r="I46" s="35"/>
-      <c r="J46" s="129"/>
+      <c r="J46" s="130"/>
       <c r="K46" s="35"/>
       <c r="L46" s="35"/>
-      <c r="M46" s="129"/>
+      <c r="M46" s="130"/>
       <c r="N46" s="35"/>
       <c r="O46" s="35"/>
     </row>
@@ -48279,10 +48205,10 @@
       <c r="G47" s="35"/>
       <c r="H47" s="35"/>
       <c r="I47" s="35"/>
-      <c r="J47" s="129"/>
+      <c r="J47" s="130"/>
       <c r="K47" s="35"/>
       <c r="L47" s="35"/>
-      <c r="M47" s="129"/>
+      <c r="M47" s="130"/>
       <c r="N47" s="35"/>
       <c r="O47" s="35"/>
     </row>
@@ -48296,10 +48222,10 @@
       <c r="G48" s="35"/>
       <c r="H48" s="35"/>
       <c r="I48" s="35"/>
-      <c r="J48" s="129"/>
+      <c r="J48" s="130"/>
       <c r="K48" s="35"/>
       <c r="L48" s="35"/>
-      <c r="M48" s="129"/>
+      <c r="M48" s="130"/>
       <c r="N48" s="35"/>
       <c r="O48" s="35"/>
     </row>
@@ -48313,10 +48239,10 @@
       <c r="G49" s="35"/>
       <c r="H49" s="35"/>
       <c r="I49" s="35"/>
-      <c r="J49" s="129"/>
+      <c r="J49" s="130"/>
       <c r="K49" s="35"/>
       <c r="L49" s="35"/>
-      <c r="M49" s="129"/>
+      <c r="M49" s="130"/>
       <c r="N49" s="35"/>
       <c r="O49" s="35"/>
     </row>
@@ -48330,10 +48256,10 @@
       <c r="G50" s="35"/>
       <c r="H50" s="35"/>
       <c r="I50" s="35"/>
-      <c r="J50" s="129"/>
+      <c r="J50" s="130"/>
       <c r="K50" s="35"/>
       <c r="L50" s="35"/>
-      <c r="M50" s="129"/>
+      <c r="M50" s="130"/>
       <c r="N50" s="35"/>
       <c r="O50" s="35"/>
     </row>
@@ -48347,10 +48273,10 @@
       <c r="G51" s="35"/>
       <c r="H51" s="35"/>
       <c r="I51" s="35"/>
-      <c r="J51" s="129"/>
+      <c r="J51" s="130"/>
       <c r="K51" s="35"/>
       <c r="L51" s="35"/>
-      <c r="M51" s="129"/>
+      <c r="M51" s="130"/>
       <c r="N51" s="35"/>
       <c r="O51" s="35"/>
     </row>
@@ -48364,10 +48290,10 @@
       <c r="G52" s="35"/>
       <c r="H52" s="35"/>
       <c r="I52" s="35"/>
-      <c r="J52" s="129"/>
+      <c r="J52" s="130"/>
       <c r="K52" s="35"/>
       <c r="L52" s="35"/>
-      <c r="M52" s="129"/>
+      <c r="M52" s="130"/>
       <c r="N52" s="35"/>
       <c r="O52" s="35"/>
     </row>
@@ -48381,10 +48307,10 @@
       <c r="G53" s="35"/>
       <c r="H53" s="35"/>
       <c r="I53" s="35"/>
-      <c r="J53" s="129"/>
+      <c r="J53" s="130"/>
       <c r="K53" s="35"/>
       <c r="L53" s="35"/>
-      <c r="M53" s="129"/>
+      <c r="M53" s="130"/>
       <c r="N53" s="35"/>
       <c r="O53" s="35"/>
     </row>
@@ -48398,10 +48324,10 @@
       <c r="G54" s="35"/>
       <c r="H54" s="35"/>
       <c r="I54" s="35"/>
-      <c r="J54" s="129"/>
+      <c r="J54" s="130"/>
       <c r="K54" s="35"/>
       <c r="L54" s="35"/>
-      <c r="M54" s="129"/>
+      <c r="M54" s="130"/>
       <c r="N54" s="35"/>
       <c r="O54" s="35"/>
     </row>
@@ -48415,10 +48341,10 @@
       <c r="G55" s="35"/>
       <c r="H55" s="35"/>
       <c r="I55" s="35"/>
-      <c r="J55" s="129"/>
+      <c r="J55" s="130"/>
       <c r="K55" s="35"/>
       <c r="L55" s="35"/>
-      <c r="M55" s="129"/>
+      <c r="M55" s="130"/>
       <c r="N55" s="35"/>
       <c r="O55" s="35"/>
     </row>
@@ -48432,10 +48358,10 @@
       <c r="G56" s="35"/>
       <c r="H56" s="35"/>
       <c r="I56" s="35"/>
-      <c r="J56" s="129"/>
+      <c r="J56" s="130"/>
       <c r="K56" s="35"/>
       <c r="L56" s="35"/>
-      <c r="M56" s="129"/>
+      <c r="M56" s="130"/>
       <c r="N56" s="35"/>
       <c r="O56" s="35"/>
     </row>
@@ -48449,10 +48375,10 @@
       <c r="G57" s="35"/>
       <c r="H57" s="35"/>
       <c r="I57" s="35"/>
-      <c r="J57" s="129"/>
+      <c r="J57" s="130"/>
       <c r="K57" s="35"/>
       <c r="L57" s="35"/>
-      <c r="M57" s="129"/>
+      <c r="M57" s="130"/>
       <c r="N57" s="35"/>
       <c r="O57" s="35"/>
     </row>
@@ -48466,10 +48392,10 @@
       <c r="G58" s="35"/>
       <c r="H58" s="35"/>
       <c r="I58" s="35"/>
-      <c r="J58" s="129"/>
+      <c r="J58" s="130"/>
       <c r="K58" s="35"/>
       <c r="L58" s="35"/>
-      <c r="M58" s="129"/>
+      <c r="M58" s="130"/>
       <c r="N58" s="35"/>
       <c r="O58" s="35"/>
     </row>
@@ -48483,10 +48409,10 @@
       <c r="G59" s="35"/>
       <c r="H59" s="35"/>
       <c r="I59" s="35"/>
-      <c r="J59" s="129"/>
+      <c r="J59" s="130"/>
       <c r="K59" s="35"/>
       <c r="L59" s="35"/>
-      <c r="M59" s="129"/>
+      <c r="M59" s="130"/>
       <c r="N59" s="35"/>
       <c r="O59" s="35"/>
     </row>
@@ -48500,10 +48426,10 @@
       <c r="G60" s="35"/>
       <c r="H60" s="35"/>
       <c r="I60" s="35"/>
-      <c r="J60" s="129"/>
+      <c r="J60" s="130"/>
       <c r="K60" s="35"/>
       <c r="L60" s="35"/>
-      <c r="M60" s="129"/>
+      <c r="M60" s="130"/>
       <c r="N60" s="35"/>
       <c r="O60" s="35"/>
     </row>
@@ -48517,10 +48443,10 @@
       <c r="G61" s="35"/>
       <c r="H61" s="35"/>
       <c r="I61" s="35"/>
-      <c r="J61" s="129"/>
+      <c r="J61" s="130"/>
       <c r="K61" s="35"/>
       <c r="L61" s="35"/>
-      <c r="M61" s="129"/>
+      <c r="M61" s="130"/>
       <c r="N61" s="35"/>
       <c r="O61" s="35"/>
     </row>
@@ -48534,10 +48460,10 @@
       <c r="G62" s="35"/>
       <c r="H62" s="35"/>
       <c r="I62" s="35"/>
-      <c r="J62" s="129"/>
+      <c r="J62" s="130"/>
       <c r="K62" s="35"/>
       <c r="L62" s="35"/>
-      <c r="M62" s="129"/>
+      <c r="M62" s="130"/>
       <c r="N62" s="35"/>
       <c r="O62" s="35"/>
     </row>
@@ -48551,10 +48477,10 @@
       <c r="G63" s="35"/>
       <c r="H63" s="35"/>
       <c r="I63" s="35"/>
-      <c r="J63" s="129"/>
+      <c r="J63" s="130"/>
       <c r="K63" s="35"/>
       <c r="L63" s="35"/>
-      <c r="M63" s="129"/>
+      <c r="M63" s="130"/>
       <c r="N63" s="35"/>
       <c r="O63" s="35"/>
     </row>
@@ -48568,10 +48494,10 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
       <c r="I64" s="35"/>
-      <c r="J64" s="129"/>
+      <c r="J64" s="130"/>
       <c r="K64" s="35"/>
       <c r="L64" s="35"/>
-      <c r="M64" s="129"/>
+      <c r="M64" s="130"/>
       <c r="N64" s="35"/>
       <c r="O64" s="35"/>
     </row>
@@ -48585,10 +48511,10 @@
       <c r="G65" s="35"/>
       <c r="H65" s="35"/>
       <c r="I65" s="35"/>
-      <c r="J65" s="129"/>
+      <c r="J65" s="130"/>
       <c r="K65" s="35"/>
       <c r="L65" s="35"/>
-      <c r="M65" s="129"/>
+      <c r="M65" s="130"/>
       <c r="N65" s="35"/>
       <c r="O65" s="35"/>
     </row>
@@ -48654,46 +48580,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="100" t="s">
         <v>1047</v>
       </c>
-      <c r="B1" s="99" t="s">
+      <c r="B1" s="100" t="s">
         <v>585</v>
       </c>
-      <c r="C1" s="100" t="s">
+      <c r="C1" s="101" t="s">
         <v>1048</v>
       </c>
-      <c r="D1" s="100" t="s">
+      <c r="D1" s="101" t="s">
         <v>1049</v>
       </c>
-      <c r="E1" s="99" t="s">
+      <c r="E1" s="100" t="s">
         <v>1050</v>
       </c>
-      <c r="F1" s="101" t="s">
+      <c r="F1" s="102" t="s">
         <v>589</v>
       </c>
-      <c r="G1" s="101" t="s">
+      <c r="G1" s="102" t="s">
         <v>318</v>
       </c>
-      <c r="H1" s="101" t="s">
+      <c r="H1" s="102" t="s">
         <v>317</v>
       </c>
-      <c r="I1" s="102" t="s">
+      <c r="I1" s="103" t="s">
         <v>587</v>
       </c>
-      <c r="J1" s="102" t="s">
+      <c r="J1" s="103" t="s">
         <v>588</v>
       </c>
-      <c r="K1" s="101" t="s">
+      <c r="K1" s="102" t="s">
         <v>583</v>
       </c>
-      <c r="L1" s="100" t="s">
+      <c r="L1" s="101" t="s">
         <v>1051</v>
       </c>
-      <c r="M1" s="100"/>
+      <c r="M1" s="101"/>
     </row>
     <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="103" t="s">
+      <c r="A2" s="104" t="s">
         <v>1052</v>
       </c>
       <c r="B2" s="45" t="s">
@@ -48711,7 +48637,7 @@
       <c r="F2" s="45" t="s">
         <v>322</v>
       </c>
-      <c r="G2" s="104" t="s">
+      <c r="G2" s="105" t="s">
         <v>328</v>
       </c>
       <c r="H2" s="36" t="s">
@@ -48731,7 +48657,7 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="103" t="s">
+      <c r="A3" s="104" t="s">
         <v>1057</v>
       </c>
       <c r="B3" s="36" t="s">
@@ -48749,7 +48675,7 @@
       <c r="F3" s="36" t="s">
         <v>1061</v>
       </c>
-      <c r="G3" s="104" t="s">
+      <c r="G3" s="105" t="s">
         <v>1062</v>
       </c>
       <c r="H3" s="36" t="s">
@@ -48769,7 +48695,7 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="103" t="s">
+      <c r="A4" s="104" t="s">
         <v>1065</v>
       </c>
       <c r="B4" s="36" t="s">
@@ -48791,7 +48717,7 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="103" t="s">
+      <c r="A5" s="104" t="s">
         <v>331</v>
       </c>
       <c r="B5" s="36" t="s">
@@ -48813,7 +48739,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="103" t="s">
+      <c r="A6" s="104" t="s">
         <v>1075</v>
       </c>
       <c r="B6" s="36"/>
@@ -48830,7 +48756,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="103" t="s">
+      <c r="A7" s="104" t="s">
         <v>1079</v>
       </c>
       <c r="B7" s="36"/>
@@ -48847,7 +48773,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="103" t="s">
+      <c r="A8" s="104" t="s">
         <v>1083</v>
       </c>
       <c r="B8" s="36"/>
@@ -48864,7 +48790,7 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="103" t="s">
+      <c r="A9" s="104" t="s">
         <v>1087</v>
       </c>
       <c r="B9" s="36"/>
@@ -48881,7 +48807,7 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="103" t="s">
+      <c r="A10" s="104" t="s">
         <v>1090</v>
       </c>
       <c r="B10" s="36"/>
@@ -48898,7 +48824,7 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="103" t="s">
+      <c r="A11" s="104" t="s">
         <v>1094</v>
       </c>
       <c r="B11" s="36"/>
@@ -48915,7 +48841,7 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="103" t="s">
+      <c r="A12" s="104" t="s">
         <v>1098</v>
       </c>
       <c r="B12" s="36"/>
@@ -48932,7 +48858,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="103" t="s">
+      <c r="A13" s="104" t="s">
         <v>1102</v>
       </c>
       <c r="B13" s="36"/>
@@ -48949,7 +48875,7 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="103" t="s">
+      <c r="A14" s="104" t="s">
         <v>332</v>
       </c>
       <c r="B14" s="36"/>
@@ -50101,7 +50027,7 @@
         <f t="array" aca="1" ref="AT2:AT6" ca="1">_xlfn.UNIQUE(INDIRECT("B2:B"&amp;$G$5),FALSE,FALSE)</f>
         <v>VCN::fwl-vcn</v>
       </c>
-      <c r="AU2" s="106" t="str">
+      <c r="AU2" s="107" t="str">
         <f ca="1">_xlfn.IFNA(IF($H2+1&gt;$G$2,"",INDEX(INDIRECT("SubnetsVLANs!$D$"&amp;$H2+2&amp;":$D$"&amp;$G$2),MATCH("Subnet*",INDIRECT("SubnetsVLANs!$E$"&amp;$H2+2&amp;":$E$"&amp;$G$2),0))),"")</f>
         <v>fwl-mgmt</v>
       </c>
@@ -50259,7 +50185,7 @@
         <f ca="1"/>
         <v>VCN::prod-vcn</v>
       </c>
-      <c r="AU3" s="106" t="str">
+      <c r="AU3" s="107" t="str">
         <f t="shared" ref="AU3:AU66" ca="1" si="1">_xlfn.IFNA(IF($H3+1&gt;$G$2,"",INDEX(INDIRECT("SubnetsVLANs!$D$"&amp;$H3+2&amp;":$D$"&amp;$G$2),MATCH("Subnet*",INDIRECT("SubnetsVLANs!$E$"&amp;$H3+2&amp;":$E$"&amp;$G$2),0))),"")</f>
         <v>fwl-pub</v>
       </c>
@@ -50387,7 +50313,7 @@
         <f ca="1"/>
         <v>VCN::nonprod-vcn</v>
       </c>
-      <c r="AU4" s="106" t="str">
+      <c r="AU4" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>fwl-priv</v>
       </c>
@@ -50494,7 +50420,7 @@
         <f ca="1"/>
         <v>VCN::exa-vcn</v>
       </c>
-      <c r="AU5" s="106" t="str">
+      <c r="AU5" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>fwl-ha</v>
       </c>
@@ -50593,7 +50519,7 @@
         <f ca="1"/>
         <v/>
       </c>
-      <c r="AU6" s="106" t="str">
+      <c r="AU6" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>prod-web</v>
       </c>
@@ -50679,7 +50605,7 @@
       <c r="AL7" s="58"/>
       <c r="AM7" s="58"/>
       <c r="AN7" s="58"/>
-      <c r="AU7" s="106" t="str">
+      <c r="AU7" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>prod-app</v>
       </c>
@@ -50765,7 +50691,7 @@
       <c r="AL8" s="58"/>
       <c r="AM8" s="58"/>
       <c r="AN8" s="58"/>
-      <c r="AU8" s="106" t="str">
+      <c r="AU8" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>prod-db</v>
       </c>
@@ -50851,7 +50777,7 @@
       <c r="AL9" s="58"/>
       <c r="AM9" s="58"/>
       <c r="AN9" s="58"/>
-      <c r="AU9" s="106" t="str">
+      <c r="AU9" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>nonprod-web</v>
       </c>
@@ -50937,7 +50863,7 @@
       <c r="AL10" s="58"/>
       <c r="AM10" s="58"/>
       <c r="AN10" s="58"/>
-      <c r="AU10" s="106" t="str">
+      <c r="AU10" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>nonprod-app</v>
       </c>
@@ -51023,7 +50949,7 @@
       <c r="AL11" s="58"/>
       <c r="AM11" s="58"/>
       <c r="AN11" s="58"/>
-      <c r="AU11" s="106" t="str">
+      <c r="AU11" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>nonprod-db</v>
       </c>
@@ -51107,7 +51033,7 @@
       <c r="AL12" s="58"/>
       <c r="AM12" s="58"/>
       <c r="AN12" s="58"/>
-      <c r="AU12" s="106" t="str">
+      <c r="AU12" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>exa-clnt</v>
       </c>
@@ -51191,7 +51117,7 @@
       <c r="AL13" s="58"/>
       <c r="AM13" s="58"/>
       <c r="AN13" s="58"/>
-      <c r="AU13" s="106" t="str">
+      <c r="AU13" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>exa-bkup</v>
       </c>
@@ -51272,7 +51198,7 @@
       <c r="AL14" s="58"/>
       <c r="AM14" s="58"/>
       <c r="AN14" s="58"/>
-      <c r="AU14" s="106" t="str">
+      <c r="AU14" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>exa-bkup</v>
       </c>
@@ -51349,7 +51275,7 @@
       <c r="AL15" s="58"/>
       <c r="AM15" s="58"/>
       <c r="AN15" s="58"/>
-      <c r="AU15" s="106" t="str">
+      <c r="AU15" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -51426,7 +51352,7 @@
       <c r="AL16" s="58"/>
       <c r="AM16" s="58"/>
       <c r="AN16" s="58"/>
-      <c r="AU16" s="106" t="str">
+      <c r="AU16" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -51503,7 +51429,7 @@
       <c r="AL17" s="58"/>
       <c r="AM17" s="58"/>
       <c r="AN17" s="58"/>
-      <c r="AU17" s="106" t="str">
+      <c r="AU17" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -51580,7 +51506,7 @@
       <c r="AL18" s="58"/>
       <c r="AM18" s="58"/>
       <c r="AN18" s="58"/>
-      <c r="AU18" s="106" t="str">
+      <c r="AU18" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -51657,7 +51583,7 @@
       <c r="AL19" s="58"/>
       <c r="AM19" s="58"/>
       <c r="AN19" s="58"/>
-      <c r="AU19" s="106" t="str">
+      <c r="AU19" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -51734,7 +51660,7 @@
       <c r="AL20" s="58"/>
       <c r="AM20" s="58"/>
       <c r="AN20" s="58"/>
-      <c r="AU20" s="106" t="str">
+      <c r="AU20" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -51811,7 +51737,7 @@
       <c r="AL21" s="58"/>
       <c r="AM21" s="58"/>
       <c r="AN21" s="58"/>
-      <c r="AU21" s="106" t="str">
+      <c r="AU21" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -51888,7 +51814,7 @@
       <c r="AL22" s="58"/>
       <c r="AM22" s="58"/>
       <c r="AN22" s="58"/>
-      <c r="AU22" s="106" t="str">
+      <c r="AU22" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -51965,7 +51891,7 @@
       <c r="AL23" s="58"/>
       <c r="AM23" s="58"/>
       <c r="AN23" s="58"/>
-      <c r="AU23" s="106" t="str">
+      <c r="AU23" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52042,7 +51968,7 @@
       <c r="AL24" s="58"/>
       <c r="AM24" s="58"/>
       <c r="AN24" s="58"/>
-      <c r="AU24" s="106" t="str">
+      <c r="AU24" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52119,7 +52045,7 @@
       <c r="AL25" s="58"/>
       <c r="AM25" s="58"/>
       <c r="AN25" s="58"/>
-      <c r="AU25" s="106" t="str">
+      <c r="AU25" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52196,7 +52122,7 @@
       <c r="AL26" s="58"/>
       <c r="AM26" s="58"/>
       <c r="AN26" s="58"/>
-      <c r="AU26" s="106" t="str">
+      <c r="AU26" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52273,7 +52199,7 @@
       <c r="AL27" s="58"/>
       <c r="AM27" s="58"/>
       <c r="AN27" s="58"/>
-      <c r="AU27" s="106" t="str">
+      <c r="AU27" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52350,7 +52276,7 @@
       <c r="AL28" s="58"/>
       <c r="AM28" s="58"/>
       <c r="AN28" s="58"/>
-      <c r="AU28" s="106" t="str">
+      <c r="AU28" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52427,7 +52353,7 @@
       <c r="AL29" s="58"/>
       <c r="AM29" s="58"/>
       <c r="AN29" s="58"/>
-      <c r="AU29" s="106" t="str">
+      <c r="AU29" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52504,7 +52430,7 @@
       <c r="AL30" s="58"/>
       <c r="AM30" s="58"/>
       <c r="AN30" s="58"/>
-      <c r="AU30" s="106" t="str">
+      <c r="AU30" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52581,7 +52507,7 @@
       <c r="AL31" s="58"/>
       <c r="AM31" s="58"/>
       <c r="AN31" s="58"/>
-      <c r="AU31" s="106" t="str">
+      <c r="AU31" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52658,7 +52584,7 @@
       <c r="AL32" s="58"/>
       <c r="AM32" s="58"/>
       <c r="AN32" s="58"/>
-      <c r="AU32" s="106" t="str">
+      <c r="AU32" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52735,7 +52661,7 @@
       <c r="AL33" s="58"/>
       <c r="AM33" s="58"/>
       <c r="AN33" s="58"/>
-      <c r="AU33" s="106" t="str">
+      <c r="AU33" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52812,7 +52738,7 @@
       <c r="AL34" s="58"/>
       <c r="AM34" s="58"/>
       <c r="AN34" s="58"/>
-      <c r="AU34" s="106" t="str">
+      <c r="AU34" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52889,7 +52815,7 @@
       <c r="AL35" s="58"/>
       <c r="AM35" s="58"/>
       <c r="AN35" s="58"/>
-      <c r="AU35" s="106" t="str">
+      <c r="AU35" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -52966,7 +52892,7 @@
       <c r="AL36" s="58"/>
       <c r="AM36" s="58"/>
       <c r="AN36" s="58"/>
-      <c r="AU36" s="106" t="str">
+      <c r="AU36" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53043,7 +52969,7 @@
       <c r="AL37" s="58"/>
       <c r="AM37" s="58"/>
       <c r="AN37" s="58"/>
-      <c r="AU37" s="106" t="str">
+      <c r="AU37" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53120,7 +53046,7 @@
       <c r="AL38" s="58"/>
       <c r="AM38" s="58"/>
       <c r="AN38" s="58"/>
-      <c r="AU38" s="106" t="str">
+      <c r="AU38" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53197,7 +53123,7 @@
       <c r="AL39" s="58"/>
       <c r="AM39" s="58"/>
       <c r="AN39" s="58"/>
-      <c r="AU39" s="106" t="str">
+      <c r="AU39" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53273,7 +53199,7 @@
       <c r="AL40" s="58"/>
       <c r="AM40" s="58"/>
       <c r="AN40" s="58"/>
-      <c r="AU40" s="106" t="str">
+      <c r="AU40" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53324,7 +53250,7 @@
         <v/>
       </c>
       <c r="AK41" s="62"/>
-      <c r="AU41" s="106" t="str">
+      <c r="AU41" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53374,7 +53300,7 @@
         <f t="array" aca="1" ref="Z42" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A42,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A42,4,4,1,"instances")))</f>
         <v/>
       </c>
-      <c r="AU42" s="106" t="str">
+      <c r="AU42" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53424,7 +53350,7 @@
         <f t="array" aca="1" ref="Z43" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A43,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A43,4,4,1,"instances")))</f>
         <v/>
       </c>
-      <c r="AU43" s="106" t="str">
+      <c r="AU43" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53474,7 +53400,7 @@
         <f t="array" aca="1" ref="Z44" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A44,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A44,4,4,1,"instances")))</f>
         <v/>
       </c>
-      <c r="AU44" s="106" t="str">
+      <c r="AU44" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53524,7 +53450,7 @@
         <f t="array" aca="1" ref="Z45" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A45,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A45,4,4,1,"instances")))</f>
         <v/>
       </c>
-      <c r="AU45" s="106" t="str">
+      <c r="AU45" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53571,7 +53497,7 @@
         <f t="array" aca="1" ref="Z46" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A46,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A46,4,4,1,"instances")))</f>
         <v/>
       </c>
-      <c r="AU46" s="106" t="str">
+      <c r="AU46" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53618,7 +53544,7 @@
         <f t="array" aca="1" ref="Z47" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A47,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A47,4,4,1,"instances")))</f>
         <v/>
       </c>
-      <c r="AU47" s="106" t="str">
+      <c r="AU47" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53665,7 +53591,7 @@
         <f t="array" aca="1" ref="Z48" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A48,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A48,4,4,1,"instances")))</f>
         <v/>
       </c>
-      <c r="AU48" s="106" t="str">
+      <c r="AU48" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53712,7 +53638,7 @@
         <f t="array" aca="1" ref="Z49" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A49,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A49,4,4,1,"instances")))</f>
         <v/>
       </c>
-      <c r="AU49" s="106" t="str">
+      <c r="AU49" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53733,7 +53659,7 @@
       <c r="I50" s="36"/>
       <c r="J50" s="36"/>
       <c r="AG50" s="63"/>
-      <c r="AU50" s="106" t="str">
+      <c r="AU50" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53754,7 +53680,7 @@
       <c r="I51" s="36"/>
       <c r="J51" s="36"/>
       <c r="L51" s="57"/>
-      <c r="AU51" s="106" t="str">
+      <c r="AU51" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53776,7 +53702,7 @@
       <c r="I52" s="36"/>
       <c r="J52" s="36"/>
       <c r="L52" s="57"/>
-      <c r="AU52" s="106" t="str">
+      <c r="AU52" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53797,7 +53723,7 @@
       </c>
       <c r="I53" s="36"/>
       <c r="J53" s="36"/>
-      <c r="AU53" s="106" t="str">
+      <c r="AU53" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53818,7 +53744,7 @@
       </c>
       <c r="I54" s="36"/>
       <c r="J54" s="36"/>
-      <c r="AU54" s="106" t="str">
+      <c r="AU54" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53839,7 +53765,7 @@
       </c>
       <c r="I55" s="36"/>
       <c r="J55" s="36"/>
-      <c r="AU55" s="106" t="str">
+      <c r="AU55" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53860,7 +53786,7 @@
       </c>
       <c r="I56" s="36"/>
       <c r="J56" s="36"/>
-      <c r="AU56" s="106" t="str">
+      <c r="AU56" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53881,7 +53807,7 @@
       </c>
       <c r="I57" s="36"/>
       <c r="J57" s="36"/>
-      <c r="AU57" s="106" t="str">
+      <c r="AU57" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53902,7 +53828,7 @@
       </c>
       <c r="I58" s="36"/>
       <c r="J58" s="36"/>
-      <c r="AU58" s="106" t="str">
+      <c r="AU58" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53923,7 +53849,7 @@
       </c>
       <c r="I59" s="36"/>
       <c r="J59" s="36"/>
-      <c r="AU59" s="106" t="str">
+      <c r="AU59" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53944,7 +53870,7 @@
       </c>
       <c r="I60" s="36"/>
       <c r="J60" s="36"/>
-      <c r="AU60" s="106" t="str">
+      <c r="AU60" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53965,7 +53891,7 @@
       </c>
       <c r="I61" s="36"/>
       <c r="J61" s="36"/>
-      <c r="AU61" s="106" t="str">
+      <c r="AU61" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -53986,7 +53912,7 @@
       </c>
       <c r="I62" s="36"/>
       <c r="J62" s="36"/>
-      <c r="AU62" s="106" t="str">
+      <c r="AU62" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -54007,7 +53933,7 @@
       </c>
       <c r="I63" s="36"/>
       <c r="J63" s="36"/>
-      <c r="AU63" s="106" t="str">
+      <c r="AU63" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -54028,7 +53954,7 @@
       </c>
       <c r="I64" s="36"/>
       <c r="J64" s="36"/>
-      <c r="AU64" s="106" t="str">
+      <c r="AU64" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -54049,7 +53975,7 @@
       </c>
       <c r="I65" s="36"/>
       <c r="J65" s="36"/>
-      <c r="AU65" s="106" t="str">
+      <c r="AU65" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -54070,7 +53996,7 @@
       </c>
       <c r="I66" s="36"/>
       <c r="J66" s="36"/>
-      <c r="AU66" s="106" t="str">
+      <c r="AU66" s="107" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
@@ -54091,7 +54017,7 @@
       </c>
       <c r="I67" s="36"/>
       <c r="J67" s="36"/>
-      <c r="AU67" s="106" t="str">
+      <c r="AU67" s="107" t="str">
         <f t="shared" ref="AU67:AU130" ca="1" si="3">_xlfn.IFNA(IF($H67+1&gt;$G$2,"",INDEX(INDIRECT("SubnetsVLANs!$D$"&amp;$H67+2&amp;":$D$"&amp;$G$2),MATCH("Subnet*",INDIRECT("SubnetsVLANs!$E$"&amp;$H67+2&amp;":$E$"&amp;$G$2),0))),"")</f>
         <v/>
       </c>
@@ -54112,7 +54038,7 @@
       </c>
       <c r="I68" s="36"/>
       <c r="J68" s="36"/>
-      <c r="AU68" s="106" t="str">
+      <c r="AU68" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54133,7 +54059,7 @@
       </c>
       <c r="I69" s="36"/>
       <c r="J69" s="36"/>
-      <c r="AU69" s="106" t="str">
+      <c r="AU69" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54154,7 +54080,7 @@
       </c>
       <c r="I70" s="36"/>
       <c r="J70" s="36"/>
-      <c r="AU70" s="106" t="str">
+      <c r="AU70" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54175,7 +54101,7 @@
       </c>
       <c r="I71" s="36"/>
       <c r="J71" s="36"/>
-      <c r="AU71" s="106" t="str">
+      <c r="AU71" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54196,7 +54122,7 @@
       </c>
       <c r="I72" s="36"/>
       <c r="J72" s="36"/>
-      <c r="AU72" s="106" t="str">
+      <c r="AU72" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54217,7 +54143,7 @@
       </c>
       <c r="I73" s="36"/>
       <c r="J73" s="36"/>
-      <c r="AU73" s="106" t="str">
+      <c r="AU73" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54238,7 +54164,7 @@
       </c>
       <c r="I74" s="36"/>
       <c r="J74" s="36"/>
-      <c r="AU74" s="106" t="str">
+      <c r="AU74" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54259,7 +54185,7 @@
       </c>
       <c r="I75" s="36"/>
       <c r="J75" s="36"/>
-      <c r="AU75" s="106" t="str">
+      <c r="AU75" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54280,7 +54206,7 @@
       </c>
       <c r="I76" s="36"/>
       <c r="J76" s="36"/>
-      <c r="AU76" s="106" t="str">
+      <c r="AU76" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54301,7 +54227,7 @@
       </c>
       <c r="I77" s="36"/>
       <c r="J77" s="36"/>
-      <c r="AU77" s="106" t="str">
+      <c r="AU77" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54322,7 +54248,7 @@
       </c>
       <c r="I78" s="36"/>
       <c r="J78" s="36"/>
-      <c r="AU78" s="106" t="str">
+      <c r="AU78" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54343,7 +54269,7 @@
       </c>
       <c r="I79" s="36"/>
       <c r="J79" s="36"/>
-      <c r="AU79" s="106" t="str">
+      <c r="AU79" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54364,7 +54290,7 @@
       </c>
       <c r="I80" s="36"/>
       <c r="J80" s="36"/>
-      <c r="AU80" s="106" t="str">
+      <c r="AU80" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54385,7 +54311,7 @@
       </c>
       <c r="I81" s="36"/>
       <c r="J81" s="36"/>
-      <c r="AU81" s="106" t="str">
+      <c r="AU81" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54406,7 +54332,7 @@
       </c>
       <c r="I82" s="36"/>
       <c r="J82" s="36"/>
-      <c r="AU82" s="106" t="str">
+      <c r="AU82" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54427,7 +54353,7 @@
       </c>
       <c r="I83" s="36"/>
       <c r="J83" s="36"/>
-      <c r="AU83" s="106" t="str">
+      <c r="AU83" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54448,7 +54374,7 @@
       </c>
       <c r="I84" s="36"/>
       <c r="J84" s="36"/>
-      <c r="AU84" s="106" t="str">
+      <c r="AU84" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54469,7 +54395,7 @@
       </c>
       <c r="I85" s="36"/>
       <c r="J85" s="36"/>
-      <c r="AU85" s="106" t="str">
+      <c r="AU85" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54490,7 +54416,7 @@
       </c>
       <c r="I86" s="36"/>
       <c r="J86" s="36"/>
-      <c r="AU86" s="106" t="str">
+      <c r="AU86" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54511,7 +54437,7 @@
       </c>
       <c r="I87" s="36"/>
       <c r="J87" s="36"/>
-      <c r="AU87" s="106" t="str">
+      <c r="AU87" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54532,7 +54458,7 @@
       </c>
       <c r="I88" s="36"/>
       <c r="J88" s="36"/>
-      <c r="AU88" s="106" t="str">
+      <c r="AU88" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54553,7 +54479,7 @@
       </c>
       <c r="I89" s="36"/>
       <c r="J89" s="36"/>
-      <c r="AU89" s="106" t="str">
+      <c r="AU89" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54574,7 +54500,7 @@
       </c>
       <c r="I90" s="36"/>
       <c r="J90" s="36"/>
-      <c r="AU90" s="106" t="str">
+      <c r="AU90" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54595,7 +54521,7 @@
       </c>
       <c r="I91" s="36"/>
       <c r="J91" s="36"/>
-      <c r="AU91" s="106" t="str">
+      <c r="AU91" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54616,7 +54542,7 @@
       </c>
       <c r="I92" s="36"/>
       <c r="J92" s="36"/>
-      <c r="AU92" s="106" t="str">
+      <c r="AU92" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54637,7 +54563,7 @@
       </c>
       <c r="I93" s="36"/>
       <c r="J93" s="36"/>
-      <c r="AU93" s="106" t="str">
+      <c r="AU93" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54658,7 +54584,7 @@
       </c>
       <c r="I94" s="36"/>
       <c r="J94" s="36"/>
-      <c r="AU94" s="106" t="str">
+      <c r="AU94" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54679,7 +54605,7 @@
       </c>
       <c r="I95" s="36"/>
       <c r="J95" s="36"/>
-      <c r="AU95" s="106" t="str">
+      <c r="AU95" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54700,7 +54626,7 @@
       </c>
       <c r="I96" s="36"/>
       <c r="J96" s="36"/>
-      <c r="AU96" s="106" t="str">
+      <c r="AU96" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54721,7 +54647,7 @@
       </c>
       <c r="I97" s="36"/>
       <c r="J97" s="36"/>
-      <c r="AU97" s="106" t="str">
+      <c r="AU97" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54742,7 +54668,7 @@
       </c>
       <c r="I98" s="36"/>
       <c r="J98" s="36"/>
-      <c r="AU98" s="106" t="str">
+      <c r="AU98" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54763,7 +54689,7 @@
       </c>
       <c r="I99" s="36"/>
       <c r="J99" s="36"/>
-      <c r="AU99" s="106" t="str">
+      <c r="AU99" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54784,7 +54710,7 @@
       </c>
       <c r="I100" s="36"/>
       <c r="J100" s="36"/>
-      <c r="AU100" s="106" t="str">
+      <c r="AU100" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54805,7 +54731,7 @@
       </c>
       <c r="I101" s="36"/>
       <c r="J101" s="36"/>
-      <c r="AU101" s="106" t="str">
+      <c r="AU101" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54826,7 +54752,7 @@
       </c>
       <c r="I102" s="36"/>
       <c r="J102" s="36"/>
-      <c r="AU102" s="106" t="str">
+      <c r="AU102" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54847,7 +54773,7 @@
       </c>
       <c r="I103" s="36"/>
       <c r="J103" s="36"/>
-      <c r="AU103" s="106" t="str">
+      <c r="AU103" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54868,7 +54794,7 @@
       </c>
       <c r="I104" s="36"/>
       <c r="J104" s="36"/>
-      <c r="AU104" s="106" t="str">
+      <c r="AU104" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54889,7 +54815,7 @@
       </c>
       <c r="I105" s="36"/>
       <c r="J105" s="36"/>
-      <c r="AU105" s="106" t="str">
+      <c r="AU105" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54910,7 +54836,7 @@
       </c>
       <c r="I106" s="36"/>
       <c r="J106" s="36"/>
-      <c r="AU106" s="106" t="str">
+      <c r="AU106" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54931,7 +54857,7 @@
       </c>
       <c r="I107" s="36"/>
       <c r="J107" s="36"/>
-      <c r="AU107" s="106" t="str">
+      <c r="AU107" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54952,7 +54878,7 @@
       </c>
       <c r="I108" s="36"/>
       <c r="J108" s="36"/>
-      <c r="AU108" s="106" t="str">
+      <c r="AU108" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54973,7 +54899,7 @@
       </c>
       <c r="I109" s="36"/>
       <c r="J109" s="36"/>
-      <c r="AU109" s="106" t="str">
+      <c r="AU109" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -54994,7 +54920,7 @@
       </c>
       <c r="I110" s="36"/>
       <c r="J110" s="36"/>
-      <c r="AU110" s="106" t="str">
+      <c r="AU110" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55015,7 +54941,7 @@
       </c>
       <c r="I111" s="36"/>
       <c r="J111" s="36"/>
-      <c r="AU111" s="106" t="str">
+      <c r="AU111" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55036,7 +54962,7 @@
       </c>
       <c r="I112" s="36"/>
       <c r="J112" s="36"/>
-      <c r="AU112" s="106" t="str">
+      <c r="AU112" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55057,7 +54983,7 @@
       </c>
       <c r="I113" s="36"/>
       <c r="J113" s="36"/>
-      <c r="AU113" s="106" t="str">
+      <c r="AU113" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55078,7 +55004,7 @@
       </c>
       <c r="I114" s="36"/>
       <c r="J114" s="36"/>
-      <c r="AU114" s="106" t="str">
+      <c r="AU114" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55099,7 +55025,7 @@
       </c>
       <c r="I115" s="36"/>
       <c r="J115" s="36"/>
-      <c r="AU115" s="106" t="str">
+      <c r="AU115" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55120,7 +55046,7 @@
       </c>
       <c r="I116" s="36"/>
       <c r="J116" s="36"/>
-      <c r="AU116" s="106" t="str">
+      <c r="AU116" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55141,7 +55067,7 @@
       </c>
       <c r="I117" s="36"/>
       <c r="J117" s="36"/>
-      <c r="AU117" s="106" t="str">
+      <c r="AU117" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55162,7 +55088,7 @@
       </c>
       <c r="I118" s="36"/>
       <c r="J118" s="36"/>
-      <c r="AU118" s="106" t="str">
+      <c r="AU118" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55183,7 +55109,7 @@
       </c>
       <c r="I119" s="36"/>
       <c r="J119" s="36"/>
-      <c r="AU119" s="106" t="str">
+      <c r="AU119" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55204,7 +55130,7 @@
       </c>
       <c r="I120" s="36"/>
       <c r="J120" s="36"/>
-      <c r="AU120" s="106" t="str">
+      <c r="AU120" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55225,7 +55151,7 @@
       </c>
       <c r="I121" s="36"/>
       <c r="J121" s="36"/>
-      <c r="AU121" s="106" t="str">
+      <c r="AU121" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55246,7 +55172,7 @@
       </c>
       <c r="I122" s="36"/>
       <c r="J122" s="36"/>
-      <c r="AU122" s="106" t="str">
+      <c r="AU122" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55267,7 +55193,7 @@
       </c>
       <c r="I123" s="36"/>
       <c r="J123" s="36"/>
-      <c r="AU123" s="106" t="str">
+      <c r="AU123" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55288,7 +55214,7 @@
       </c>
       <c r="I124" s="36"/>
       <c r="J124" s="36"/>
-      <c r="AU124" s="106" t="str">
+      <c r="AU124" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55309,7 +55235,7 @@
       </c>
       <c r="I125" s="36"/>
       <c r="J125" s="36"/>
-      <c r="AU125" s="106" t="str">
+      <c r="AU125" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55330,7 +55256,7 @@
       </c>
       <c r="I126" s="36"/>
       <c r="J126" s="36"/>
-      <c r="AU126" s="106" t="str">
+      <c r="AU126" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55351,7 +55277,7 @@
       </c>
       <c r="I127" s="36"/>
       <c r="J127" s="36"/>
-      <c r="AU127" s="106" t="str">
+      <c r="AU127" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55372,7 +55298,7 @@
       </c>
       <c r="I128" s="36"/>
       <c r="J128" s="36"/>
-      <c r="AU128" s="106" t="str">
+      <c r="AU128" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55393,7 +55319,7 @@
       </c>
       <c r="I129" s="36"/>
       <c r="J129" s="36"/>
-      <c r="AU129" s="106" t="str">
+      <c r="AU129" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55414,7 +55340,7 @@
       </c>
       <c r="I130" s="36"/>
       <c r="J130" s="36"/>
-      <c r="AU130" s="106" t="str">
+      <c r="AU130" s="107" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
@@ -55435,7 +55361,7 @@
       </c>
       <c r="I131" s="36"/>
       <c r="J131" s="36"/>
-      <c r="AU131" s="106" t="str">
+      <c r="AU131" s="107" t="str">
         <f t="shared" ref="AU131:AU194" ca="1" si="5">_xlfn.IFNA(IF($H131+1&gt;$G$2,"",INDEX(INDIRECT("SubnetsVLANs!$D$"&amp;$H131+2&amp;":$D$"&amp;$G$2),MATCH("Subnet*",INDIRECT("SubnetsVLANs!$E$"&amp;$H131+2&amp;":$E$"&amp;$G$2),0))),"")</f>
         <v/>
       </c>
@@ -55456,7 +55382,7 @@
       </c>
       <c r="I132" s="36"/>
       <c r="J132" s="36"/>
-      <c r="AU132" s="106" t="str">
+      <c r="AU132" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55477,7 +55403,7 @@
       </c>
       <c r="I133" s="36"/>
       <c r="J133" s="36"/>
-      <c r="AU133" s="106" t="str">
+      <c r="AU133" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55498,7 +55424,7 @@
       </c>
       <c r="I134" s="36"/>
       <c r="J134" s="36"/>
-      <c r="AU134" s="106" t="str">
+      <c r="AU134" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55519,7 +55445,7 @@
       </c>
       <c r="I135" s="36"/>
       <c r="J135" s="36"/>
-      <c r="AU135" s="106" t="str">
+      <c r="AU135" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55540,7 +55466,7 @@
       </c>
       <c r="I136" s="36"/>
       <c r="J136" s="36"/>
-      <c r="AU136" s="106" t="str">
+      <c r="AU136" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55561,7 +55487,7 @@
       </c>
       <c r="I137" s="36"/>
       <c r="J137" s="36"/>
-      <c r="AU137" s="106" t="str">
+      <c r="AU137" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55582,7 +55508,7 @@
       </c>
       <c r="I138" s="36"/>
       <c r="J138" s="36"/>
-      <c r="AU138" s="106" t="str">
+      <c r="AU138" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55603,7 +55529,7 @@
       </c>
       <c r="I139" s="36"/>
       <c r="J139" s="36"/>
-      <c r="AU139" s="106" t="str">
+      <c r="AU139" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55624,7 +55550,7 @@
       </c>
       <c r="I140" s="36"/>
       <c r="J140" s="36"/>
-      <c r="AU140" s="106" t="str">
+      <c r="AU140" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55645,7 +55571,7 @@
       </c>
       <c r="I141" s="36"/>
       <c r="J141" s="36"/>
-      <c r="AU141" s="106" t="str">
+      <c r="AU141" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55666,7 +55592,7 @@
       </c>
       <c r="I142" s="36"/>
       <c r="J142" s="36"/>
-      <c r="AU142" s="106" t="str">
+      <c r="AU142" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55687,7 +55613,7 @@
       </c>
       <c r="I143" s="36"/>
       <c r="J143" s="36"/>
-      <c r="AU143" s="106" t="str">
+      <c r="AU143" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55708,7 +55634,7 @@
       </c>
       <c r="I144" s="36"/>
       <c r="J144" s="36"/>
-      <c r="AU144" s="106" t="str">
+      <c r="AU144" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55729,7 +55655,7 @@
       </c>
       <c r="I145" s="36"/>
       <c r="J145" s="36"/>
-      <c r="AU145" s="106" t="str">
+      <c r="AU145" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55750,7 +55676,7 @@
       </c>
       <c r="I146" s="36"/>
       <c r="J146" s="36"/>
-      <c r="AU146" s="106" t="str">
+      <c r="AU146" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55771,7 +55697,7 @@
       </c>
       <c r="I147" s="36"/>
       <c r="J147" s="36"/>
-      <c r="AU147" s="106" t="str">
+      <c r="AU147" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55792,7 +55718,7 @@
       </c>
       <c r="I148" s="36"/>
       <c r="J148" s="36"/>
-      <c r="AU148" s="106" t="str">
+      <c r="AU148" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55813,7 +55739,7 @@
       </c>
       <c r="I149" s="36"/>
       <c r="J149" s="36"/>
-      <c r="AU149" s="106" t="str">
+      <c r="AU149" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55834,7 +55760,7 @@
       </c>
       <c r="I150" s="36"/>
       <c r="J150" s="36"/>
-      <c r="AU150" s="106" t="str">
+      <c r="AU150" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55855,7 +55781,7 @@
       </c>
       <c r="I151" s="36"/>
       <c r="J151" s="36"/>
-      <c r="AU151" s="106" t="str">
+      <c r="AU151" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55876,7 +55802,7 @@
       </c>
       <c r="I152" s="36"/>
       <c r="J152" s="36"/>
-      <c r="AU152" s="106" t="str">
+      <c r="AU152" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55897,7 +55823,7 @@
       </c>
       <c r="I153" s="36"/>
       <c r="J153" s="36"/>
-      <c r="AU153" s="106" t="str">
+      <c r="AU153" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55918,7 +55844,7 @@
       </c>
       <c r="I154" s="36"/>
       <c r="J154" s="36"/>
-      <c r="AU154" s="106" t="str">
+      <c r="AU154" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55939,7 +55865,7 @@
       </c>
       <c r="I155" s="36"/>
       <c r="J155" s="36"/>
-      <c r="AU155" s="106" t="str">
+      <c r="AU155" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55960,7 +55886,7 @@
       </c>
       <c r="I156" s="36"/>
       <c r="J156" s="36"/>
-      <c r="AU156" s="106" t="str">
+      <c r="AU156" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -55981,7 +55907,7 @@
       </c>
       <c r="I157" s="36"/>
       <c r="J157" s="36"/>
-      <c r="AU157" s="106" t="str">
+      <c r="AU157" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56002,7 +55928,7 @@
       </c>
       <c r="I158" s="36"/>
       <c r="J158" s="36"/>
-      <c r="AU158" s="106" t="str">
+      <c r="AU158" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56023,7 +55949,7 @@
       </c>
       <c r="I159" s="36"/>
       <c r="J159" s="36"/>
-      <c r="AU159" s="106" t="str">
+      <c r="AU159" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56044,7 +55970,7 @@
       </c>
       <c r="I160" s="36"/>
       <c r="J160" s="36"/>
-      <c r="AU160" s="106" t="str">
+      <c r="AU160" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56065,7 +55991,7 @@
       </c>
       <c r="I161" s="36"/>
       <c r="J161" s="36"/>
-      <c r="AU161" s="106" t="str">
+      <c r="AU161" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56086,7 +56012,7 @@
       </c>
       <c r="I162" s="36"/>
       <c r="J162" s="36"/>
-      <c r="AU162" s="106" t="str">
+      <c r="AU162" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56107,7 +56033,7 @@
       </c>
       <c r="I163" s="36"/>
       <c r="J163" s="36"/>
-      <c r="AU163" s="106" t="str">
+      <c r="AU163" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56128,7 +56054,7 @@
       </c>
       <c r="I164" s="36"/>
       <c r="J164" s="36"/>
-      <c r="AU164" s="106" t="str">
+      <c r="AU164" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56149,7 +56075,7 @@
       </c>
       <c r="I165" s="36"/>
       <c r="J165" s="36"/>
-      <c r="AU165" s="106" t="str">
+      <c r="AU165" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56170,7 +56096,7 @@
       </c>
       <c r="I166" s="36"/>
       <c r="J166" s="36"/>
-      <c r="AU166" s="106" t="str">
+      <c r="AU166" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56191,7 +56117,7 @@
       </c>
       <c r="I167" s="36"/>
       <c r="J167" s="36"/>
-      <c r="AU167" s="106" t="str">
+      <c r="AU167" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56212,7 +56138,7 @@
       </c>
       <c r="I168" s="36"/>
       <c r="J168" s="36"/>
-      <c r="AU168" s="106" t="str">
+      <c r="AU168" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56233,7 +56159,7 @@
       </c>
       <c r="I169" s="36"/>
       <c r="J169" s="36"/>
-      <c r="AU169" s="106" t="str">
+      <c r="AU169" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56254,7 +56180,7 @@
       </c>
       <c r="I170" s="36"/>
       <c r="J170" s="36"/>
-      <c r="AU170" s="106" t="str">
+      <c r="AU170" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56275,7 +56201,7 @@
       </c>
       <c r="I171" s="36"/>
       <c r="J171" s="36"/>
-      <c r="AU171" s="106" t="str">
+      <c r="AU171" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56296,7 +56222,7 @@
       </c>
       <c r="I172" s="36"/>
       <c r="J172" s="36"/>
-      <c r="AU172" s="106" t="str">
+      <c r="AU172" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56317,7 +56243,7 @@
       </c>
       <c r="I173" s="36"/>
       <c r="J173" s="36"/>
-      <c r="AU173" s="106" t="str">
+      <c r="AU173" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56338,7 +56264,7 @@
       </c>
       <c r="I174" s="36"/>
       <c r="J174" s="36"/>
-      <c r="AU174" s="106" t="str">
+      <c r="AU174" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56359,7 +56285,7 @@
       </c>
       <c r="I175" s="36"/>
       <c r="J175" s="36"/>
-      <c r="AU175" s="106" t="str">
+      <c r="AU175" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56380,7 +56306,7 @@
       </c>
       <c r="I176" s="36"/>
       <c r="J176" s="36"/>
-      <c r="AU176" s="106" t="str">
+      <c r="AU176" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56401,7 +56327,7 @@
       </c>
       <c r="I177" s="36"/>
       <c r="J177" s="36"/>
-      <c r="AU177" s="106" t="str">
+      <c r="AU177" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56422,7 +56348,7 @@
       </c>
       <c r="I178" s="36"/>
       <c r="J178" s="36"/>
-      <c r="AU178" s="106" t="str">
+      <c r="AU178" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56443,7 +56369,7 @@
       </c>
       <c r="I179" s="36"/>
       <c r="J179" s="36"/>
-      <c r="AU179" s="106" t="str">
+      <c r="AU179" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56464,7 +56390,7 @@
       </c>
       <c r="I180" s="36"/>
       <c r="J180" s="36"/>
-      <c r="AU180" s="106" t="str">
+      <c r="AU180" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56485,7 +56411,7 @@
       </c>
       <c r="I181" s="36"/>
       <c r="J181" s="36"/>
-      <c r="AU181" s="106" t="str">
+      <c r="AU181" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56506,7 +56432,7 @@
       </c>
       <c r="I182" s="36"/>
       <c r="J182" s="36"/>
-      <c r="AU182" s="106" t="str">
+      <c r="AU182" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56527,7 +56453,7 @@
       </c>
       <c r="I183" s="36"/>
       <c r="J183" s="36"/>
-      <c r="AU183" s="106" t="str">
+      <c r="AU183" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56548,7 +56474,7 @@
       </c>
       <c r="I184" s="36"/>
       <c r="J184" s="36"/>
-      <c r="AU184" s="106" t="str">
+      <c r="AU184" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56569,7 +56495,7 @@
       </c>
       <c r="I185" s="36"/>
       <c r="J185" s="36"/>
-      <c r="AU185" s="106" t="str">
+      <c r="AU185" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56590,7 +56516,7 @@
       </c>
       <c r="I186" s="36"/>
       <c r="J186" s="36"/>
-      <c r="AU186" s="106" t="str">
+      <c r="AU186" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56611,7 +56537,7 @@
       </c>
       <c r="I187" s="36"/>
       <c r="J187" s="36"/>
-      <c r="AU187" s="106" t="str">
+      <c r="AU187" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56632,7 +56558,7 @@
       </c>
       <c r="I188" s="36"/>
       <c r="J188" s="36"/>
-      <c r="AU188" s="106" t="str">
+      <c r="AU188" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56653,7 +56579,7 @@
       </c>
       <c r="I189" s="36"/>
       <c r="J189" s="36"/>
-      <c r="AU189" s="106" t="str">
+      <c r="AU189" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56674,7 +56600,7 @@
       </c>
       <c r="I190" s="36"/>
       <c r="J190" s="36"/>
-      <c r="AU190" s="106" t="str">
+      <c r="AU190" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56695,7 +56621,7 @@
       </c>
       <c r="I191" s="36"/>
       <c r="J191" s="36"/>
-      <c r="AU191" s="106" t="str">
+      <c r="AU191" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56716,7 +56642,7 @@
       </c>
       <c r="I192" s="36"/>
       <c r="J192" s="36"/>
-      <c r="AU192" s="106" t="str">
+      <c r="AU192" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56737,7 +56663,7 @@
       </c>
       <c r="I193" s="36"/>
       <c r="J193" s="36"/>
-      <c r="AU193" s="106" t="str">
+      <c r="AU193" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56758,7 +56684,7 @@
       </c>
       <c r="I194" s="36"/>
       <c r="J194" s="36"/>
-      <c r="AU194" s="106" t="str">
+      <c r="AU194" s="107" t="str">
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
@@ -56779,7 +56705,7 @@
       </c>
       <c r="I195" s="36"/>
       <c r="J195" s="36"/>
-      <c r="AU195" s="106" t="str">
+      <c r="AU195" s="107" t="str">
         <f t="shared" ref="AU195:AU200" ca="1" si="7">_xlfn.IFNA(IF($H195+1&gt;$G$2,"",INDEX(INDIRECT("SubnetsVLANs!$D$"&amp;$H195+2&amp;":$D$"&amp;$G$2),MATCH("Subnet*",INDIRECT("SubnetsVLANs!$E$"&amp;$H195+2&amp;":$E$"&amp;$G$2),0))),"")</f>
         <v/>
       </c>
@@ -56800,7 +56726,7 @@
       </c>
       <c r="I196" s="36"/>
       <c r="J196" s="36"/>
-      <c r="AU196" s="106" t="str">
+      <c r="AU196" s="107" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
@@ -56821,7 +56747,7 @@
       </c>
       <c r="I197" s="36"/>
       <c r="J197" s="36"/>
-      <c r="AU197" s="106" t="str">
+      <c r="AU197" s="107" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
@@ -56842,7 +56768,7 @@
       </c>
       <c r="I198" s="36"/>
       <c r="J198" s="36"/>
-      <c r="AU198" s="106" t="str">
+      <c r="AU198" s="107" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
@@ -56863,7 +56789,7 @@
       </c>
       <c r="I199" s="36"/>
       <c r="J199" s="36"/>
-      <c r="AU199" s="106" t="str">
+      <c r="AU199" s="107" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
@@ -56884,7 +56810,7 @@
       </c>
       <c r="I200" s="36"/>
       <c r="J200" s="36"/>
-      <c r="AU200" s="106" t="str">
+      <c r="AU200" s="107" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
@@ -57428,14 +57354,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="43" customFormat="1" ht="134.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="132" t="s">
         <v>1353</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="135"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="136"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
@@ -57496,16 +57422,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="43" customFormat="1" ht="113" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="132" t="s">
         <v>1312</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
     </row>
     <row r="2" spans="1:8" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
@@ -58513,7 +58439,7 @@
       <c r="E80" s="35" t="s">
         <v>1365</v>
       </c>
-      <c r="F80" s="107"/>
+      <c r="F80" s="108"/>
       <c r="G80" s="35"/>
       <c r="H80" s="35"/>
     </row>
@@ -59634,7 +59560,7 @@
       <c r="D171" s="35" t="s">
         <v>603</v>
       </c>
-      <c r="E171" s="98" t="s">
+      <c r="E171" s="99" t="s">
         <v>1030</v>
       </c>
       <c r="F171" s="35"/>
@@ -60896,19 +60822,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="133" t="s">
         <v>576</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="137" t="s">
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="138" t="s">
         <v>850</v>
       </c>
-      <c r="H1" s="138"/>
-      <c r="I1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="140"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="40" t="s">
@@ -61273,28 +61199,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="43" customFormat="1" ht="92" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="132" t="s">
         <v>1481</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="108" t="s">
+      <c r="A2" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="109" t="s">
+      <c r="C2" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="109" t="s">
+      <c r="D2" s="110" t="s">
         <v>1422</v>
       </c>
-      <c r="E2" s="110" t="s">
+      <c r="E2" s="111" t="s">
         <v>402</v>
       </c>
     </row>
@@ -61321,18 +61247,6 @@
     <dataValidation allowBlank="1" sqref="A1:XFD1" xr:uid="{69821E7D-0BEE-4017-9F1B-D7BEFAB77982}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{2E2303BB-372A-3948-A232-9907FC736C12}">
-          <x14:formula1>
-            <xm:f>drop_down_rule_set!$L$2:$L$44</xm:f>
-          </x14:formula1>
-          <xm:sqref>A3:A1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -61350,73 +61264,73 @@
     <col min="5" max="5" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" style="123" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5" style="124" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" style="124" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" style="124" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5" style="125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" style="125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="65.6640625" customWidth="1"/>
-    <col min="14" max="14" width="41.5" style="125" customWidth="1"/>
+    <col min="14" max="14" width="41.5" style="126" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="43" customFormat="1" ht="207" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="132" t="s">
         <v>1548</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="135"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="136"/>
     </row>
     <row r="2" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="108" t="s">
+      <c r="A2" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="109" t="s">
+      <c r="C2" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="109" t="s">
+      <c r="D2" s="110" t="s">
         <v>1443</v>
       </c>
-      <c r="E2" s="110" t="s">
+      <c r="E2" s="111" t="s">
         <v>1444</v>
       </c>
-      <c r="F2" s="110" t="s">
+      <c r="F2" s="111" t="s">
         <v>1445</v>
       </c>
-      <c r="G2" s="110" t="s">
+      <c r="G2" s="111" t="s">
         <v>1446</v>
       </c>
-      <c r="H2" s="116" t="s">
+      <c r="H2" s="117" t="s">
         <v>1447</v>
       </c>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="118" t="s">
         <v>1448</v>
       </c>
-      <c r="J2" s="117" t="s">
+      <c r="J2" s="118" t="s">
         <v>1449</v>
       </c>
-      <c r="K2" s="110" t="s">
+      <c r="K2" s="111" t="s">
         <v>1450</v>
       </c>
-      <c r="L2" s="110" t="s">
+      <c r="L2" s="111" t="s">
         <v>1451</v>
       </c>
-      <c r="M2" s="110" t="s">
+      <c r="M2" s="111" t="s">
         <v>1452</v>
       </c>
-      <c r="N2" s="118" t="s">
+      <c r="N2" s="119" t="s">
         <v>402</v>
       </c>
     </row>
@@ -61442,11 +61356,11 @@
       <c r="G3" s="35">
         <v>10</v>
       </c>
-      <c r="H3" s="119"/>
-      <c r="I3" s="120" t="s">
+      <c r="H3" s="120"/>
+      <c r="I3" s="121" t="s">
         <v>1457</v>
       </c>
-      <c r="J3" s="120" t="s">
+      <c r="J3" s="121" t="s">
         <v>1458</v>
       </c>
       <c r="K3" s="35"/>
@@ -61476,17 +61390,17 @@
       <c r="G4" s="35">
         <v>100</v>
       </c>
-      <c r="H4" s="119">
+      <c r="H4" s="120">
         <v>5</v>
       </c>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
       <c r="K4" s="35" t="s">
         <v>1463</v>
       </c>
-      <c r="L4" s="121"/>
+      <c r="L4" s="122"/>
       <c r="M4" s="35"/>
-      <c r="N4" s="122"/>
+      <c r="N4" s="123"/>
     </row>
     <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="35"/>
@@ -61496,9 +61410,9 @@
       <c r="E5" s="35"/>
       <c r="F5" s="35"/>
       <c r="G5" s="35"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="121"/>
+      <c r="J5" s="121"/>
       <c r="K5" s="35" t="s">
         <v>1469</v>
       </c>
@@ -61508,7 +61422,7 @@
       <c r="M5" s="35" t="s">
         <v>1465</v>
       </c>
-      <c r="N5" s="122"/>
+      <c r="N5" s="123"/>
     </row>
     <row r="6" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="35"/>
@@ -61518,9 +61432,9 @@
       <c r="E6" s="35"/>
       <c r="F6" s="35"/>
       <c r="G6" s="35"/>
-      <c r="H6" s="119"/>
-      <c r="I6" s="120"/>
-      <c r="J6" s="120"/>
+      <c r="H6" s="120"/>
+      <c r="I6" s="121"/>
+      <c r="J6" s="121"/>
       <c r="K6" s="35" t="s">
         <v>1466</v>
       </c>
@@ -61528,7 +61442,7 @@
         <v>1467</v>
       </c>
       <c r="M6" s="35"/>
-      <c r="N6" s="122"/>
+      <c r="N6" s="123"/>
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="35" t="s">
@@ -61540,13 +61454,13 @@
       <c r="E7" s="35"/>
       <c r="F7" s="35"/>
       <c r="G7" s="35"/>
-      <c r="H7" s="119"/>
-      <c r="I7" s="120"/>
-      <c r="J7" s="120"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="121"/>
+      <c r="J7" s="121"/>
       <c r="K7" s="35"/>
       <c r="L7" s="35"/>
       <c r="M7" s="35"/>
-      <c r="N7" s="122"/>
+      <c r="N7" s="123"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -61578,17 +61492,5 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{02290C8B-B188-2048-8777-E965DBFF9BA3}">
-          <x14:formula1>
-            <xm:f>drop_down_rule_set!$L$2:$L$44</xm:f>
-          </x14:formula1>
-          <xm:sqref>A3:A1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
--- a/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E567C0B5-D4CE-2846-83B9-1B15A1900F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C32D143-0D08-2342-8320-9E6F7AC263A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4540" yWindow="2600" windowWidth="30240" windowHeight="17400" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3960" yWindow="2600" windowWidth="30240" windowHeight="17400" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
@@ -779,7 +779,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3434" uniqueCount="1761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3435" uniqueCount="1762">
   <si>
     <t>Region</t>
   </si>
@@ -14124,6 +14124,9 @@
       <t xml:space="preserve">
 Updated Instances sheet, Exa-Infra sheet</t>
     </r>
+  </si>
+  <si>
+    <t>Plugin OS Management Service Agent</t>
   </si>
 </sst>
 </file>
@@ -31314,7 +31317,7 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:AJ8"/>
+  <dimension ref="A1:AK8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
@@ -31345,10 +31348,11 @@
     <col min="26" max="26" width="17.6640625" hidden="1" customWidth="1"/>
     <col min="27" max="27" width="16.6640625" hidden="1" customWidth="1"/>
     <col min="28" max="28" width="14.1640625" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="6.1640625" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="9.5" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="6.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="311" customHeight="1">
+    <row r="1" spans="1:37" ht="311" customHeight="1">
       <c r="A1" s="152" t="s">
         <v>1678</v>
       </c>
@@ -31388,9 +31392,10 @@
       <c r="AG1" s="139"/>
       <c r="AH1" s="139"/>
       <c r="AI1" s="139"/>
-      <c r="AJ1" s="140"/>
-    </row>
-    <row r="2" spans="1:36" s="43" customFormat="1" ht="83.25" customHeight="1">
+      <c r="AJ1" s="139"/>
+      <c r="AK1" s="140"/>
+    </row>
+    <row r="2" spans="1:37" s="43" customFormat="1" ht="83.25" customHeight="1">
       <c r="A2" s="30" t="s">
         <v>0</v>
       </c>
@@ -31476,31 +31481,34 @@
         <v>1757</v>
       </c>
       <c r="AC2" s="31" t="s">
+        <v>1761</v>
+      </c>
+      <c r="AD2" s="31" t="s">
         <v>1758</v>
       </c>
-      <c r="AD2" s="30" t="s">
+      <c r="AE2" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="AE2" s="30" t="s">
+      <c r="AF2" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="AF2" s="31" t="s">
+      <c r="AG2" s="31" t="s">
         <v>413</v>
       </c>
-      <c r="AG2" s="30" t="s">
+      <c r="AH2" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="AH2" s="31" t="s">
+      <c r="AI2" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="AI2" s="31" t="s">
+      <c r="AJ2" s="31" t="s">
         <v>960</v>
       </c>
-      <c r="AJ2" s="30" t="s">
+      <c r="AK2" s="30" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="64">
+    <row r="3" spans="1:37" ht="64">
       <c r="A3" s="36" t="s">
         <v>311</v>
       </c>
@@ -31552,19 +31560,20 @@
       <c r="AA3" s="36"/>
       <c r="AB3" s="36"/>
       <c r="AC3" s="36"/>
-      <c r="AD3" s="36" t="s">
+      <c r="AD3" s="36"/>
+      <c r="AE3" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="AE3" s="36" t="s">
+      <c r="AF3" s="36" t="s">
         <v>537</v>
       </c>
-      <c r="AF3" s="36"/>
       <c r="AG3" s="36"/>
       <c r="AH3" s="36"/>
       <c r="AI3" s="36"/>
       <c r="AJ3" s="36"/>
-    </row>
-    <row r="4" spans="1:36">
+      <c r="AK3" s="36"/>
+    </row>
+    <row r="4" spans="1:37">
       <c r="A4" s="8" t="s">
         <v>4</v>
       </c>
@@ -31589,15 +31598,15 @@
       <c r="T4" s="8"/>
       <c r="U4" s="8"/>
       <c r="V4" s="36"/>
-      <c r="AD4" s="8"/>
-      <c r="AE4" s="36"/>
+      <c r="AE4" s="8"/>
       <c r="AF4" s="36"/>
-      <c r="AG4" s="8"/>
+      <c r="AG4" s="36"/>
       <c r="AH4" s="8"/>
       <c r="AI4" s="8"/>
-      <c r="AJ4" s="36"/>
-    </row>
-    <row r="5" spans="1:36" ht="128">
+      <c r="AJ4" s="8"/>
+      <c r="AK4" s="36"/>
+    </row>
+    <row r="5" spans="1:37" ht="128">
       <c r="A5" s="52" t="s">
         <v>5</v>
       </c>
@@ -31649,27 +31658,28 @@
       <c r="AA5" s="52"/>
       <c r="AB5" s="52"/>
       <c r="AC5" s="52"/>
-      <c r="AD5" s="52" t="s">
+      <c r="AD5" s="52"/>
+      <c r="AE5" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="AE5" s="52" t="s">
+      <c r="AF5" s="52" t="s">
         <v>414</v>
       </c>
-      <c r="AF5" s="52" t="s">
+      <c r="AG5" s="52" t="s">
         <v>345</v>
       </c>
-      <c r="AG5" s="52"/>
-      <c r="AH5" s="52" t="s">
+      <c r="AH5" s="52"/>
+      <c r="AI5" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="AI5" s="53" t="s">
+      <c r="AJ5" s="53" t="s">
         <v>1084</v>
       </c>
-      <c r="AJ5" s="53" t="s">
+      <c r="AK5" s="53" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="96">
+    <row r="6" spans="1:37" ht="96">
       <c r="A6" s="52" t="s">
         <v>5</v>
       </c>
@@ -31721,23 +31731,24 @@
       <c r="AA6" s="52"/>
       <c r="AB6" s="52"/>
       <c r="AC6" s="52"/>
-      <c r="AD6" s="52" t="s">
+      <c r="AD6" s="52"/>
+      <c r="AE6" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="AE6" s="52" t="s">
+      <c r="AF6" s="52" t="s">
         <v>369</v>
       </c>
-      <c r="AF6" s="52"/>
-      <c r="AG6" s="52" t="s">
+      <c r="AG6" s="52"/>
+      <c r="AH6" s="52" t="s">
         <v>367</v>
       </c>
-      <c r="AH6" s="52"/>
-      <c r="AI6" s="53" t="s">
+      <c r="AI6" s="52"/>
+      <c r="AJ6" s="53" t="s">
         <v>1085</v>
       </c>
-      <c r="AJ6" s="52"/>
-    </row>
-    <row r="7" spans="1:36" ht="96">
+      <c r="AK6" s="52"/>
+    </row>
+    <row r="7" spans="1:37" ht="96">
       <c r="A7" s="52" t="s">
         <v>5</v>
       </c>
@@ -31785,21 +31796,22 @@
       <c r="AA7" s="52"/>
       <c r="AB7" s="52"/>
       <c r="AC7" s="52"/>
-      <c r="AD7" s="52" t="s">
+      <c r="AD7" s="52"/>
+      <c r="AE7" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="AE7" s="52" t="s">
+      <c r="AF7" s="52" t="s">
         <v>369</v>
       </c>
-      <c r="AF7" s="52"/>
-      <c r="AG7" s="52" t="s">
+      <c r="AG7" s="52"/>
+      <c r="AH7" s="52" t="s">
         <v>368</v>
       </c>
-      <c r="AH7" s="52"/>
       <c r="AI7" s="52"/>
       <c r="AJ7" s="52"/>
-    </row>
-    <row r="8" spans="1:36" ht="96">
+      <c r="AK7" s="52"/>
+    </row>
+    <row r="8" spans="1:37" ht="96">
       <c r="A8" s="52" t="s">
         <v>5</v>
       </c>
@@ -31847,27 +31859,28 @@
       <c r="AA8" s="52"/>
       <c r="AB8" s="52"/>
       <c r="AC8" s="52"/>
-      <c r="AD8" s="52" t="s">
+      <c r="AD8" s="52"/>
+      <c r="AE8" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="AE8" s="52" t="s">
+      <c r="AF8" s="52" t="s">
         <v>369</v>
       </c>
-      <c r="AF8" s="52"/>
-      <c r="AG8" s="52" t="s">
+      <c r="AG8" s="52"/>
+      <c r="AH8" s="52" t="s">
         <v>368</v>
       </c>
-      <c r="AH8" s="52"/>
       <c r="AI8" s="52"/>
       <c r="AJ8" s="52"/>
+      <c r="AK8" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="I1:AJ1"/>
+    <mergeCell ref="I1:AK1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="E1:XFD2 A1:C2 AD9:AJ1048576 H3:P1048576 D1:D1048576 AK3:XFD1048576 S3:AC1048576 AD3:AD8 AG3:AJ8" xr:uid="{B727580F-A9BA-874F-B6B3-796C3608F9F2}"/>
+    <dataValidation allowBlank="1" sqref="E1:XFD2 A1:C2 AE9:AK1048576 H3:P1048576 D1:D1048576 AL3:XFD1048576 S3:AD1048576 AE3:AE8 AH3:AK8" xr:uid="{B727580F-A9BA-874F-B6B3-796C3608F9F2}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -31882,7 +31895,7 @@
           <x14:formula1>
             <xm:f>drop_down_rule_comp!$B$2:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>R3:R1048576 AF3:AF8</xm:sqref>
+          <xm:sqref>R3:R1048576 AG3:AG8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{30FA0D2E-D10A-A343-878C-E48A2407AF2B}">
           <x14:formula1>
@@ -31906,7 +31919,7 @@
           <x14:formula1>
             <xm:f>drop_down_rule_set!$X$2:$X$4</xm:f>
           </x14:formula1>
-          <xm:sqref>Q3:Q1048576 AE3:AE8</xm:sqref>
+          <xm:sqref>Q3:Q1048576 AF3:AF8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{FA9E97A5-BF62-FC44-A415-693980FFBD5A}">
           <x14:formula1>

--- a/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C32D143-0D08-2342-8320-9E6F7AC263A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A2BACB-E41A-6943-8CF6-78868B8DCB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2600" windowWidth="30240" windowHeight="17400" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -779,7 +779,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3435" uniqueCount="1762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3434" uniqueCount="1761">
   <si>
     <t>Region</t>
   </si>
@@ -13587,9 +13587,6 @@
   </si>
   <si>
     <t>allow group Auditors to read capture-filters in tenancy</t>
-  </si>
-  <si>
-    <t>Oracle-Tags.CreatedOn=2025-09-25T11:07:41.577Z;Oracle-Tags.CreatedBy=oracleidentitycloudservice/ulaganathan.namachivayam@oracle.com</t>
   </si>
   <si>
     <t>AccessGovernanceAdmins-Policy</t>
@@ -20315,7 +20312,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1">
       <c r="A2" s="79" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
     </row>
   </sheetData>
@@ -20351,7 +20348,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="247" customHeight="1">
       <c r="A1" s="141" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B1" s="142"/>
       <c r="C1" s="142"/>
@@ -20384,7 +20381,7 @@
         <v>595</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="F2" s="19" t="s">
         <v>1710</v>
@@ -31364,7 +31361,7 @@
       <c r="G1" s="153"/>
       <c r="H1" s="154"/>
       <c r="I1" s="137" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="J1" s="139"/>
       <c r="K1" s="139"/>
@@ -31439,52 +31436,52 @@
         <v>610</v>
       </c>
       <c r="O2" s="31" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="P2" s="31" t="s">
         <v>1093</v>
       </c>
       <c r="Q2" s="31" t="s">
+        <v>1745</v>
+      </c>
+      <c r="R2" s="31" t="s">
         <v>1746</v>
       </c>
-      <c r="R2" s="31" t="s">
+      <c r="S2" s="31" t="s">
         <v>1747</v>
       </c>
-      <c r="S2" s="31" t="s">
+      <c r="T2" s="31" t="s">
         <v>1748</v>
       </c>
-      <c r="T2" s="31" t="s">
+      <c r="U2" s="31" t="s">
         <v>1749</v>
       </c>
-      <c r="U2" s="31" t="s">
+      <c r="V2" s="31" t="s">
         <v>1750</v>
       </c>
-      <c r="V2" s="31" t="s">
+      <c r="W2" s="31" t="s">
         <v>1751</v>
       </c>
-      <c r="W2" s="31" t="s">
+      <c r="X2" s="31" t="s">
         <v>1752</v>
       </c>
-      <c r="X2" s="31" t="s">
+      <c r="Y2" s="31" t="s">
         <v>1753</v>
       </c>
-      <c r="Y2" s="31" t="s">
+      <c r="Z2" s="31" t="s">
         <v>1754</v>
       </c>
-      <c r="Z2" s="31" t="s">
+      <c r="AA2" s="31" t="s">
         <v>1755</v>
       </c>
-      <c r="AA2" s="31" t="s">
+      <c r="AB2" s="31" t="s">
         <v>1756</v>
       </c>
-      <c r="AB2" s="31" t="s">
+      <c r="AC2" s="31" t="s">
+        <v>1760</v>
+      </c>
+      <c r="AD2" s="31" t="s">
         <v>1757</v>
-      </c>
-      <c r="AC2" s="31" t="s">
-        <v>1761</v>
-      </c>
-      <c r="AD2" s="31" t="s">
-        <v>1758</v>
       </c>
       <c r="AE2" s="30" t="s">
         <v>91</v>
@@ -66811,7 +66808,7 @@
     <col min="8" max="8" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="43" customFormat="1" ht="131" customHeight="1">
+    <row r="1" spans="1:8" s="43" customFormat="1" ht="131" customHeight="1">
       <c r="A1" s="137" t="s">
         <v>1545</v>
       </c>
@@ -66823,7 +66820,7 @@
       <c r="G1" s="137"/>
       <c r="H1" s="137"/>
     </row>
-    <row r="2" spans="1:9" s="43" customFormat="1">
+    <row r="2" spans="1:8" s="43" customFormat="1">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -66849,7 +66846,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="69.75" customHeight="1">
+    <row r="3" spans="1:8" ht="69.75" customHeight="1">
       <c r="A3" s="35" t="s">
         <v>5</v>
       </c>
@@ -66869,7 +66866,7 @@
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
     </row>
-    <row r="4" spans="1:9" ht="69.75" customHeight="1">
+    <row r="4" spans="1:8" ht="69.75" customHeight="1">
       <c r="A4" s="35"/>
       <c r="B4" s="35"/>
       <c r="C4" s="35"/>
@@ -66881,56 +66878,51 @@
       <c r="G4" s="35"/>
       <c r="H4" s="35"/>
     </row>
-    <row r="5" spans="1:9" ht="80">
+    <row r="5" spans="1:8" ht="48">
       <c r="A5" s="35" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="C5" s="35" t="s">
         <v>377</v>
       </c>
       <c r="D5" s="35" t="s">
+        <v>1738</v>
+      </c>
+      <c r="E5" s="35" t="s">
         <v>1739</v>
-      </c>
-      <c r="E5" s="35" t="s">
-        <v>1740</v>
       </c>
       <c r="F5" s="35"/>
       <c r="G5" s="35"/>
-      <c r="H5" s="35" t="s">
-        <v>1737</v>
-      </c>
-      <c r="I5" s="36"/>
-    </row>
-    <row r="6" spans="1:9" ht="32">
+      <c r="H5" s="35"/>
+    </row>
+    <row r="6" spans="1:8" ht="32">
       <c r="A6" s="35"/>
       <c r="B6" s="35"/>
       <c r="C6" s="35"/>
       <c r="D6" s="35"/>
       <c r="E6" s="35" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="F6" s="35"/>
       <c r="G6" s="35"/>
       <c r="H6" s="35"/>
-      <c r="I6" s="36"/>
-    </row>
-    <row r="7" spans="1:9" ht="32">
+    </row>
+    <row r="7" spans="1:8" ht="32">
       <c r="A7" s="35"/>
       <c r="B7" s="35"/>
       <c r="C7" s="35"/>
       <c r="D7" s="35"/>
       <c r="E7" s="35" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="F7" s="35"/>
       <c r="G7" s="35"/>
       <c r="H7" s="35"/>
-      <c r="I7" s="36"/>
-    </row>
-    <row r="8" spans="1:9" ht="102.75" customHeight="1">
+    </row>
+    <row r="8" spans="1:8" ht="102.75" customHeight="1">
       <c r="A8" s="35" t="s">
         <v>5</v>
       </c>
@@ -66950,7 +66942,7 @@
       <c r="G8" s="35"/>
       <c r="H8" s="35"/>
     </row>
-    <row r="9" spans="1:9" ht="29.25" customHeight="1">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1">
       <c r="A9" s="35"/>
       <c r="B9" s="35"/>
       <c r="C9" s="35"/>
@@ -66962,7 +66954,7 @@
       <c r="G9" s="35"/>
       <c r="H9" s="35"/>
     </row>
-    <row r="10" spans="1:9" ht="29.25" customHeight="1">
+    <row r="10" spans="1:8" ht="29.25" customHeight="1">
       <c r="A10" s="35"/>
       <c r="B10" s="35"/>
       <c r="C10" s="35"/>
@@ -66974,7 +66966,7 @@
       <c r="G10" s="35"/>
       <c r="H10" s="35"/>
     </row>
-    <row r="11" spans="1:9" ht="29.25" customHeight="1">
+    <row r="11" spans="1:8" ht="29.25" customHeight="1">
       <c r="A11" s="35"/>
       <c r="B11" s="35"/>
       <c r="C11" s="35"/>
@@ -66986,7 +66978,7 @@
       <c r="G11" s="35"/>
       <c r="H11" s="35"/>
     </row>
-    <row r="12" spans="1:9" ht="29.25" customHeight="1">
+    <row r="12" spans="1:8" ht="29.25" customHeight="1">
       <c r="A12" s="35"/>
       <c r="B12" s="35"/>
       <c r="C12" s="35"/>
@@ -66998,7 +66990,7 @@
       <c r="G12" s="35"/>
       <c r="H12" s="35"/>
     </row>
-    <row r="13" spans="1:9" ht="29.25" customHeight="1">
+    <row r="13" spans="1:8" ht="29.25" customHeight="1">
       <c r="A13" s="35"/>
       <c r="B13" s="35"/>
       <c r="C13" s="35"/>
@@ -67010,7 +67002,7 @@
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
     </row>
-    <row r="14" spans="1:9" ht="29.25" customHeight="1">
+    <row r="14" spans="1:8" ht="29.25" customHeight="1">
       <c r="A14" s="35"/>
       <c r="B14" s="35"/>
       <c r="C14" s="35"/>
@@ -67022,7 +67014,7 @@
       <c r="G14" s="35"/>
       <c r="H14" s="35"/>
     </row>
-    <row r="15" spans="1:9" ht="29.25" customHeight="1">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1">
       <c r="A15" s="35"/>
       <c r="B15" s="35"/>
       <c r="C15" s="35"/>
@@ -67034,7 +67026,7 @@
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
     </row>
-    <row r="16" spans="1:9" ht="29.25" customHeight="1">
+    <row r="16" spans="1:8" ht="29.25" customHeight="1">
       <c r="A16" s="35"/>
       <c r="B16" s="35"/>
       <c r="C16" s="35"/>

--- a/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A2BACB-E41A-6943-8CF6-78868B8DCB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEDCA8C-9564-5C4F-BB1E-851EDE1D26A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2600" windowWidth="30240" windowHeight="17400" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -779,7 +779,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3434" uniqueCount="1761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3434" uniqueCount="1760">
   <si>
     <t>Region</t>
   </si>
@@ -4481,21 +4481,6 @@
     <t>Sanjose</t>
   </si>
   <si>
-    <t>gov-ashburn</t>
-  </si>
-  <si>
-    <t>gov-chicago</t>
-  </si>
-  <si>
-    <t>gov-phoenix</t>
-  </si>
-  <si>
-    <t>gov-london</t>
-  </si>
-  <si>
-    <t>gov-cardiff</t>
-  </si>
-  <si>
     <t>Abudhabi</t>
   </si>
   <si>
@@ -14124,6 +14109,18 @@
   </si>
   <si>
     <t>Plugin OS Management Service Agent</t>
+  </si>
+  <si>
+    <t>ashburn</t>
+  </si>
+  <si>
+    <t>chicago</t>
+  </si>
+  <si>
+    <t>london</t>
+  </si>
+  <si>
+    <t>cardiff</t>
   </si>
 </sst>
 </file>
@@ -20312,7 +20309,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1">
       <c r="A2" s="79" t="s">
-        <v>1759</v>
+        <v>1754</v>
       </c>
     </row>
   </sheetData>
@@ -20348,7 +20345,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="247" customHeight="1">
       <c r="A1" s="141" t="s">
-        <v>1742</v>
+        <v>1737</v>
       </c>
       <c r="B1" s="142"/>
       <c r="C1" s="142"/>
@@ -20359,7 +20356,7 @@
       <c r="H1" s="142"/>
       <c r="I1" s="143"/>
       <c r="J1" s="141" t="s">
-        <v>1559</v>
+        <v>1554</v>
       </c>
       <c r="K1" s="142"/>
       <c r="L1" s="142"/>
@@ -20381,13 +20378,13 @@
         <v>595</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>1743</v>
+        <v>1738</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>1710</v>
+        <v>1705</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>1711</v>
+        <v>1706</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>12</v>
@@ -20431,14 +20428,14 @@
         <v>1</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>1713</v>
+        <v>1708</v>
       </c>
       <c r="G3" s="36"/>
       <c r="H3" s="36" t="s">
         <v>437</v>
       </c>
       <c r="I3" s="36" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="J3" s="36" t="s">
         <v>21</v>
@@ -20642,7 +20639,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="222" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1560</v>
+        <v>1555</v>
       </c>
       <c r="B1" s="137"/>
       <c r="C1" s="137"/>
@@ -20650,7 +20647,7 @@
       <c r="E1" s="137"/>
       <c r="F1" s="137"/>
       <c r="G1" s="147" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="H1" s="147"/>
       <c r="I1" s="147"/>
@@ -20669,7 +20666,7 @@
         <v>473</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
       <c r="F2" s="30" t="s">
         <v>474</v>
@@ -20796,13 +20793,13 @@
         <v>437</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="G8" s="36"/>
       <c r="H8" s="36"/>
@@ -20816,16 +20813,16 @@
         <v>331</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>1071</v>
+        <v>1066</v>
       </c>
       <c r="D9" s="35" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E9" s="36" t="s">
         <v>1072</v>
       </c>
-      <c r="E9" s="36" t="s">
-        <v>1077</v>
-      </c>
       <c r="F9" s="35" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="G9" s="36"/>
       <c r="H9" s="36"/>
@@ -20955,7 +20952,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="106" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="B1" s="137"/>
       <c r="C1" s="137"/>
@@ -21255,7 +21252,7 @@
   <sheetData>
     <row r="1" spans="1:21" ht="192.75" customHeight="1">
       <c r="A1" s="141" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="B1" s="142"/>
       <c r="C1" s="142"/>
@@ -21267,7 +21264,7 @@
       <c r="I1" s="142"/>
       <c r="J1" s="143"/>
       <c r="K1" s="148" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="L1" s="148"/>
       <c r="M1" s="148"/>
@@ -21294,13 +21291,13 @@
         <v>307</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1712</v>
+        <v>1707</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>39</v>
@@ -21365,7 +21362,7 @@
         <v>599</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>1714</v>
+        <v>1709</v>
       </c>
       <c r="H3" s="33" t="s">
         <v>50</v>
@@ -21997,7 +21994,7 @@
         <v>704</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
       <c r="E14" s="36" t="s">
         <v>507</v>
@@ -22084,13 +22081,13 @@
         <v>439</v>
       </c>
       <c r="D16" s="52" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="E16" s="52" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="F16" s="52" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="G16" s="52"/>
       <c r="H16" s="52" t="s">
@@ -22101,7 +22098,7 @@
       </c>
       <c r="J16" s="52"/>
       <c r="K16" s="52" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="L16" s="52"/>
       <c r="M16" s="53" t="s">
@@ -22141,13 +22138,13 @@
         <v>439</v>
       </c>
       <c r="D17" s="52" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="E17" s="52" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="F17" s="52" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="G17" s="52"/>
       <c r="H17" s="52" t="s">
@@ -22158,7 +22155,7 @@
       </c>
       <c r="J17" s="52"/>
       <c r="K17" s="52" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="L17" s="52"/>
       <c r="M17" s="53"/>
@@ -27418,7 +27415,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="63" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="B1" s="137"/>
       <c r="C1" s="137"/>
@@ -27544,7 +27541,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="63" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="B1" s="137"/>
       <c r="C1" s="137"/>
@@ -27650,7 +27647,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="60" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="B1" s="137"/>
       <c r="C1" s="137"/>
@@ -27804,7 +27801,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="118.75" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="B1" s="137"/>
       <c r="C1" s="137"/>
@@ -30311,7 +30308,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="179.25" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
       <c r="B1" s="149"/>
       <c r="C1" s="149"/>
@@ -30330,22 +30327,22 @@
         <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>978</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>979</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>980</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>981</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2" s="30" t="s">
         <v>983</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>984</v>
-      </c>
-      <c r="E2" s="30" t="s">
-        <v>985</v>
-      </c>
-      <c r="F2" s="30" t="s">
-        <v>986</v>
-      </c>
-      <c r="G2" s="30" t="s">
-        <v>987</v>
-      </c>
-      <c r="H2" s="30" t="s">
-        <v>988</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>395</v>
@@ -30372,19 +30369,19 @@
         <v>331</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="H4" s="35">
         <v>3600</v>
@@ -30399,19 +30396,19 @@
         <v>331</v>
       </c>
       <c r="C5" s="35" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E5" s="35" t="s">
         <v>1034</v>
       </c>
-      <c r="D5" s="35" t="s">
-        <v>1036</v>
-      </c>
-      <c r="E5" s="35" t="s">
-        <v>1039</v>
-      </c>
       <c r="F5" s="35" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="H5" s="35">
         <v>300</v>
@@ -30426,19 +30423,19 @@
         <v>331</v>
       </c>
       <c r="C6" s="35" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E6" s="35" t="s">
         <v>1035</v>
       </c>
-      <c r="D6" s="35" t="s">
-        <v>1037</v>
-      </c>
-      <c r="E6" s="35" t="s">
-        <v>1040</v>
-      </c>
       <c r="F6" s="35" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="H6" s="35">
         <v>300</v>
@@ -30708,7 +30705,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="43" customFormat="1" ht="108" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="B1" s="137"/>
       <c r="C1" s="137"/>
@@ -30740,7 +30737,7 @@
         <v>417</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="D3" s="35" t="s">
         <v>377</v>
@@ -30755,7 +30752,7 @@
         <v>418</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1297</v>
+        <v>1292</v>
       </c>
       <c r="D4" s="35" t="s">
         <v>377</v>
@@ -30770,7 +30767,7 @@
         <v>331</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
       <c r="D5" s="35" t="s">
         <v>377</v>
@@ -30779,13 +30776,13 @@
     </row>
     <row r="6" spans="1:5" ht="28.5" customHeight="1">
       <c r="A6" s="35" t="s">
-        <v>1691</v>
+        <v>1686</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="D6" s="35" t="s">
         <v>377</v>
@@ -30970,7 +30967,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="191.25" customHeight="1">
       <c r="A1" s="150" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="B1" s="151"/>
       <c r="C1" s="151"/>
@@ -30997,22 +30994,22 @@
         <v>307</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="G2" s="30" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="H2" s="30" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="I2" s="30" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="J2" s="30" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="K2" s="30" t="s">
         <v>395</v>
@@ -31047,20 +31044,20 @@
         <v>438</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="G4" s="36" t="s">
         <v>441</v>
       </c>
       <c r="H4" s="33" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="I4" s="32"/>
       <c r="J4" s="33" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="K4" s="33"/>
     </row>
@@ -31078,16 +31075,16 @@
         <v>438</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="G5" s="36" t="s">
         <v>441</v>
       </c>
       <c r="H5" s="33" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="I5" s="33"/>
       <c r="J5" s="33"/>
@@ -31156,7 +31153,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="82" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="B1" s="137"/>
       <c r="C1" s="137"/>
@@ -31351,7 +31348,7 @@
   <sheetData>
     <row r="1" spans="1:37" ht="311" customHeight="1">
       <c r="A1" s="152" t="s">
-        <v>1678</v>
+        <v>1673</v>
       </c>
       <c r="B1" s="153"/>
       <c r="C1" s="153"/>
@@ -31361,7 +31358,7 @@
       <c r="G1" s="153"/>
       <c r="H1" s="154"/>
       <c r="I1" s="137" t="s">
-        <v>1758</v>
+        <v>1753</v>
       </c>
       <c r="J1" s="139"/>
       <c r="K1" s="139"/>
@@ -31409,7 +31406,7 @@
         <v>82</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="G2" s="30" t="s">
         <v>88</v>
@@ -31436,52 +31433,52 @@
         <v>610</v>
       </c>
       <c r="O2" s="31" t="s">
+        <v>1739</v>
+      </c>
+      <c r="P2" s="31" t="s">
+        <v>1088</v>
+      </c>
+      <c r="Q2" s="31" t="s">
+        <v>1740</v>
+      </c>
+      <c r="R2" s="31" t="s">
+        <v>1741</v>
+      </c>
+      <c r="S2" s="31" t="s">
+        <v>1742</v>
+      </c>
+      <c r="T2" s="31" t="s">
+        <v>1743</v>
+      </c>
+      <c r="U2" s="31" t="s">
         <v>1744</v>
       </c>
-      <c r="P2" s="31" t="s">
-        <v>1093</v>
-      </c>
-      <c r="Q2" s="31" t="s">
+      <c r="V2" s="31" t="s">
         <v>1745</v>
       </c>
-      <c r="R2" s="31" t="s">
+      <c r="W2" s="31" t="s">
         <v>1746</v>
       </c>
-      <c r="S2" s="31" t="s">
+      <c r="X2" s="31" t="s">
         <v>1747</v>
       </c>
-      <c r="T2" s="31" t="s">
+      <c r="Y2" s="31" t="s">
         <v>1748</v>
       </c>
-      <c r="U2" s="31" t="s">
+      <c r="Z2" s="31" t="s">
         <v>1749</v>
       </c>
-      <c r="V2" s="31" t="s">
+      <c r="AA2" s="31" t="s">
         <v>1750</v>
       </c>
-      <c r="W2" s="31" t="s">
+      <c r="AB2" s="31" t="s">
         <v>1751</v>
       </c>
-      <c r="X2" s="31" t="s">
+      <c r="AC2" s="31" t="s">
+        <v>1755</v>
+      </c>
+      <c r="AD2" s="31" t="s">
         <v>1752</v>
-      </c>
-      <c r="Y2" s="31" t="s">
-        <v>1753</v>
-      </c>
-      <c r="Z2" s="31" t="s">
-        <v>1754</v>
-      </c>
-      <c r="AA2" s="31" t="s">
-        <v>1755</v>
-      </c>
-      <c r="AB2" s="31" t="s">
-        <v>1756</v>
-      </c>
-      <c r="AC2" s="31" t="s">
-        <v>1760</v>
-      </c>
-      <c r="AD2" s="31" t="s">
-        <v>1757</v>
       </c>
       <c r="AE2" s="30" t="s">
         <v>91</v>
@@ -31499,7 +31496,7 @@
         <v>94</v>
       </c>
       <c r="AJ2" s="31" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="AK2" s="30" t="s">
         <v>395</v>
@@ -31522,7 +31519,7 @@
         <v>330</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="G3" s="36" t="b">
         <v>0</v>
@@ -31620,7 +31617,7 @@
         <v>99</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="G5" s="52" t="b">
         <v>0</v>
@@ -31639,7 +31636,7 @@
       </c>
       <c r="N5" s="52"/>
       <c r="O5" s="52" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="P5" s="52"/>
       <c r="Q5" s="52"/>
@@ -31670,7 +31667,7 @@
         <v>87</v>
       </c>
       <c r="AJ5" s="53" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="AK5" s="53" t="s">
         <v>403</v>
@@ -31693,7 +31690,7 @@
         <v>330</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>1238</v>
+        <v>1233</v>
       </c>
       <c r="G6" s="52" t="b">
         <v>0</v>
@@ -31741,7 +31738,7 @@
       </c>
       <c r="AI6" s="52"/>
       <c r="AJ6" s="53" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="AK6" s="52"/>
     </row>
@@ -31762,7 +31759,7 @@
         <v>99</v>
       </c>
       <c r="F7" s="53" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="G7" s="52" t="b">
         <v>0</v>
@@ -31825,7 +31822,7 @@
         <v>330</v>
       </c>
       <c r="F8" s="53" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
       <c r="G8" s="52" t="b">
         <v>0</v>
@@ -31971,7 +31968,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="201" customHeight="1">
       <c r="A1" s="141" t="s">
-        <v>1557</v>
+        <v>1552</v>
       </c>
       <c r="B1" s="142"/>
       <c r="C1" s="142"/>
@@ -32002,7 +31999,7 @@
         <v>101</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="E2" s="30" t="s">
         <v>102</v>
@@ -32023,16 +32020,16 @@
         <v>404</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
       <c r="L2" s="31" t="s">
+        <v>1158</v>
+      </c>
+      <c r="M2" s="31" t="s">
+        <v>1159</v>
+      </c>
+      <c r="N2" s="31" t="s">
         <v>1163</v>
-      </c>
-      <c r="M2" s="31" t="s">
-        <v>1164</v>
-      </c>
-      <c r="N2" s="31" t="s">
-        <v>1168</v>
       </c>
       <c r="O2" s="31" t="s">
         <v>611</v>
@@ -32098,19 +32095,19 @@
         <v>613</v>
       </c>
       <c r="J4" s="124" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="K4" s="124" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
       <c r="L4" s="124">
         <v>100</v>
       </c>
       <c r="M4" s="124" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
       <c r="N4" s="124" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="O4" s="84" t="b">
         <v>1</v>
@@ -32229,7 +32226,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="133" customHeight="1">
       <c r="A1" s="141" t="s">
-        <v>1237</v>
+        <v>1232</v>
       </c>
       <c r="B1" s="142"/>
       <c r="C1" s="142"/>
@@ -32243,7 +32240,7 @@
       <c r="K1" s="142"/>
       <c r="L1" s="143"/>
       <c r="M1" s="155" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="N1" s="156"/>
       <c r="O1" s="156"/>
@@ -32269,7 +32266,7 @@
         <v>106</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>107</v>
@@ -32284,13 +32281,13 @@
         <v>109</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="L2" s="31" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>110</v>
@@ -32314,10 +32311,10 @@
         <v>116</v>
       </c>
       <c r="T2" s="31" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="U2" s="31" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="V2" s="10" t="s">
         <v>395</v>
@@ -32365,7 +32362,7 @@
         <v>117</v>
       </c>
       <c r="E4" s="53" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="F4" s="87"/>
       <c r="G4" s="87" t="s">
@@ -32469,7 +32466,7 @@
         <v>117</v>
       </c>
       <c r="E7" s="53" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="F7" s="87"/>
       <c r="G7" s="87"/>
@@ -32507,7 +32504,7 @@
         <v>125</v>
       </c>
       <c r="E8" s="53" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="F8" s="87"/>
       <c r="G8" s="87"/>
@@ -32549,7 +32546,7 @@
         <v>128</v>
       </c>
       <c r="E9" s="53" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="F9" s="87"/>
       <c r="G9" s="87"/>
@@ -32591,7 +32588,7 @@
         <v>130</v>
       </c>
       <c r="E10" s="53" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="F10" s="87"/>
       <c r="G10" s="87"/>
@@ -32626,10 +32623,10 @@
         <v>86</v>
       </c>
       <c r="D11" s="87" t="s">
-        <v>1224</v>
+        <v>1219</v>
       </c>
       <c r="E11" s="53" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="F11" s="87"/>
       <c r="G11" s="87"/>
@@ -32665,7 +32662,7 @@
       <c r="G12" s="87"/>
       <c r="H12" s="52"/>
       <c r="I12" s="87" t="s">
-        <v>1225</v>
+        <v>1220</v>
       </c>
       <c r="J12" s="52"/>
       <c r="K12" s="52"/>
@@ -32775,7 +32772,7 @@
   <sheetData>
     <row r="1" spans="1:35" ht="145" customHeight="1">
       <c r="A1" s="141" t="s">
-        <v>1241</v>
+        <v>1236</v>
       </c>
       <c r="B1" s="142"/>
       <c r="C1" s="142"/>
@@ -32792,7 +32789,7 @@
       <c r="N1" s="142"/>
       <c r="O1" s="143"/>
       <c r="P1" s="152" t="s">
-        <v>1270</v>
+        <v>1265</v>
       </c>
       <c r="Q1" s="153"/>
       <c r="R1" s="153"/>
@@ -32825,7 +32822,7 @@
         <v>769</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="E2" s="31" t="s">
         <v>768</v>
@@ -32837,10 +32834,10 @@
         <v>766</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>1242</v>
+        <v>1237</v>
       </c>
       <c r="I2" s="31" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="J2" s="31" t="s">
         <v>765</v>
@@ -32855,7 +32852,7 @@
         <v>762</v>
       </c>
       <c r="N2" s="31" t="s">
-        <v>1261</v>
+        <v>1256</v>
       </c>
       <c r="O2" s="31" t="s">
         <v>761</v>
@@ -32879,13 +32876,13 @@
         <v>759</v>
       </c>
       <c r="V2" s="31" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
       <c r="W2" s="31" t="s">
         <v>80</v>
       </c>
       <c r="X2" s="31" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="Y2" s="31" t="s">
         <v>758</v>
@@ -32894,7 +32891,7 @@
         <v>757</v>
       </c>
       <c r="AA2" s="31" t="s">
-        <v>1267</v>
+        <v>1262</v>
       </c>
       <c r="AB2" s="31" t="s">
         <v>756</v>
@@ -32912,13 +32909,13 @@
         <v>754</v>
       </c>
       <c r="AG2" s="31" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AH2" s="31" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AI2" s="31" t="s">
         <v>1113</v>
-      </c>
-      <c r="AH2" s="31" t="s">
-        <v>1114</v>
-      </c>
-      <c r="AI2" s="31" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1">
@@ -32971,10 +32968,10 @@
         <v>753</v>
       </c>
       <c r="D4" s="95" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="E4" s="95" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="F4" s="95" t="s">
         <v>752</v>
@@ -32983,10 +32980,10 @@
         <v>1</v>
       </c>
       <c r="H4" s="95" t="s">
-        <v>1268</v>
+        <v>1263</v>
       </c>
       <c r="I4" s="95" t="s">
-        <v>1268</v>
+        <v>1263</v>
       </c>
       <c r="J4" s="53" t="b">
         <v>0</v>
@@ -33001,10 +32998,10 @@
         <v>670</v>
       </c>
       <c r="N4" s="95" t="s">
-        <v>1262</v>
+        <v>1257</v>
       </c>
       <c r="O4" s="95" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="P4" s="95">
         <v>1</v>
@@ -33025,13 +33022,13 @@
         <v>669</v>
       </c>
       <c r="V4" s="95" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
       <c r="W4" s="95" t="s">
         <v>95</v>
       </c>
       <c r="X4" s="95" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
       <c r="Y4" s="95"/>
       <c r="Z4" s="95"/>
@@ -33066,10 +33063,10 @@
       <c r="L5" s="53"/>
       <c r="M5" s="53"/>
       <c r="N5" s="53" t="s">
-        <v>1263</v>
+        <v>1258</v>
       </c>
       <c r="O5" s="95" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="P5" s="53">
         <v>2</v>
@@ -33088,13 +33085,13 @@
       </c>
       <c r="U5" s="53"/>
       <c r="V5" s="95" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
       <c r="W5" s="53" t="s">
         <v>86</v>
       </c>
       <c r="X5" s="95" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="Y5" s="53"/>
       <c r="Z5" s="53"/>
@@ -33123,10 +33120,10 @@
         <v>745</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
       <c r="E6" s="53" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="F6" s="53" t="s">
         <v>744</v>
@@ -33135,10 +33132,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="95" t="s">
-        <v>1268</v>
+        <v>1263</v>
       </c>
       <c r="I6" s="95" t="s">
-        <v>1268</v>
+        <v>1263</v>
       </c>
       <c r="J6" s="53" t="b">
         <v>0</v>
@@ -33147,10 +33144,10 @@
       <c r="L6" s="53"/>
       <c r="M6" s="53"/>
       <c r="N6" s="53" t="s">
-        <v>1264</v>
+        <v>1259</v>
       </c>
       <c r="O6" s="95" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="P6" s="53">
         <v>1</v>
@@ -33171,20 +33168,20 @@
         <v>669</v>
       </c>
       <c r="V6" s="95" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
       <c r="W6" s="53" t="s">
         <v>95</v>
       </c>
       <c r="X6" s="95" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="Y6" s="53">
         <v>2</v>
       </c>
       <c r="Z6" s="53"/>
       <c r="AA6" s="95" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
       <c r="AB6" s="97"/>
       <c r="AC6" s="53" t="s">
@@ -33196,7 +33193,7 @@
       <c r="AG6" s="52"/>
       <c r="AH6" s="52"/>
       <c r="AI6" s="53" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
     </row>
   </sheetData>
@@ -33290,7 +33287,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="122.5" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="B1" s="137"/>
       <c r="C1" s="137"/>
@@ -33331,7 +33328,7 @@
         <v>503</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="H2" s="19" t="s">
         <v>133</v>
@@ -33409,7 +33406,7 @@
       <c r="E4" s="52"/>
       <c r="F4" s="52"/>
       <c r="G4" s="53" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="H4" s="52" t="b">
         <v>1</v>
@@ -33483,7 +33480,7 @@
       <c r="E6" s="52"/>
       <c r="F6" s="52"/>
       <c r="G6" s="53" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="H6" s="52" t="b">
         <v>0</v>
@@ -33590,7 +33587,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="118" customHeight="1">
       <c r="A1" s="141" t="s">
-        <v>1259</v>
+        <v>1254</v>
       </c>
       <c r="B1" s="142"/>
       <c r="C1" s="142"/>
@@ -33634,7 +33631,7 @@
         <v>150</v>
       </c>
       <c r="G2" s="37" t="s">
-        <v>1252</v>
+        <v>1247</v>
       </c>
       <c r="H2" s="37" t="s">
         <v>151</v>
@@ -33724,7 +33721,7 @@
         <v>161</v>
       </c>
       <c r="G4" s="53" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="H4" s="52" t="s">
         <v>162</v>
@@ -33784,7 +33781,7 @@
         <v>167</v>
       </c>
       <c r="G5" s="52" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
       <c r="H5" s="52" t="s">
         <v>162</v>
@@ -33832,7 +33829,7 @@
         <v>170</v>
       </c>
       <c r="G6" s="52" t="s">
-        <v>1255</v>
+        <v>1250</v>
       </c>
       <c r="H6" s="52" t="s">
         <v>162</v>
@@ -34932,7 +34929,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="43" customFormat="1" ht="173" customHeight="1">
       <c r="A1" s="138" t="s">
-        <v>1275</v>
+        <v>1270</v>
       </c>
       <c r="B1" s="139"/>
       <c r="C1" s="139"/>
@@ -34952,10 +34949,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="110" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
       <c r="E2" s="110" t="s">
-        <v>1271</v>
+        <v>1266</v>
       </c>
       <c r="F2" s="130" t="s">
         <v>399</v>
@@ -34972,7 +34969,7 @@
         <v>419</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="D3" s="35"/>
       <c r="E3" s="36"/>
@@ -34987,7 +34984,7 @@
         <v>645</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="D4" s="35"/>
       <c r="E4" s="36"/>
@@ -35017,7 +35014,7 @@
         <v>422</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
       <c r="D6" s="35"/>
       <c r="E6" s="36"/>
@@ -35032,7 +35029,7 @@
         <v>423</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="D7" s="35"/>
       <c r="E7" s="23"/>
@@ -35047,7 +35044,7 @@
         <v>424</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="D8" s="23"/>
       <c r="E8" s="35"/>
@@ -35062,7 +35059,7 @@
         <v>425</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="D9" s="35"/>
       <c r="E9" s="35"/>
@@ -35092,7 +35089,7 @@
         <v>479</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
@@ -35119,10 +35116,10 @@
         <v>5</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>1715</v>
+        <v>1710</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>1716</v>
+        <v>1711</v>
       </c>
       <c r="D13" s="35"/>
       <c r="E13" s="36"/>
@@ -35148,7 +35145,7 @@
         <v>651</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
       <c r="D15" s="36"/>
       <c r="E15" s="8"/>
@@ -35165,7 +35162,7 @@
         <v>653</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
       <c r="D16" s="36"/>
       <c r="E16" s="36"/>
@@ -35182,7 +35179,7 @@
         <v>655</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="D17" s="36"/>
       <c r="E17" s="36"/>
@@ -35410,7 +35407,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="64" customHeight="1">
       <c r="A1" s="148" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="B1" s="149"/>
       <c r="C1" s="149"/>
@@ -35424,10 +35421,10 @@
         <v>132</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16">
@@ -35446,10 +35443,10 @@
         <v>375</v>
       </c>
       <c r="C4" s="53" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="D4" s="53" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="93.5" customHeight="1">
@@ -35460,10 +35457,10 @@
         <v>375</v>
       </c>
       <c r="C5" s="53" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="D5" s="53" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
     </row>
   </sheetData>
@@ -35544,7 +35541,7 @@
         <v>622</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="E2" s="31" t="s">
         <v>623</v>
@@ -35606,7 +35603,7 @@
         <v>630</v>
       </c>
       <c r="D4" s="53" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="E4" s="53" t="b">
         <v>0</v>
@@ -35644,7 +35641,7 @@
         <v>626</v>
       </c>
       <c r="D5" s="53" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
       <c r="E5" s="53" t="b">
         <v>1</v>
@@ -36110,10 +36107,10 @@
         <v>634</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
       <c r="I2" s="31" t="s">
         <v>153</v>
@@ -36125,7 +36122,7 @@
         <v>412</v>
       </c>
       <c r="L2" s="31" t="s">
-        <v>1252</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="29.25" customHeight="1">
@@ -36177,7 +36174,7 @@
         <v>10000</v>
       </c>
       <c r="L4" s="53" t="s">
-        <v>1256</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="32">
@@ -36211,7 +36208,7 @@
         <v>10000</v>
       </c>
       <c r="L5" s="53" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="16">
@@ -36228,10 +36225,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="53" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="H6" s="53" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="I6" s="53">
         <v>53</v>
@@ -36241,7 +36238,7 @@
         <v>20000</v>
       </c>
       <c r="L6" s="53" t="s">
-        <v>1258</v>
+        <v>1253</v>
       </c>
     </row>
   </sheetData>
@@ -36304,7 +36301,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="216" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1707</v>
+        <v>1702</v>
       </c>
       <c r="B1" s="137"/>
       <c r="C1" s="137"/>
@@ -36337,10 +36334,10 @@
         <v>732</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>1693</v>
+        <v>1688</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="F2" s="19" t="s">
         <v>733</v>
@@ -36355,16 +36352,16 @@
         <v>309</v>
       </c>
       <c r="J2" s="19" t="s">
+        <v>1689</v>
+      </c>
+      <c r="K2" s="19" t="s">
         <v>1694</v>
       </c>
-      <c r="K2" s="19" t="s">
-        <v>1699</v>
-      </c>
       <c r="L2" s="19" t="s">
-        <v>1695</v>
+        <v>1690</v>
       </c>
       <c r="M2" s="19" t="s">
-        <v>1696</v>
+        <v>1691</v>
       </c>
       <c r="N2" s="19" t="s">
         <v>734</v>
@@ -36424,7 +36421,7 @@
       </c>
       <c r="D4" s="52"/>
       <c r="E4" s="53" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="F4" s="52"/>
       <c r="G4" s="52" t="s">
@@ -36437,23 +36434,23 @@
         <v>321</v>
       </c>
       <c r="J4" s="52" t="s">
-        <v>1697</v>
+        <v>1692</v>
       </c>
       <c r="K4" s="52"/>
       <c r="L4" s="52" t="b">
         <v>1</v>
       </c>
       <c r="M4" s="53" t="s">
-        <v>1706</v>
+        <v>1701</v>
       </c>
       <c r="N4" s="52" t="s">
         <v>313</v>
       </c>
       <c r="O4" s="53" t="s">
-        <v>1703</v>
+        <v>1698</v>
       </c>
       <c r="P4" s="52" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="Q4" s="52" t="s">
         <v>323</v>
@@ -36472,39 +36469,39 @@
         <v>418</v>
       </c>
       <c r="C5" s="53" t="s">
-        <v>1704</v>
+        <v>1699</v>
       </c>
       <c r="D5" s="53" t="s">
-        <v>1708</v>
+        <v>1703</v>
       </c>
       <c r="E5" s="53" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="F5" s="53"/>
       <c r="G5" s="53" t="s">
-        <v>1705</v>
+        <v>1700</v>
       </c>
       <c r="H5" s="53"/>
       <c r="I5" s="135" t="s">
-        <v>1709</v>
+        <v>1704</v>
       </c>
       <c r="J5" s="53" t="s">
-        <v>1700</v>
+        <v>1695</v>
       </c>
       <c r="K5" s="53" t="s">
-        <v>1701</v>
+        <v>1696</v>
       </c>
       <c r="L5" s="53" t="b">
         <v>1</v>
       </c>
       <c r="M5" s="53" t="s">
+        <v>1693</v>
+      </c>
+      <c r="N5" s="53" t="s">
+        <v>1697</v>
+      </c>
+      <c r="O5" s="53" t="s">
         <v>1698</v>
-      </c>
-      <c r="N5" s="53" t="s">
-        <v>1702</v>
-      </c>
-      <c r="O5" s="53" t="s">
-        <v>1703</v>
       </c>
       <c r="P5" s="53" t="s">
         <v>318</v>
@@ -36759,7 +36756,7 @@
   <sheetData>
     <row r="1" spans="1:27" s="1" customFormat="1" ht="135.75" customHeight="1">
       <c r="A1" s="141" t="s">
-        <v>1247</v>
+        <v>1242</v>
       </c>
       <c r="B1" s="142"/>
       <c r="C1" s="142"/>
@@ -36799,7 +36796,7 @@
         <v>80</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="E2" s="50" t="s">
         <v>565</v>
@@ -36913,7 +36910,7 @@
         <v>55</v>
       </c>
       <c r="D4" s="53" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="E4" s="92" t="s">
         <v>589</v>
@@ -36988,7 +36985,7 @@
         <v>86</v>
       </c>
       <c r="D5" s="53" t="s">
-        <v>1246</v>
+        <v>1241</v>
       </c>
       <c r="E5" s="92" t="s">
         <v>591</v>
@@ -40157,7 +40154,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="119.25" customHeight="1">
       <c r="A1" s="141" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="B1" s="142"/>
       <c r="C1" s="142"/>
@@ -43075,7 +43072,7 @@
   <sheetData>
     <row r="1" spans="1:28" s="1" customFormat="1" ht="195" customHeight="1">
       <c r="A1" s="152" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B1" s="153"/>
       <c r="C1" s="153"/>
@@ -43119,10 +43116,10 @@
         <v>580</v>
       </c>
       <c r="E2" s="65" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="F2" s="65" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
       <c r="G2" s="65" t="s">
         <v>567</v>
@@ -43137,16 +43134,16 @@
         <v>581</v>
       </c>
       <c r="K2" s="65" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="L2" s="65" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
       <c r="M2" s="65" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="N2" s="65" t="s">
-        <v>1091</v>
+        <v>1086</v>
       </c>
       <c r="O2" s="65" t="s">
         <v>582</v>
@@ -43215,10 +43212,10 @@
         <v>593</v>
       </c>
       <c r="E4" s="53" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="F4" s="53" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="G4" s="52">
         <v>4</v>
@@ -43242,7 +43239,7 @@
         <v>96</v>
       </c>
       <c r="N4" s="91" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="O4" s="91" t="b">
         <v>1</v>
@@ -47542,7 +47539,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="150" customHeight="1">
       <c r="A1" s="163" t="s">
-        <v>1558</v>
+        <v>1553</v>
       </c>
       <c r="B1" s="164"/>
       <c r="C1" s="164"/>
@@ -47571,46 +47568,46 @@
         <v>6</v>
       </c>
       <c r="C2" s="37" t="s">
+        <v>956</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E2" s="111" t="s">
+        <v>957</v>
+      </c>
+      <c r="F2" s="111" t="s">
+        <v>958</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>959</v>
+      </c>
+      <c r="H2" s="111" t="s">
+        <v>960</v>
+      </c>
+      <c r="I2" s="37" t="s">
+        <v>977</v>
+      </c>
+      <c r="J2" s="37" t="s">
         <v>961</v>
       </c>
-      <c r="D2" s="37" t="s">
-        <v>1120</v>
-      </c>
-      <c r="E2" s="111" t="s">
+      <c r="K2" s="37" t="s">
         <v>962</v>
       </c>
-      <c r="F2" s="111" t="s">
+      <c r="L2" s="129" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M2" s="129" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N2" s="37" t="s">
         <v>963</v>
       </c>
-      <c r="G2" s="37" t="s">
+      <c r="O2" s="37" t="s">
         <v>964</v>
       </c>
-      <c r="H2" s="111" t="s">
+      <c r="P2" s="37" t="s">
         <v>965</v>
-      </c>
-      <c r="I2" s="37" t="s">
-        <v>982</v>
-      </c>
-      <c r="J2" s="37" t="s">
-        <v>966</v>
-      </c>
-      <c r="K2" s="37" t="s">
-        <v>967</v>
-      </c>
-      <c r="L2" s="129" t="s">
-        <v>1086</v>
-      </c>
-      <c r="M2" s="129" t="s">
-        <v>1087</v>
-      </c>
-      <c r="N2" s="37" t="s">
-        <v>968</v>
-      </c>
-      <c r="O2" s="37" t="s">
-        <v>969</v>
-      </c>
-      <c r="P2" s="37" t="s">
-        <v>970</v>
       </c>
       <c r="Q2" s="37" t="s">
         <v>91</v>
@@ -47627,49 +47624,49 @@
         <v>417</v>
       </c>
       <c r="C3" s="35" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H3" s="35" t="s">
         <v>1121</v>
-      </c>
-      <c r="D3" s="35" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E3" s="35" t="s">
-        <v>1123</v>
-      </c>
-      <c r="F3" s="35" t="s">
-        <v>1124</v>
-      </c>
-      <c r="G3" s="35" t="s">
-        <v>1125</v>
-      </c>
-      <c r="H3" s="35" t="s">
-        <v>1126</v>
       </c>
       <c r="I3" s="35" t="s">
         <v>55</v>
       </c>
       <c r="J3" s="35" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
       <c r="K3" s="35">
         <v>16</v>
       </c>
       <c r="L3" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
       <c r="M3" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="N3" s="35">
         <v>3</v>
       </c>
       <c r="O3" s="35" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="P3" s="35" t="b">
         <v>0</v>
       </c>
       <c r="Q3" s="35" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
       <c r="R3" s="32"/>
     </row>
@@ -47681,18 +47678,18 @@
         <v>417</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
       <c r="E4" s="35"/>
       <c r="F4" s="35"/>
       <c r="G4" s="35" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
       <c r="H4" s="35" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="I4" s="35" t="s">
         <v>55</v>
@@ -47709,7 +47706,7 @@
         <v>3</v>
       </c>
       <c r="O4" s="35" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="P4" s="35" t="b">
         <v>0</v>
@@ -47814,7 +47811,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="56" customHeight="1">
       <c r="A1" s="152" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
       <c r="B1" s="164"/>
       <c r="C1" s="164"/>
@@ -47835,43 +47832,43 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="C2" s="111" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="D2" s="37" t="s">
+        <v>966</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>967</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>968</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>969</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>970</v>
+      </c>
+      <c r="I2" s="37" t="s">
         <v>971</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="J2" s="37" t="s">
         <v>972</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="K2" s="37" t="s">
         <v>973</v>
       </c>
-      <c r="G2" s="37" t="s">
+      <c r="L2" s="37" t="s">
         <v>974</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="M2" s="37" t="s">
         <v>975</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="N2" s="37" t="s">
         <v>976</v>
-      </c>
-      <c r="J2" s="37" t="s">
-        <v>977</v>
-      </c>
-      <c r="K2" s="37" t="s">
-        <v>978</v>
-      </c>
-      <c r="L2" s="37" t="s">
-        <v>979</v>
-      </c>
-      <c r="M2" s="37" t="s">
-        <v>980</v>
-      </c>
-      <c r="N2" s="37" t="s">
-        <v>981</v>
       </c>
       <c r="O2" s="48"/>
     </row>
@@ -47880,43 +47877,43 @@
         <v>5</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>1251</v>
+        <v>1246</v>
       </c>
       <c r="D3" s="35" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>1180</v>
+      </c>
+      <c r="H3" s="35" t="s">
+        <v>1181</v>
+      </c>
+      <c r="I3" s="35" t="s">
         <v>1182</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="J3" s="35" t="s">
         <v>1183</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="K3" s="35" t="s">
         <v>1184</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="L3" s="35" t="s">
         <v>1185</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="M3" s="35" t="s">
         <v>1186</v>
       </c>
-      <c r="I3" s="35" t="s">
-        <v>1187</v>
-      </c>
-      <c r="J3" s="35" t="s">
-        <v>1188</v>
-      </c>
-      <c r="K3" s="35" t="s">
-        <v>1189</v>
-      </c>
-      <c r="L3" s="35" t="s">
-        <v>1190</v>
-      </c>
-      <c r="M3" s="35" t="s">
-        <v>1191</v>
-      </c>
       <c r="N3" s="35" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="O3" s="112"/>
     </row>
@@ -47925,41 +47922,41 @@
         <v>5</v>
       </c>
       <c r="B4" s="76" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1251</v>
+        <v>1246</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
       <c r="E4" s="35"/>
       <c r="F4" s="35" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G4" s="35" t="s">
+        <v>1180</v>
+      </c>
+      <c r="H4" s="35" t="s">
+        <v>1181</v>
+      </c>
+      <c r="I4" s="35" t="s">
+        <v>1182</v>
+      </c>
+      <c r="J4" s="35" t="s">
+        <v>1183</v>
+      </c>
+      <c r="K4" s="35" t="s">
         <v>1184</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="L4" s="35" t="s">
         <v>1185</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="M4" s="35" t="s">
         <v>1186</v>
       </c>
-      <c r="I4" s="35" t="s">
-        <v>1187</v>
-      </c>
-      <c r="J4" s="35" t="s">
-        <v>1188</v>
-      </c>
-      <c r="K4" s="35" t="s">
-        <v>1189</v>
-      </c>
-      <c r="L4" s="35" t="s">
-        <v>1190</v>
-      </c>
-      <c r="M4" s="35" t="s">
-        <v>1191</v>
-      </c>
       <c r="N4" s="35" t="s">
-        <v>1134</v>
+        <v>1129</v>
       </c>
       <c r="O4" s="112"/>
     </row>
@@ -48051,7 +48048,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="43" customFormat="1" ht="166" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="B1" s="139"/>
       <c r="C1" s="139"/>
@@ -48066,22 +48063,22 @@
         <v>0</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="D2" s="30" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1273</v>
+        <v>1268</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1274</v>
+        <v>1269</v>
       </c>
       <c r="G2" s="131" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
       <c r="H2" s="30" t="s">
         <v>395</v>
@@ -49040,7 +49037,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="287" customHeight="1">
       <c r="A1" s="166" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="B1" s="167"/>
       <c r="C1" s="167"/>
@@ -49068,49 +49065,49 @@
         <v>6</v>
       </c>
       <c r="C2" s="30" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I2" s="30" t="s">
         <v>1010</v>
       </c>
-      <c r="D2" s="30" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E2" s="30" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F2" s="30" t="s">
+      <c r="J2" s="30" t="s">
+        <v>1002</v>
+      </c>
+      <c r="K2" s="31" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>1011</v>
+      </c>
+      <c r="M2" s="31" t="s">
         <v>1012</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="N2" s="31" t="s">
         <v>1013</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="O2" s="31" t="s">
         <v>1014</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="P2" s="31" t="s">
         <v>1015</v>
       </c>
-      <c r="J2" s="30" t="s">
-        <v>1007</v>
-      </c>
-      <c r="K2" s="31" t="s">
-        <v>1006</v>
-      </c>
-      <c r="L2" s="30" t="s">
+      <c r="Q2" s="31" t="s">
         <v>1016</v>
-      </c>
-      <c r="M2" s="31" t="s">
-        <v>1017</v>
-      </c>
-      <c r="N2" s="31" t="s">
-        <v>1018</v>
-      </c>
-      <c r="O2" s="31" t="s">
-        <v>1019</v>
-      </c>
-      <c r="P2" s="31" t="s">
-        <v>1020</v>
-      </c>
-      <c r="Q2" s="31" t="s">
-        <v>1021</v>
       </c>
       <c r="R2" s="30" t="s">
         <v>395</v>
@@ -49129,43 +49126,43 @@
         <v>417</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="D4" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>990</v>
+      </c>
+      <c r="H4" s="36" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>1073</v>
+      </c>
+      <c r="J4" s="32" t="s">
         <v>996</v>
       </c>
-      <c r="E4" s="36" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F4" s="36" t="s">
-        <v>1023</v>
-      </c>
-      <c r="G4" s="36" t="s">
-        <v>995</v>
-      </c>
-      <c r="H4" s="36" t="s">
-        <v>1022</v>
-      </c>
-      <c r="I4" s="33" t="s">
-        <v>1078</v>
-      </c>
-      <c r="J4" s="32" t="s">
-        <v>1001</v>
-      </c>
       <c r="K4" s="32" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="L4" s="32" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="M4" s="32" t="b">
         <v>1</v>
       </c>
       <c r="N4" s="33" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="O4" s="32" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="P4" s="32"/>
       <c r="Q4" s="32"/>
@@ -49178,40 +49175,40 @@
         <v>417</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="G5" s="36" t="s">
+        <v>990</v>
+      </c>
+      <c r="H5" s="36" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I5" s="33" t="s">
+        <v>1073</v>
+      </c>
+      <c r="J5" s="32" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K5" s="32" t="s">
         <v>995</v>
       </c>
-      <c r="H5" s="36" t="s">
-        <v>1022</v>
-      </c>
-      <c r="I5" s="33" t="s">
-        <v>1078</v>
-      </c>
-      <c r="J5" s="32" t="s">
-        <v>1050</v>
-      </c>
-      <c r="K5" s="32" t="s">
-        <v>1000</v>
-      </c>
       <c r="L5" s="32" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="M5" s="32" t="b">
         <v>1</v>
       </c>
       <c r="N5" s="33" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="O5" s="32"/>
       <c r="P5" s="32"/>
@@ -49225,22 +49222,22 @@
         <v>417</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="G6" s="36" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="H6" s="36" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="I6" s="33"/>
       <c r="J6" s="32"/>
@@ -49260,38 +49257,38 @@
         <v>417</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="F7" s="36" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="G7" s="36" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="H7" s="36" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="I7" s="33" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="J7" s="32"/>
       <c r="K7" s="32" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="L7" s="32" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="M7" s="32" t="b">
         <v>1</v>
       </c>
       <c r="N7" s="33" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="O7" s="32"/>
       <c r="P7" s="32"/>
@@ -49413,7 +49410,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="234" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1561</v>
+        <v>1556</v>
       </c>
       <c r="B1" s="137"/>
       <c r="C1" s="137"/>
@@ -49422,7 +49419,7 @@
       <c r="F1" s="137"/>
       <c r="G1" s="137"/>
       <c r="H1" s="148" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="I1" s="137"/>
       <c r="J1" s="137"/>
@@ -49437,46 +49434,46 @@
         <v>0</v>
       </c>
       <c r="B2" s="19" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C2" s="125" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F2" s="19" t="s">
         <v>1195</v>
       </c>
-      <c r="C2" s="125" t="s">
+      <c r="G2" s="49" t="s">
         <v>1196</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="H2" s="81" t="s">
         <v>1197</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="I2" s="19" t="s">
         <v>1198</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="J2" s="126" t="s">
+        <v>1199</v>
+      </c>
+      <c r="K2" s="19" t="s">
         <v>1200</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="L2" s="19" t="s">
         <v>1201</v>
       </c>
-      <c r="H2" s="81" t="s">
+      <c r="M2" s="128" t="s">
         <v>1202</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="N2" s="19" t="s">
+        <v>1194</v>
+      </c>
+      <c r="O2" s="19" t="s">
         <v>1203</v>
-      </c>
-      <c r="J2" s="126" t="s">
-        <v>1204</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>1205</v>
-      </c>
-      <c r="L2" s="19" t="s">
-        <v>1206</v>
-      </c>
-      <c r="M2" s="128" t="s">
-        <v>1207</v>
-      </c>
-      <c r="N2" s="19" t="s">
-        <v>1199</v>
-      </c>
-      <c r="O2" s="19" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="16">
@@ -49503,26 +49500,26 @@
         <v>311</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="E4" s="35"/>
       <c r="F4" s="35" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="H4" s="35" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="I4" s="35" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
       <c r="J4" s="127">
         <v>256</v>
@@ -49543,19 +49540,19 @@
         <v>417</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="H5" s="35" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="I5" s="35" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="J5" s="127">
         <v>384</v>
       </c>
       <c r="K5" s="35" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="L5" s="35"/>
       <c r="M5" s="127"/>
@@ -49567,28 +49564,28 @@
         <v>311</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>1219</v>
+        <v>1214</v>
       </c>
       <c r="E6" s="35" t="s">
         <v>5</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="I6" s="35" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
       <c r="J6" s="127">
         <v>128</v>
@@ -49613,13 +49610,13 @@
         <v>417</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="H7" s="35" t="s">
+        <v>1211</v>
+      </c>
+      <c r="I7" s="35" t="s">
         <v>1216</v>
-      </c>
-      <c r="I7" s="35" t="s">
-        <v>1221</v>
       </c>
       <c r="J7" s="127">
         <v>3072</v>
@@ -49640,19 +49637,19 @@
         <v>418</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="I8" s="35" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="J8" s="127">
         <v>521</v>
       </c>
       <c r="K8" s="35" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="L8" s="35" t="b">
         <v>1</v>
@@ -50718,7 +50715,7 @@
   <sheetData>
     <row r="1" spans="1:29" ht="212" customHeight="1">
       <c r="A1" s="169" t="s">
-        <v>1690</v>
+        <v>1685</v>
       </c>
       <c r="B1" s="164"/>
       <c r="C1" s="164"/>
@@ -50728,7 +50725,7 @@
       <c r="G1" s="164"/>
       <c r="H1" s="165"/>
       <c r="I1" s="152" t="s">
-        <v>1688</v>
+        <v>1683</v>
       </c>
       <c r="J1" s="153"/>
       <c r="K1" s="153"/>
@@ -50765,10 +50762,10 @@
         <v>2</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>1562</v>
+        <v>1557</v>
       </c>
       <c r="F2" s="38" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
       <c r="G2" s="37" t="s">
         <v>80</v>
@@ -50777,64 +50774,64 @@
         <v>82</v>
       </c>
       <c r="I2" s="37" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="J2" s="38" t="s">
         <v>81</v>
       </c>
       <c r="K2" s="38" t="s">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="L2" s="38" t="s">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="M2" s="37" t="s">
         <v>89</v>
       </c>
       <c r="N2" s="37" t="s">
+        <v>1561</v>
+      </c>
+      <c r="O2" s="37" t="s">
+        <v>1562</v>
+      </c>
+      <c r="P2" s="37" t="s">
+        <v>1563</v>
+      </c>
+      <c r="Q2" s="37" t="s">
+        <v>1564</v>
+      </c>
+      <c r="R2" s="37" t="s">
+        <v>1565</v>
+      </c>
+      <c r="S2" s="37" t="s">
         <v>1566</v>
       </c>
-      <c r="O2" s="37" t="s">
+      <c r="T2" s="37" t="s">
         <v>1567</v>
       </c>
-      <c r="P2" s="37" t="s">
+      <c r="U2" s="37" t="s">
         <v>1568</v>
       </c>
-      <c r="Q2" s="37" t="s">
+      <c r="V2" s="37" t="s">
         <v>1569</v>
       </c>
-      <c r="R2" s="37" t="s">
+      <c r="W2" s="37" t="s">
         <v>1570</v>
       </c>
-      <c r="S2" s="37" t="s">
+      <c r="X2" s="37" t="s">
         <v>1571</v>
       </c>
-      <c r="T2" s="37" t="s">
+      <c r="Y2" s="37" t="s">
         <v>1572</v>
       </c>
-      <c r="U2" s="37" t="s">
+      <c r="Z2" s="37" t="s">
         <v>1573</v>
-      </c>
-      <c r="V2" s="37" t="s">
-        <v>1574</v>
-      </c>
-      <c r="W2" s="37" t="s">
-        <v>1575</v>
-      </c>
-      <c r="X2" s="37" t="s">
-        <v>1576</v>
-      </c>
-      <c r="Y2" s="37" t="s">
-        <v>1577</v>
-      </c>
-      <c r="Z2" s="37" t="s">
-        <v>1578</v>
       </c>
       <c r="AA2" s="37" t="s">
         <v>75</v>
       </c>
       <c r="AB2" s="37" t="s">
-        <v>1579</v>
+        <v>1574</v>
       </c>
       <c r="AC2" s="38" t="s">
         <v>395</v>
@@ -50881,16 +50878,16 @@
         <v>418</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>1679</v>
+        <v>1674</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>1681</v>
+        <v>1676</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>1683</v>
+        <v>1678</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="G4" s="22" t="s">
         <v>55</v>
@@ -50899,58 +50896,58 @@
         <v>330</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>1246</v>
+        <v>1241</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="K4" s="22"/>
       <c r="L4" s="22"/>
       <c r="M4" s="36" t="s">
-        <v>1685</v>
+        <v>1680</v>
       </c>
       <c r="N4" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="O4" s="22" t="s">
+        <v>1577</v>
+      </c>
+      <c r="P4" s="22" t="s">
+        <v>1578</v>
+      </c>
+      <c r="Q4" s="22" t="s">
+        <v>1579</v>
+      </c>
+      <c r="R4" s="22" t="s">
+        <v>1580</v>
+      </c>
+      <c r="S4" s="22" t="s">
+        <v>1581</v>
+      </c>
+      <c r="T4" s="22" t="s">
         <v>1582</v>
-      </c>
-      <c r="O4" s="22" t="s">
-        <v>1582</v>
-      </c>
-      <c r="P4" s="22" t="s">
-        <v>1583</v>
-      </c>
-      <c r="Q4" s="22" t="s">
-        <v>1584</v>
-      </c>
-      <c r="R4" s="22" t="s">
-        <v>1585</v>
-      </c>
-      <c r="S4" s="22" t="s">
-        <v>1586</v>
-      </c>
-      <c r="T4" s="22" t="s">
-        <v>1587</v>
       </c>
       <c r="U4" s="22" t="s">
         <v>188</v>
       </c>
       <c r="V4" s="22" t="s">
-        <v>1588</v>
+        <v>1583</v>
       </c>
       <c r="W4" s="22" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="X4" s="133" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="Y4" s="22" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
       <c r="Z4" s="22" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="AA4" s="22"/>
       <c r="AB4" s="8" t="s">
-        <v>1687</v>
+        <v>1682</v>
       </c>
       <c r="AC4" s="22"/>
     </row>
@@ -50962,16 +50959,16 @@
         <v>418</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>1680</v>
+        <v>1675</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>1682</v>
+        <v>1677</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1684</v>
+        <v>1679</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>86</v>
@@ -50980,56 +50977,56 @@
         <v>99</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="J5" s="35" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="K5" s="35"/>
       <c r="L5" s="35"/>
       <c r="M5" s="35"/>
       <c r="N5" s="35" t="s">
+        <v>1577</v>
+      </c>
+      <c r="O5" s="35" t="s">
+        <v>1577</v>
+      </c>
+      <c r="P5" s="35" t="s">
+        <v>1578</v>
+      </c>
+      <c r="Q5" s="35" t="s">
+        <v>1579</v>
+      </c>
+      <c r="R5" s="35" t="s">
+        <v>1580</v>
+      </c>
+      <c r="S5" s="35" t="s">
+        <v>1581</v>
+      </c>
+      <c r="T5" s="35" t="s">
         <v>1582</v>
-      </c>
-      <c r="O5" s="35" t="s">
-        <v>1582</v>
-      </c>
-      <c r="P5" s="35" t="s">
-        <v>1583</v>
-      </c>
-      <c r="Q5" s="35" t="s">
-        <v>1584</v>
-      </c>
-      <c r="R5" s="35" t="s">
-        <v>1585</v>
-      </c>
-      <c r="S5" s="35" t="s">
-        <v>1586</v>
-      </c>
-      <c r="T5" s="35" t="s">
-        <v>1587</v>
       </c>
       <c r="U5" s="35" t="s">
         <v>188</v>
       </c>
       <c r="V5" s="35" t="s">
-        <v>1588</v>
+        <v>1583</v>
       </c>
       <c r="W5" s="35" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="X5" s="35" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="Y5" s="35" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
       <c r="Z5" s="35" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="AA5" s="35"/>
       <c r="AB5" s="36" t="s">
-        <v>1686</v>
+        <v>1681</v>
       </c>
       <c r="AC5" s="35"/>
     </row>
@@ -56993,7 +56990,7 @@
   <sheetData>
     <row r="1" spans="1:81" ht="185" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1689</v>
+        <v>1684</v>
       </c>
       <c r="B1" s="137"/>
       <c r="C1" s="137"/>
@@ -57019,13 +57016,13 @@
         <v>2</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
       <c r="G2" s="30" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
       <c r="H2" s="30" t="s">
         <v>395</v>
@@ -57048,23 +57045,23 @@
     </row>
     <row r="4" spans="1:81" ht="32" customHeight="1">
       <c r="A4" s="35" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="B4" s="35" t="s">
         <v>418</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1679</v>
+        <v>1674</v>
       </c>
       <c r="D4" s="35"/>
       <c r="E4" s="35" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
       <c r="H4" s="35"/>
     </row>
@@ -57075,32 +57072,32 @@
       <c r="D5" s="35"/>
       <c r="E5" s="35"/>
       <c r="F5" s="35" t="s">
-        <v>1598</v>
+        <v>1593</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>1599</v>
+        <v>1594</v>
       </c>
       <c r="H5" s="35"/>
     </row>
     <row r="6" spans="1:81" ht="32" customHeight="1">
       <c r="A6" s="35" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="B6" s="35" t="s">
         <v>418</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>1680</v>
+        <v>1675</v>
       </c>
       <c r="D6" s="35"/>
       <c r="E6" s="35" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
       <c r="H6" s="35"/>
     </row>
@@ -57111,10 +57108,10 @@
       <c r="D7" s="35"/>
       <c r="E7" s="35"/>
       <c r="F7" s="35" t="s">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>1601</v>
+        <v>1596</v>
       </c>
       <c r="H7" s="35"/>
     </row>
@@ -57125,10 +57122,10 @@
       <c r="D8" s="35"/>
       <c r="E8" s="35"/>
       <c r="F8" s="35" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>1603</v>
+        <v>1598</v>
       </c>
       <c r="H8" s="35"/>
     </row>
@@ -58353,19 +58350,19 @@
   <sheetData>
     <row r="1" spans="1:13" ht="32">
       <c r="A1" s="99" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="B1" s="99" t="s">
         <v>568</v>
       </c>
       <c r="C1" s="100" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="D1" s="100" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="E1" s="99" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="F1" s="101" t="s">
         <v>572</v>
@@ -58386,27 +58383,27 @@
         <v>566</v>
       </c>
       <c r="L1" s="100" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="M1" s="100" t="s">
-        <v>1618</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16">
       <c r="A2" s="103" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="B2" s="45" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D2" s="36" t="s">
         <v>322</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="F2" s="45" t="s">
         <v>318</v>
@@ -58421,7 +58418,7 @@
         <v>80</v>
       </c>
       <c r="J2" s="35" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="K2" s="36">
         <v>1</v>
@@ -58430,39 +58427,39 @@
         <v>313</v>
       </c>
       <c r="M2" s="35" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="16">
       <c r="A3" s="103" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="B3" s="36" t="s">
         <v>388</v>
       </c>
       <c r="C3" s="36" t="s">
+        <v>803</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>805</v>
+      </c>
+      <c r="F3" s="36" t="s">
+        <v>806</v>
+      </c>
+      <c r="G3" s="104" t="s">
+        <v>807</v>
+      </c>
+      <c r="H3" s="36" t="s">
         <v>808</v>
-      </c>
-      <c r="D3" s="36" t="s">
-        <v>809</v>
-      </c>
-      <c r="E3" s="36" t="s">
-        <v>810</v>
-      </c>
-      <c r="F3" s="36" t="s">
-        <v>811</v>
-      </c>
-      <c r="G3" s="104" t="s">
-        <v>812</v>
-      </c>
-      <c r="H3" s="36" t="s">
-        <v>813</v>
       </c>
       <c r="I3" s="35">
         <v>40</v>
       </c>
       <c r="J3" s="35" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="K3" s="36">
         <v>2</v>
@@ -58471,32 +58468,32 @@
         <v>312</v>
       </c>
       <c r="M3" s="35" t="s">
-        <v>1616</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="16">
       <c r="A4" s="103" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="B4" s="36" t="s">
         <v>328</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="D4" s="36"/>
       <c r="E4" s="36" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="F4" s="36"/>
       <c r="H4" s="8" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="L4" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="M4" s="35" t="s">
-        <v>1617</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="16">
@@ -58504,89 +58501,89 @@
         <v>326</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="D5" s="36"/>
       <c r="E5" s="36" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="F5" s="36"/>
       <c r="H5" s="36" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="L5" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="M5" s="35" t="s">
-        <v>1604</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="16">
       <c r="A6" s="103" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="B6" s="36"/>
       <c r="C6" s="36" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="D6" s="36"/>
       <c r="E6" s="36" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="F6" s="36"/>
       <c r="H6" s="36" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="M6" s="35" t="s">
-        <v>1620</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="16">
       <c r="A7" s="103" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="B7" s="36"/>
       <c r="C7" s="36" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="D7" s="36"/>
       <c r="E7" s="36" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="F7" s="36"/>
       <c r="H7" s="36" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="M7" s="35" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16">
       <c r="A8" s="103" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="B8" s="36"/>
       <c r="C8" s="36" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="D8" s="36"/>
       <c r="E8" s="36" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="F8" s="36"/>
       <c r="H8" s="36" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="M8" s="35" t="s">
-        <v>1621</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="16">
       <c r="A9" s="103" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="B9" s="36"/>
       <c r="C9" s="36" t="s">
@@ -58594,94 +58591,94 @@
       </c>
       <c r="D9" s="36"/>
       <c r="E9" s="36" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="F9" s="36"/>
       <c r="H9" s="36" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="M9" s="35" t="s">
-        <v>1622</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="16">
       <c r="A10" s="103" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="B10" s="36"/>
       <c r="C10" s="36" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="D10" s="36"/>
       <c r="E10" s="36" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="F10" s="36"/>
       <c r="H10" s="36" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="M10" s="35" t="s">
-        <v>1623</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="16">
       <c r="A11" s="103" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="B11" s="36"/>
       <c r="C11" s="36" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="D11" s="36"/>
       <c r="E11" s="36" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="F11" s="36"/>
       <c r="H11" s="36" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="M11" s="35" t="s">
-        <v>1624</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="16">
       <c r="A12" s="103" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="B12" s="36"/>
       <c r="C12" s="36" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="D12" s="36"/>
       <c r="E12" s="36" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="F12" s="36"/>
       <c r="H12" s="36" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="M12" s="35" t="s">
-        <v>1625</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="16">
       <c r="A13" s="103" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="B13" s="36"/>
       <c r="C13" s="36" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="D13" s="36"/>
       <c r="E13" s="36" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="F13" s="36"/>
       <c r="H13" s="36" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="M13" s="35" t="s">
-        <v>1626</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="16">
@@ -58690,666 +58687,666 @@
       </c>
       <c r="B14" s="36"/>
       <c r="C14" s="36" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="D14" s="36"/>
       <c r="E14" s="36"/>
       <c r="F14" s="36"/>
       <c r="H14" s="36" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="M14" s="35" t="s">
-        <v>1627</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="16">
       <c r="H15" s="36" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="M15" s="35" t="s">
-        <v>1628</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="16">
       <c r="H16" s="36" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="M16" s="35" t="s">
-        <v>1629</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="17" spans="8:13" ht="16">
       <c r="H17" s="36" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="M17" s="35" t="s">
-        <v>1630</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="18" spans="8:13" ht="16">
       <c r="H18" s="36" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="M18" s="35" t="s">
-        <v>1606</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="19" spans="8:13" ht="16">
       <c r="H19" s="36" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="M19" s="35" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="20" spans="8:13" ht="16">
       <c r="H20" s="36" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="M20" s="35" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="21" spans="8:13" ht="16">
       <c r="H21" s="36" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="M21" s="35" t="s">
-        <v>1607</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="22" spans="8:13" ht="16">
       <c r="H22" s="36" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="M22" s="35" t="s">
-        <v>1608</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="23" spans="8:13" ht="16">
       <c r="H23" s="36" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="M23" s="35" t="s">
-        <v>1633</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="24" spans="8:13" ht="16">
       <c r="H24" s="36" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="M24" s="35" t="s">
-        <v>1634</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="25" spans="8:13" ht="16">
       <c r="H25" s="36" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="M25" s="35" t="s">
-        <v>1635</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="26" spans="8:13" ht="16">
       <c r="H26" s="36" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="M26" s="35" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="27" spans="8:13" ht="16">
       <c r="H27" s="36" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="M27" s="35" t="s">
-        <v>1637</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="28" spans="8:13" ht="16">
       <c r="H28" s="36" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="M28" s="35" t="s">
-        <v>1638</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="29" spans="8:13" ht="16">
       <c r="H29" s="36" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="M29" s="35" t="s">
-        <v>1609</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="30" spans="8:13" ht="16">
       <c r="H30" s="36" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="M30" s="35" t="s">
-        <v>1639</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="31" spans="8:13" ht="16">
       <c r="H31" s="36" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="M31" s="35" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="32" spans="8:13" ht="16">
       <c r="H32" s="36" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="M32" s="35" t="s">
-        <v>1641</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="33" spans="8:13" ht="16">
       <c r="H33" s="36" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="M33" s="35" t="s">
-        <v>1642</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="34" spans="8:13" ht="16">
       <c r="H34" s="36" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="M34" s="35" t="s">
-        <v>1610</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="35" spans="8:13" ht="16">
       <c r="H35" s="36" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="M35" s="35" t="s">
-        <v>1643</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="36" spans="8:13" ht="16">
       <c r="H36" s="36" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="M36" s="35" t="s">
-        <v>1644</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="37" spans="8:13" ht="16">
       <c r="H37" s="36" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="M37" s="35" t="s">
-        <v>1645</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="38" spans="8:13" ht="16">
       <c r="H38" s="36" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="M38" s="35" t="s">
-        <v>1611</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="39" spans="8:13" ht="16">
       <c r="H39" s="36" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="M39" s="35" t="s">
-        <v>1612</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="40" spans="8:13" ht="16">
       <c r="H40" s="36" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="M40" s="35" t="s">
-        <v>1646</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="41" spans="8:13" ht="16">
       <c r="H41" s="36" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="M41" s="35" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="42" spans="8:13" ht="16">
       <c r="H42" s="36" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="M42" s="35" t="s">
-        <v>1647</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="43" spans="8:13" ht="16">
       <c r="H43" s="36" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="M43" s="35" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="44" spans="8:13" ht="16">
       <c r="H44" s="36" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="M44" s="35" t="s">
-        <v>1648</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="45" spans="8:13" ht="16">
       <c r="H45" s="36" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="M45" s="35" t="s">
-        <v>1649</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="46" spans="8:13" ht="16">
       <c r="H46" s="36" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="M46" s="35" t="s">
-        <v>1650</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="47" spans="8:13" ht="16">
       <c r="H47" s="36" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="M47" s="35" t="s">
-        <v>1651</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="48" spans="8:13" ht="16">
       <c r="H48" s="36" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="M48" s="35" t="s">
-        <v>1652</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="49" spans="8:13" ht="16">
       <c r="H49" s="36" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="M49" s="35" t="s">
-        <v>1653</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="50" spans="8:13" ht="16">
       <c r="H50" s="36" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="M50" s="35" t="s">
-        <v>1654</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="51" spans="8:13" ht="16">
       <c r="H51" s="36" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="M51" s="35" t="s">
-        <v>1655</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="52" spans="8:13" ht="16">
       <c r="H52" s="36" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="M52" s="35" t="s">
-        <v>1656</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="53" spans="8:13" ht="16">
       <c r="H53" s="36" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="M53" s="35" t="s">
-        <v>1657</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="54" spans="8:13" ht="16">
       <c r="H54" s="36" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="M54" s="35" t="s">
-        <v>1658</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="55" spans="8:13" ht="16">
       <c r="H55" s="36" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="M55" s="35" t="s">
-        <v>1659</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="56" spans="8:13" ht="16">
       <c r="H56" s="36" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="M56" s="35" t="s">
-        <v>1660</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="57" spans="8:13" ht="16">
       <c r="H57" s="36" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="M57" s="35" t="s">
-        <v>1661</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="58" spans="8:13" ht="16">
       <c r="H58" s="36" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="M58" s="35" t="s">
-        <v>1662</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="59" spans="8:13" ht="16">
       <c r="H59" s="36" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="M59" s="35" t="s">
-        <v>1663</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="60" spans="8:13" ht="16">
       <c r="H60" s="36" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="M60" s="35" t="s">
-        <v>1664</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="61" spans="8:13" ht="16">
       <c r="H61" s="36" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="M61" s="35" t="s">
-        <v>1665</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="62" spans="8:13" ht="16">
       <c r="H62" s="36" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="M62" s="35" t="s">
-        <v>1666</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="63" spans="8:13" ht="16">
       <c r="H63" s="36" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="M63" s="35" t="s">
-        <v>1667</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="64" spans="8:13" ht="16">
       <c r="H64" s="36" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="M64" s="35" t="s">
-        <v>1668</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="65" spans="8:13" ht="16">
       <c r="H65" s="36" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="M65" s="35" t="s">
-        <v>1669</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="66" spans="8:13" ht="16">
       <c r="H66" s="36" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="M66" s="35" t="s">
-        <v>1670</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="67" spans="8:13" ht="16">
       <c r="H67" s="36" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="M67" s="35" t="s">
-        <v>1671</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="68" spans="8:13" ht="16">
       <c r="H68" s="36" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="M68" s="35" t="s">
-        <v>1672</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="69" spans="8:13" ht="16">
       <c r="H69" s="36" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="M69" s="35" t="s">
-        <v>1673</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="70" spans="8:13" ht="16">
       <c r="H70" s="36" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="M70" s="35" t="s">
-        <v>1674</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="71" spans="8:13" ht="16">
       <c r="H71" s="36" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="M71" s="35" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="72" spans="8:13" ht="16">
       <c r="H72" s="36" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="M72" s="35" t="s">
-        <v>1675</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="73" spans="8:13" ht="16">
       <c r="H73" s="36" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="M73" s="35" t="s">
-        <v>1676</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="74" spans="8:13" ht="16">
       <c r="H74" s="36" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="M74" s="35" t="s">
-        <v>1677</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="75" spans="8:13">
       <c r="H75" s="36" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
     </row>
     <row r="76" spans="8:13">
       <c r="H76" s="36" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
     </row>
     <row r="77" spans="8:13">
       <c r="H77" s="36" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
     </row>
     <row r="78" spans="8:13">
       <c r="H78" s="36" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
     </row>
     <row r="79" spans="8:13">
       <c r="H79" s="36" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
     </row>
     <row r="80" spans="8:13">
       <c r="H80" s="36" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
     </row>
     <row r="81" spans="8:8">
       <c r="H81" s="36" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
     </row>
     <row r="82" spans="8:8">
       <c r="H82" s="36" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
     </row>
     <row r="83" spans="8:8">
       <c r="H83" s="36" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
     </row>
     <row r="84" spans="8:8">
       <c r="H84" s="36" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
     </row>
     <row r="85" spans="8:8">
       <c r="H85" s="36" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
     </row>
     <row r="86" spans="8:8">
       <c r="H86" s="36" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
     </row>
     <row r="87" spans="8:8">
       <c r="H87" s="36" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
     </row>
     <row r="88" spans="8:8">
       <c r="H88" s="36" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
     </row>
     <row r="89" spans="8:8">
       <c r="H89" s="36" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
     </row>
     <row r="90" spans="8:8">
       <c r="H90" s="36" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
     </row>
     <row r="91" spans="8:8">
       <c r="H91" s="36" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
     </row>
     <row r="92" spans="8:8">
       <c r="H92" s="36" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
     </row>
     <row r="93" spans="8:8">
       <c r="H93" s="36" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
     </row>
     <row r="94" spans="8:8">
       <c r="H94" s="36" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
     </row>
     <row r="95" spans="8:8">
       <c r="H95" s="36" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
     </row>
     <row r="96" spans="8:8">
       <c r="H96" s="36" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
     </row>
     <row r="97" spans="8:8">
       <c r="H97" s="36" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
     </row>
     <row r="98" spans="8:8">
       <c r="H98" s="36" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
     </row>
     <row r="99" spans="8:8">
       <c r="H99" s="36" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
     </row>
     <row r="100" spans="8:8">
       <c r="H100" s="36" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
     </row>
     <row r="101" spans="8:8">
       <c r="H101" s="36" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="102" spans="8:8">
       <c r="H102" s="36" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="103" spans="8:8">
       <c r="H103" s="36" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
     </row>
     <row r="104" spans="8:8">
       <c r="H104" s="36" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
     </row>
     <row r="105" spans="8:8">
       <c r="H105" s="36" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
     </row>
     <row r="106" spans="8:8">
       <c r="H106" s="36" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
     </row>
     <row r="107" spans="8:8">
       <c r="H107" s="36" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
     </row>
     <row r="108" spans="8:8">
       <c r="H108" s="36" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
     </row>
   </sheetData>
@@ -59742,23 +59739,23 @@
         <v>506</v>
       </c>
       <c r="D1" s="64" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="E1" s="64"/>
       <c r="F1" s="64" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="G1" s="64" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="H1" s="64" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="I1" s="64" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="J1" s="64" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="K1" s="64" t="s">
         <v>508</v>
@@ -59866,13 +59863,13 @@
         <v>772</v>
       </c>
       <c r="AT1" s="55" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="AU1" s="55" t="s">
         <v>507</v>
       </c>
       <c r="AV1" s="55" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="2" spans="1:48" s="57" customFormat="1" ht="16">
@@ -59918,7 +59915,7 @@
         <v>21</v>
       </c>
       <c r="L2" s="132" t="s">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="M2" s="58" t="s">
         <v>38</v>
@@ -60076,7 +60073,7 @@
         <v>23</v>
       </c>
       <c r="L3" s="36" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="M3" s="58" t="s">
         <v>36</v>
@@ -60467,7 +60464,7 @@
       <c r="J6" s="36"/>
       <c r="K6" s="58"/>
       <c r="L6" t="s">
-        <v>1281</v>
+        <v>1276</v>
       </c>
       <c r="M6" s="58"/>
       <c r="N6" s="58"/>
@@ -60559,7 +60556,7 @@
       <c r="J7" s="36"/>
       <c r="K7" s="58"/>
       <c r="L7" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="M7" s="58"/>
       <c r="N7" s="58"/>
@@ -61308,7 +61305,7 @@
       <c r="J16" s="36"/>
       <c r="K16" s="58"/>
       <c r="L16" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="M16" s="58"/>
       <c r="N16" s="58"/>
@@ -61847,7 +61844,7 @@
       <c r="J23" s="36"/>
       <c r="K23" s="58"/>
       <c r="L23" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="M23" s="58"/>
       <c r="N23" s="58"/>
@@ -62001,7 +61998,7 @@
       <c r="J25" s="36"/>
       <c r="K25" s="58"/>
       <c r="L25" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="M25" s="58"/>
       <c r="N25" s="58"/>
@@ -62155,7 +62152,7 @@
       <c r="J27" s="36"/>
       <c r="K27" s="58"/>
       <c r="L27" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="M27" s="58"/>
       <c r="N27" s="58"/>
@@ -62378,7 +62375,7 @@
       <c r="J30" s="36"/>
       <c r="K30" s="58"/>
       <c r="L30" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="M30" s="58"/>
       <c r="N30" s="58"/>
@@ -62597,7 +62594,7 @@
       <c r="J33" s="36"/>
       <c r="K33" s="58"/>
       <c r="L33" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="M33" s="58"/>
       <c r="N33" s="58"/>
@@ -62743,7 +62740,7 @@
       <c r="J35" s="36"/>
       <c r="K35" s="58"/>
       <c r="L35" t="s">
-        <v>1691</v>
+        <v>1686</v>
       </c>
       <c r="M35" s="58"/>
       <c r="N35" s="58"/>
@@ -62800,7 +62797,7 @@
       <c r="J36" s="36"/>
       <c r="K36" s="58"/>
       <c r="L36" t="s">
-        <v>1692</v>
+        <v>1687</v>
       </c>
       <c r="M36" s="58"/>
       <c r="N36" s="58"/>
@@ -62856,7 +62853,7 @@
       <c r="J37" s="36"/>
       <c r="K37" s="58"/>
       <c r="L37" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="M37" s="58"/>
       <c r="N37" s="58"/>
@@ -63148,7 +63145,7 @@
       <c r="J41" s="36"/>
       <c r="K41" s="58"/>
       <c r="L41" s="63" t="s">
-        <v>1280</v>
+        <v>1275</v>
       </c>
       <c r="M41" s="58"/>
       <c r="N41" s="58"/>
@@ -63358,7 +63355,7 @@
       <c r="I45" s="36"/>
       <c r="J45" s="36"/>
       <c r="L45" s="57" t="s">
-        <v>1279</v>
+        <v>1274</v>
       </c>
       <c r="P45" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P45" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A45,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A45,4,4,1,"DHCP")))</f>
@@ -63404,7 +63401,7 @@
       <c r="I46" s="36"/>
       <c r="J46" s="36"/>
       <c r="L46" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="P46" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P46" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A46,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A46,4,4,1,"DHCP")))</f>
@@ -63450,7 +63447,7 @@
       <c r="I47" s="36"/>
       <c r="J47" s="36"/>
       <c r="L47" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="P47" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P47" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A47,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A47,4,4,1,"DHCP")))</f>
@@ -63496,7 +63493,7 @@
       <c r="I48" s="36"/>
       <c r="J48" s="36"/>
       <c r="L48" s="43" t="s">
-        <v>1276</v>
+        <v>1271</v>
       </c>
       <c r="P48" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P48" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A48,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A48,4,4,1,"DHCP")))</f>
@@ -63542,7 +63539,7 @@
       <c r="I49" s="36"/>
       <c r="J49" s="36"/>
       <c r="L49" t="s">
-        <v>782</v>
+        <v>1756</v>
       </c>
       <c r="P49" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P49" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A49,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A49,4,4,1,"DHCP")))</f>
@@ -63588,7 +63585,7 @@
       <c r="I50" s="36"/>
       <c r="J50" s="36"/>
       <c r="L50" t="s">
-        <v>783</v>
+        <v>1757</v>
       </c>
       <c r="P50" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P50" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A50,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A50,4,4,1,"DHCP")))</f>
@@ -63623,7 +63620,7 @@
       <c r="I51" s="36"/>
       <c r="J51" s="36"/>
       <c r="L51" t="s">
-        <v>784</v>
+        <v>1590</v>
       </c>
       <c r="AG51" s="63"/>
       <c r="AU51" s="106" t="str">
@@ -63643,7 +63640,7 @@
       <c r="I52" s="36"/>
       <c r="J52" s="36"/>
       <c r="L52" s="43" t="s">
-        <v>1278</v>
+        <v>1273</v>
       </c>
       <c r="AU52" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -63663,7 +63660,7 @@
       <c r="I53" s="36"/>
       <c r="J53" s="36"/>
       <c r="L53" t="s">
-        <v>785</v>
+        <v>1758</v>
       </c>
       <c r="AU53" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -63683,7 +63680,7 @@
       <c r="I54" s="36"/>
       <c r="J54" s="36"/>
       <c r="L54" t="s">
-        <v>786</v>
+        <v>1759</v>
       </c>
       <c r="AU54" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -66235,10 +66232,10 @@
         <v>558</v>
       </c>
       <c r="C1" s="55" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="D1" s="55" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -66738,7 +66735,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="43" customFormat="1" ht="134.25" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="B1" s="139"/>
       <c r="C1" s="139"/>
@@ -66757,10 +66754,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="F2" s="30" t="s">
         <v>395</v>
@@ -66810,7 +66807,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="43" customFormat="1" ht="131" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="B1" s="137"/>
       <c r="C1" s="137"/>
@@ -66860,7 +66857,7 @@
         <v>463</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="F3" s="35"/>
       <c r="G3" s="35"/>
@@ -66872,7 +66869,7 @@
       <c r="C4" s="35"/>
       <c r="D4" s="35"/>
       <c r="E4" s="35" t="s">
-        <v>1299</v>
+        <v>1294</v>
       </c>
       <c r="F4" s="35"/>
       <c r="G4" s="35"/>
@@ -66883,16 +66880,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>1737</v>
+        <v>1732</v>
       </c>
       <c r="C5" s="35" t="s">
         <v>377</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>1738</v>
+        <v>1733</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1739</v>
+        <v>1734</v>
       </c>
       <c r="F5" s="35"/>
       <c r="G5" s="35"/>
@@ -66904,7 +66901,7 @@
       <c r="C6" s="35"/>
       <c r="D6" s="35"/>
       <c r="E6" s="35" t="s">
-        <v>1740</v>
+        <v>1735</v>
       </c>
       <c r="F6" s="35"/>
       <c r="G6" s="35"/>
@@ -66916,7 +66913,7 @@
       <c r="C7" s="35"/>
       <c r="D7" s="35"/>
       <c r="E7" s="35" t="s">
-        <v>1741</v>
+        <v>1736</v>
       </c>
       <c r="F7" s="35"/>
       <c r="G7" s="35"/>
@@ -66936,7 +66933,7 @@
         <v>427</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="F8" s="35"/>
       <c r="G8" s="35"/>
@@ -66948,7 +66945,7 @@
       <c r="C9" s="35"/>
       <c r="D9" s="35"/>
       <c r="E9" s="35" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="F9" s="35"/>
       <c r="G9" s="35"/>
@@ -66960,7 +66957,7 @@
       <c r="C10" s="35"/>
       <c r="D10" s="35"/>
       <c r="E10" s="35" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="F10" s="35"/>
       <c r="G10" s="35"/>
@@ -66972,7 +66969,7 @@
       <c r="C11" s="35"/>
       <c r="D11" s="35"/>
       <c r="E11" s="35" t="s">
-        <v>1303</v>
+        <v>1298</v>
       </c>
       <c r="F11" s="35"/>
       <c r="G11" s="35"/>
@@ -66984,7 +66981,7 @@
       <c r="C12" s="35"/>
       <c r="D12" s="35"/>
       <c r="E12" s="35" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="F12" s="35"/>
       <c r="G12" s="35"/>
@@ -66996,7 +66993,7 @@
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
       <c r="E13" s="35" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
       <c r="F13" s="35"/>
       <c r="G13" s="35"/>
@@ -67008,7 +67005,7 @@
       <c r="C14" s="35"/>
       <c r="D14" s="35"/>
       <c r="E14" s="35" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="F14" s="35"/>
       <c r="G14" s="35"/>
@@ -67020,7 +67017,7 @@
       <c r="C15" s="35"/>
       <c r="D15" s="35"/>
       <c r="E15" s="35" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="F15" s="35"/>
       <c r="G15" s="35"/>
@@ -67032,7 +67029,7 @@
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
       <c r="E16" s="35" t="s">
-        <v>1308</v>
+        <v>1303</v>
       </c>
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
@@ -67044,7 +67041,7 @@
       <c r="C17" s="35"/>
       <c r="D17" s="35"/>
       <c r="E17" s="35" t="s">
-        <v>1309</v>
+        <v>1304</v>
       </c>
       <c r="F17" s="35"/>
       <c r="G17" s="35"/>
@@ -67056,7 +67053,7 @@
       <c r="C18" s="35"/>
       <c r="D18" s="35"/>
       <c r="E18" s="35" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="F18" s="35"/>
       <c r="G18" s="35"/>
@@ -67068,7 +67065,7 @@
       <c r="C19" s="35"/>
       <c r="D19" s="35"/>
       <c r="E19" s="35" t="s">
-        <v>1311</v>
+        <v>1306</v>
       </c>
       <c r="F19" s="35"/>
       <c r="G19" s="35"/>
@@ -67080,7 +67077,7 @@
       <c r="C20" s="35"/>
       <c r="D20" s="35"/>
       <c r="E20" s="35" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="F20" s="35"/>
       <c r="G20" s="35"/>
@@ -67092,7 +67089,7 @@
       <c r="C21" s="35"/>
       <c r="D21" s="35"/>
       <c r="E21" s="35" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="F21" s="35"/>
       <c r="G21" s="35"/>
@@ -67104,7 +67101,7 @@
       <c r="C22" s="35"/>
       <c r="D22" s="35"/>
       <c r="E22" s="35" t="s">
-        <v>1314</v>
+        <v>1309</v>
       </c>
       <c r="F22" s="35"/>
       <c r="G22" s="35"/>
@@ -67116,7 +67113,7 @@
       <c r="C23" s="35"/>
       <c r="D23" s="35"/>
       <c r="E23" s="35" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="F23" s="35"/>
       <c r="G23" s="35"/>
@@ -67128,7 +67125,7 @@
       <c r="C24" s="35"/>
       <c r="D24" s="35"/>
       <c r="E24" s="35" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
       <c r="F24" s="35"/>
       <c r="G24" s="35"/>
@@ -67140,7 +67137,7 @@
       <c r="C25" s="35"/>
       <c r="D25" s="35"/>
       <c r="E25" s="35" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
       <c r="F25" s="35"/>
       <c r="G25" s="35"/>
@@ -67152,7 +67149,7 @@
       <c r="C26" s="35"/>
       <c r="D26" s="35"/>
       <c r="E26" s="35" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="F26" s="35"/>
       <c r="G26" s="35"/>
@@ -67164,7 +67161,7 @@
       <c r="C27" s="35"/>
       <c r="D27" s="35"/>
       <c r="E27" s="35" t="s">
-        <v>1319</v>
+        <v>1314</v>
       </c>
       <c r="F27" s="35"/>
       <c r="G27" s="35"/>
@@ -67176,7 +67173,7 @@
       <c r="C28" s="35"/>
       <c r="D28" s="35"/>
       <c r="E28" s="35" t="s">
-        <v>1320</v>
+        <v>1315</v>
       </c>
       <c r="F28" s="35"/>
       <c r="G28" s="35"/>
@@ -67188,7 +67185,7 @@
       <c r="C29" s="35"/>
       <c r="D29" s="35"/>
       <c r="E29" s="35" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="F29" s="35"/>
       <c r="G29" s="35"/>
@@ -67200,7 +67197,7 @@
       <c r="C30" s="35"/>
       <c r="D30" s="35"/>
       <c r="E30" s="35" t="s">
-        <v>1322</v>
+        <v>1317</v>
       </c>
       <c r="F30" s="35"/>
       <c r="G30" s="35"/>
@@ -67212,7 +67209,7 @@
       <c r="C31" s="35"/>
       <c r="D31" s="35"/>
       <c r="E31" s="35" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
       <c r="F31" s="35"/>
       <c r="G31" s="35"/>
@@ -67224,7 +67221,7 @@
       <c r="C32" s="35"/>
       <c r="D32" s="35"/>
       <c r="E32" s="35" t="s">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="F32" s="35"/>
       <c r="G32" s="35"/>
@@ -67236,7 +67233,7 @@
       <c r="C33" s="35"/>
       <c r="D33" s="35"/>
       <c r="E33" s="35" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="F33" s="35"/>
       <c r="G33" s="35"/>
@@ -67248,7 +67245,7 @@
       <c r="C34" s="35"/>
       <c r="D34" s="35"/>
       <c r="E34" s="35" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="F34" s="35"/>
       <c r="G34" s="35"/>
@@ -67260,7 +67257,7 @@
       <c r="C35" s="35"/>
       <c r="D35" s="35"/>
       <c r="E35" s="35" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="F35" s="35"/>
       <c r="G35" s="35"/>
@@ -67272,7 +67269,7 @@
       <c r="C36" s="35"/>
       <c r="D36" s="35"/>
       <c r="E36" s="35" t="s">
-        <v>1717</v>
+        <v>1712</v>
       </c>
       <c r="F36" s="35"/>
       <c r="G36" s="35"/>
@@ -67284,7 +67281,7 @@
       <c r="C37" s="35"/>
       <c r="D37" s="35"/>
       <c r="E37" s="35" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
       <c r="F37" s="35"/>
       <c r="G37" s="35"/>
@@ -67296,7 +67293,7 @@
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
       <c r="E38" s="35" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
@@ -67308,7 +67305,7 @@
       <c r="C39" s="35"/>
       <c r="D39" s="35"/>
       <c r="E39" s="35" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
       <c r="F39" s="35"/>
       <c r="G39" s="35"/>
@@ -67320,7 +67317,7 @@
       <c r="C40" s="35"/>
       <c r="D40" s="35"/>
       <c r="E40" s="35" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="F40" s="35"/>
       <c r="G40" s="35"/>
@@ -67332,7 +67329,7 @@
       <c r="C41" s="35"/>
       <c r="D41" s="35"/>
       <c r="E41" s="35" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="F41" s="35"/>
       <c r="G41" s="35"/>
@@ -67344,7 +67341,7 @@
       <c r="C42" s="35"/>
       <c r="D42" s="35"/>
       <c r="E42" s="35" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="F42" s="35"/>
       <c r="G42" s="35"/>
@@ -67356,7 +67353,7 @@
       <c r="C43" s="35"/>
       <c r="D43" s="35"/>
       <c r="E43" s="35" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
@@ -67368,7 +67365,7 @@
       <c r="C44" s="35"/>
       <c r="D44" s="35"/>
       <c r="E44" s="35" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="F44" s="35"/>
       <c r="G44" s="35"/>
@@ -67380,7 +67377,7 @@
       <c r="C45" s="35"/>
       <c r="D45" s="35"/>
       <c r="E45" s="35" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="F45" s="35"/>
       <c r="G45" s="35"/>
@@ -67392,7 +67389,7 @@
       <c r="C46" s="35"/>
       <c r="D46" s="35"/>
       <c r="E46" s="35" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="F46" s="35"/>
       <c r="G46" s="35"/>
@@ -67404,7 +67401,7 @@
       <c r="C47" s="35"/>
       <c r="D47" s="35"/>
       <c r="E47" s="35" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
       <c r="F47" s="35"/>
       <c r="G47" s="35"/>
@@ -67416,7 +67413,7 @@
       <c r="C48" s="35"/>
       <c r="D48" s="35"/>
       <c r="E48" s="35" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
       <c r="F48" s="35"/>
       <c r="G48" s="35"/>
@@ -67428,7 +67425,7 @@
       <c r="C49" s="35"/>
       <c r="D49" s="35"/>
       <c r="E49" s="35" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
       <c r="F49" s="35"/>
       <c r="G49" s="35"/>
@@ -67440,7 +67437,7 @@
       <c r="C50" s="35"/>
       <c r="D50" s="35"/>
       <c r="E50" s="35" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="F50" s="35"/>
       <c r="G50" s="35"/>
@@ -67460,7 +67457,7 @@
         <v>429</v>
       </c>
       <c r="E51" s="35" t="s">
-        <v>1342</v>
+        <v>1337</v>
       </c>
       <c r="F51" s="35"/>
       <c r="G51" s="35"/>
@@ -67472,7 +67469,7 @@
       <c r="C52" s="35"/>
       <c r="D52" s="35"/>
       <c r="E52" s="35" t="s">
-        <v>1343</v>
+        <v>1338</v>
       </c>
       <c r="F52" s="35"/>
       <c r="G52" s="35"/>
@@ -67484,7 +67481,7 @@
       <c r="C53" s="35"/>
       <c r="D53" s="35"/>
       <c r="E53" s="35" t="s">
-        <v>1344</v>
+        <v>1339</v>
       </c>
       <c r="F53" s="35"/>
       <c r="G53" s="35"/>
@@ -67496,7 +67493,7 @@
       <c r="C54" s="35"/>
       <c r="D54" s="35"/>
       <c r="E54" s="35" t="s">
-        <v>1345</v>
+        <v>1340</v>
       </c>
       <c r="F54" s="35"/>
       <c r="G54" s="35"/>
@@ -67508,7 +67505,7 @@
       <c r="C55" s="35"/>
       <c r="D55" s="35"/>
       <c r="E55" s="35" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
@@ -67520,7 +67517,7 @@
       <c r="C56" s="35"/>
       <c r="D56" s="35"/>
       <c r="E56" s="35" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="F56" s="35"/>
       <c r="G56" s="35"/>
@@ -67532,7 +67529,7 @@
       <c r="C57" s="35"/>
       <c r="D57" s="35"/>
       <c r="E57" s="35" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
       <c r="F57" s="35"/>
       <c r="G57" s="35"/>
@@ -67544,7 +67541,7 @@
       <c r="C58" s="35"/>
       <c r="D58" s="35"/>
       <c r="E58" s="35" t="s">
-        <v>1349</v>
+        <v>1344</v>
       </c>
       <c r="F58" s="35"/>
       <c r="G58" s="35"/>
@@ -67556,7 +67553,7 @@
       <c r="C59" s="35"/>
       <c r="D59" s="35"/>
       <c r="E59" s="35" t="s">
-        <v>1350</v>
+        <v>1345</v>
       </c>
       <c r="F59" s="35"/>
       <c r="G59" s="35"/>
@@ -67568,7 +67565,7 @@
       <c r="C60" s="35"/>
       <c r="D60" s="35"/>
       <c r="E60" s="35" t="s">
-        <v>1351</v>
+        <v>1346</v>
       </c>
       <c r="F60" s="35"/>
       <c r="G60" s="35"/>
@@ -67580,7 +67577,7 @@
       <c r="C61" s="35"/>
       <c r="D61" s="35"/>
       <c r="E61" s="35" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="F61" s="35"/>
       <c r="G61" s="35"/>
@@ -67592,7 +67589,7 @@
       <c r="C62" s="35"/>
       <c r="D62" s="35"/>
       <c r="E62" s="35" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
       <c r="F62" s="35"/>
       <c r="G62" s="35"/>
@@ -67604,7 +67601,7 @@
       <c r="C63" s="35"/>
       <c r="D63" s="35"/>
       <c r="E63" s="35" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
       <c r="F63" s="35"/>
       <c r="G63" s="35"/>
@@ -67616,7 +67613,7 @@
       <c r="C64" s="35"/>
       <c r="D64" s="35"/>
       <c r="E64" s="35" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="F64" s="35"/>
       <c r="G64" s="35"/>
@@ -67628,7 +67625,7 @@
       <c r="C65" s="35"/>
       <c r="D65" s="35"/>
       <c r="E65" s="35" t="s">
-        <v>1356</v>
+        <v>1351</v>
       </c>
       <c r="F65" s="35"/>
       <c r="G65" s="35"/>
@@ -67640,7 +67637,7 @@
       <c r="C66" s="35"/>
       <c r="D66" s="35"/>
       <c r="E66" s="35" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="F66" s="35"/>
       <c r="G66" s="35"/>
@@ -67652,7 +67649,7 @@
       <c r="C67" s="35"/>
       <c r="D67" s="35"/>
       <c r="E67" s="35" t="s">
-        <v>1358</v>
+        <v>1353</v>
       </c>
       <c r="F67" s="35"/>
       <c r="G67" s="35"/>
@@ -67664,7 +67661,7 @@
       <c r="C68" s="35"/>
       <c r="D68" s="35"/>
       <c r="E68" s="35" t="s">
-        <v>1727</v>
+        <v>1722</v>
       </c>
       <c r="F68" s="35"/>
       <c r="G68" s="35"/>
@@ -67676,7 +67673,7 @@
       <c r="C69" s="35"/>
       <c r="D69" s="35"/>
       <c r="E69" s="35" t="s">
-        <v>1728</v>
+        <v>1723</v>
       </c>
       <c r="F69" s="35"/>
       <c r="G69" s="35"/>
@@ -67688,7 +67685,7 @@
       <c r="C70" s="35"/>
       <c r="D70" s="35"/>
       <c r="E70" s="35" t="s">
-        <v>1729</v>
+        <v>1724</v>
       </c>
       <c r="F70" s="35"/>
       <c r="G70" s="35"/>
@@ -67700,7 +67697,7 @@
       <c r="C71" s="35"/>
       <c r="D71" s="35"/>
       <c r="E71" s="35" t="s">
-        <v>1730</v>
+        <v>1725</v>
       </c>
       <c r="F71" s="35"/>
       <c r="G71" s="35"/>
@@ -67712,7 +67709,7 @@
       <c r="C72" s="35"/>
       <c r="D72" s="35"/>
       <c r="E72" s="35" t="s">
-        <v>1731</v>
+        <v>1726</v>
       </c>
       <c r="F72" s="35"/>
       <c r="G72" s="35"/>
@@ -67724,7 +67721,7 @@
       <c r="C73" s="35"/>
       <c r="D73" s="35"/>
       <c r="E73" s="35" t="s">
-        <v>1732</v>
+        <v>1727</v>
       </c>
       <c r="F73" s="35"/>
       <c r="G73" s="35"/>
@@ -67736,7 +67733,7 @@
       <c r="C74" s="35"/>
       <c r="D74" s="35"/>
       <c r="E74" s="35" t="s">
-        <v>1733</v>
+        <v>1728</v>
       </c>
       <c r="F74" s="35"/>
       <c r="G74" s="35"/>
@@ -67748,7 +67745,7 @@
       <c r="C75" s="35"/>
       <c r="D75" s="35"/>
       <c r="E75" s="35" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="F75" s="35"/>
       <c r="G75" s="35"/>
@@ -67760,7 +67757,7 @@
       <c r="C76" s="35"/>
       <c r="D76" s="35"/>
       <c r="E76" s="35" t="s">
-        <v>1735</v>
+        <v>1730</v>
       </c>
       <c r="F76" s="35"/>
       <c r="G76" s="35"/>
@@ -67772,7 +67769,7 @@
       <c r="C77" s="35"/>
       <c r="D77" s="35"/>
       <c r="E77" s="35" t="s">
-        <v>1736</v>
+        <v>1731</v>
       </c>
       <c r="F77" s="35"/>
       <c r="G77" s="35"/>
@@ -67783,16 +67780,16 @@
         <v>5</v>
       </c>
       <c r="B78" s="35" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="C78" s="35" t="s">
         <v>377</v>
       </c>
       <c r="D78" s="35" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="E78" s="136" t="s">
-        <v>1359</v>
+        <v>1354</v>
       </c>
       <c r="F78" s="35"/>
       <c r="G78" s="35"/>
@@ -67804,7 +67801,7 @@
       <c r="C79" s="35"/>
       <c r="D79" s="35"/>
       <c r="E79" s="35" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="F79" s="35"/>
       <c r="G79" s="35"/>
@@ -67816,7 +67813,7 @@
       <c r="C80" s="35"/>
       <c r="D80" s="35"/>
       <c r="E80" s="35" t="s">
-        <v>1361</v>
+        <v>1356</v>
       </c>
       <c r="F80" s="35"/>
       <c r="G80" s="35"/>
@@ -67828,7 +67825,7 @@
       <c r="C81" s="35"/>
       <c r="D81" s="35"/>
       <c r="E81" s="35" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="F81" s="35"/>
       <c r="G81" s="35"/>
@@ -67845,10 +67842,10 @@
         <v>377</v>
       </c>
       <c r="D82" s="35" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="E82" s="35" t="s">
-        <v>1363</v>
+        <v>1358</v>
       </c>
       <c r="F82" s="35"/>
       <c r="G82" s="35"/>
@@ -67860,7 +67857,7 @@
       <c r="C83" s="35"/>
       <c r="D83" s="35"/>
       <c r="E83" s="35" t="s">
-        <v>1364</v>
+        <v>1359</v>
       </c>
       <c r="F83" s="35"/>
       <c r="G83" s="35"/>
@@ -67872,7 +67869,7 @@
       <c r="C84" s="35"/>
       <c r="D84" s="35"/>
       <c r="E84" s="35" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
       <c r="F84" s="35"/>
       <c r="G84" s="35"/>
@@ -67884,7 +67881,7 @@
       <c r="C85" s="35"/>
       <c r="D85" s="35"/>
       <c r="E85" s="35" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="F85" s="35"/>
       <c r="G85" s="35"/>
@@ -67895,7 +67892,7 @@
         <v>5</v>
       </c>
       <c r="B86" s="35" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="C86" s="35" t="s">
         <v>377</v>
@@ -67904,7 +67901,7 @@
         <v>650</v>
       </c>
       <c r="E86" s="35" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="F86" s="35"/>
       <c r="G86" s="35"/>
@@ -67916,7 +67913,7 @@
       <c r="C87" s="35"/>
       <c r="D87" s="35"/>
       <c r="E87" s="35" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
       <c r="F87" s="35"/>
       <c r="G87" s="35"/>
@@ -67928,7 +67925,7 @@
       <c r="C88" s="35"/>
       <c r="D88" s="35"/>
       <c r="E88" s="35" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="F88" s="35"/>
       <c r="G88" s="35"/>
@@ -67940,7 +67937,7 @@
       <c r="C89" s="35"/>
       <c r="D89" s="35"/>
       <c r="E89" s="35" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="F89" s="35"/>
       <c r="G89" s="35"/>
@@ -67952,7 +67949,7 @@
       <c r="C90" s="35"/>
       <c r="D90" s="35"/>
       <c r="E90" s="35" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="F90" s="35"/>
       <c r="G90" s="35"/>
@@ -67964,7 +67961,7 @@
       <c r="C91" s="35"/>
       <c r="D91" s="35"/>
       <c r="E91" s="35" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="F91" s="35"/>
       <c r="G91" s="35"/>
@@ -67976,7 +67973,7 @@
       <c r="C92" s="35"/>
       <c r="D92" s="35"/>
       <c r="E92" s="35" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="F92" s="35"/>
       <c r="G92" s="35"/>
@@ -67988,7 +67985,7 @@
       <c r="C93" s="35"/>
       <c r="D93" s="35"/>
       <c r="E93" s="35" t="s">
-        <v>1369</v>
+        <v>1364</v>
       </c>
       <c r="F93" s="35"/>
       <c r="G93" s="35"/>
@@ -68000,7 +67997,7 @@
       <c r="C94" s="35"/>
       <c r="D94" s="35"/>
       <c r="E94" s="35" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="F94" s="107"/>
       <c r="G94" s="35"/>
@@ -68020,7 +68017,7 @@
         <v>647</v>
       </c>
       <c r="E95" s="35" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
       <c r="F95" s="35"/>
       <c r="G95" s="35"/>
@@ -68032,7 +68029,7 @@
       <c r="C96" s="35"/>
       <c r="D96" s="35"/>
       <c r="E96" s="35" t="s">
-        <v>1371</v>
+        <v>1366</v>
       </c>
       <c r="F96" s="35"/>
       <c r="G96" s="35"/>
@@ -68044,7 +68041,7 @@
       <c r="C97" s="35"/>
       <c r="D97" s="35"/>
       <c r="E97" s="35" t="s">
-        <v>1372</v>
+        <v>1367</v>
       </c>
       <c r="F97" s="35"/>
       <c r="G97" s="35"/>
@@ -68056,7 +68053,7 @@
       <c r="C98" s="35"/>
       <c r="D98" s="35"/>
       <c r="E98" s="33" t="s">
-        <v>1373</v>
+        <v>1368</v>
       </c>
       <c r="F98" s="35"/>
       <c r="G98" s="35"/>
@@ -68068,7 +68065,7 @@
       <c r="C99" s="35"/>
       <c r="D99" s="35"/>
       <c r="E99" s="33" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="F99" s="35"/>
       <c r="G99" s="35"/>
@@ -68080,7 +68077,7 @@
       <c r="C100" s="35"/>
       <c r="D100" s="35"/>
       <c r="E100" s="33" t="s">
-        <v>1375</v>
+        <v>1370</v>
       </c>
       <c r="F100" s="35"/>
       <c r="G100" s="35"/>
@@ -68092,7 +68089,7 @@
       <c r="C101" s="35"/>
       <c r="D101" s="35"/>
       <c r="E101" s="33" t="s">
-        <v>1376</v>
+        <v>1371</v>
       </c>
       <c r="F101" s="35"/>
       <c r="G101" s="35"/>
@@ -68104,7 +68101,7 @@
       <c r="C102" s="35"/>
       <c r="D102" s="35"/>
       <c r="E102" s="33" t="s">
-        <v>1377</v>
+        <v>1372</v>
       </c>
       <c r="F102" s="35"/>
       <c r="G102" s="35"/>
@@ -68116,7 +68113,7 @@
       <c r="C103" s="35"/>
       <c r="D103" s="35"/>
       <c r="E103" s="33" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="F103" s="35"/>
       <c r="G103" s="35"/>
@@ -68128,7 +68125,7 @@
       <c r="C104" s="35"/>
       <c r="D104" s="35"/>
       <c r="E104" s="33" t="s">
-        <v>1379</v>
+        <v>1374</v>
       </c>
       <c r="F104" s="35"/>
       <c r="G104" s="35"/>
@@ -68140,7 +68137,7 @@
       <c r="C105" s="35"/>
       <c r="D105" s="35"/>
       <c r="E105" s="33" t="s">
-        <v>1380</v>
+        <v>1375</v>
       </c>
       <c r="F105" s="35"/>
       <c r="G105" s="35"/>
@@ -68152,7 +68149,7 @@
       <c r="C106" s="35"/>
       <c r="D106" s="35"/>
       <c r="E106" s="33" t="s">
-        <v>1381</v>
+        <v>1376</v>
       </c>
       <c r="F106" s="35"/>
       <c r="G106" s="35"/>
@@ -68164,7 +68161,7 @@
       <c r="C107" s="35"/>
       <c r="D107" s="35"/>
       <c r="E107" s="33" t="s">
-        <v>1382</v>
+        <v>1377</v>
       </c>
       <c r="F107" s="35"/>
       <c r="G107" s="35"/>
@@ -68176,7 +68173,7 @@
       <c r="C108" s="35"/>
       <c r="D108" s="35"/>
       <c r="E108" s="33" t="s">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="F108" s="35"/>
       <c r="G108" s="35"/>
@@ -68188,7 +68185,7 @@
       <c r="C109" s="35"/>
       <c r="D109" s="35"/>
       <c r="E109" s="33" t="s">
-        <v>1384</v>
+        <v>1379</v>
       </c>
       <c r="F109" s="35"/>
       <c r="G109" s="35"/>
@@ -68200,7 +68197,7 @@
       <c r="C110" s="35"/>
       <c r="D110" s="35"/>
       <c r="E110" s="33" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="F110" s="35"/>
       <c r="G110" s="35"/>
@@ -68212,7 +68209,7 @@
       <c r="C111" s="35"/>
       <c r="D111" s="35"/>
       <c r="E111" s="33" t="s">
-        <v>1386</v>
+        <v>1381</v>
       </c>
       <c r="F111" s="35"/>
       <c r="G111" s="35"/>
@@ -68224,7 +68221,7 @@
       <c r="C112" s="35"/>
       <c r="D112" s="35"/>
       <c r="E112" s="33" t="s">
-        <v>1387</v>
+        <v>1382</v>
       </c>
       <c r="F112" s="35"/>
       <c r="G112" s="35"/>
@@ -68236,7 +68233,7 @@
       <c r="C113" s="35"/>
       <c r="D113" s="35"/>
       <c r="E113" s="33" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F113" s="35"/>
       <c r="G113" s="35"/>
@@ -68248,7 +68245,7 @@
       <c r="C114" s="35"/>
       <c r="D114" s="35"/>
       <c r="E114" s="33" t="s">
-        <v>1389</v>
+        <v>1384</v>
       </c>
       <c r="F114" s="35"/>
       <c r="G114" s="35"/>
@@ -68260,7 +68257,7 @@
       <c r="C115" s="35"/>
       <c r="D115" s="35"/>
       <c r="E115" s="33" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F115" s="35"/>
       <c r="G115" s="35"/>
@@ -68272,7 +68269,7 @@
       <c r="C116" s="35"/>
       <c r="D116" s="35"/>
       <c r="E116" s="33" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="F116" s="35"/>
       <c r="G116" s="35"/>
@@ -68284,7 +68281,7 @@
       <c r="C117" s="35"/>
       <c r="D117" s="35"/>
       <c r="E117" s="33" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="F117" s="35"/>
       <c r="G117" s="35"/>
@@ -68296,7 +68293,7 @@
       <c r="C118" s="35"/>
       <c r="D118" s="35"/>
       <c r="E118" s="33" t="s">
-        <v>1393</v>
+        <v>1388</v>
       </c>
       <c r="F118" s="35"/>
       <c r="G118" s="35"/>
@@ -68308,7 +68305,7 @@
       <c r="C119" s="35"/>
       <c r="D119" s="35"/>
       <c r="E119" s="33" t="s">
-        <v>1394</v>
+        <v>1389</v>
       </c>
       <c r="F119" s="35"/>
       <c r="G119" s="35"/>
@@ -68320,7 +68317,7 @@
       <c r="C120" s="35"/>
       <c r="D120" s="35"/>
       <c r="E120" s="33" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="F120" s="35"/>
       <c r="G120" s="35"/>
@@ -68332,7 +68329,7 @@
       <c r="C121" s="35"/>
       <c r="D121" s="35"/>
       <c r="E121" s="33" t="s">
-        <v>1396</v>
+        <v>1391</v>
       </c>
       <c r="F121" s="35"/>
       <c r="G121" s="35"/>
@@ -68344,7 +68341,7 @@
       <c r="C122" s="35"/>
       <c r="D122" s="35"/>
       <c r="E122" s="33" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="F122" s="35"/>
       <c r="G122" s="35"/>
@@ -68356,7 +68353,7 @@
       <c r="C123" s="35"/>
       <c r="D123" s="35"/>
       <c r="E123" s="33" t="s">
-        <v>1398</v>
+        <v>1393</v>
       </c>
       <c r="F123" s="35"/>
       <c r="G123" s="35"/>
@@ -68368,7 +68365,7 @@
       <c r="C124" s="35"/>
       <c r="D124" s="35"/>
       <c r="E124" s="33" t="s">
-        <v>1399</v>
+        <v>1394</v>
       </c>
       <c r="F124" s="35"/>
       <c r="G124" s="35"/>
@@ -68380,7 +68377,7 @@
       <c r="C125" s="35"/>
       <c r="D125" s="35"/>
       <c r="E125" s="33" t="s">
-        <v>1400</v>
+        <v>1395</v>
       </c>
       <c r="F125" s="35"/>
       <c r="G125" s="35"/>
@@ -68392,7 +68389,7 @@
       <c r="C126" s="35"/>
       <c r="D126" s="35"/>
       <c r="E126" s="33" t="s">
-        <v>1401</v>
+        <v>1396</v>
       </c>
       <c r="F126" s="35"/>
       <c r="G126" s="35"/>
@@ -68404,7 +68401,7 @@
       <c r="C127" s="35"/>
       <c r="D127" s="35"/>
       <c r="E127" s="33" t="s">
-        <v>1402</v>
+        <v>1397</v>
       </c>
       <c r="F127" s="35"/>
       <c r="G127" s="35"/>
@@ -68416,7 +68413,7 @@
       <c r="C128" s="35"/>
       <c r="D128" s="35"/>
       <c r="E128" s="33" t="s">
-        <v>1403</v>
+        <v>1398</v>
       </c>
       <c r="F128" s="35"/>
       <c r="G128" s="35"/>
@@ -68428,7 +68425,7 @@
       <c r="C129" s="35"/>
       <c r="D129" s="35"/>
       <c r="E129" s="33" t="s">
-        <v>1404</v>
+        <v>1399</v>
       </c>
       <c r="F129" s="35"/>
       <c r="G129" s="35"/>
@@ -68440,7 +68437,7 @@
       <c r="C130" s="35"/>
       <c r="D130" s="35"/>
       <c r="E130" s="33" t="s">
-        <v>1405</v>
+        <v>1400</v>
       </c>
       <c r="F130" s="35"/>
       <c r="G130" s="35"/>
@@ -68452,7 +68449,7 @@
       <c r="C131" s="35"/>
       <c r="D131" s="35"/>
       <c r="E131" s="35" t="s">
-        <v>1718</v>
+        <v>1713</v>
       </c>
       <c r="F131" s="35"/>
       <c r="G131" s="35"/>
@@ -68464,7 +68461,7 @@
       <c r="C132" s="35"/>
       <c r="D132" s="35"/>
       <c r="E132" s="35" t="s">
-        <v>1719</v>
+        <v>1714</v>
       </c>
       <c r="F132" s="35"/>
       <c r="G132" s="35"/>
@@ -68476,7 +68473,7 @@
       <c r="C133" s="35"/>
       <c r="D133" s="35"/>
       <c r="E133" s="35" t="s">
-        <v>1406</v>
+        <v>1401</v>
       </c>
       <c r="F133" s="35"/>
       <c r="G133" s="35"/>
@@ -68488,7 +68485,7 @@
       <c r="C134" s="35"/>
       <c r="D134" s="35"/>
       <c r="E134" s="35" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="F134" s="35"/>
       <c r="G134" s="35"/>
@@ -68500,7 +68497,7 @@
       <c r="C135" s="35"/>
       <c r="D135" s="35"/>
       <c r="E135" s="35" t="s">
-        <v>1408</v>
+        <v>1403</v>
       </c>
       <c r="F135" s="35"/>
       <c r="G135" s="35"/>
@@ -68512,7 +68509,7 @@
       <c r="C136" s="35"/>
       <c r="D136" s="35"/>
       <c r="E136" s="35" t="s">
-        <v>1409</v>
+        <v>1404</v>
       </c>
       <c r="F136" s="35"/>
       <c r="G136" s="35"/>
@@ -68532,7 +68529,7 @@
         <v>432</v>
       </c>
       <c r="E137" s="74" t="s">
-        <v>1410</v>
+        <v>1405</v>
       </c>
       <c r="F137" s="35"/>
       <c r="G137" s="35"/>
@@ -68544,7 +68541,7 @@
       <c r="C138" s="35"/>
       <c r="D138" s="35"/>
       <c r="E138" s="74" t="s">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="F138" s="35"/>
       <c r="G138" s="35"/>
@@ -68556,7 +68553,7 @@
       <c r="C139" s="35"/>
       <c r="D139" s="35"/>
       <c r="E139" s="35" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="F139" s="35"/>
       <c r="G139" s="35"/>
@@ -68568,7 +68565,7 @@
       <c r="C140" s="35"/>
       <c r="D140" s="35"/>
       <c r="E140" s="35" t="s">
-        <v>1413</v>
+        <v>1408</v>
       </c>
       <c r="F140" s="35"/>
       <c r="G140" s="35"/>
@@ -68580,7 +68577,7 @@
       <c r="C141" s="35"/>
       <c r="D141" s="35"/>
       <c r="E141" s="35" t="s">
-        <v>1414</v>
+        <v>1409</v>
       </c>
       <c r="F141" s="35"/>
       <c r="G141" s="35"/>
@@ -68592,7 +68589,7 @@
       <c r="C142" s="35"/>
       <c r="D142" s="35"/>
       <c r="E142" s="35" t="s">
-        <v>1415</v>
+        <v>1410</v>
       </c>
       <c r="F142" s="35"/>
       <c r="G142" s="35"/>
@@ -68604,7 +68601,7 @@
       <c r="C143" s="35"/>
       <c r="D143" s="35"/>
       <c r="E143" s="35" t="s">
-        <v>1416</v>
+        <v>1411</v>
       </c>
       <c r="F143" s="35"/>
       <c r="G143" s="35"/>
@@ -68616,7 +68613,7 @@
       <c r="C144" s="35"/>
       <c r="D144" s="35"/>
       <c r="E144" s="35" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="F144" s="35"/>
       <c r="G144" s="35"/>
@@ -68628,7 +68625,7 @@
       <c r="C145" s="35"/>
       <c r="D145" s="35"/>
       <c r="E145" s="35" t="s">
-        <v>1418</v>
+        <v>1413</v>
       </c>
       <c r="F145" s="35"/>
       <c r="G145" s="35"/>
@@ -68640,7 +68637,7 @@
       <c r="C146" s="35"/>
       <c r="D146" s="35"/>
       <c r="E146" s="35" t="s">
-        <v>1419</v>
+        <v>1414</v>
       </c>
       <c r="F146" s="35"/>
       <c r="G146" s="35"/>
@@ -68652,7 +68649,7 @@
       <c r="C147" s="35"/>
       <c r="D147" s="35"/>
       <c r="E147" s="35" t="s">
-        <v>1420</v>
+        <v>1415</v>
       </c>
       <c r="F147" s="35"/>
       <c r="G147" s="35"/>
@@ -68664,7 +68661,7 @@
       <c r="C148" s="35"/>
       <c r="D148" s="35"/>
       <c r="E148" s="35" t="s">
-        <v>1421</v>
+        <v>1416</v>
       </c>
       <c r="F148" s="35"/>
       <c r="G148" s="35"/>
@@ -68676,7 +68673,7 @@
       <c r="C149" s="35"/>
       <c r="D149" s="35"/>
       <c r="E149" s="35" t="s">
-        <v>1422</v>
+        <v>1417</v>
       </c>
       <c r="F149" s="35"/>
       <c r="G149" s="35"/>
@@ -68688,7 +68685,7 @@
       <c r="C150" s="35"/>
       <c r="D150" s="35"/>
       <c r="E150" s="35" t="s">
-        <v>1423</v>
+        <v>1418</v>
       </c>
       <c r="F150" s="35"/>
       <c r="G150" s="35"/>
@@ -68700,7 +68697,7 @@
       <c r="C151" s="35"/>
       <c r="D151" s="35"/>
       <c r="E151" s="35" t="s">
-        <v>1424</v>
+        <v>1419</v>
       </c>
       <c r="F151" s="35"/>
       <c r="G151" s="35"/>
@@ -68712,7 +68709,7 @@
       <c r="C152" s="35"/>
       <c r="D152" s="35"/>
       <c r="E152" s="35" t="s">
-        <v>1425</v>
+        <v>1420</v>
       </c>
       <c r="F152" s="35"/>
       <c r="G152" s="35"/>
@@ -68724,7 +68721,7 @@
       <c r="C153" s="35"/>
       <c r="D153" s="35"/>
       <c r="E153" s="35" t="s">
-        <v>1426</v>
+        <v>1421</v>
       </c>
       <c r="F153" s="35"/>
       <c r="G153" s="35"/>
@@ -68736,7 +68733,7 @@
       <c r="C154" s="35"/>
       <c r="D154" s="35"/>
       <c r="E154" s="35" t="s">
-        <v>1427</v>
+        <v>1422</v>
       </c>
       <c r="F154" s="35"/>
       <c r="G154" s="35"/>
@@ -68748,7 +68745,7 @@
       <c r="C155" s="35"/>
       <c r="D155" s="35"/>
       <c r="E155" s="35" t="s">
-        <v>1428</v>
+        <v>1423</v>
       </c>
       <c r="F155" s="35"/>
       <c r="G155" s="35"/>
@@ -68760,7 +68757,7 @@
       <c r="C156" s="35"/>
       <c r="D156" s="35"/>
       <c r="E156" s="35" t="s">
-        <v>1429</v>
+        <v>1424</v>
       </c>
       <c r="F156" s="35"/>
       <c r="G156" s="35"/>
@@ -68780,7 +68777,7 @@
         <v>434</v>
       </c>
       <c r="E157" s="35" t="s">
-        <v>1430</v>
+        <v>1425</v>
       </c>
       <c r="F157" s="35"/>
       <c r="G157" s="35"/>
@@ -68792,7 +68789,7 @@
       <c r="C158" s="35"/>
       <c r="D158" s="35"/>
       <c r="E158" s="35" t="s">
-        <v>1431</v>
+        <v>1426</v>
       </c>
       <c r="F158" s="35"/>
       <c r="G158" s="35"/>
@@ -68804,7 +68801,7 @@
       <c r="C159" s="35"/>
       <c r="D159" s="35"/>
       <c r="E159" s="35" t="s">
-        <v>1432</v>
+        <v>1427</v>
       </c>
       <c r="F159" s="35"/>
       <c r="G159" s="35"/>
@@ -68816,7 +68813,7 @@
       <c r="C160" s="35"/>
       <c r="D160" s="35"/>
       <c r="E160" s="35" t="s">
-        <v>1433</v>
+        <v>1428</v>
       </c>
       <c r="F160" s="35"/>
       <c r="G160" s="35"/>
@@ -68828,7 +68825,7 @@
       <c r="C161" s="35"/>
       <c r="D161" s="35"/>
       <c r="E161" s="35" t="s">
-        <v>1434</v>
+        <v>1429</v>
       </c>
       <c r="F161" s="35"/>
       <c r="G161" s="35"/>
@@ -68840,7 +68837,7 @@
       <c r="C162" s="35"/>
       <c r="D162" s="35"/>
       <c r="E162" s="35" t="s">
-        <v>1435</v>
+        <v>1430</v>
       </c>
       <c r="F162" s="35"/>
       <c r="G162" s="35"/>
@@ -68852,7 +68849,7 @@
       <c r="C163" s="35"/>
       <c r="D163" s="35"/>
       <c r="E163" s="35" t="s">
-        <v>1436</v>
+        <v>1431</v>
       </c>
       <c r="F163" s="35"/>
       <c r="G163" s="35"/>
@@ -68864,7 +68861,7 @@
       <c r="C164" s="35"/>
       <c r="D164" s="35"/>
       <c r="E164" s="35" t="s">
-        <v>1437</v>
+        <v>1432</v>
       </c>
       <c r="F164" s="35"/>
       <c r="G164" s="35"/>
@@ -68876,7 +68873,7 @@
       <c r="C165" s="35"/>
       <c r="D165" s="35"/>
       <c r="E165" s="35" t="s">
-        <v>1438</v>
+        <v>1433</v>
       </c>
       <c r="F165" s="35"/>
       <c r="G165" s="35"/>
@@ -68888,7 +68885,7 @@
       <c r="C166" s="35"/>
       <c r="D166" s="35"/>
       <c r="E166" s="35" t="s">
-        <v>1439</v>
+        <v>1434</v>
       </c>
       <c r="F166" s="35"/>
       <c r="G166" s="35"/>
@@ -68900,7 +68897,7 @@
       <c r="C167" s="35"/>
       <c r="D167" s="35"/>
       <c r="E167" s="35" t="s">
-        <v>1440</v>
+        <v>1435</v>
       </c>
       <c r="F167" s="35"/>
       <c r="G167" s="35"/>
@@ -68912,7 +68909,7 @@
       <c r="C168" s="35"/>
       <c r="D168" s="35"/>
       <c r="E168" s="35" t="s">
-        <v>1441</v>
+        <v>1436</v>
       </c>
       <c r="F168" s="35"/>
       <c r="G168" s="35"/>
@@ -68924,7 +68921,7 @@
       <c r="C169" s="35"/>
       <c r="D169" s="35"/>
       <c r="E169" s="35" t="s">
-        <v>1442</v>
+        <v>1437</v>
       </c>
       <c r="F169" s="35"/>
       <c r="G169" s="35"/>
@@ -68936,7 +68933,7 @@
       <c r="C170" s="35"/>
       <c r="D170" s="35"/>
       <c r="E170" s="35" t="s">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="F170" s="35"/>
       <c r="G170" s="35"/>
@@ -68948,7 +68945,7 @@
       <c r="C171" s="35"/>
       <c r="D171" s="35"/>
       <c r="E171" s="35" t="s">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="F171" s="35"/>
       <c r="G171" s="35"/>
@@ -68960,7 +68957,7 @@
       <c r="C172" s="35"/>
       <c r="D172" s="35"/>
       <c r="E172" s="35" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
       <c r="F172" s="35"/>
       <c r="G172" s="35"/>
@@ -68972,7 +68969,7 @@
       <c r="C173" s="35"/>
       <c r="D173" s="35"/>
       <c r="E173" s="35" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="F173" s="35"/>
       <c r="G173" s="35"/>
@@ -68984,7 +68981,7 @@
       <c r="C174" s="35"/>
       <c r="D174" s="35"/>
       <c r="E174" s="35" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="F174" s="35"/>
       <c r="G174" s="35"/>
@@ -68996,7 +68993,7 @@
       <c r="C175" s="35"/>
       <c r="D175" s="35"/>
       <c r="E175" s="35" t="s">
-        <v>1434</v>
+        <v>1429</v>
       </c>
       <c r="F175" s="35"/>
       <c r="G175" s="35"/>
@@ -69008,7 +69005,7 @@
       <c r="C176" s="35"/>
       <c r="D176" s="35"/>
       <c r="E176" s="35" t="s">
-        <v>1435</v>
+        <v>1430</v>
       </c>
       <c r="F176" s="35"/>
       <c r="G176" s="35"/>
@@ -69020,7 +69017,7 @@
       <c r="C177" s="35"/>
       <c r="D177" s="35"/>
       <c r="E177" s="35" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="F177" s="35"/>
       <c r="G177" s="35"/>
@@ -69032,7 +69029,7 @@
       <c r="C178" s="35"/>
       <c r="D178" s="35"/>
       <c r="E178" s="35" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="F178" s="35"/>
       <c r="G178" s="35"/>
@@ -69044,7 +69041,7 @@
       <c r="C179" s="35"/>
       <c r="D179" s="35"/>
       <c r="E179" s="35" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="F179" s="35"/>
       <c r="G179" s="35"/>
@@ -69056,7 +69053,7 @@
       <c r="C180" s="35"/>
       <c r="D180" s="35"/>
       <c r="E180" s="35" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="F180" s="35"/>
       <c r="G180" s="35"/>
@@ -69068,7 +69065,7 @@
       <c r="C181" s="35"/>
       <c r="D181" s="35"/>
       <c r="E181" s="35" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="F181" s="35"/>
       <c r="G181" s="35"/>
@@ -69080,7 +69077,7 @@
       <c r="C182" s="35"/>
       <c r="D182" s="35"/>
       <c r="E182" s="35" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="F182" s="35"/>
       <c r="G182" s="35"/>
@@ -69092,7 +69089,7 @@
       <c r="C183" s="35"/>
       <c r="D183" s="35"/>
       <c r="E183" s="35" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="F183" s="35"/>
       <c r="G183" s="35"/>
@@ -69104,7 +69101,7 @@
       <c r="C184" s="35"/>
       <c r="D184" s="35"/>
       <c r="E184" s="35" t="s">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="F184" s="35"/>
       <c r="G184" s="35"/>
@@ -69116,7 +69113,7 @@
       <c r="C185" s="35"/>
       <c r="D185" s="35"/>
       <c r="E185" s="35" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
       <c r="F185" s="35"/>
       <c r="G185" s="35"/>
@@ -69128,7 +69125,7 @@
       <c r="C186" s="35"/>
       <c r="D186" s="35"/>
       <c r="E186" s="35" t="s">
-        <v>1720</v>
+        <v>1715</v>
       </c>
       <c r="F186" s="35"/>
       <c r="G186" s="35"/>
@@ -69140,7 +69137,7 @@
       <c r="C187" s="35"/>
       <c r="D187" s="35"/>
       <c r="E187" s="35" t="s">
-        <v>1721</v>
+        <v>1716</v>
       </c>
       <c r="F187" s="35"/>
       <c r="G187" s="35"/>
@@ -69152,7 +69149,7 @@
       <c r="C188" s="35"/>
       <c r="D188" s="35"/>
       <c r="E188" s="35" t="s">
-        <v>1722</v>
+        <v>1717</v>
       </c>
       <c r="F188" s="35"/>
       <c r="G188" s="35"/>
@@ -69172,7 +69169,7 @@
         <v>585</v>
       </c>
       <c r="E189" s="98" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="F189" s="35"/>
       <c r="G189" s="35"/>
@@ -69196,7 +69193,7 @@
       <c r="C191" s="35"/>
       <c r="D191" s="35"/>
       <c r="E191" s="35" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="F191" s="35"/>
       <c r="G191" s="35"/>
@@ -69208,7 +69205,7 @@
       <c r="C192" s="35"/>
       <c r="D192" s="35"/>
       <c r="E192" s="35" t="s">
-        <v>1458</v>
+        <v>1453</v>
       </c>
       <c r="F192" s="35"/>
       <c r="G192" s="35"/>
@@ -69228,7 +69225,7 @@
         <v>436</v>
       </c>
       <c r="E193" s="35" t="s">
-        <v>1459</v>
+        <v>1454</v>
       </c>
       <c r="F193" s="35"/>
       <c r="G193" s="35"/>
@@ -69240,7 +69237,7 @@
       <c r="C194" s="35"/>
       <c r="D194" s="35"/>
       <c r="E194" s="35" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="F194" s="35"/>
       <c r="G194" s="35"/>
@@ -69252,7 +69249,7 @@
       <c r="C195" s="35"/>
       <c r="D195" s="35"/>
       <c r="E195" s="35" t="s">
-        <v>1461</v>
+        <v>1456</v>
       </c>
       <c r="F195" s="35"/>
       <c r="G195" s="35"/>
@@ -69264,7 +69261,7 @@
       <c r="C196" s="35"/>
       <c r="D196" s="35"/>
       <c r="E196" s="35" t="s">
-        <v>1462</v>
+        <v>1457</v>
       </c>
       <c r="F196" s="35"/>
       <c r="G196" s="35"/>
@@ -69276,7 +69273,7 @@
       <c r="C197" s="35"/>
       <c r="D197" s="35"/>
       <c r="E197" s="35" t="s">
-        <v>1463</v>
+        <v>1458</v>
       </c>
       <c r="F197" s="35"/>
       <c r="G197" s="35"/>
@@ -69288,7 +69285,7 @@
       <c r="C198" s="35"/>
       <c r="D198" s="35"/>
       <c r="E198" s="35" t="s">
-        <v>1464</v>
+        <v>1459</v>
       </c>
       <c r="F198" s="35"/>
       <c r="G198" s="35"/>
@@ -69300,7 +69297,7 @@
       <c r="C199" s="35"/>
       <c r="D199" s="35"/>
       <c r="E199" s="35" t="s">
-        <v>1465</v>
+        <v>1460</v>
       </c>
       <c r="F199" s="35"/>
       <c r="G199" s="35"/>
@@ -69312,7 +69309,7 @@
       <c r="C200" s="35"/>
       <c r="D200" s="35"/>
       <c r="E200" s="35" t="s">
-        <v>1466</v>
+        <v>1461</v>
       </c>
       <c r="F200" s="35"/>
       <c r="G200" s="35"/>
@@ -69324,7 +69321,7 @@
       <c r="C201" s="35"/>
       <c r="D201" s="35"/>
       <c r="E201" s="35" t="s">
-        <v>1467</v>
+        <v>1462</v>
       </c>
       <c r="F201" s="35"/>
       <c r="G201" s="35"/>
@@ -69336,7 +69333,7 @@
       <c r="C202" s="35"/>
       <c r="D202" s="35"/>
       <c r="E202" s="35" t="s">
-        <v>1468</v>
+        <v>1463</v>
       </c>
       <c r="F202" s="35"/>
       <c r="G202" s="35"/>
@@ -69348,7 +69345,7 @@
       <c r="C203" s="35"/>
       <c r="D203" s="35"/>
       <c r="E203" s="35" t="s">
-        <v>1469</v>
+        <v>1464</v>
       </c>
       <c r="F203" s="35"/>
       <c r="G203" s="35"/>
@@ -69360,7 +69357,7 @@
       <c r="C204" s="35"/>
       <c r="D204" s="35"/>
       <c r="E204" s="35" t="s">
-        <v>1470</v>
+        <v>1465</v>
       </c>
       <c r="F204" s="35"/>
       <c r="G204" s="35"/>
@@ -69372,7 +69369,7 @@
       <c r="C205" s="35"/>
       <c r="D205" s="35"/>
       <c r="E205" s="35" t="s">
-        <v>1471</v>
+        <v>1466</v>
       </c>
       <c r="F205" s="35"/>
       <c r="G205" s="35"/>
@@ -69384,7 +69381,7 @@
       <c r="C206" s="35"/>
       <c r="D206" s="35"/>
       <c r="E206" s="35" t="s">
-        <v>1472</v>
+        <v>1467</v>
       </c>
       <c r="F206" s="35"/>
       <c r="G206" s="35"/>
@@ -69396,7 +69393,7 @@
       <c r="C207" s="35"/>
       <c r="D207" s="35"/>
       <c r="E207" s="35" t="s">
-        <v>1473</v>
+        <v>1468</v>
       </c>
       <c r="F207" s="35"/>
       <c r="G207" s="35"/>
@@ -69408,7 +69405,7 @@
       <c r="C208" s="35"/>
       <c r="D208" s="35"/>
       <c r="E208" s="35" t="s">
-        <v>1474</v>
+        <v>1469</v>
       </c>
       <c r="F208" s="35"/>
       <c r="G208" s="35"/>
@@ -69420,7 +69417,7 @@
       <c r="C209" s="35"/>
       <c r="D209" s="35"/>
       <c r="E209" s="35" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="F209" s="35"/>
       <c r="G209" s="35"/>
@@ -69432,7 +69429,7 @@
       <c r="C210" s="35"/>
       <c r="D210" s="35"/>
       <c r="E210" s="35" t="s">
-        <v>1476</v>
+        <v>1471</v>
       </c>
       <c r="F210" s="35"/>
       <c r="G210" s="35"/>
@@ -69444,7 +69441,7 @@
       <c r="C211" s="35"/>
       <c r="D211" s="35"/>
       <c r="E211" s="35" t="s">
-        <v>1477</v>
+        <v>1472</v>
       </c>
       <c r="F211" s="35"/>
       <c r="G211" s="35"/>
@@ -69456,7 +69453,7 @@
       <c r="C212" s="35"/>
       <c r="D212" s="35"/>
       <c r="E212" s="35" t="s">
-        <v>1478</v>
+        <v>1473</v>
       </c>
       <c r="F212" s="35"/>
       <c r="G212" s="35"/>
@@ -69468,7 +69465,7 @@
       <c r="C213" s="35"/>
       <c r="D213" s="35"/>
       <c r="E213" s="35" t="s">
-        <v>1479</v>
+        <v>1474</v>
       </c>
       <c r="F213" s="35"/>
       <c r="G213" s="35"/>
@@ -69480,7 +69477,7 @@
       <c r="C214" s="35"/>
       <c r="D214" s="35"/>
       <c r="E214" s="35" t="s">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="F214" s="35"/>
       <c r="G214" s="35"/>
@@ -69492,7 +69489,7 @@
       <c r="C215" s="35"/>
       <c r="D215" s="35"/>
       <c r="E215" s="35" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="F215" s="35"/>
       <c r="G215" s="35"/>
@@ -69504,7 +69501,7 @@
       <c r="C216" s="35"/>
       <c r="D216" s="35"/>
       <c r="E216" s="35" t="s">
-        <v>1482</v>
+        <v>1477</v>
       </c>
       <c r="F216" s="35"/>
       <c r="G216" s="35"/>
@@ -69516,7 +69513,7 @@
       <c r="C217" s="35"/>
       <c r="D217" s="35"/>
       <c r="E217" s="35" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="F217" s="35"/>
       <c r="G217" s="35"/>
@@ -69528,7 +69525,7 @@
       <c r="C218" s="35"/>
       <c r="D218" s="35"/>
       <c r="E218" s="35" t="s">
-        <v>1484</v>
+        <v>1479</v>
       </c>
       <c r="F218" s="35"/>
       <c r="G218" s="35"/>
@@ -69540,7 +69537,7 @@
       <c r="C219" s="35"/>
       <c r="D219" s="35"/>
       <c r="E219" s="35" t="s">
-        <v>1485</v>
+        <v>1480</v>
       </c>
       <c r="F219" s="35"/>
       <c r="G219" s="35"/>
@@ -69552,7 +69549,7 @@
       <c r="C220" s="35"/>
       <c r="D220" s="35"/>
       <c r="E220" s="35" t="s">
-        <v>1486</v>
+        <v>1481</v>
       </c>
       <c r="F220" s="35"/>
       <c r="G220" s="35"/>
@@ -69564,7 +69561,7 @@
       <c r="C221" s="35"/>
       <c r="D221" s="35"/>
       <c r="E221" s="35" t="s">
-        <v>1487</v>
+        <v>1482</v>
       </c>
       <c r="F221" s="35"/>
       <c r="G221" s="35"/>
@@ -69576,7 +69573,7 @@
       <c r="C222" s="35"/>
       <c r="D222" s="35"/>
       <c r="E222" s="35" t="s">
-        <v>1488</v>
+        <v>1483</v>
       </c>
       <c r="F222" s="35"/>
       <c r="G222" s="35"/>
@@ -69588,7 +69585,7 @@
       <c r="C223" s="35"/>
       <c r="D223" s="35"/>
       <c r="E223" s="35" t="s">
-        <v>1489</v>
+        <v>1484</v>
       </c>
       <c r="F223" s="35"/>
       <c r="G223" s="35"/>
@@ -69600,7 +69597,7 @@
       <c r="C224" s="35"/>
       <c r="D224" s="35"/>
       <c r="E224" s="35" t="s">
-        <v>1490</v>
+        <v>1485</v>
       </c>
       <c r="F224" s="35"/>
       <c r="G224" s="35"/>
@@ -69612,7 +69609,7 @@
       <c r="C225" s="35"/>
       <c r="D225" s="35"/>
       <c r="E225" s="35" t="s">
-        <v>1491</v>
+        <v>1486</v>
       </c>
       <c r="F225" s="35"/>
       <c r="G225" s="35"/>
@@ -69624,7 +69621,7 @@
       <c r="C226" s="35"/>
       <c r="D226" s="35"/>
       <c r="E226" s="35" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
       <c r="F226" s="35"/>
       <c r="G226" s="35"/>
@@ -69636,7 +69633,7 @@
       <c r="C227" s="35"/>
       <c r="D227" s="35"/>
       <c r="E227" s="35" t="s">
-        <v>1493</v>
+        <v>1488</v>
       </c>
       <c r="F227" s="35"/>
       <c r="G227" s="35"/>
@@ -69648,7 +69645,7 @@
       <c r="C228" s="35"/>
       <c r="D228" s="35"/>
       <c r="E228" s="35" t="s">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="F228" s="35"/>
       <c r="G228" s="35"/>
@@ -69660,7 +69657,7 @@
       <c r="C229" s="35"/>
       <c r="D229" s="35"/>
       <c r="E229" s="35" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="F229" s="35"/>
       <c r="G229" s="35"/>
@@ -69672,7 +69669,7 @@
       <c r="C230" s="35"/>
       <c r="D230" s="35"/>
       <c r="E230" s="35" t="s">
-        <v>1496</v>
+        <v>1491</v>
       </c>
       <c r="F230" s="35"/>
       <c r="G230" s="35"/>
@@ -69684,7 +69681,7 @@
       <c r="C231" s="35"/>
       <c r="D231" s="35"/>
       <c r="E231" s="35" t="s">
-        <v>1723</v>
+        <v>1718</v>
       </c>
       <c r="F231" s="35"/>
       <c r="G231" s="35"/>
@@ -69696,7 +69693,7 @@
       <c r="C232" s="35"/>
       <c r="D232" s="35"/>
       <c r="E232" s="35" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
       <c r="F232" s="35"/>
       <c r="G232" s="35"/>
@@ -69708,7 +69705,7 @@
       <c r="C233" s="35"/>
       <c r="D233" s="35"/>
       <c r="E233" s="35" t="s">
-        <v>1498</v>
+        <v>1493</v>
       </c>
       <c r="F233" s="35"/>
       <c r="G233" s="35"/>
@@ -69720,7 +69717,7 @@
       <c r="C234" s="35"/>
       <c r="D234" s="35"/>
       <c r="E234" s="35" t="s">
-        <v>1499</v>
+        <v>1494</v>
       </c>
       <c r="F234" s="35"/>
       <c r="G234" s="35"/>
@@ -69732,7 +69729,7 @@
       <c r="C235" s="35"/>
       <c r="D235" s="35"/>
       <c r="E235" s="35" t="s">
-        <v>1500</v>
+        <v>1495</v>
       </c>
       <c r="F235" s="35"/>
       <c r="G235" s="35"/>
@@ -69744,7 +69741,7 @@
       <c r="C236" s="35"/>
       <c r="D236" s="35"/>
       <c r="E236" s="35" t="s">
-        <v>1501</v>
+        <v>1496</v>
       </c>
       <c r="F236" s="35"/>
       <c r="G236" s="35"/>
@@ -69756,7 +69753,7 @@
       <c r="C237" s="35"/>
       <c r="D237" s="35"/>
       <c r="E237" s="35" t="s">
-        <v>1502</v>
+        <v>1497</v>
       </c>
       <c r="F237" s="35"/>
       <c r="G237" s="35"/>
@@ -69768,7 +69765,7 @@
       <c r="C238" s="35"/>
       <c r="D238" s="35"/>
       <c r="E238" s="35" t="s">
-        <v>1503</v>
+        <v>1498</v>
       </c>
       <c r="F238" s="35"/>
       <c r="G238" s="35"/>
@@ -69780,7 +69777,7 @@
       <c r="C239" s="35"/>
       <c r="D239" s="35"/>
       <c r="E239" s="35" t="s">
-        <v>1504</v>
+        <v>1499</v>
       </c>
       <c r="F239" s="35"/>
       <c r="G239" s="35"/>
@@ -69792,7 +69789,7 @@
       <c r="C240" s="35"/>
       <c r="D240" s="35"/>
       <c r="E240" s="35" t="s">
-        <v>1505</v>
+        <v>1500</v>
       </c>
       <c r="F240" s="35"/>
       <c r="G240" s="35"/>
@@ -69800,7 +69797,7 @@
     </row>
     <row r="241" spans="1:9" s="36" customFormat="1" ht="16">
       <c r="E241" s="35" t="s">
-        <v>1506</v>
+        <v>1501</v>
       </c>
       <c r="I241" s="73"/>
     </row>
@@ -69810,7 +69807,7 @@
       <c r="C242" s="36"/>
       <c r="D242" s="36"/>
       <c r="E242" s="35" t="s">
-        <v>1724</v>
+        <v>1719</v>
       </c>
       <c r="F242" s="36"/>
       <c r="G242" s="36"/>
@@ -69822,7 +69819,7 @@
       <c r="C243" s="36"/>
       <c r="D243" s="36"/>
       <c r="E243" s="35" t="s">
-        <v>1725</v>
+        <v>1720</v>
       </c>
       <c r="F243" s="36"/>
       <c r="G243" s="36"/>
@@ -69834,7 +69831,7 @@
       <c r="C244" s="36"/>
       <c r="D244" s="36"/>
       <c r="E244" s="35" t="s">
-        <v>1726</v>
+        <v>1721</v>
       </c>
       <c r="F244" s="36"/>
       <c r="G244" s="36"/>
@@ -69854,7 +69851,7 @@
         <v>649</v>
       </c>
       <c r="E245" s="35" t="s">
-        <v>1507</v>
+        <v>1502</v>
       </c>
       <c r="F245" s="36"/>
       <c r="G245" s="36"/>
@@ -69866,7 +69863,7 @@
       <c r="C246" s="36"/>
       <c r="D246" s="36"/>
       <c r="E246" s="35" t="s">
-        <v>1508</v>
+        <v>1503</v>
       </c>
       <c r="F246" s="36"/>
       <c r="G246" s="36"/>
@@ -69878,7 +69875,7 @@
       <c r="C247" s="36"/>
       <c r="D247" s="36"/>
       <c r="E247" s="35" t="s">
-        <v>1509</v>
+        <v>1504</v>
       </c>
       <c r="F247" s="36"/>
       <c r="G247" s="36"/>
@@ -69890,7 +69887,7 @@
       <c r="C248" s="36"/>
       <c r="D248" s="36"/>
       <c r="E248" s="35" t="s">
-        <v>1510</v>
+        <v>1505</v>
       </c>
       <c r="F248" s="36"/>
       <c r="G248" s="36"/>
@@ -69902,7 +69899,7 @@
       <c r="C249" s="36"/>
       <c r="D249" s="36"/>
       <c r="E249" s="35" t="s">
-        <v>1511</v>
+        <v>1506</v>
       </c>
       <c r="F249" s="36"/>
       <c r="G249" s="36"/>
@@ -69914,7 +69911,7 @@
       <c r="C250" s="36"/>
       <c r="D250" s="36"/>
       <c r="E250" s="35" t="s">
-        <v>1512</v>
+        <v>1507</v>
       </c>
       <c r="F250" s="36"/>
       <c r="G250" s="36"/>
@@ -69926,7 +69923,7 @@
       <c r="C251" s="36"/>
       <c r="D251" s="36"/>
       <c r="E251" s="35" t="s">
-        <v>1513</v>
+        <v>1508</v>
       </c>
       <c r="F251" s="36"/>
       <c r="G251" s="36"/>
@@ -69938,7 +69935,7 @@
       <c r="C252" s="36"/>
       <c r="D252" s="36"/>
       <c r="E252" s="35" t="s">
-        <v>1514</v>
+        <v>1509</v>
       </c>
       <c r="F252" s="36"/>
       <c r="G252" s="36"/>
@@ -69950,7 +69947,7 @@
       <c r="C253" s="36"/>
       <c r="D253" s="36"/>
       <c r="E253" s="35" t="s">
-        <v>1515</v>
+        <v>1510</v>
       </c>
       <c r="F253" s="36"/>
       <c r="G253" s="36"/>
@@ -69962,7 +69959,7 @@
       <c r="C254" s="36"/>
       <c r="D254" s="36"/>
       <c r="E254" s="35" t="s">
-        <v>1516</v>
+        <v>1511</v>
       </c>
       <c r="F254" s="36"/>
       <c r="G254" s="36"/>
@@ -69974,7 +69971,7 @@
       <c r="C255" s="36"/>
       <c r="D255" s="36"/>
       <c r="E255" s="35" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="F255" s="36"/>
       <c r="G255" s="36"/>
@@ -69986,7 +69983,7 @@
       <c r="C256" s="36"/>
       <c r="D256" s="36"/>
       <c r="E256" s="35" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="F256" s="36"/>
       <c r="G256" s="36"/>
@@ -69998,7 +69995,7 @@
       <c r="C257" s="36"/>
       <c r="D257" s="36"/>
       <c r="E257" s="35" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="F257" s="36"/>
       <c r="G257" s="36"/>
@@ -70010,7 +70007,7 @@
       <c r="C258" s="36"/>
       <c r="D258" s="36"/>
       <c r="E258" s="35" t="s">
-        <v>1520</v>
+        <v>1515</v>
       </c>
       <c r="F258" s="36"/>
       <c r="G258" s="36"/>
@@ -70022,7 +70019,7 @@
       <c r="C259" s="36"/>
       <c r="D259" s="36"/>
       <c r="E259" s="35" t="s">
-        <v>1521</v>
+        <v>1516</v>
       </c>
       <c r="F259" s="36"/>
       <c r="G259" s="36"/>
@@ -70034,7 +70031,7 @@
       <c r="C260" s="36"/>
       <c r="D260" s="36"/>
       <c r="E260" s="35" t="s">
-        <v>1522</v>
+        <v>1517</v>
       </c>
       <c r="F260" s="36"/>
       <c r="G260" s="36"/>
@@ -70046,7 +70043,7 @@
       <c r="C261" s="36"/>
       <c r="D261" s="36"/>
       <c r="E261" s="35" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="F261" s="36"/>
       <c r="G261" s="36"/>
@@ -70058,7 +70055,7 @@
       <c r="C262" s="36"/>
       <c r="D262" s="36"/>
       <c r="E262" s="35" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
       <c r="F262" s="36"/>
       <c r="G262" s="36"/>
@@ -70070,7 +70067,7 @@
       <c r="C263" s="36"/>
       <c r="D263" s="36"/>
       <c r="E263" s="35" t="s">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="F263" s="36"/>
       <c r="G263" s="36"/>
@@ -70082,7 +70079,7 @@
       <c r="C264" s="36"/>
       <c r="D264" s="36"/>
       <c r="E264" s="35" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="F264" s="36"/>
       <c r="G264" s="36"/>
@@ -70094,7 +70091,7 @@
       <c r="C265" s="36"/>
       <c r="D265" s="36"/>
       <c r="E265" s="35" t="s">
-        <v>1527</v>
+        <v>1522</v>
       </c>
       <c r="F265" s="36"/>
       <c r="G265" s="36"/>
@@ -70106,7 +70103,7 @@
       <c r="C266" s="36"/>
       <c r="D266" s="36"/>
       <c r="E266" s="35" t="s">
-        <v>1528</v>
+        <v>1523</v>
       </c>
       <c r="F266" s="36"/>
       <c r="G266" s="36"/>
@@ -70118,7 +70115,7 @@
       <c r="C267" s="36"/>
       <c r="D267" s="36"/>
       <c r="E267" s="35" t="s">
-        <v>1529</v>
+        <v>1524</v>
       </c>
       <c r="F267" s="36"/>
       <c r="G267" s="36"/>
@@ -70130,7 +70127,7 @@
       <c r="C268" s="36"/>
       <c r="D268" s="36"/>
       <c r="E268" s="35" t="s">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="F268" s="36"/>
       <c r="G268" s="36"/>
@@ -70142,7 +70139,7 @@
       <c r="C269" s="36"/>
       <c r="D269" s="36"/>
       <c r="E269" s="35" t="s">
-        <v>1531</v>
+        <v>1526</v>
       </c>
       <c r="F269" s="36"/>
       <c r="G269" s="36"/>
@@ -70154,7 +70151,7 @@
       <c r="C270" s="36"/>
       <c r="D270" s="36"/>
       <c r="E270" s="35" t="s">
-        <v>1532</v>
+        <v>1527</v>
       </c>
       <c r="F270" s="36"/>
       <c r="G270" s="36"/>
@@ -70166,7 +70163,7 @@
       <c r="C271" s="36"/>
       <c r="D271" s="36"/>
       <c r="E271" s="35" t="s">
-        <v>1533</v>
+        <v>1528</v>
       </c>
       <c r="F271" s="36"/>
       <c r="G271" s="36"/>
@@ -70178,7 +70175,7 @@
       <c r="C272" s="36"/>
       <c r="D272" s="36"/>
       <c r="E272" s="35" t="s">
-        <v>1534</v>
+        <v>1529</v>
       </c>
       <c r="F272" s="36"/>
       <c r="G272" s="36"/>
@@ -70189,16 +70186,16 @@
         <v>5</v>
       </c>
       <c r="B273" s="35" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="C273" s="36" t="s">
         <v>377</v>
       </c>
       <c r="D273" s="35" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="E273" s="35" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="F273" s="36"/>
       <c r="G273" s="36"/>
@@ -70210,7 +70207,7 @@
       <c r="C274" s="36"/>
       <c r="D274" s="35"/>
       <c r="E274" s="35" t="s">
-        <v>1536</v>
+        <v>1531</v>
       </c>
       <c r="F274" s="36"/>
       <c r="G274" s="36"/>
@@ -70222,7 +70219,7 @@
       <c r="C275" s="36"/>
       <c r="D275" s="35"/>
       <c r="E275" s="35" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
       <c r="F275" s="36"/>
       <c r="G275" s="36"/>
@@ -70234,7 +70231,7 @@
       <c r="C276" s="36"/>
       <c r="D276" s="35"/>
       <c r="E276" s="35" t="s">
-        <v>1538</v>
+        <v>1533</v>
       </c>
       <c r="F276" s="36"/>
       <c r="G276" s="36"/>
@@ -70266,7 +70263,7 @@
         <v>660</v>
       </c>
       <c r="E278" s="35" t="s">
-        <v>1539</v>
+        <v>1534</v>
       </c>
       <c r="F278" s="35"/>
       <c r="G278" s="35"/>
@@ -70278,7 +70275,7 @@
       <c r="C279" s="35"/>
       <c r="D279" s="35"/>
       <c r="E279" s="35" t="s">
-        <v>1540</v>
+        <v>1535</v>
       </c>
       <c r="F279" s="35"/>
       <c r="G279" s="35"/>
@@ -70290,7 +70287,7 @@
       <c r="C280" s="35"/>
       <c r="D280" s="35"/>
       <c r="E280" s="35" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="F280" s="35"/>
       <c r="G280" s="35"/>
@@ -70310,7 +70307,7 @@
         <v>663</v>
       </c>
       <c r="E281" s="35" t="s">
-        <v>1542</v>
+        <v>1537</v>
       </c>
       <c r="F281" s="35"/>
       <c r="G281" s="35"/>
@@ -70322,7 +70319,7 @@
       <c r="C282" s="35"/>
       <c r="D282" s="35"/>
       <c r="E282" s="35" t="s">
-        <v>1543</v>
+        <v>1538</v>
       </c>
       <c r="F282" s="35"/>
       <c r="G282" s="35"/>
@@ -70334,7 +70331,7 @@
       <c r="C283" s="35"/>
       <c r="D283" s="35"/>
       <c r="E283" s="35" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F283" s="35"/>
       <c r="G283" s="35"/>
@@ -70558,7 +70555,7 @@
         <v>294</v>
       </c>
       <c r="F4" s="52" t="s">
-        <v>1548</v>
+        <v>1543</v>
       </c>
       <c r="G4" s="52" t="b">
         <v>0</v>
@@ -70587,7 +70584,7 @@
         <v>296</v>
       </c>
       <c r="F5" s="52" t="s">
-        <v>1549</v>
+        <v>1544</v>
       </c>
       <c r="G5" s="52" t="b">
         <v>0</v>
@@ -70608,13 +70605,13 @@
         <v>297</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>1556</v>
+        <v>1551</v>
       </c>
       <c r="E6" s="52" t="s">
         <v>298</v>
       </c>
       <c r="F6" s="52" t="s">
-        <v>1550</v>
+        <v>1545</v>
       </c>
       <c r="G6" s="52" t="b">
         <v>0</v>
@@ -70639,7 +70636,7 @@
         <v>299</v>
       </c>
       <c r="F7" s="52" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="G7" s="52" t="b">
         <v>0</v>
@@ -70664,7 +70661,7 @@
         <v>300</v>
       </c>
       <c r="F8" s="52" t="s">
-        <v>1552</v>
+        <v>1547</v>
       </c>
       <c r="G8" s="52" t="b">
         <v>0</v>
@@ -70683,7 +70680,7 @@
         <v>301</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>1547</v>
+        <v>1542</v>
       </c>
       <c r="E9" s="52" t="s">
         <v>302</v>
@@ -70710,13 +70707,13 @@
         <v>301</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>1547</v>
+        <v>1542</v>
       </c>
       <c r="E10" s="52" t="s">
         <v>304</v>
       </c>
       <c r="F10" s="52" t="s">
-        <v>1553</v>
+        <v>1548</v>
       </c>
       <c r="G10" s="52" t="b">
         <v>0</v>
@@ -70735,13 +70732,13 @@
         <v>301</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>1547</v>
+        <v>1542</v>
       </c>
       <c r="E11" s="52" t="s">
         <v>305</v>
       </c>
       <c r="F11" s="52" t="s">
-        <v>1554</v>
+        <v>1549</v>
       </c>
       <c r="G11" s="52" t="b">
         <v>0</v>
@@ -70760,13 +70757,13 @@
         <v>301</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>1547</v>
+        <v>1542</v>
       </c>
       <c r="E12" s="52" t="s">
         <v>306</v>
       </c>
       <c r="F12" s="52" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="G12" s="52" t="b">
         <v>0</v>
@@ -70893,7 +70890,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="43" customFormat="1" ht="92" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="B1" s="137"/>
       <c r="C1" s="137"/>
@@ -70911,7 +70908,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="109" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
       <c r="E2" s="110" t="s">
         <v>395</v>
@@ -70922,13 +70919,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
       <c r="C3" s="63" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>1160</v>
+        <v>1155</v>
       </c>
       <c r="E3" s="36"/>
     </row>
@@ -70983,7 +70980,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="43" customFormat="1" ht="207" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="B1" s="139"/>
       <c r="C1" s="139"/>
@@ -71010,34 +71007,34 @@
         <v>2</v>
       </c>
       <c r="D2" s="109" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E2" s="110" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F2" s="110" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G2" s="110" t="s">
+        <v>1133</v>
+      </c>
+      <c r="H2" s="114" t="s">
+        <v>1134</v>
+      </c>
+      <c r="I2" s="115" t="s">
         <v>1135</v>
       </c>
-      <c r="E2" s="110" t="s">
+      <c r="J2" s="115" t="s">
         <v>1136</v>
       </c>
-      <c r="F2" s="110" t="s">
+      <c r="K2" s="110" t="s">
         <v>1137</v>
       </c>
-      <c r="G2" s="110" t="s">
+      <c r="L2" s="110" t="s">
         <v>1138</v>
       </c>
-      <c r="H2" s="114" t="s">
+      <c r="M2" s="110" t="s">
         <v>1139</v>
-      </c>
-      <c r="I2" s="115" t="s">
-        <v>1140</v>
-      </c>
-      <c r="J2" s="115" t="s">
-        <v>1141</v>
-      </c>
-      <c r="K2" s="110" t="s">
-        <v>1142</v>
-      </c>
-      <c r="L2" s="110" t="s">
-        <v>1143</v>
-      </c>
-      <c r="M2" s="110" t="s">
-        <v>1144</v>
       </c>
       <c r="N2" s="116" t="s">
         <v>395</v>
@@ -71048,29 +71045,29 @@
         <v>5</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
       <c r="E3" s="35" t="s">
         <v>377</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>1148</v>
+        <v>1143</v>
       </c>
       <c r="G3" s="35">
         <v>10</v>
       </c>
       <c r="H3" s="117"/>
       <c r="I3" s="118" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="J3" s="118" t="s">
-        <v>1150</v>
+        <v>1145</v>
       </c>
       <c r="K3" s="35"/>
       <c r="L3" s="35"/>
@@ -71082,19 +71079,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1152</v>
+        <v>1147</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1154</v>
+        <v>1149</v>
       </c>
       <c r="G4" s="35">
         <v>100</v>
@@ -71105,7 +71102,7 @@
       <c r="I4" s="118"/>
       <c r="J4" s="118"/>
       <c r="K4" s="35" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="L4" s="119"/>
       <c r="M4" s="35"/>
@@ -71123,13 +71120,13 @@
       <c r="I5" s="118"/>
       <c r="J5" s="118"/>
       <c r="K5" s="35" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="L5" s="36" t="s">
-        <v>1156</v>
+        <v>1151</v>
       </c>
       <c r="M5" s="35" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="N5" s="120"/>
     </row>
@@ -71145,10 +71142,10 @@
       <c r="I6" s="118"/>
       <c r="J6" s="118"/>
       <c r="K6" s="35" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
       <c r="L6" s="36" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="M6" s="35"/>
       <c r="N6" s="120"/>

--- a/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-CIS-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEDCA8C-9564-5C4F-BB1E-851EDE1D26A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F47BBF-E46A-5F47-A224-6D9A39CD83F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2600" windowWidth="30240" windowHeight="17400" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -779,7 +779,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3434" uniqueCount="1760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3435" uniqueCount="1760">
   <si>
     <t>Region</t>
   </si>
@@ -14063,6 +14063,21 @@
     </r>
   </si>
   <si>
+    <t>Plugin OS Management Service Agent</t>
+  </si>
+  <si>
+    <t>ashburn</t>
+  </si>
+  <si>
+    <t>chicago</t>
+  </si>
+  <si>
+    <t>london</t>
+  </si>
+  <si>
+    <t>cardiff</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -14104,23 +14119,8 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-Updated Instances sheet, Exa-Infra sheet</t>
-    </r>
-  </si>
-  <si>
-    <t>Plugin OS Management Service Agent</t>
-  </si>
-  <si>
-    <t>ashburn</t>
-  </si>
-  <si>
-    <t>chicago</t>
-  </si>
-  <si>
-    <t>london</t>
-  </si>
-  <si>
-    <t>cardiff</t>
+Updated Instances sheet, Exa-Infra sheet, LB-Listener sheet</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -20309,7 +20309,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1">
       <c r="A2" s="79" t="s">
-        <v>1754</v>
+        <v>1759</v>
       </c>
     </row>
   </sheetData>
@@ -31475,7 +31475,7 @@
         <v>1751</v>
       </c>
       <c r="AC2" s="31" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="AD2" s="31" t="s">
         <v>1752</v>
@@ -33924,21 +33924,22 @@
   <sheetPr>
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="9.5" customWidth="1"/>
     <col min="3" max="3" width="10.5" customWidth="1"/>
     <col min="4" max="4" width="17.83203125" customWidth="1"/>
-    <col min="5" max="5" width="9.83203125" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" customWidth="1"/>
-    <col min="8" max="9" width="12.5" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="13" max="13" width="10.1640625" customWidth="1"/>
-    <col min="17" max="17" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="9.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" customWidth="1"/>
+    <col min="9" max="10" width="12.5" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="14" max="14" width="10.1640625" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="120" customHeight="1">
+    <row r="1" spans="1:18" ht="120" customHeight="1">
       <c r="A1" s="137" t="s">
         <v>615</v>
       </c>
@@ -33958,8 +33959,9 @@
       <c r="O1" s="137"/>
       <c r="P1" s="137"/>
       <c r="Q1" s="137"/>
-    </row>
-    <row r="2" spans="1:17" ht="46.5" customHeight="1">
+      <c r="R1" s="137"/>
+    </row>
+    <row r="2" spans="1:18" ht="46.5" customHeight="1">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
@@ -33972,47 +33974,50 @@
       <c r="D2" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="31" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="I2" s="31" t="s">
         <v>607</v>
       </c>
-      <c r="I2" s="31" t="s">
+      <c r="J2" s="31" t="s">
         <v>616</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="K2" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="L2" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="M2" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="N2" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="N2" s="31" t="s">
+      <c r="O2" s="31" t="s">
         <v>380</v>
       </c>
-      <c r="O2" s="31" t="s">
+      <c r="P2" s="31" t="s">
         <v>379</v>
       </c>
-      <c r="P2" s="31" t="s">
+      <c r="Q2" s="31" t="s">
         <v>410</v>
       </c>
-      <c r="Q2" s="31" t="s">
+      <c r="R2" s="31" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3" s="36" t="s">
         <v>4</v>
       </c>
@@ -34032,8 +34037,9 @@
       <c r="O3" s="36"/>
       <c r="P3" s="36"/>
       <c r="Q3" s="36"/>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" s="36"/>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="52" t="s">
         <v>5</v>
       </c>
@@ -34046,66 +34052,68 @@
       <c r="D4" s="52" t="s">
         <v>241</v>
       </c>
-      <c r="E4" s="52" t="s">
+      <c r="E4" s="52"/>
+      <c r="F4" s="52" t="s">
         <v>226</v>
       </c>
-      <c r="F4" s="52" t="s">
+      <c r="G4" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="H4" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="52"/>
       <c r="I4" s="52"/>
-      <c r="J4" s="52" t="s">
+      <c r="J4" s="52"/>
+      <c r="K4" s="52" t="s">
         <v>346</v>
       </c>
-      <c r="K4" s="52"/>
       <c r="L4" s="52"/>
       <c r="M4" s="52"/>
-      <c r="N4" s="52" t="s">
+      <c r="N4" s="52"/>
+      <c r="O4" s="52" t="s">
         <v>390</v>
       </c>
-      <c r="O4" s="90" t="s">
+      <c r="P4" s="90" t="s">
         <v>391</v>
       </c>
-      <c r="P4" s="52">
+      <c r="Q4" s="52">
         <v>2</v>
       </c>
-      <c r="Q4" s="52" t="b">
+      <c r="R4" s="52" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5" s="52"/>
       <c r="B5" s="52"/>
       <c r="C5" s="52" t="s">
         <v>167</v>
       </c>
       <c r="D5" s="52"/>
-      <c r="E5" s="52" t="s">
+      <c r="E5" s="52"/>
+      <c r="F5" s="52" t="s">
         <v>229</v>
       </c>
-      <c r="F5" s="52" t="s">
+      <c r="G5" s="52" t="s">
         <v>222</v>
       </c>
-      <c r="G5" s="52" t="s">
+      <c r="H5" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="52"/>
       <c r="I5" s="52"/>
-      <c r="J5" s="52" t="s">
+      <c r="J5" s="52"/>
+      <c r="K5" s="52" t="s">
         <v>398</v>
       </c>
-      <c r="K5" s="52"/>
       <c r="L5" s="52"/>
       <c r="M5" s="52"/>
       <c r="N5" s="52"/>
       <c r="O5" s="52"/>
       <c r="P5" s="52"/>
       <c r="Q5" s="52"/>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" s="52"/>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="52" t="s">
         <v>5</v>
       </c>
@@ -34118,42 +34126,43 @@
       <c r="D6" s="52" t="s">
         <v>242</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="E6" s="52"/>
+      <c r="F6" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="G6" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="H6" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="52" t="s">
+      <c r="I6" s="52" t="s">
         <v>148</v>
       </c>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52" t="s">
+      <c r="J6" s="52"/>
+      <c r="K6" s="52" t="s">
         <v>244</v>
       </c>
-      <c r="K6" s="52" t="s">
+      <c r="L6" s="52" t="s">
         <v>163</v>
       </c>
-      <c r="L6" s="52">
+      <c r="M6" s="52">
         <v>80</v>
       </c>
-      <c r="M6" s="52">
+      <c r="N6" s="52">
         <v>5</v>
       </c>
-      <c r="N6" s="52"/>
       <c r="O6" s="52"/>
       <c r="P6" s="52"/>
       <c r="Q6" s="52"/>
+      <c r="R6" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" prompt="Select an OCI region" sqref="A1:A2 B1:J1048576 L1:XFD1048576 K1:K2" xr:uid="{9392C9D8-9AE8-4A43-8A71-82012B36194C}"/>
+    <dataValidation allowBlank="1" prompt="Select an OCI region" sqref="A1:A2 B1:K1048576 M1:XFD1048576 L1:L2" xr:uid="{9392C9D8-9AE8-4A43-8A71-82012B36194C}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -34168,7 +34177,7 @@
           <x14:formula1>
             <xm:f>drop_down_rule_set!$AG$2:$AG$3</xm:f>
           </x14:formula1>
-          <xm:sqref>K3:K1048576</xm:sqref>
+          <xm:sqref>L3:L1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" prompt="Select an OCI Region." xr:uid="{D1F99000-9956-7C46-A142-556AC0160147}">
           <x14:formula1>
@@ -63539,7 +63548,7 @@
       <c r="I49" s="36"/>
       <c r="J49" s="36"/>
       <c r="L49" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="P49" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P49" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A49,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A49,4,4,1,"DHCP")))</f>
@@ -63585,7 +63594,7 @@
       <c r="I50" s="36"/>
       <c r="J50" s="36"/>
       <c r="L50" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="P50" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P50" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A50,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A50,4,4,1,"DHCP")))</f>
@@ -63660,7 +63669,7 @@
       <c r="I53" s="36"/>
       <c r="J53" s="36"/>
       <c r="L53" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="AU53" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -63680,7 +63689,7 @@
       <c r="I54" s="36"/>
       <c r="J54" s="36"/>
       <c r="L54" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="AU54" s="106" t="str">
         <f t="shared" ca="1" si="1"/>
